--- a/Översikt GRUMS.xlsx
+++ b/Översikt GRUMS.xlsx
@@ -601,7 +601,7 @@
         <v>44978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45343</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44788</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44498</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44819</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 53755-2024</t>
+          <t>A 34099-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45615</v>
+        <v>46252</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>6.1</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
@@ -1344,151 +1344,151 @@
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp
+Björksplintborre
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 34099-2026 artfynd.xlsx", "A 34099-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 34099-2026 karta.png", "A 34099-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 34099-2026 georefererad karta.tif", "A 34099-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 34099-2026 FSC-klagomål.docx", "A 34099-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 34099-2026 FSC-klagomål mail.docx", "A 34099-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 34099-2026 tillsynsbegäran.docx", "A 34099-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 34099-2026 tillsynsbegäran mail.docx", "A 34099-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 53755-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45615</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>3</v>
       </c>
-      <c r="U8" t="n">
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Björksplintborre
 Bronshjon</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 53755-2024 artfynd.xlsx", "A 53755-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 53755-2024 karta.png", "A 53755-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 53755-2024 georefererad karta.tif", "A 53755-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 53755-2024 FSC-klagomål.docx", "A 53755-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 53755-2024 FSC-klagomål mail.docx", "A 53755-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 53755-2024 tillsynsbegäran.docx", "A 53755-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 53755-2024 tillsynsbegäran mail.docx", "A 53755-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 34099-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46252</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>6</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Dofttaggsvamp
-Björksplintborre
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 34099-2026 artfynd.xlsx", "A 34099-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 34099-2026 karta.png", "A 34099-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 34099-2026 georefererad karta.tif", "A 34099-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 34099-2026 FSC-klagomål.docx", "A 34099-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 34099-2026 FSC-klagomål mail.docx", "A 34099-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 34099-2026 tillsynsbegäran.docx", "A 34099-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 34099-2026 tillsynsbegäran mail.docx", "A 34099-2026")</f>
         <v/>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
         <v>44981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45099</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>45898</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45078</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 66053-2021</t>
+          <t>A 5280-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44517</v>
+        <v>44593</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1972,14 +1972,19 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>37.1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1988,7 +1993,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1997,174 +2002,169 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 5280-2022 artfynd.xlsx", "A 5280-2022")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 5280-2022 karta.png", "A 5280-2022")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 5280-2022 georefererad karta.tif", "A 5280-2022")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 5280-2022 FSC-klagomål.docx", "A 5280-2022")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 5280-2022 FSC-klagomål mail.docx", "A 5280-2022")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 5280-2022 tillsynsbegäran.docx", "A 5280-2022")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 5280-2022 tillsynsbegäran mail.docx", "A 5280-2022")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 5280-2022 prioriterade fågelarter.docx", "A 5280-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 66053-2021</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44517</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
         <v>6</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>6</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Bronshjon</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 66053-2021 artfynd.xlsx", "A 66053-2021")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 66053-2021 karta.png", "A 66053-2021")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 66053-2021 georefererad karta.tif", "A 66053-2021")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 66053-2021 FSC-klagomål.docx", "A 66053-2021")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 66053-2021 FSC-klagomål mail.docx", "A 66053-2021")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 66053-2021 tillsynsbegäran.docx", "A 66053-2021")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 66053-2021 tillsynsbegäran mail.docx", "A 66053-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 5280-2022</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44593</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 5280-2022 artfynd.xlsx", "A 5280-2022")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 5280-2022 karta.png", "A 5280-2022")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 5280-2022 georefererad karta.tif", "A 5280-2022")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 5280-2022 FSC-klagomål.docx", "A 5280-2022")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 5280-2022 FSC-klagomål mail.docx", "A 5280-2022")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 5280-2022 tillsynsbegäran.docx", "A 5280-2022")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 5280-2022 tillsynsbegäran mail.docx", "A 5280-2022")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 5280-2022 prioriterade fågelarter.docx", "A 5280-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 54042-2021</t>
+          <t>A 57233-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44470</v>
+        <v>45245</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2194,17 +2194,17 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.8</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2227,370 +2227,370 @@
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>6</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin
+Skogsklocka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 57233-2023 artfynd.xlsx", "A 57233-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 57233-2023 karta.png", "A 57233-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 57233-2023 georefererad karta.tif", "A 57233-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 57233-2023 FSC-klagomål.docx", "A 57233-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 57233-2023 FSC-klagomål mail.docx", "A 57233-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 57233-2023 tillsynsbegäran.docx", "A 57233-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 57233-2023 tillsynsbegäran mail.docx", "A 57233-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 54042-2021</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44470</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 54042-2021 artfynd.xlsx", "A 54042-2021")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 54042-2021 karta.png", "A 54042-2021")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 54042-2021 georefererad karta.tif", "A 54042-2021")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 54042-2021 FSC-klagomål.docx", "A 54042-2021")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 54042-2021 FSC-klagomål mail.docx", "A 54042-2021")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 54042-2021 tillsynsbegäran.docx", "A 54042-2021")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 54042-2021 tillsynsbegäran mail.docx", "A 54042-2021")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 54042-2021 prioriterade fågelarter.docx", "A 54042-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 7931-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45706</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 7931-2025 artfynd.xlsx", "A 7931-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 7931-2025 karta.png", "A 7931-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 7931-2025 georefererad karta.tif", "A 7931-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 7931-2025 FSC-klagomål.docx", "A 7931-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 7931-2025 FSC-klagomål mail.docx", "A 7931-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 7931-2025 tillsynsbegäran.docx", "A 7931-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 7931-2025 tillsynsbegäran mail.docx", "A 7931-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 56386-2022</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>44890</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>4.2</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M19" t="n">
         <v>1</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R19" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Vågfibbla
 Rönnfibbla</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 56386-2022 artfynd.xlsx", "A 56386-2022")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 56386-2022 karta.png", "A 56386-2022")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 56386-2022 georefererad karta.tif", "A 56386-2022")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 56386-2022 FSC-klagomål.docx", "A 56386-2022")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 56386-2022 FSC-klagomål mail.docx", "A 56386-2022")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 56386-2022 tillsynsbegäran.docx", "A 56386-2022")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 56386-2022 tillsynsbegäran mail.docx", "A 56386-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 57233-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45245</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>6</v>
-      </c>
-      <c r="U18" t="n">
-        <v>6</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Skogsklocka</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 57233-2023 artfynd.xlsx", "A 57233-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 57233-2023 karta.png", "A 57233-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 57233-2023 georefererad karta.tif", "A 57233-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 57233-2023 FSC-klagomål.docx", "A 57233-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 57233-2023 FSC-klagomål mail.docx", "A 57233-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 57233-2023 tillsynsbegäran.docx", "A 57233-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 57233-2023 tillsynsbegäran mail.docx", "A 57233-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 7931-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45706</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 7931-2025 artfynd.xlsx", "A 7931-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 7931-2025 karta.png", "A 7931-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 7931-2025 georefererad karta.tif", "A 7931-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 7931-2025 FSC-klagomål.docx", "A 7931-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 7931-2025 FSC-klagomål mail.docx", "A 7931-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 7931-2025 tillsynsbegäran.docx", "A 7931-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 7931-2025 tillsynsbegäran mail.docx", "A 7931-2025")</f>
         <v/>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
         <v>45099</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>44901</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44494</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>44588</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>44470</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>44792</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 37339-2022</t>
+          <t>A 29582-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44806</v>
+        <v>45484</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3280,17 +3280,22 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3305,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3321,42 +3326,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 37339-2022 artfynd.xlsx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 29582-2024 artfynd.xlsx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 37339-2022 karta.png", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 29582-2024 karta.png", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 37339-2022 georefererad karta.tif", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 29582-2024 georefererad karta.tif", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 37339-2022 FSC-klagomål.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 29582-2024 FSC-klagomål.docx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 37339-2022 FSC-klagomål mail.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 29582-2024 FSC-klagomål mail.docx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 37339-2022 tillsynsbegäran.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 29582-2024 tillsynsbegäran.docx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 37339-2022 tillsynsbegäran mail.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 29582-2024 tillsynsbegäran mail.docx", "A 29582-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 10647-2024</t>
+          <t>A 13121-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3366,14 +3371,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45368</v>
+        <v>45002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3386,7 +3391,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3426,42 +3431,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 10647-2024 artfynd.xlsx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 13121-2023 artfynd.xlsx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 10647-2024 karta.png", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 13121-2023 karta.png", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 10647-2024 georefererad karta.tif", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 13121-2023 georefererad karta.tif", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 10647-2024 FSC-klagomål.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 13121-2023 FSC-klagomål.docx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 10647-2024 FSC-klagomål mail.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 13121-2023 FSC-klagomål mail.docx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 10647-2024 tillsynsbegäran.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 13121-2023 tillsynsbegäran.docx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 10647-2024 tillsynsbegäran mail.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 13121-2023 tillsynsbegäran mail.docx", "A 13121-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 41878-2024</t>
+          <t>A 15321-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3475,10 +3480,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45561</v>
+        <v>45019</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3490,22 +3495,17 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>15.9</v>
+        <v>5.2</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3520,7 +3520,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3529,53 +3529,49 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 41878-2024 artfynd.xlsx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 15321-2023 artfynd.xlsx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 41878-2024 karta.png", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 15321-2023 karta.png", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 41878-2024 georefererad karta.tif", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 15321-2023 georefererad karta.tif", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 41878-2024 FSC-klagomål.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 15321-2023 FSC-klagomål.docx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 41878-2024 FSC-klagomål mail.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 15321-2023 FSC-klagomål mail.docx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 41878-2024 tillsynsbegäran.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 15321-2023 tillsynsbegäran.docx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 41878-2024 tillsynsbegäran mail.docx", "A 41878-2024")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 41878-2024 prioriterade fågelarter.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 15321-2023 tillsynsbegäran mail.docx", "A 15321-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17122-2024</t>
+          <t>A 47146-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3585,14 +3581,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45412</v>
+        <v>45929</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3604,11 +3600,16 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>7</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3641,46 +3642,50 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 17122-2024 artfynd.xlsx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 47146-2025 artfynd.xlsx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 17122-2024 karta.png", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 47146-2025 karta.png", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 17122-2024 georefererad karta.tif", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 47146-2025 georefererad karta.tif", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 17122-2024 FSC-klagomål.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 47146-2025 FSC-klagomål.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 17122-2024 FSC-klagomål mail.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 47146-2025 FSC-klagomål mail.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 17122-2024 tillsynsbegäran.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 47146-2025 tillsynsbegäran.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 17122-2024 tillsynsbegäran mail.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 47146-2025 tillsynsbegäran mail.docx", "A 47146-2025")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 47146-2025 prioriterade fågelarter.docx", "A 47146-2025")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 19524-2024</t>
+          <t>A 12296-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3694,10 +3699,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45429</v>
+        <v>46087</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3710,10 +3715,10 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3746,50 +3751,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19524-2024 artfynd.xlsx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 12296-2026 artfynd.xlsx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19524-2024 karta.png", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 12296-2026 karta.png", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19524-2024 georefererad karta.tif", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 12296-2026 georefererad karta.tif", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19524-2024 FSC-klagomål.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 12296-2026 FSC-klagomål.docx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19524-2024 FSC-klagomål mail.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 12296-2026 FSC-klagomål mail.docx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19524-2024 tillsynsbegäran.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 12296-2026 tillsynsbegäran.docx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19524-2024 tillsynsbegäran mail.docx", "A 19524-2024")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 19524-2024 prioriterade fågelarter.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 12296-2026 tillsynsbegäran mail.docx", "A 12296-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 47146-2025</t>
+          <t>A 30411-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3803,10 +3804,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45929</v>
+        <v>45827</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3818,13 +3819,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -3833,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3848,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3860,50 +3856,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 47146-2025 artfynd.xlsx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 30411-2025 artfynd.xlsx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 47146-2025 karta.png", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 30411-2025 karta.png", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 47146-2025 georefererad karta.tif", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 30411-2025 georefererad karta.tif", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 47146-2025 FSC-klagomål.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 30411-2025 FSC-klagomål.docx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 47146-2025 FSC-klagomål mail.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 30411-2025 FSC-klagomål mail.docx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 47146-2025 tillsynsbegäran.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 30411-2025 tillsynsbegäran.docx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 47146-2025 tillsynsbegäran mail.docx", "A 47146-2025")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 47146-2025 prioriterade fågelarter.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 30411-2025 tillsynsbegäran mail.docx", "A 30411-2025")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 19052-2024</t>
+          <t>A 10647-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3917,10 +3909,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45427</v>
+        <v>45368</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3933,10 +3925,10 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>7.7</v>
+        <v>4.1</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3948,7 +3940,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -3957,10 +3949,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3973,42 +3965,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19052-2024 artfynd.xlsx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 10647-2024 artfynd.xlsx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19052-2024 karta.png", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 10647-2024 karta.png", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19052-2024 georefererad karta.tif", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 10647-2024 georefererad karta.tif", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19052-2024 FSC-klagomål.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 10647-2024 FSC-klagomål.docx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19052-2024 FSC-klagomål mail.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 10647-2024 FSC-klagomål mail.docx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19052-2024 tillsynsbegäran.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 10647-2024 tillsynsbegäran.docx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19052-2024 tillsynsbegäran mail.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 10647-2024 tillsynsbegäran mail.docx", "A 10647-2024")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12296-2026</t>
+          <t>A 62675-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4018,14 +4010,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46087</v>
+        <v>45271</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4038,16 +4030,16 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4062,7 +4054,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4078,42 +4070,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 12296-2026 artfynd.xlsx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 62675-2023 artfynd.xlsx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 12296-2026 karta.png", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 62675-2023 karta.png", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 12296-2026 georefererad karta.tif", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 62675-2023 georefererad karta.tif", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 12296-2026 FSC-klagomål.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 62675-2023 FSC-klagomål.docx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 12296-2026 FSC-klagomål mail.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 62675-2023 FSC-klagomål mail.docx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 12296-2026 tillsynsbegäran.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 62675-2023 tillsynsbegäran.docx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 12296-2026 tillsynsbegäran mail.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 62675-2023 tillsynsbegäran mail.docx", "A 62675-2023")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 15321-2023</t>
+          <t>A 34076-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4127,10 +4119,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45019</v>
+        <v>46252</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4143,17 +4135,17 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>1</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
@@ -4167,7 +4159,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4183,42 +4175,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 15321-2023 artfynd.xlsx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 34076-2026 artfynd.xlsx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 15321-2023 karta.png", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 34076-2026 karta.png", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 15321-2023 georefererad karta.tif", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 34076-2026 georefererad karta.tif", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 15321-2023 FSC-klagomål.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 34076-2026 FSC-klagomål.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 15321-2023 FSC-klagomål mail.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 34076-2026 FSC-klagomål mail.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 15321-2023 tillsynsbegäran.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 34076-2026 tillsynsbegäran.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 15321-2023 tillsynsbegäran mail.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 34076-2026 tillsynsbegäran mail.docx", "A 34076-2026")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 13121-2023</t>
+          <t>A 19052-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4228,14 +4220,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45002</v>
+        <v>45427</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4248,23 +4240,23 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>7.7</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
@@ -4272,10 +4264,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4288,42 +4280,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 13121-2023 artfynd.xlsx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19052-2024 artfynd.xlsx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 13121-2023 karta.png", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19052-2024 karta.png", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 13121-2023 georefererad karta.tif", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19052-2024 georefererad karta.tif", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 13121-2023 FSC-klagomål.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19052-2024 FSC-klagomål.docx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 13121-2023 FSC-klagomål mail.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19052-2024 FSC-klagomål mail.docx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 13121-2023 tillsynsbegäran.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19052-2024 tillsynsbegäran.docx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 13121-2023 tillsynsbegäran mail.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19052-2024 tillsynsbegäran mail.docx", "A 19052-2024")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30411-2025</t>
+          <t>A 37339-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4337,10 +4329,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45827</v>
+        <v>44806</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4353,17 +4345,17 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
@@ -4377,7 +4369,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4393,35 +4385,35 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 30411-2025 artfynd.xlsx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 37339-2022 artfynd.xlsx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 30411-2025 karta.png", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 37339-2022 karta.png", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 30411-2025 georefererad karta.tif", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 37339-2022 georefererad karta.tif", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 30411-2025 FSC-klagomål.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 37339-2022 FSC-klagomål.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 30411-2025 FSC-klagomål mail.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 37339-2022 FSC-klagomål mail.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 30411-2025 tillsynsbegäran.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 37339-2022 tillsynsbegäran.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 30411-2025 tillsynsbegäran mail.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 37339-2022 tillsynsbegäran mail.docx", "A 37339-2022")</f>
         <v/>
       </c>
     </row>
@@ -4445,7 +4437,7 @@
         <v>45708</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4533,7 +4525,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 35077-2024</t>
+          <t>A 17122-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4543,14 +4535,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45527</v>
+        <v>45412</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4563,19 +4555,19 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
         <v>1</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -4590,7 +4582,7 @@
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4603,46 +4595,42 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 35077-2024 artfynd.xlsx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 17122-2024 artfynd.xlsx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 35077-2024 karta.png", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 17122-2024 karta.png", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 35077-2024 georefererad karta.tif", "A 35077-2024")</f>
-        <v/>
-      </c>
-      <c r="Z38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/knärot/A 35077-2024 karta knärot.png", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 17122-2024 georefererad karta.tif", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 35077-2024 FSC-klagomål.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 17122-2024 FSC-klagomål.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 35077-2024 FSC-klagomål mail.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 17122-2024 FSC-klagomål mail.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 35077-2024 tillsynsbegäran.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 17122-2024 tillsynsbegäran.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 35077-2024 tillsynsbegäran mail.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 17122-2024 tillsynsbegäran mail.docx", "A 17122-2024")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 34076-2026</t>
+          <t>A 41878-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4656,10 +4644,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46252</v>
+        <v>45561</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4671,11 +4659,16 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>4.9</v>
+        <v>15.9</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -4705,49 +4698,53 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 34076-2026 artfynd.xlsx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 41878-2024 artfynd.xlsx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 34076-2026 karta.png", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 41878-2024 karta.png", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 34076-2026 georefererad karta.tif", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 41878-2024 georefererad karta.tif", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 34076-2026 FSC-klagomål.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 41878-2024 FSC-klagomål.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 34076-2026 FSC-klagomål mail.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 41878-2024 FSC-klagomål mail.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 34076-2026 tillsynsbegäran.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 41878-2024 tillsynsbegäran.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 34076-2026 tillsynsbegäran mail.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 41878-2024 tillsynsbegäran mail.docx", "A 41878-2024")</f>
+        <v/>
+      </c>
+      <c r="AE39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 41878-2024 prioriterade fågelarter.docx", "A 41878-2024")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 29582-2024</t>
+          <t>A 35077-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4761,10 +4758,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45484</v>
+        <v>45527</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4776,26 +4773,21 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
       </c>
       <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
         <v>1</v>
       </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
@@ -4806,10 +4798,10 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4822,42 +4814,46 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 29582-2024 artfynd.xlsx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 35077-2024 artfynd.xlsx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 29582-2024 karta.png", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 35077-2024 karta.png", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 29582-2024 georefererad karta.tif", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 35077-2024 georefererad karta.tif", "A 35077-2024")</f>
+        <v/>
+      </c>
+      <c r="Z40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/knärot/A 35077-2024 karta knärot.png", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 29582-2024 FSC-klagomål.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 35077-2024 FSC-klagomål.docx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 29582-2024 FSC-klagomål mail.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 35077-2024 FSC-klagomål mail.docx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 29582-2024 tillsynsbegäran.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 35077-2024 tillsynsbegäran.docx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 29582-2024 tillsynsbegäran mail.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 35077-2024 tillsynsbegäran mail.docx", "A 35077-2024")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62675-2023</t>
+          <t>A 19524-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4867,14 +4863,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45271</v>
+        <v>45429</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4887,17 +4883,17 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
@@ -4911,7 +4907,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -4923,39 +4919,43 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 62675-2023 artfynd.xlsx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19524-2024 artfynd.xlsx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 62675-2023 karta.png", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19524-2024 karta.png", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 62675-2023 georefererad karta.tif", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19524-2024 georefererad karta.tif", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 62675-2023 FSC-klagomål.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19524-2024 FSC-klagomål.docx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 62675-2023 FSC-klagomål mail.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19524-2024 FSC-klagomål mail.docx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 62675-2023 tillsynsbegäran.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19524-2024 tillsynsbegäran.docx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 62675-2023 tillsynsbegäran mail.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19524-2024 tillsynsbegäran mail.docx", "A 19524-2024")</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 19524-2024 prioriterade fågelarter.docx", "A 19524-2024")</f>
         <v/>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
         <v>44484</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>44607</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>44781</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>44509</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44575</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>44795</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>44782</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>44860</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>44494</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44844</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>44838</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44690</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>44734</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44694</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44743</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>44467</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>44509</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>44498</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>44798</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44762</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44620</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>44627</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>44735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>44882</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>44806</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>44494</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>44467</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>44732</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>44577</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>44460</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 29699-2022</t>
+          <t>A 30334-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7213,10 +7213,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44755</v>
+        <v>44760</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7272,7 +7272,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30334-2022</t>
+          <t>A 29699-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7286,10 +7286,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44760</v>
+        <v>44755</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7362,7 +7362,7 @@
         <v>44547</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 12311-2024</t>
+          <t>A 5025-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45378</v>
+        <v>44958</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7491,7 +7491,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 37486-2022</t>
+          <t>A 73901-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44809</v>
+        <v>44552</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>8.6</v>
+        <v>1.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7564,7 +7564,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 21528-2024</t>
+          <t>A 5841-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7578,10 +7578,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45441</v>
+        <v>44596</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7637,7 +7637,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 20238-2024</t>
+          <t>A 28228-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7651,10 +7651,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45434</v>
+        <v>45477</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7710,7 +7710,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 19053-2024</t>
+          <t>A 5126-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7724,10 +7724,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45427</v>
+        <v>44958</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.7</v>
+        <v>14.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7783,7 +7783,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 42557-2022</t>
+          <t>A 17437-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44831</v>
+        <v>45757</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>13.7</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7856,7 +7856,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 23189-2024</t>
+          <t>A 17443-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7870,10 +7870,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45450</v>
+        <v>45757</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7885,13 +7885,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7934,7 +7929,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 13382-2024</t>
+          <t>A 73033-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7948,10 +7943,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45387</v>
+        <v>44550</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7964,7 +7959,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8007,7 +8002,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 25840-2024</t>
+          <t>A 13382-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8021,10 +8016,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45467</v>
+        <v>45387</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8037,7 +8032,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8080,7 +8075,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 28228-2024</t>
+          <t>A 57236-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8094,10 +8089,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45477</v>
+        <v>45245</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8110,7 +8105,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8153,7 +8148,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 25014-2024</t>
+          <t>A 57237-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8167,10 +8162,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45461</v>
+        <v>45245</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8183,7 +8178,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>12.8</v>
+        <v>18.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8226,7 +8221,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 53209-2021</t>
+          <t>A 5810-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8240,10 +8235,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44468</v>
+        <v>44963</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8256,7 +8251,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>11.6</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8299,7 +8294,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 73310-2021</t>
+          <t>A 47152-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8313,10 +8308,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44547</v>
+        <v>45201</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8329,7 +8324,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>6.2</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8372,7 +8367,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 45467-2022</t>
+          <t>A 26840-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8386,10 +8381,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44845</v>
+        <v>45093</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8402,7 +8397,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8445,7 +8440,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 58705-2024</t>
+          <t>A 18341-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8459,10 +8454,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45635</v>
+        <v>45762</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8474,13 +8469,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8523,7 +8513,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17081-2024</t>
+          <t>A 53209-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8537,10 +8527,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45412</v>
+        <v>44468</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8553,7 +8543,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.8</v>
+        <v>11.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8596,7 +8586,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 36644-2023</t>
+          <t>A 58514-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8610,10 +8600,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45153</v>
+        <v>44902</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8626,7 +8616,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8669,7 +8659,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 62682-2023</t>
+          <t>A 37119-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8683,10 +8673,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45271</v>
+        <v>45539</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8699,7 +8689,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.7</v>
+        <v>6.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8742,7 +8732,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 7922-2022</t>
+          <t>A 17910-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8756,10 +8746,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44608</v>
+        <v>45419</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8772,7 +8762,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8815,7 +8805,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 62905-2023</t>
+          <t>A 2253-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8829,10 +8819,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45272</v>
+        <v>45310</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8845,7 +8835,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>13.8</v>
+        <v>3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8888,7 +8878,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 5126-2023</t>
+          <t>A 13289-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8902,10 +8892,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44958</v>
+        <v>45735</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8918,7 +8908,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>14.3</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8961,7 +8951,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 10892-2022</t>
+          <t>A 59391-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8971,14 +8961,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44627</v>
+        <v>45989</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8991,7 +8981,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9034,7 +9024,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 31362-2024</t>
+          <t>A 6721-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9044,14 +9034,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45505</v>
+        <v>45700</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9063,8 +9053,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>0.6</v>
+        <v>5.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9107,7 +9102,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 29260-2025</t>
+          <t>A 27218-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9121,10 +9116,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45824</v>
+        <v>45096</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9137,7 +9132,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9180,7 +9175,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 62557-2022</t>
+          <t>A 49300-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9194,10 +9189,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44924</v>
+        <v>44861</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9210,7 +9205,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9253,7 +9248,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 8732-2026</t>
+          <t>A 36420-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9267,10 +9262,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46066</v>
+        <v>45152</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9283,7 +9278,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>6.1</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9326,7 +9321,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 7991-2024</t>
+          <t>A 5957-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9336,14 +9331,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45350</v>
+        <v>45336</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9356,7 +9351,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9399,7 +9394,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 30563-2025</t>
+          <t>A 17399-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9413,10 +9408,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45831</v>
+        <v>45757</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9429,7 +9424,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9472,7 +9467,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 5810-2023</t>
+          <t>A 3054-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9486,10 +9481,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44963</v>
+        <v>46039</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9502,7 +9497,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9545,7 +9540,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 32327-2025</t>
+          <t>A 29260-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9559,10 +9554,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45836</v>
+        <v>45824</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9575,7 +9570,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9618,7 +9613,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 5236-2023</t>
+          <t>A 20238-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9632,10 +9627,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44956</v>
+        <v>45434</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9648,7 +9643,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9691,7 +9686,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 8359-2025</t>
+          <t>A 30563-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9705,10 +9700,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45708</v>
+        <v>45831</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9721,7 +9716,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9764,7 +9759,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 62947-2023</t>
+          <t>A 56219-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9778,10 +9773,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45272</v>
+        <v>45240</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9794,7 +9789,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9837,7 +9832,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 35425-2025</t>
+          <t>A 680-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9851,10 +9846,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45855</v>
+        <v>45300</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9867,7 +9862,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9910,7 +9905,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 7993-2024</t>
+          <t>A 30339-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9924,10 +9919,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45350</v>
+        <v>44760</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9940,7 +9935,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9983,7 +9978,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 33081-2022</t>
+          <t>A 44497-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9997,10 +9992,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44785</v>
+        <v>45916</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10013,7 +10008,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10056,7 +10051,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 44497-2025</t>
+          <t>A 32327-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10070,10 +10065,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45916</v>
+        <v>45836</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10086,7 +10081,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10129,7 +10124,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 29762-2023</t>
+          <t>A 8359-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10143,10 +10138,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45107</v>
+        <v>45708</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10159,7 +10154,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10202,7 +10197,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 37517-2025</t>
+          <t>A 975-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10216,10 +10211,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45877</v>
+        <v>45665</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10232,7 +10227,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10275,7 +10270,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 37515-2025</t>
+          <t>A 62557-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10289,10 +10284,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45877</v>
+        <v>44924</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10305,7 +10300,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10348,7 +10343,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 37495-2025</t>
+          <t>A 47507-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10362,10 +10357,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45877</v>
+        <v>45930</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10378,7 +10373,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10421,7 +10416,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 29736-2023</t>
+          <t>A 35425-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10435,10 +10430,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45107</v>
+        <v>45855</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10451,7 +10446,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10494,7 +10489,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 47507-2025</t>
+          <t>A 8732-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10508,10 +10503,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45930</v>
+        <v>46066</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10524,7 +10519,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.9</v>
+        <v>6.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10567,7 +10562,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 50640-2023</t>
+          <t>A 21402-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10581,10 +10576,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45217</v>
+        <v>45441</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10597,7 +10592,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10657,7 +10652,7 @@
         <v>45939</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10713,7 +10708,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 17910-2024</t>
+          <t>A 29736-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10727,10 +10722,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45419</v>
+        <v>45107</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10743,7 +10738,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>6.8</v>
+        <v>0.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10786,7 +10781,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 12283-2026</t>
+          <t>A 37515-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10800,10 +10795,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46087</v>
+        <v>45877</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10816,7 +10811,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10859,7 +10854,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 8361-2025</t>
+          <t>A 37495-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10873,10 +10868,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45708</v>
+        <v>45877</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10889,7 +10884,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10932,7 +10927,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 31964-2023</t>
+          <t>A 37517-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10946,10 +10941,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45107</v>
+        <v>45877</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10962,7 +10957,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11005,7 +11000,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 35253-2022</t>
+          <t>A 53138-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11019,10 +11014,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44797</v>
+        <v>45229</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11035,7 +11030,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11078,7 +11073,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 51509-2025</t>
+          <t>A 19566-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11088,14 +11083,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45950</v>
+        <v>45049</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11108,7 +11103,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11151,7 +11146,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 14688-2026</t>
+          <t>A 29762-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11161,14 +11156,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46101</v>
+        <v>45107</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11181,7 +11176,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11224,7 +11219,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 29426-2022</t>
+          <t>A 12283-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11238,10 +11233,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44753</v>
+        <v>46087</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11253,13 +11248,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>14.4</v>
+        <v>1.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11302,7 +11292,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 30339-2022</t>
+          <t>A 51509-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11312,14 +11302,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44760</v>
+        <v>45950</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11332,7 +11322,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11375,7 +11365,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 52700-2025</t>
+          <t>A 8364-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11389,10 +11379,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45956</v>
+        <v>45708</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11405,7 +11395,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11448,7 +11438,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 52699-2025</t>
+          <t>A 62896-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11462,10 +11452,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45956</v>
+        <v>45272</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11478,7 +11468,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.9</v>
+        <v>13.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11521,7 +11511,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 6751-2025</t>
+          <t>A 69847-2021</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11535,10 +11525,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45700</v>
+        <v>44532</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11551,7 +11541,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11594,7 +11584,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 975-2025</t>
+          <t>A 58705-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11608,10 +11598,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45665</v>
+        <v>45635</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11623,8 +11613,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11667,7 +11662,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 15543-2026</t>
+          <t>A 22347-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11681,10 +11676,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46106</v>
+        <v>45070</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11697,7 +11692,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11740,7 +11735,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 63919-2021</t>
+          <t>A 14688-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11750,14 +11745,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44509</v>
+        <v>46101</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11770,7 +11765,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11813,7 +11808,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 15549-2026</t>
+          <t>A 52699-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11827,10 +11822,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46106</v>
+        <v>45956</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11843,7 +11838,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11886,7 +11881,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 9144-2024</t>
+          <t>A 52700-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11900,10 +11895,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45358</v>
+        <v>45956</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11916,7 +11911,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11959,7 +11954,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 58747-2025</t>
+          <t>A 15549-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11973,10 +11968,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45986</v>
+        <v>46106</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12032,7 +12027,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 58751-2025</t>
+          <t>A 15543-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12046,10 +12041,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45986</v>
+        <v>46106</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12062,7 +12057,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12105,7 +12100,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 33948-2023</t>
+          <t>A 19054-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12119,10 +12114,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45124</v>
+        <v>46132</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12135,7 +12130,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12178,7 +12173,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 19054-2026</t>
+          <t>A 59617-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12192,10 +12187,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46132</v>
+        <v>45992</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12208,7 +12203,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12251,7 +12246,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 27222-2023</t>
+          <t>A 33081-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12265,10 +12260,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45096</v>
+        <v>44785</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12281,7 +12276,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12324,7 +12319,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 60656-2025</t>
+          <t>A 29256-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12338,10 +12333,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45996</v>
+        <v>45824</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12354,7 +12349,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12397,7 +12392,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 17972-2025</t>
+          <t>A 25840-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12411,10 +12406,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45761</v>
+        <v>45467</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12427,7 +12422,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12470,7 +12465,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 62896-2023</t>
+          <t>A 614-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12484,10 +12479,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45272</v>
+        <v>46024</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12500,7 +12495,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>13.8</v>
+        <v>5.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12543,7 +12538,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 6938-2024</t>
+          <t>A 58751-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12553,14 +12548,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45343</v>
+        <v>45986</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12573,7 +12568,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12616,7 +12611,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 29256-2025</t>
+          <t>A 42143-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12630,10 +12625,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45824</v>
+        <v>45904</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12646,7 +12641,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12689,7 +12684,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 26829-2023</t>
+          <t>A 58747-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12703,10 +12698,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45093</v>
+        <v>45986</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12762,7 +12757,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 13895-2024</t>
+          <t>A 37676-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12772,14 +12767,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45391</v>
+        <v>45159</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12791,13 +12786,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12840,7 +12830,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 26815-2023</t>
+          <t>A 6751-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12854,10 +12844,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45093</v>
+        <v>45700</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12870,7 +12860,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12913,7 +12903,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 17565-2025</t>
+          <t>A 20784-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12927,10 +12917,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45757</v>
+        <v>45776</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12943,7 +12933,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.1</v>
+        <v>9.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12986,7 +12976,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 25443-2023</t>
+          <t>A 50640-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13000,10 +12990,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45089</v>
+        <v>45217</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13016,7 +13006,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13059,7 +13049,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 21248-2022</t>
+          <t>A 34580-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13073,10 +13063,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44705</v>
+        <v>44795</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13089,7 +13079,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>12.4</v>
+        <v>0.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13132,7 +13122,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 14306-2023</t>
+          <t>A 12000-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13146,10 +13136,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45011</v>
+        <v>44635</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13162,7 +13152,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13205,7 +13195,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 59391-2025</t>
+          <t>A 42557-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13215,14 +13205,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45989</v>
+        <v>44831</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13235,7 +13225,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4.4</v>
+        <v>13.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13278,7 +13268,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 42143-2025</t>
+          <t>A 60656-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13292,10 +13282,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45904</v>
+        <v>45996</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13308,7 +13298,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13351,7 +13341,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 40522-2025</t>
+          <t>A 35253-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13365,10 +13355,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45896</v>
+        <v>44797</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13381,7 +13371,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13424,7 +13414,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 5214-2025</t>
+          <t>A 40524-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13438,10 +13428,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45691</v>
+        <v>45896</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13454,7 +13444,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13497,7 +13487,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 5025-2023</t>
+          <t>A 21248-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13511,10 +13501,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44958</v>
+        <v>44705</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13527,7 +13517,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.9</v>
+        <v>12.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13570,7 +13560,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 31974-2023</t>
+          <t>A 40522-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13584,10 +13574,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45107</v>
+        <v>45896</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13600,7 +13590,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13643,7 +13633,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 5957-2024</t>
+          <t>A 13820-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13657,10 +13647,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45336</v>
+        <v>45390</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13673,7 +13663,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2</v>
+        <v>7.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13716,7 +13706,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 2253-2024</t>
+          <t>A 17565-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13730,10 +13720,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45310</v>
+        <v>45757</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13746,7 +13736,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13789,7 +13779,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 4870-2024</t>
+          <t>A 31362-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13799,14 +13789,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45329</v>
+        <v>45505</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13819,7 +13809,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>8.4</v>
+        <v>0.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13862,7 +13852,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 20784-2025</t>
+          <t>A 5214-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13876,10 +13866,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45776</v>
+        <v>45691</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13892,7 +13882,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13935,7 +13925,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 3054-2026</t>
+          <t>A 31561-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13949,10 +13939,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46039</v>
+        <v>45117</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13965,7 +13955,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14008,7 +13998,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 69847-2021</t>
+          <t>A 3065-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14022,10 +14012,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44532</v>
+        <v>45316</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14038,7 +14028,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14081,7 +14071,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 58514-2022</t>
+          <t>A 17081-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14095,10 +14085,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44902</v>
+        <v>45412</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14111,7 +14101,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14154,7 +14144,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 614-2026</t>
+          <t>A 7993-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14168,10 +14158,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46024</v>
+        <v>45350</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14184,7 +14174,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14227,7 +14217,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 71706-2021</t>
+          <t>A 45467-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14241,10 +14231,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44543</v>
+        <v>44845</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14257,7 +14247,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14300,7 +14290,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 47152-2023</t>
+          <t>A 5011-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14314,10 +14304,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45201</v>
+        <v>45329</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14330,7 +14320,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.5</v>
+        <v>22</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14373,7 +14363,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 40524-2025</t>
+          <t>A 53137-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14387,10 +14377,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45896</v>
+        <v>45229</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14403,7 +14393,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14446,7 +14436,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 59617-2025</t>
+          <t>A 9144-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14460,10 +14450,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45992</v>
+        <v>45358</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14476,7 +14466,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14519,7 +14509,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 31561-2023</t>
+          <t>A 22406-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14533,10 +14523,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45117</v>
+        <v>46154</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14549,7 +14539,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14592,7 +14582,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 53138-2023</t>
+          <t>A 62682-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14606,10 +14596,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45229</v>
+        <v>45271</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14622,7 +14612,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14665,7 +14655,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 16772-2024</t>
+          <t>A 71903-2021</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14679,10 +14669,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45411</v>
+        <v>44543</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14695,7 +14685,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14738,7 +14728,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 66056-2021</t>
+          <t>A 3779-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14752,10 +14742,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44517</v>
+        <v>45681</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14767,8 +14757,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>BillerudKorsnäs AB</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14811,7 +14806,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 3065-2024</t>
+          <t>A 39334-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14825,10 +14820,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45316</v>
+        <v>45889</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14841,7 +14836,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14884,7 +14879,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 12082-2024</t>
+          <t>A 23733-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14898,10 +14893,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45377</v>
+        <v>46164</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14913,8 +14908,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14957,7 +14957,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 12084-2024</t>
+          <t>A 23945-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14971,10 +14971,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45377</v>
+        <v>46167</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14986,8 +14986,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15030,7 +15035,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 20954-2023</t>
+          <t>A 23757-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15044,10 +15049,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45061</v>
+        <v>46164</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15060,7 +15065,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15103,7 +15108,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 17443-2025</t>
+          <t>A 23702-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15117,10 +15122,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45757</v>
+        <v>46164</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15132,8 +15137,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15176,7 +15186,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 22406-2026</t>
+          <t>A 24754-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15190,10 +15200,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46154</v>
+        <v>46171</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15206,7 +15216,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>5.2</v>
+        <v>2.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15249,7 +15259,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 20369-2024</t>
+          <t>A 26015-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15259,14 +15269,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45435</v>
+        <v>46181</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15278,8 +15288,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15322,7 +15337,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 11601-2025</t>
+          <t>A 4982-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15336,10 +15351,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45727</v>
+        <v>45329</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15352,7 +15367,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15395,7 +15410,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 4976-2024</t>
+          <t>A 62947-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15409,10 +15424,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45329</v>
+        <v>45272</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15425,7 +15440,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15468,7 +15483,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 12175-2024</t>
+          <t>A 31930-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15478,14 +15493,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45377</v>
+        <v>45510</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15498,7 +15513,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15541,7 +15556,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 39334-2025</t>
+          <t>A 28513-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15555,10 +15570,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45889</v>
+        <v>46197</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15571,7 +15586,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15614,7 +15629,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 3779-2025</t>
+          <t>A 11103-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15628,10 +15643,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45681</v>
+        <v>44628</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15643,13 +15658,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>BillerudKorsnäs AB</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15692,7 +15702,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 71903-2021</t>
+          <t>A 29205-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15706,10 +15716,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44543</v>
+        <v>46202</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15722,7 +15732,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>6.3</v>
+        <v>1.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15765,7 +15775,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 30527-2022</t>
+          <t>A 71706-2021</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15779,10 +15789,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44762</v>
+        <v>44543</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15795,7 +15805,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15838,7 +15848,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 22347-2023</t>
+          <t>A 29222-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15852,10 +15862,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45070</v>
+        <v>46202</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15868,7 +15878,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15911,7 +15921,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 23702-2026</t>
+          <t>A 40935-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15921,14 +15931,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46164</v>
+        <v>44823</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15942,11 +15952,11 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15989,7 +15999,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 23733-2026</t>
+          <t>A 29191-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16003,10 +16013,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46164</v>
+        <v>46202</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16018,13 +16028,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16067,7 +16072,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 23757-2026</t>
+          <t>A 32302-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16081,10 +16086,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46164</v>
+        <v>45512</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16096,8 +16101,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16140,7 +16150,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 56220-2023</t>
+          <t>A 32942-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16154,10 +16164,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45240</v>
+        <v>46244</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16170,7 +16180,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16213,7 +16223,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 23945-2026</t>
+          <t>A 6938-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16223,14 +16233,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46167</v>
+        <v>45343</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16242,13 +16252,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16291,7 +16296,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 56219-2023</t>
+          <t>A 34538-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16305,10 +16310,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45240</v>
+        <v>46255</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16321,7 +16326,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16364,7 +16369,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 6721-2025</t>
+          <t>A 31034-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16378,10 +16383,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45700</v>
+        <v>46214</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16393,13 +16398,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16442,7 +16442,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 17437-2025</t>
+          <t>A 14306-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16456,10 +16456,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45757</v>
+        <v>45011</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16515,7 +16515,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 5841-2022</t>
+          <t>A 17972-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16529,10 +16529,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44596</v>
+        <v>45761</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16588,7 +16588,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 12000-2022</t>
+          <t>A 27222-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16602,10 +16602,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44635</v>
+        <v>45096</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16661,7 +16661,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 40935-2022</t>
+          <t>A 36644-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16671,14 +16671,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44823</v>
+        <v>45153</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16690,13 +16690,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16739,7 +16734,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 36646-2023</t>
+          <t>A 31559-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16753,10 +16748,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45153</v>
+        <v>46224</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16769,7 +16764,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16812,7 +16807,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 24754-2026</t>
+          <t>A 8788-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16826,10 +16821,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46171</v>
+        <v>45356</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16842,7 +16837,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16885,7 +16880,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 29724-2023</t>
+          <t>A 62554-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16895,14 +16890,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45107</v>
+        <v>44924</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16915,7 +16910,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16958,7 +16953,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 8362-2025</t>
+          <t>A 21528-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16972,10 +16967,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45708</v>
+        <v>45441</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16988,7 +16983,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>7.7</v>
+        <v>1.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17031,7 +17026,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 972-2025</t>
+          <t>A 20954-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17045,10 +17040,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45665</v>
+        <v>45061</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17061,7 +17056,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17104,7 +17099,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 49300-2022</t>
+          <t>A 10892-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17118,10 +17113,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44861</v>
+        <v>44627</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17134,7 +17129,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17177,7 +17172,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 16635-2024</t>
+          <t>A 29426-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17191,10 +17186,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45408</v>
+        <v>44753</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17206,8 +17201,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>0.7</v>
+        <v>14.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17250,7 +17250,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 37676-2023</t>
+          <t>A 37221-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17260,14 +17260,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45159</v>
+        <v>46274</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17323,7 +17323,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 26015-2026</t>
+          <t>A 37243-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17333,14 +17333,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46181</v>
+        <v>46274</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17352,13 +17352,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>0.7</v>
+        <v>13.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17401,7 +17396,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 53137-2023</t>
+          <t>A 44048-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17415,10 +17410,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45229</v>
+        <v>45188</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17431,7 +17426,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17474,7 +17469,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 8788-2024</t>
+          <t>A 62905-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17488,10 +17483,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45356</v>
+        <v>45272</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17504,7 +17499,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.9</v>
+        <v>13.8</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17547,7 +17542,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 680-2024</t>
+          <t>A 37486-2022</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17561,10 +17556,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45300</v>
+        <v>44809</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17577,7 +17572,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.8</v>
+        <v>8.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17637,7 +17632,7 @@
         <v>44847</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17693,7 +17688,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 62554-2022</t>
+          <t>A 5236-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17707,10 +17702,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44924</v>
+        <v>44956</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17723,7 +17718,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17766,7 +17761,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 57236-2023</t>
+          <t>A 56220-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17780,10 +17775,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45245</v>
+        <v>45240</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17796,7 +17791,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17839,7 +17834,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 57237-2023</t>
+          <t>A 972-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17853,10 +17848,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45245</v>
+        <v>45665</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17869,7 +17864,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>18.2</v>
+        <v>1.1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17912,7 +17907,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 29577-2024</t>
+          <t>A 13895-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17926,10 +17921,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45484</v>
+        <v>45391</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17947,7 +17942,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>10.1</v>
+        <v>3.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17990,7 +17985,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 27443-2024</t>
+          <t>A 29724-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18000,14 +17995,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45474</v>
+        <v>45107</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18020,7 +18015,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18063,7 +18058,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 32959-2022</t>
+          <t>A 31974-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18077,10 +18072,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44784</v>
+        <v>45107</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18093,7 +18088,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18136,7 +18131,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 11103-2022</t>
+          <t>A 19802-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18150,10 +18145,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44628</v>
+        <v>45432</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18165,8 +18160,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I221" t="n">
-        <v>5.7</v>
+        <v>2.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18209,7 +18209,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 13320-2024</t>
+          <t>A 16635-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18223,10 +18223,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45386</v>
+        <v>45408</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18282,7 +18282,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 38517-2024</t>
+          <t>A 7922-2022</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18296,10 +18296,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45546</v>
+        <v>44608</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18355,7 +18355,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 28513-2026</t>
+          <t>A 1556-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18369,10 +18369,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46197</v>
+        <v>45670</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18428,7 +18428,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 37119-2024</t>
+          <t>A 12311-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18442,10 +18442,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45539</v>
+        <v>45378</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>6.7</v>
+        <v>2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18501,7 +18501,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 19802-2024</t>
+          <t>A 33948-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18515,10 +18515,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45432</v>
+        <v>45124</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18530,13 +18530,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18579,7 +18574,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 34580-2022</t>
+          <t>A 13320-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18593,10 +18588,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44795</v>
+        <v>45386</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18609,7 +18604,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.9</v>
+        <v>6</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18652,7 +18647,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 32302-2024</t>
+          <t>A 55227-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18666,10 +18661,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45512</v>
+        <v>45231</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18681,13 +18676,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18730,7 +18720,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 32942-2026</t>
+          <t>A 25014-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18744,10 +18734,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46244</v>
+        <v>45461</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18760,7 +18750,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>2.1</v>
+        <v>12.8</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18803,7 +18793,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 29205-2026</t>
+          <t>A 31964-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18817,10 +18807,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46202</v>
+        <v>45107</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18833,7 +18823,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18876,7 +18866,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 29222-2026</t>
+          <t>A 12082-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18890,10 +18880,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46202</v>
+        <v>45377</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18906,7 +18896,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18949,7 +18939,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 19566-2023</t>
+          <t>A 12084-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18963,10 +18953,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45049</v>
+        <v>45377</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18979,7 +18969,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -19022,7 +19012,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 29191-2026</t>
+          <t>A 4976-2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -19036,10 +19026,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46202</v>
+        <v>45329</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19095,7 +19085,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 7272-2022</t>
+          <t>A 64304-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -19109,10 +19099,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>44606</v>
+        <v>45280</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19125,7 +19115,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -19168,7 +19158,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 22822-2024</t>
+          <t>A 48553-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -19182,10 +19172,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45448</v>
+        <v>45208</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19198,7 +19188,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -19241,7 +19231,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 59542-2022</t>
+          <t>A 26815-2023</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19255,10 +19245,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>44907</v>
+        <v>45093</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19271,7 +19261,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19314,7 +19304,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 21402-2024</t>
+          <t>A 16772-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19328,10 +19318,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45441</v>
+        <v>45411</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19344,7 +19334,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19387,7 +19377,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 71781-2021</t>
+          <t>A 25443-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19401,10 +19391,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>44539</v>
+        <v>45089</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19416,13 +19406,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I238" t="n">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19465,7 +19450,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 31930-2024</t>
+          <t>A 66056-2021</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19475,14 +19460,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45510</v>
+        <v>44517</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19495,7 +19480,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19538,7 +19523,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 73901-2021</t>
+          <t>A 23189-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19552,10 +19537,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>44552</v>
+        <v>45450</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19565,6 +19550,11 @@
       <c r="G240" t="inlineStr">
         <is>
           <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I240" t="n">
@@ -19611,7 +19601,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 26840-2023</t>
+          <t>A 7991-2024</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19621,14 +19611,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45093</v>
+        <v>45350</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19684,7 +19674,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 13820-2024</t>
+          <t>A 59542-2022</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19698,10 +19688,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45390</v>
+        <v>44907</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19714,7 +19704,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19757,7 +19747,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 5011-2024</t>
+          <t>A 52848-2021</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19771,10 +19761,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45329</v>
+        <v>44467</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19787,7 +19777,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19830,7 +19820,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 34538-2026</t>
+          <t>A 8361-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19844,10 +19834,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46255</v>
+        <v>45708</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19860,7 +19850,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19903,7 +19893,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 31034-2026</t>
+          <t>A 73310-2021</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19917,10 +19907,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46214</v>
+        <v>44547</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19933,7 +19923,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>2.9</v>
+        <v>6.2</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19976,7 +19966,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 18341-2025</t>
+          <t>A 71781-2021</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19990,10 +19980,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45762</v>
+        <v>44539</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20005,8 +19995,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I246" t="n">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -20049,7 +20044,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 52848-2021</t>
+          <t>A 8362-2025</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -20063,10 +20058,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>44467</v>
+        <v>45708</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20079,7 +20074,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>3</v>
+        <v>7.7</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -20122,7 +20117,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 19753-2024</t>
+          <t>A 30527-2022</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -20136,10 +20131,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45432</v>
+        <v>44762</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20152,7 +20147,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -20195,7 +20190,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 4982-2024</t>
+          <t>A 17573-2025</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -20209,10 +20204,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45329</v>
+        <v>45757</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20225,7 +20220,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -20268,7 +20263,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 55227-2023</t>
+          <t>A 9837-2023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -20282,10 +20277,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45231</v>
+        <v>44984</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20298,7 +20293,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -20341,7 +20336,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 9837-2023</t>
+          <t>A 19753-2024</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20355,10 +20350,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>44984</v>
+        <v>45432</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20371,7 +20366,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20414,7 +20409,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 1556-2025</t>
+          <t>A 27443-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20428,10 +20423,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45670</v>
+        <v>45474</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20487,7 +20482,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 73033-2021</t>
+          <t>A 32959-2022</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20501,10 +20496,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>44550</v>
+        <v>44784</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20517,7 +20512,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20560,7 +20555,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 31559-2026</t>
+          <t>A 30914-2023</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20574,10 +20569,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>46224</v>
+        <v>45113</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20590,7 +20585,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20633,7 +20628,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 64304-2023</t>
+          <t>A 20369-2024</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20647,10 +20642,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45280</v>
+        <v>45435</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20663,7 +20658,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20706,7 +20701,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 8364-2025</t>
+          <t>A 7272-2022</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20720,10 +20715,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45708</v>
+        <v>44606</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20736,7 +20731,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20779,7 +20774,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 37221-2026</t>
+          <t>A 26829-2023</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20793,10 +20788,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>46274</v>
+        <v>45093</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20809,7 +20804,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20852,7 +20847,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 37243-2026</t>
+          <t>A 38517-2024</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20866,10 +20861,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>46274</v>
+        <v>45546</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20882,7 +20877,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>13.9</v>
+        <v>1.3</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20925,7 +20920,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 48553-2023</t>
+          <t>A 63919-2021</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20939,10 +20934,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45208</v>
+        <v>44509</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20955,7 +20950,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>1.7</v>
+        <v>5.2</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20998,7 +20993,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 17573-2025</t>
+          <t>A 4870-2024</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -21012,10 +21007,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45757</v>
+        <v>45329</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21028,7 +21023,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>0.7</v>
+        <v>8.4</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -21071,7 +21066,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 44048-2023</t>
+          <t>A 36646-2023</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -21085,10 +21080,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45188</v>
+        <v>45153</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21101,7 +21096,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -21144,7 +21139,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 30914-2023</t>
+          <t>A 22822-2024</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -21158,10 +21153,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45113</v>
+        <v>45448</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21174,7 +21169,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -21217,7 +21212,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 8370-2023</t>
+          <t>A 19053-2024</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -21231,10 +21226,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>44977</v>
+        <v>45427</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21247,7 +21242,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -21290,7 +21285,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 12217-2025</t>
+          <t>A 11601-2025</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -21304,10 +21299,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45729</v>
+        <v>45727</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21320,7 +21315,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -21363,7 +21358,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 22133-2025</t>
+          <t>A 12175-2024</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21377,10 +21372,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45785</v>
+        <v>45377</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21393,7 +21388,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -21436,7 +21431,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 22537-2025</t>
+          <t>A 29577-2024</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21446,14 +21441,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45787</v>
+        <v>45484</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21465,8 +21460,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I266" t="n">
-        <v>0.8</v>
+        <v>10.1</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -21509,7 +21509,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 13289-2025</t>
+          <t>A 8370-2023</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21523,10 +21523,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45735</v>
+        <v>44977</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21582,7 +21582,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 27218-2023</t>
+          <t>A 12217-2025</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21596,10 +21596,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45096</v>
+        <v>45729</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21655,7 +21655,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 36420-2023</t>
+          <t>A 22133-2025</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21669,10 +21669,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45152</v>
+        <v>45785</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21728,7 +21728,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 17399-2025</t>
+          <t>A 22537-2025</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21738,14 +21738,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45757</v>
+        <v>45787</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21818,7 +21818,7 @@
         <v>45099</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>45272</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>45846</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>45973</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>46035</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>

--- a/Översikt GRUMS.xlsx
+++ b/Översikt GRUMS.xlsx
@@ -601,7 +601,7 @@
         <v>44978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45343</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44788</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44498</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44819</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45615</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>46252</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>44981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45099</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>45898</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45078</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 5280-2022</t>
+          <t>A 66053-2021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44593</v>
+        <v>44517</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1972,19 +1972,14 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>37.1</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1993,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2002,169 +1997,174 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Bronshjon</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 66053-2021 artfynd.xlsx", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 66053-2021 karta.png", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 66053-2021 georefererad karta.tif", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 66053-2021 FSC-klagomål.docx", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 66053-2021 FSC-klagomål mail.docx", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 66053-2021 tillsynsbegäran.docx", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 66053-2021 tillsynsbegäran mail.docx", "A 66053-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 5280-2022</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44593</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
         <v>4</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>1</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Ask
 Tjäder</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 5280-2022 artfynd.xlsx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 5280-2022 karta.png", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 5280-2022 georefererad karta.tif", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 5280-2022 FSC-klagomål.docx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 5280-2022 FSC-klagomål mail.docx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 5280-2022 tillsynsbegäran.docx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 5280-2022 tillsynsbegäran mail.docx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 5280-2022 prioriterade fågelarter.docx", "A 5280-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 66053-2021</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44517</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>6</v>
-      </c>
-      <c r="U15" t="n">
-        <v>6</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Bronshjon</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 66053-2021 artfynd.xlsx", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 66053-2021 karta.png", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 66053-2021 georefererad karta.tif", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 66053-2021 FSC-klagomål.docx", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 66053-2021 FSC-klagomål mail.docx", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 66053-2021 tillsynsbegäran.docx", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 66053-2021 tillsynsbegäran mail.docx", "A 66053-2021")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57233-2023</t>
+          <t>A 54042-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45245</v>
+        <v>44470</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2194,16 +2194,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>7.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2218,7 +2218,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2227,370 +2227,370 @@
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 54042-2021 artfynd.xlsx", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 54042-2021 karta.png", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 54042-2021 georefererad karta.tif", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 54042-2021 FSC-klagomål.docx", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 54042-2021 FSC-klagomål mail.docx", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 54042-2021 tillsynsbegäran.docx", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 54042-2021 tillsynsbegäran mail.docx", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 54042-2021 prioriterade fågelarter.docx", "A 54042-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 56386-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44890</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Vågfibbla
+Rönnfibbla</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 56386-2022 artfynd.xlsx", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 56386-2022 karta.png", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 56386-2022 georefererad karta.tif", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 56386-2022 FSC-klagomål.docx", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 56386-2022 FSC-klagomål mail.docx", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 56386-2022 tillsynsbegäran.docx", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 56386-2022 tillsynsbegäran mail.docx", "A 56386-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 57233-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45245</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
         <v>6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" t="n">
         <v>6</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin
 Skogsklocka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 57233-2023 artfynd.xlsx", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 57233-2023 karta.png", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 57233-2023 georefererad karta.tif", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 57233-2023 FSC-klagomål.docx", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 57233-2023 FSC-klagomål mail.docx", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 57233-2023 tillsynsbegäran.docx", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 57233-2023 tillsynsbegäran mail.docx", "A 57233-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 54042-2021</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44470</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J17" t="n">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 7931-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45706</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 54042-2021 artfynd.xlsx", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 54042-2021 karta.png", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 54042-2021 georefererad karta.tif", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 54042-2021 FSC-klagomål.docx", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 54042-2021 FSC-klagomål mail.docx", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 54042-2021 tillsynsbegäran.docx", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 54042-2021 tillsynsbegäran mail.docx", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 54042-2021 prioriterade fågelarter.docx", "A 54042-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 7931-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45706</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>1</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Skogsödla</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 7931-2025 artfynd.xlsx", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 7931-2025 karta.png", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 7931-2025 georefererad karta.tif", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 7931-2025 FSC-klagomål.docx", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 7931-2025 FSC-klagomål mail.docx", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 7931-2025 tillsynsbegäran.docx", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 7931-2025 tillsynsbegäran mail.docx", "A 7931-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 56386-2022</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44890</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Vågfibbla
-Rönnfibbla</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 56386-2022 artfynd.xlsx", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 56386-2022 karta.png", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 56386-2022 georefererad karta.tif", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 56386-2022 FSC-klagomål.docx", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 56386-2022 FSC-klagomål mail.docx", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 56386-2022 tillsynsbegäran.docx", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 56386-2022 tillsynsbegäran mail.docx", "A 56386-2022")</f>
         <v/>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
         <v>45099</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>44901</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44494</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4178-2022</t>
+          <t>A 54073-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44588</v>
+        <v>44470</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,16 +2962,16 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>20.6</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2986,7 +2986,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2995,49 +2995,53 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 4178-2022 artfynd.xlsx", "A 4178-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 54073-2021 artfynd.xlsx", "A 54073-2021")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 4178-2022 karta.png", "A 4178-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 54073-2021 karta.png", "A 54073-2021")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 4178-2022 georefererad karta.tif", "A 4178-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 54073-2021 georefererad karta.tif", "A 54073-2021")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 4178-2022 FSC-klagomål.docx", "A 4178-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 54073-2021 FSC-klagomål.docx", "A 54073-2021")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 4178-2022 FSC-klagomål mail.docx", "A 4178-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 54073-2021 FSC-klagomål mail.docx", "A 54073-2021")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 4178-2022 tillsynsbegäran.docx", "A 4178-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 54073-2021 tillsynsbegäran.docx", "A 54073-2021")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 4178-2022 tillsynsbegäran mail.docx", "A 4178-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 54073-2021 tillsynsbegäran mail.docx", "A 54073-2021")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 54073-2021 prioriterade fågelarter.docx", "A 54073-2021")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 54073-2021</t>
+          <t>A 4178-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3051,10 +3055,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44470</v>
+        <v>44588</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3067,17 +3071,17 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>20.6</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3091,7 +3095,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3100,46 +3104,42 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 54073-2021 artfynd.xlsx", "A 54073-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 4178-2022 artfynd.xlsx", "A 4178-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 54073-2021 karta.png", "A 54073-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 4178-2022 karta.png", "A 4178-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 54073-2021 georefererad karta.tif", "A 54073-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 4178-2022 georefererad karta.tif", "A 4178-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 54073-2021 FSC-klagomål.docx", "A 54073-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 4178-2022 FSC-klagomål.docx", "A 4178-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 54073-2021 FSC-klagomål mail.docx", "A 54073-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 4178-2022 FSC-klagomål mail.docx", "A 4178-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 54073-2021 tillsynsbegäran.docx", "A 54073-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 4178-2022 tillsynsbegäran.docx", "A 4178-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 54073-2021 tillsynsbegäran mail.docx", "A 54073-2021")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 54073-2021 prioriterade fågelarter.docx", "A 54073-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 4178-2022 tillsynsbegäran mail.docx", "A 4178-2022")</f>
         <v/>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
         <v>44792</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 29582-2024</t>
+          <t>A 37339-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45484</v>
+        <v>44806</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3280,37 +3280,32 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3326,42 +3321,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 29582-2024 artfynd.xlsx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 37339-2022 artfynd.xlsx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 29582-2024 karta.png", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 37339-2022 karta.png", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 29582-2024 georefererad karta.tif", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 37339-2022 georefererad karta.tif", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 29582-2024 FSC-klagomål.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 37339-2022 FSC-klagomål.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 29582-2024 FSC-klagomål mail.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 37339-2022 FSC-klagomål mail.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 29582-2024 tillsynsbegäran.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 37339-2022 tillsynsbegäran.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 29582-2024 tillsynsbegäran mail.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 37339-2022 tillsynsbegäran mail.docx", "A 37339-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13121-2023</t>
+          <t>A 10647-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3371,14 +3366,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45002</v>
+        <v>45368</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3391,7 +3386,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3431,42 +3426,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 13121-2023 artfynd.xlsx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 10647-2024 artfynd.xlsx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 13121-2023 karta.png", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 10647-2024 karta.png", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 13121-2023 georefererad karta.tif", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 10647-2024 georefererad karta.tif", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 13121-2023 FSC-klagomål.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 10647-2024 FSC-klagomål.docx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 13121-2023 FSC-klagomål mail.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 10647-2024 FSC-klagomål mail.docx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 13121-2023 tillsynsbegäran.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 10647-2024 tillsynsbegäran.docx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 13121-2023 tillsynsbegäran mail.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 10647-2024 tillsynsbegäran mail.docx", "A 10647-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15321-2023</t>
+          <t>A 41878-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3480,10 +3475,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45019</v>
+        <v>45561</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3495,18 +3490,23 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>15.9</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3529,49 +3529,53 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 15321-2023 artfynd.xlsx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 41878-2024 artfynd.xlsx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 15321-2023 karta.png", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 41878-2024 karta.png", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 15321-2023 georefererad karta.tif", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 41878-2024 georefererad karta.tif", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 15321-2023 FSC-klagomål.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 41878-2024 FSC-klagomål.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 15321-2023 FSC-klagomål mail.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 41878-2024 FSC-klagomål mail.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 15321-2023 tillsynsbegäran.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 41878-2024 tillsynsbegäran.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 15321-2023 tillsynsbegäran mail.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 41878-2024 tillsynsbegäran mail.docx", "A 41878-2024")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 41878-2024 prioriterade fågelarter.docx", "A 41878-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 47146-2025</t>
+          <t>A 17122-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3581,14 +3585,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45929</v>
+        <v>45412</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3600,16 +3604,11 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3642,50 +3641,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 47146-2025 artfynd.xlsx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 17122-2024 artfynd.xlsx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 47146-2025 karta.png", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 17122-2024 karta.png", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 47146-2025 georefererad karta.tif", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 17122-2024 georefererad karta.tif", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 47146-2025 FSC-klagomål.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 17122-2024 FSC-klagomål.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 47146-2025 FSC-klagomål mail.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 17122-2024 FSC-klagomål mail.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 47146-2025 tillsynsbegäran.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 17122-2024 tillsynsbegäran.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 47146-2025 tillsynsbegäran mail.docx", "A 47146-2025")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 47146-2025 prioriterade fågelarter.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 17122-2024 tillsynsbegäran mail.docx", "A 17122-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 10647-2024</t>
+          <t>A 12296-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3699,10 +3694,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45368</v>
+        <v>46087</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3715,17 +3710,17 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
@@ -3739,7 +3734,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3751,46 +3746,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 10647-2024 artfynd.xlsx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 12296-2026 artfynd.xlsx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 10647-2024 karta.png", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 12296-2026 karta.png", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 10647-2024 georefererad karta.tif", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 12296-2026 georefererad karta.tif", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 10647-2024 FSC-klagomål.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 12296-2026 FSC-klagomål.docx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 10647-2024 FSC-klagomål mail.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 12296-2026 FSC-klagomål mail.docx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 10647-2024 tillsynsbegäran.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 12296-2026 tillsynsbegäran.docx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 10647-2024 tillsynsbegäran mail.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 12296-2026 tillsynsbegäran mail.docx", "A 12296-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12296-2026</t>
+          <t>A 19524-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3804,10 +3799,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46087</v>
+        <v>45429</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3820,10 +3815,10 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -3856,46 +3851,50 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 12296-2026 artfynd.xlsx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19524-2024 artfynd.xlsx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 12296-2026 karta.png", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19524-2024 karta.png", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 12296-2026 georefererad karta.tif", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19524-2024 georefererad karta.tif", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 12296-2026 FSC-klagomål.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19524-2024 FSC-klagomål.docx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 12296-2026 FSC-klagomål mail.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19524-2024 FSC-klagomål mail.docx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 12296-2026 tillsynsbegäran.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19524-2024 tillsynsbegäran.docx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 12296-2026 tillsynsbegäran mail.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19524-2024 tillsynsbegäran mail.docx", "A 19524-2024")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 19524-2024 prioriterade fågelarter.docx", "A 19524-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62675-2023</t>
+          <t>A 19052-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3905,14 +3904,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45271</v>
+        <v>45427</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3925,23 +3924,23 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>7.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>1</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
@@ -3949,10 +3948,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3961,46 +3960,46 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 62675-2023 artfynd.xlsx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19052-2024 artfynd.xlsx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 62675-2023 karta.png", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19052-2024 karta.png", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 62675-2023 georefererad karta.tif", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19052-2024 georefererad karta.tif", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 62675-2023 FSC-klagomål.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19052-2024 FSC-klagomål.docx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 62675-2023 FSC-klagomål mail.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19052-2024 FSC-klagomål mail.docx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 62675-2023 tillsynsbegäran.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19052-2024 tillsynsbegäran.docx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 62675-2023 tillsynsbegäran mail.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19052-2024 tillsynsbegäran mail.docx", "A 19052-2024")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30411-2025</t>
+          <t>A 15321-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4014,10 +4013,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45827</v>
+        <v>45019</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4030,13 +4029,13 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -4063,49 +4062,49 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 30411-2025 artfynd.xlsx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 15321-2023 artfynd.xlsx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 30411-2025 karta.png", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 15321-2023 karta.png", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 30411-2025 georefererad karta.tif", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 15321-2023 georefererad karta.tif", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 30411-2025 FSC-klagomål.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 15321-2023 FSC-klagomål.docx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 30411-2025 FSC-klagomål mail.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 15321-2023 FSC-klagomål mail.docx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 30411-2025 tillsynsbegäran.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 15321-2023 tillsynsbegäran.docx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 30411-2025 tillsynsbegäran mail.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 15321-2023 tillsynsbegäran mail.docx", "A 15321-2023")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 19052-2024</t>
+          <t>A 13121-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4115,14 +4114,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45427</v>
+        <v>45002</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4135,10 +4134,10 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>7.7</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -4150,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4159,10 +4158,10 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4175,42 +4174,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19052-2024 artfynd.xlsx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 13121-2023 artfynd.xlsx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19052-2024 karta.png", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 13121-2023 karta.png", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19052-2024 georefererad karta.tif", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 13121-2023 georefererad karta.tif", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19052-2024 FSC-klagomål.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 13121-2023 FSC-klagomål.docx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19052-2024 FSC-klagomål mail.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 13121-2023 FSC-klagomål mail.docx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19052-2024 tillsynsbegäran.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 13121-2023 tillsynsbegäran.docx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19052-2024 tillsynsbegäran mail.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 13121-2023 tillsynsbegäran mail.docx", "A 13121-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 34076-2026</t>
+          <t>A 30411-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4224,10 +4223,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46252</v>
+        <v>45827</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4240,16 +4239,16 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4264,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4273,49 +4272,49 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 34076-2026 artfynd.xlsx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 30411-2025 artfynd.xlsx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 34076-2026 karta.png", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 30411-2025 karta.png", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 34076-2026 georefererad karta.tif", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 30411-2025 georefererad karta.tif", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 34076-2026 FSC-klagomål.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 30411-2025 FSC-klagomål.docx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 34076-2026 FSC-klagomål mail.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 30411-2025 FSC-klagomål mail.docx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 34076-2026 tillsynsbegäran.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 30411-2025 tillsynsbegäran.docx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 34076-2026 tillsynsbegäran mail.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 30411-2025 tillsynsbegäran mail.docx", "A 30411-2025")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 37339-2022</t>
+          <t>A 47146-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4329,10 +4328,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44806</v>
+        <v>45929</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4344,11 +4343,16 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -4381,46 +4385,50 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 37339-2022 artfynd.xlsx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 47146-2025 artfynd.xlsx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 37339-2022 karta.png", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 47146-2025 karta.png", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 37339-2022 georefererad karta.tif", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 47146-2025 georefererad karta.tif", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 37339-2022 FSC-klagomål.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 47146-2025 FSC-klagomål.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 37339-2022 FSC-klagomål mail.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 47146-2025 FSC-klagomål mail.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 37339-2022 tillsynsbegäran.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 47146-2025 tillsynsbegäran.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 37339-2022 tillsynsbegäran mail.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 47146-2025 tillsynsbegäran mail.docx", "A 47146-2025")</f>
+        <v/>
+      </c>
+      <c r="AE36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 47146-2025 prioriterade fågelarter.docx", "A 47146-2025")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8363-2025</t>
+          <t>A 34076-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4434,10 +4442,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45708</v>
+        <v>46252</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4450,17 +4458,17 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
         <v>1</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
@@ -4474,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4483,49 +4491,49 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 8363-2025 artfynd.xlsx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 34076-2026 artfynd.xlsx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 8363-2025 karta.png", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 34076-2026 karta.png", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 8363-2025 georefererad karta.tif", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 34076-2026 georefererad karta.tif", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 8363-2025 FSC-klagomål.docx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 34076-2026 FSC-klagomål.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 8363-2025 FSC-klagomål mail.docx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 34076-2026 FSC-klagomål mail.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 8363-2025 tillsynsbegäran.docx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 34076-2026 tillsynsbegäran.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 8363-2025 tillsynsbegäran mail.docx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 34076-2026 tillsynsbegäran mail.docx", "A 34076-2026")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17122-2024</t>
+          <t>A 8363-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4535,14 +4543,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45412</v>
+        <v>45708</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4561,10 +4569,10 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4579,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4595,42 +4603,42 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 17122-2024 artfynd.xlsx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 8363-2025 artfynd.xlsx", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 17122-2024 karta.png", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 8363-2025 karta.png", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 17122-2024 georefererad karta.tif", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 8363-2025 georefererad karta.tif", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 17122-2024 FSC-klagomål.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 8363-2025 FSC-klagomål.docx", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 17122-2024 FSC-klagomål mail.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 8363-2025 FSC-klagomål mail.docx", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 17122-2024 tillsynsbegäran.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 8363-2025 tillsynsbegäran.docx", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 17122-2024 tillsynsbegäran mail.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 8363-2025 tillsynsbegäran mail.docx", "A 8363-2025")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 41878-2024</t>
+          <t>A 35077-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4644,10 +4652,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45561</v>
+        <v>45527</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4659,13 +4667,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>15.9</v>
+        <v>2.1</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -4674,10 +4677,10 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>1</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -4692,7 +4695,7 @@
         <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4705,46 +4708,46 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 41878-2024 artfynd.xlsx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 35077-2024 artfynd.xlsx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 41878-2024 karta.png", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 35077-2024 karta.png", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 41878-2024 georefererad karta.tif", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 35077-2024 georefererad karta.tif", "A 35077-2024")</f>
+        <v/>
+      </c>
+      <c r="Z39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/knärot/A 35077-2024 karta knärot.png", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 41878-2024 FSC-klagomål.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 35077-2024 FSC-klagomål.docx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 41878-2024 FSC-klagomål mail.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 35077-2024 FSC-klagomål mail.docx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 41878-2024 tillsynsbegäran.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 35077-2024 tillsynsbegäran.docx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 41878-2024 tillsynsbegäran mail.docx", "A 41878-2024")</f>
-        <v/>
-      </c>
-      <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 41878-2024 prioriterade fågelarter.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 35077-2024 tillsynsbegäran mail.docx", "A 35077-2024")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 35077-2024</t>
+          <t>A 29582-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4758,10 +4761,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45527</v>
+        <v>45484</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4773,20 +4776,25 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -4798,10 +4806,10 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4814,46 +4822,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 35077-2024 artfynd.xlsx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 29582-2024 artfynd.xlsx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 35077-2024 karta.png", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 29582-2024 karta.png", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 35077-2024 georefererad karta.tif", "A 35077-2024")</f>
-        <v/>
-      </c>
-      <c r="Z40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/knärot/A 35077-2024 karta knärot.png", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 29582-2024 georefererad karta.tif", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 35077-2024 FSC-klagomål.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 29582-2024 FSC-klagomål.docx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 35077-2024 FSC-klagomål mail.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 29582-2024 FSC-klagomål mail.docx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 35077-2024 tillsynsbegäran.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 29582-2024 tillsynsbegäran.docx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 35077-2024 tillsynsbegäran mail.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 29582-2024 tillsynsbegäran mail.docx", "A 29582-2024")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19524-2024</t>
+          <t>A 62675-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4863,14 +4867,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45429</v>
+        <v>45271</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4883,16 +4887,16 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -4907,7 +4911,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -4919,43 +4923,39 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19524-2024 artfynd.xlsx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 62675-2023 artfynd.xlsx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19524-2024 karta.png", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 62675-2023 karta.png", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19524-2024 georefererad karta.tif", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 62675-2023 georefererad karta.tif", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19524-2024 FSC-klagomål.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 62675-2023 FSC-klagomål.docx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19524-2024 FSC-klagomål mail.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 62675-2023 FSC-klagomål mail.docx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19524-2024 tillsynsbegäran.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 62675-2023 tillsynsbegäran.docx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19524-2024 tillsynsbegäran mail.docx", "A 19524-2024")</f>
-        <v/>
-      </c>
-      <c r="AE41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 19524-2024 prioriterade fågelarter.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 62675-2023 tillsynsbegäran mail.docx", "A 62675-2023")</f>
         <v/>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
         <v>44484</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>44607</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>44781</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>44509</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44575</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 34652-2022</t>
+          <t>A 32443-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44795</v>
+        <v>44782</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5432,7 +5432,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 32443-2022</t>
+          <t>A 34652-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5446,10 +5446,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44782</v>
+        <v>44795</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
         <v>44860</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>44494</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44844</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>44838</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44690</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>44734</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44694</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44743</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>44467</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>44509</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>44498</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>44798</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44762</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44620</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>44627</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>44735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>44882</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>44806</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>44494</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>44467</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>44732</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>44577</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>44460</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>44755</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>44760</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>44547</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 5841-2022</t>
+          <t>A 12311-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44596</v>
+        <v>45378</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7491,7 +7491,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 5126-2023</t>
+          <t>A 37486-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44958</v>
+        <v>44809</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>14.3</v>
+        <v>8.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7564,7 +7564,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 73033-2021</t>
+          <t>A 21528-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7578,10 +7578,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44550</v>
+        <v>45441</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7637,7 +7637,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13382-2024</t>
+          <t>A 20238-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7651,10 +7651,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45387</v>
+        <v>45434</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7710,7 +7710,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 57236-2023</t>
+          <t>A 42557-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7724,10 +7724,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45245</v>
+        <v>44831</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.9</v>
+        <v>13.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7783,7 +7783,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 57237-2023</t>
+          <t>A 23189-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45245</v>
+        <v>45450</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7812,8 +7812,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>18.2</v>
+        <v>1.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7856,7 +7861,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 5025-2023</t>
+          <t>A 19053-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7870,10 +7875,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44958</v>
+        <v>45427</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7886,7 +7891,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7929,7 +7934,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 73901-2021</t>
+          <t>A 13382-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7943,10 +7948,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44552</v>
+        <v>45387</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7959,7 +7964,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8002,7 +8007,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 5810-2023</t>
+          <t>A 25840-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8016,10 +8021,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44963</v>
+        <v>45467</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8032,7 +8037,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8075,7 +8080,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 47152-2023</t>
+          <t>A 28228-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8089,10 +8094,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45201</v>
+        <v>45477</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8105,7 +8110,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8148,7 +8153,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 28228-2024</t>
+          <t>A 17081-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8162,10 +8167,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45477</v>
+        <v>45412</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8178,7 +8183,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8221,7 +8226,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 26840-2023</t>
+          <t>A 62682-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8235,10 +8240,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45093</v>
+        <v>45271</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8251,7 +8256,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8294,7 +8299,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 18341-2025</t>
+          <t>A 25014-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8308,10 +8313,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45762</v>
+        <v>45461</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8324,7 +8329,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.1</v>
+        <v>12.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8384,7 +8389,7 @@
         <v>44468</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8440,7 +8445,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 58514-2022</t>
+          <t>A 73310-2021</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8454,10 +8459,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44902</v>
+        <v>44547</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8470,7 +8475,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8513,7 +8518,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17437-2025</t>
+          <t>A 45467-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8527,10 +8532,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45757</v>
+        <v>44845</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8543,7 +8548,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8586,7 +8591,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 17443-2025</t>
+          <t>A 58705-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8600,10 +8605,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45757</v>
+        <v>45635</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8615,8 +8620,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8659,7 +8669,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 37119-2024</t>
+          <t>A 36644-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8673,10 +8683,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45539</v>
+        <v>45153</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8689,7 +8699,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>6.7</v>
+        <v>0.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8732,7 +8742,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 17910-2024</t>
+          <t>A 7922-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8746,10 +8756,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45419</v>
+        <v>44608</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8762,7 +8772,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8805,7 +8815,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 2253-2024</t>
+          <t>A 62905-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8819,10 +8829,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45310</v>
+        <v>45272</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8835,7 +8845,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3</v>
+        <v>13.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8878,7 +8888,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 5957-2024</t>
+          <t>A 10892-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8892,10 +8902,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45336</v>
+        <v>44627</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8908,7 +8918,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8951,7 +8961,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 6721-2025</t>
+          <t>A 5126-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8965,10 +8975,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45700</v>
+        <v>44958</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8980,13 +8990,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>5.7</v>
+        <v>14.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9029,7 +9034,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 49300-2022</t>
+          <t>A 31362-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9039,14 +9044,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44861</v>
+        <v>45505</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9059,7 +9064,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9102,7 +9107,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 13289-2025</t>
+          <t>A 8732-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9116,10 +9121,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45735</v>
+        <v>46066</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9132,7 +9137,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>6.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9175,7 +9180,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 20238-2024</t>
+          <t>A 29260-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9189,10 +9194,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45434</v>
+        <v>45824</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9205,7 +9210,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9248,7 +9253,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 27218-2023</t>
+          <t>A 62557-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9262,10 +9267,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45096</v>
+        <v>44924</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9278,7 +9283,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9321,7 +9326,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 36420-2023</t>
+          <t>A 7991-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9331,14 +9336,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45152</v>
+        <v>45350</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9351,7 +9356,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9394,7 +9399,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 17399-2025</t>
+          <t>A 30563-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9408,10 +9413,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45757</v>
+        <v>45831</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9424,7 +9429,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9467,7 +9472,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 56219-2023</t>
+          <t>A 5810-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9481,10 +9486,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45240</v>
+        <v>44963</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9497,7 +9502,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9540,7 +9545,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 680-2024</t>
+          <t>A 32327-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9554,10 +9559,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45300</v>
+        <v>45836</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9570,7 +9575,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9613,7 +9618,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 30339-2022</t>
+          <t>A 12283-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9627,10 +9632,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44760</v>
+        <v>46087</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9643,7 +9648,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>5.3</v>
+        <v>1.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9686,7 +9691,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 29260-2025</t>
+          <t>A 5236-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9700,10 +9705,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45824</v>
+        <v>44956</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9716,7 +9721,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9759,7 +9764,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 30563-2025</t>
+          <t>A 62947-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9773,10 +9778,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45831</v>
+        <v>45272</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9789,7 +9794,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9832,7 +9837,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 975-2025</t>
+          <t>A 8359-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9846,10 +9851,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45665</v>
+        <v>45708</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9862,7 +9867,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9905,7 +9910,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 62557-2022</t>
+          <t>A 7993-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9919,10 +9924,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44924</v>
+        <v>45350</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9935,7 +9940,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9978,7 +9983,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 32327-2025</t>
+          <t>A 33081-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9992,10 +9997,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45836</v>
+        <v>44785</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10008,7 +10013,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10051,7 +10056,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 21402-2024</t>
+          <t>A 14688-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10061,14 +10066,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45441</v>
+        <v>46101</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10081,7 +10086,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10124,7 +10129,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 44497-2025</t>
+          <t>A 35425-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10138,10 +10143,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45916</v>
+        <v>45855</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10154,7 +10159,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10197,7 +10202,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 29736-2023</t>
+          <t>A 15543-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10211,10 +10216,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45107</v>
+        <v>46106</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10227,7 +10232,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10270,7 +10275,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 53138-2023</t>
+          <t>A 15549-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10284,10 +10289,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45229</v>
+        <v>46106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10300,7 +10305,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10343,7 +10348,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 8359-2025</t>
+          <t>A 29762-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10357,10 +10362,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45708</v>
+        <v>45107</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10373,7 +10378,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10416,7 +10421,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 19566-2023</t>
+          <t>A 29736-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10430,10 +10435,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45049</v>
+        <v>45107</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10446,7 +10451,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10489,7 +10494,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 3054-2026</t>
+          <t>A 37517-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10503,10 +10508,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46039</v>
+        <v>45877</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10519,7 +10524,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10562,7 +10567,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 29762-2023</t>
+          <t>A 37515-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10576,10 +10581,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45107</v>
+        <v>45877</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10592,7 +10597,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10635,7 +10640,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 35425-2025</t>
+          <t>A 37495-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10649,10 +10654,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45855</v>
+        <v>45877</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10665,7 +10670,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10708,7 +10713,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 47507-2025</t>
+          <t>A 50640-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10722,10 +10727,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45930</v>
+        <v>45217</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10738,7 +10743,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10781,7 +10786,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 8364-2025</t>
+          <t>A 17910-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10795,10 +10800,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45708</v>
+        <v>45419</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10811,7 +10816,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10854,7 +10859,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 49507-2025</t>
+          <t>A 19054-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10868,10 +10873,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45939</v>
+        <v>46132</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10884,7 +10889,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10927,7 +10932,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 62896-2023</t>
+          <t>A 8361-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10941,10 +10946,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45272</v>
+        <v>45708</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10957,7 +10962,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>13.8</v>
+        <v>2.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11000,7 +11005,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 37515-2025</t>
+          <t>A 31964-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11014,10 +11019,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45877</v>
+        <v>45107</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11030,7 +11035,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11073,7 +11078,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 69847-2021</t>
+          <t>A 35253-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11087,10 +11092,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44532</v>
+        <v>44797</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11103,7 +11108,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11146,7 +11151,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 37495-2025</t>
+          <t>A 29256-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11160,10 +11165,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45877</v>
+        <v>45824</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11176,7 +11181,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11219,7 +11224,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 37517-2025</t>
+          <t>A 29426-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11233,10 +11238,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45877</v>
+        <v>44753</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11248,8 +11253,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>2.9</v>
+        <v>14.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11292,7 +11302,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 58705-2024</t>
+          <t>A 21248-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11306,10 +11316,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45635</v>
+        <v>44705</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11321,13 +11331,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>4.3</v>
+        <v>12.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11370,7 +11375,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 22347-2023</t>
+          <t>A 44497-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11384,10 +11389,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45070</v>
+        <v>45916</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11400,7 +11405,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11443,7 +11448,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 51509-2025</t>
+          <t>A 30339-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11453,14 +11458,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45950</v>
+        <v>44760</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11473,7 +11478,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11516,7 +11521,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 52699-2025</t>
+          <t>A 42143-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11530,10 +11535,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45956</v>
+        <v>45904</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11546,7 +11551,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11589,7 +11594,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 52700-2025</t>
+          <t>A 40522-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11603,10 +11608,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45956</v>
+        <v>45896</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11619,7 +11624,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11662,7 +11667,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 8732-2026</t>
+          <t>A 6751-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11676,10 +11681,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46066</v>
+        <v>45700</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11692,7 +11697,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11735,7 +11740,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 33081-2022</t>
+          <t>A 5214-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11749,10 +11754,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44785</v>
+        <v>45691</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11765,7 +11770,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11808,7 +11813,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 25840-2024</t>
+          <t>A 975-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11822,10 +11827,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45467</v>
+        <v>45665</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11838,7 +11843,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11881,7 +11886,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 37676-2023</t>
+          <t>A 63919-2021</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11891,14 +11896,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45159</v>
+        <v>44509</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11911,7 +11916,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11954,7 +11959,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 6751-2025</t>
+          <t>A 9144-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11968,10 +11973,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45700</v>
+        <v>45358</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11984,7 +11989,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12027,7 +12032,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 58751-2025</t>
+          <t>A 20784-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12041,10 +12046,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45986</v>
+        <v>45776</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12057,7 +12062,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>9.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12100,7 +12105,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 50640-2023</t>
+          <t>A 614-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12114,10 +12119,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45217</v>
+        <v>46024</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12130,7 +12135,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12173,7 +12178,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 34580-2022</t>
+          <t>A 40524-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12187,10 +12192,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44795</v>
+        <v>45896</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12203,7 +12208,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12246,7 +12251,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 12000-2022</t>
+          <t>A 59617-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12260,10 +12265,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44635</v>
+        <v>45992</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12276,7 +12281,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12319,7 +12324,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 42557-2022</t>
+          <t>A 31561-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12333,10 +12338,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44831</v>
+        <v>45117</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12349,7 +12354,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>13.7</v>
+        <v>1.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12392,7 +12397,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 58747-2025</t>
+          <t>A 33948-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12406,10 +12411,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45986</v>
+        <v>45124</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12422,7 +12427,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12465,7 +12470,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 35253-2022</t>
+          <t>A 27222-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12479,10 +12484,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44797</v>
+        <v>45096</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12495,7 +12500,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12538,7 +12543,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 60656-2025</t>
+          <t>A 17972-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12552,10 +12557,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45996</v>
+        <v>45761</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12568,7 +12573,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12611,7 +12616,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 12283-2026</t>
+          <t>A 62896-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12625,10 +12630,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46087</v>
+        <v>45272</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12641,7 +12646,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.9</v>
+        <v>13.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12684,7 +12689,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 13820-2024</t>
+          <t>A 6938-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12694,14 +12699,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45390</v>
+        <v>45343</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12714,7 +12719,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>7.2</v>
+        <v>2.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12757,7 +12762,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 17565-2025</t>
+          <t>A 26829-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12771,10 +12776,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45757</v>
+        <v>45093</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12787,7 +12792,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12830,7 +12835,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 31362-2024</t>
+          <t>A 13895-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12840,14 +12845,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45505</v>
+        <v>45391</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12859,8 +12864,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12903,7 +12913,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 59391-2025</t>
+          <t>A 26815-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12913,14 +12923,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45989</v>
+        <v>45093</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12933,7 +12943,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12976,7 +12986,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 3065-2024</t>
+          <t>A 47507-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12990,10 +13000,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45316</v>
+        <v>45930</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13006,7 +13016,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13049,7 +13059,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 17081-2024</t>
+          <t>A 17565-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13063,10 +13073,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45412</v>
+        <v>45757</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13079,7 +13089,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13122,7 +13132,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 14688-2026</t>
+          <t>A 25443-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13132,14 +13142,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46101</v>
+        <v>45089</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13152,7 +13162,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13195,7 +13205,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 7993-2024</t>
+          <t>A 22406-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13209,10 +13219,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45350</v>
+        <v>46154</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13225,7 +13235,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.1</v>
+        <v>5.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13268,7 +13278,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 45467-2022</t>
+          <t>A 14306-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13282,10 +13292,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44845</v>
+        <v>45011</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13298,7 +13308,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13341,7 +13351,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 15549-2026</t>
+          <t>A 5025-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13355,10 +13365,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46106</v>
+        <v>44958</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13371,7 +13381,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13414,7 +13424,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 5011-2024</t>
+          <t>A 31974-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13428,10 +13438,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45329</v>
+        <v>45107</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13444,7 +13454,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>22</v>
+        <v>3.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13487,7 +13497,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 15543-2026</t>
+          <t>A 39334-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13501,10 +13511,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46106</v>
+        <v>45889</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13517,7 +13527,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13560,7 +13570,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 53137-2023</t>
+          <t>A 5957-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13574,10 +13584,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45229</v>
+        <v>45336</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13590,7 +13600,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13633,7 +13643,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 9144-2024</t>
+          <t>A 3779-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13647,10 +13657,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45358</v>
+        <v>45681</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13662,8 +13672,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>BillerudKorsnäs AB</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>0.8</v>
+        <v>7.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13706,7 +13721,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 62682-2023</t>
+          <t>A 71903-2021</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13720,10 +13735,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45271</v>
+        <v>44543</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13736,7 +13751,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.7</v>
+        <v>6.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13779,7 +13794,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 4982-2024</t>
+          <t>A 49507-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13793,10 +13808,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45329</v>
+        <v>45939</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13809,7 +13824,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13852,7 +13867,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 62947-2023</t>
+          <t>A 23702-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13866,10 +13881,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45272</v>
+        <v>46164</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13881,8 +13896,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13925,7 +13945,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 31930-2024</t>
+          <t>A 2253-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13935,14 +13955,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45510</v>
+        <v>45310</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13955,7 +13975,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13998,7 +14018,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 19054-2026</t>
+          <t>A 4870-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14012,10 +14032,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46132</v>
+        <v>45329</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14028,7 +14048,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.2</v>
+        <v>8.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14071,7 +14091,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 71706-2021</t>
+          <t>A 23733-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14085,10 +14105,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44543</v>
+        <v>46164</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14100,8 +14120,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14144,7 +14169,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 40935-2022</t>
+          <t>A 23757-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14154,14 +14179,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44823</v>
+        <v>46164</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14173,13 +14198,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14222,7 +14242,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 59617-2025</t>
+          <t>A 69847-2021</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14236,10 +14256,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45992</v>
+        <v>44532</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14295,7 +14315,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 6938-2024</t>
+          <t>A 58514-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14305,14 +14325,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45343</v>
+        <v>44902</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14325,7 +14345,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14368,7 +14388,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 29256-2025</t>
+          <t>A 71706-2021</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14382,10 +14402,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45824</v>
+        <v>44543</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14398,7 +14418,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14441,7 +14461,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 614-2026</t>
+          <t>A 23945-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14455,10 +14475,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46024</v>
+        <v>46167</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14470,8 +14490,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14514,7 +14539,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 42143-2025</t>
+          <t>A 47152-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14528,10 +14553,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45904</v>
+        <v>45201</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14544,7 +14569,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14587,7 +14612,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 14306-2023</t>
+          <t>A 24754-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14601,10 +14626,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45011</v>
+        <v>46171</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14617,7 +14642,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14660,7 +14685,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 17972-2025</t>
+          <t>A 51509-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14670,14 +14695,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45761</v>
+        <v>45950</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14690,7 +14715,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14733,7 +14758,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 27222-2023</t>
+          <t>A 53138-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14747,10 +14772,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45096</v>
+        <v>45229</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14763,7 +14788,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14806,7 +14831,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 20784-2025</t>
+          <t>A 16772-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14820,10 +14845,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45776</v>
+        <v>45411</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14836,7 +14861,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>9.5</v>
+        <v>0.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14879,7 +14904,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 36644-2023</t>
+          <t>A 26015-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14889,14 +14914,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45153</v>
+        <v>46181</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14908,8 +14933,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14952,7 +14982,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 40524-2025</t>
+          <t>A 66056-2021</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14966,10 +14996,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45896</v>
+        <v>44517</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14982,7 +15012,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15025,7 +15055,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 21248-2022</t>
+          <t>A 3065-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15039,10 +15069,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44705</v>
+        <v>45316</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15055,7 +15085,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>12.4</v>
+        <v>0.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15098,7 +15128,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 40522-2025</t>
+          <t>A 52700-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15112,10 +15142,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45896</v>
+        <v>45956</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15128,7 +15158,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15171,7 +15201,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 8788-2024</t>
+          <t>A 12082-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15185,10 +15215,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45356</v>
+        <v>45377</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15201,7 +15231,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15244,7 +15274,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 62554-2022</t>
+          <t>A 12084-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15258,10 +15288,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44924</v>
+        <v>45377</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15274,7 +15304,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15317,7 +15347,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 21528-2024</t>
+          <t>A 52699-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15331,10 +15361,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45441</v>
+        <v>45956</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15347,7 +15377,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15407,7 +15437,7 @@
         <v>45061</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15463,7 +15493,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 5214-2025</t>
+          <t>A 17443-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15477,10 +15507,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45691</v>
+        <v>45757</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15493,7 +15523,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15536,7 +15566,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 10892-2022</t>
+          <t>A 11103-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15550,10 +15580,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44627</v>
+        <v>44628</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15566,7 +15596,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15609,7 +15639,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 29426-2022</t>
+          <t>A 20369-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15623,10 +15653,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44753</v>
+        <v>45435</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15638,13 +15668,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>14.4</v>
+        <v>1.4</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15687,7 +15712,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 31561-2023</t>
+          <t>A 11601-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15701,10 +15726,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45117</v>
+        <v>45727</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15717,7 +15742,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15760,7 +15785,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 44048-2023</t>
+          <t>A 4976-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15774,10 +15799,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45188</v>
+        <v>45329</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15790,7 +15815,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15833,7 +15858,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 62905-2023</t>
+          <t>A 28513-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15847,10 +15872,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45272</v>
+        <v>46197</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15863,7 +15888,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>13.8</v>
+        <v>2.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15906,7 +15931,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 37486-2022</t>
+          <t>A 12175-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15920,10 +15945,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44809</v>
+        <v>45377</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15936,7 +15961,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15979,7 +16004,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 46299-2022</t>
+          <t>A 30527-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15993,10 +16018,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44847</v>
+        <v>44762</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16009,7 +16034,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16052,7 +16077,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 22406-2026</t>
+          <t>A 22347-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16066,10 +16091,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46154</v>
+        <v>45070</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16082,7 +16107,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16125,7 +16150,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 5236-2023</t>
+          <t>A 32302-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16139,10 +16164,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44956</v>
+        <v>45512</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16154,8 +16179,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16198,7 +16228,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 56220-2023</t>
+          <t>A 32942-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16212,10 +16242,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45240</v>
+        <v>46244</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16228,7 +16258,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16271,7 +16301,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 972-2025</t>
+          <t>A 29205-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16285,10 +16315,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45665</v>
+        <v>46202</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16301,7 +16331,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16344,7 +16374,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 71903-2021</t>
+          <t>A 29222-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16358,10 +16388,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44543</v>
+        <v>46202</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16374,7 +16404,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>6.3</v>
+        <v>3.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16417,7 +16447,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 3779-2025</t>
+          <t>A 56220-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16431,10 +16461,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45681</v>
+        <v>45240</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16446,13 +16476,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>BillerudKorsnäs AB</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16495,7 +16520,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 39334-2025</t>
+          <t>A 29191-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16509,10 +16534,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45889</v>
+        <v>46202</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16525,7 +16550,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16568,7 +16593,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 13895-2024</t>
+          <t>A 56219-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16582,10 +16607,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45391</v>
+        <v>45240</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16597,13 +16622,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16646,7 +16666,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 23733-2026</t>
+          <t>A 6721-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16660,10 +16680,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46164</v>
+        <v>45700</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16677,11 +16697,11 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16724,7 +16744,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 23945-2026</t>
+          <t>A 58747-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16738,10 +16758,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46167</v>
+        <v>45986</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16753,13 +16773,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16802,7 +16817,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 29724-2023</t>
+          <t>A 58751-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16812,14 +16827,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45107</v>
+        <v>45986</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16832,7 +16847,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16875,7 +16890,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 23757-2026</t>
+          <t>A 17437-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16889,10 +16904,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46164</v>
+        <v>45757</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16905,7 +16920,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16948,7 +16963,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 23702-2026</t>
+          <t>A 5841-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16962,10 +16977,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46164</v>
+        <v>44596</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16977,13 +16992,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17026,7 +17036,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 31974-2023</t>
+          <t>A 12000-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17040,10 +17050,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45107</v>
+        <v>44635</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17056,7 +17066,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17099,7 +17109,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 19802-2024</t>
+          <t>A 40935-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17109,14 +17119,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45432</v>
+        <v>44823</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17134,7 +17144,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17177,7 +17187,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 16635-2024</t>
+          <t>A 36646-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17191,10 +17201,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45408</v>
+        <v>45153</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17207,7 +17217,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17250,7 +17260,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 24754-2026</t>
+          <t>A 29724-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17260,14 +17270,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46171</v>
+        <v>45107</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17280,7 +17290,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17323,7 +17333,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 7922-2022</t>
+          <t>A 8362-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17337,10 +17347,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44608</v>
+        <v>45708</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17353,7 +17363,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.2</v>
+        <v>7.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17396,7 +17406,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 1556-2025</t>
+          <t>A 972-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17410,10 +17420,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45670</v>
+        <v>45665</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17426,7 +17436,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17469,7 +17479,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 12311-2024</t>
+          <t>A 49300-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17483,10 +17493,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45378</v>
+        <v>44861</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17499,7 +17509,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17542,7 +17552,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 26015-2026</t>
+          <t>A 16635-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17552,14 +17562,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46181</v>
+        <v>45408</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17569,11 +17579,6 @@
       <c r="G213" t="inlineStr">
         <is>
           <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I213" t="n">
@@ -17620,7 +17625,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 33948-2023</t>
+          <t>A 37676-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17630,14 +17635,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45124</v>
+        <v>45159</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17650,7 +17655,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17693,7 +17698,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 13320-2024</t>
+          <t>A 34538-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17707,10 +17712,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45386</v>
+        <v>46255</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17723,7 +17728,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17766,7 +17771,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 55227-2023</t>
+          <t>A 31034-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17780,10 +17785,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45231</v>
+        <v>46214</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17796,7 +17801,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17839,7 +17844,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 25014-2024</t>
+          <t>A 53137-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17853,10 +17858,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45461</v>
+        <v>45229</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17869,7 +17874,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>12.8</v>
+        <v>1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17912,7 +17917,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 31964-2023</t>
+          <t>A 8788-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17926,10 +17931,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45107</v>
+        <v>45356</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17942,7 +17947,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17985,7 +17990,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 12082-2024</t>
+          <t>A 680-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17999,10 +18004,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45377</v>
+        <v>45300</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18015,7 +18020,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18058,7 +18063,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 12084-2024</t>
+          <t>A 60656-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18072,10 +18077,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45377</v>
+        <v>45996</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18088,7 +18093,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18131,7 +18136,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 4976-2024</t>
+          <t>A 46299-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18145,10 +18150,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45329</v>
+        <v>44847</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18161,7 +18166,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18204,7 +18209,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 64304-2023</t>
+          <t>A 62554-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18218,10 +18223,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45280</v>
+        <v>44924</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18234,7 +18239,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18277,7 +18282,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 48553-2023</t>
+          <t>A 57236-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18291,10 +18296,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45208</v>
+        <v>45245</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18307,7 +18312,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18350,7 +18355,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 26815-2023</t>
+          <t>A 57237-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18364,10 +18369,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45093</v>
+        <v>45245</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18380,7 +18385,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.1</v>
+        <v>18.2</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18423,7 +18428,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 16772-2024</t>
+          <t>A 31559-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18437,10 +18442,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45411</v>
+        <v>46224</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18453,7 +18458,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18496,7 +18501,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 25443-2023</t>
+          <t>A 29577-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18510,10 +18515,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45089</v>
+        <v>45484</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18525,8 +18530,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>3.8</v>
+        <v>10.1</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18569,7 +18579,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 66056-2021</t>
+          <t>A 27443-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18583,10 +18593,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44517</v>
+        <v>45474</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18599,7 +18609,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18642,7 +18652,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 23189-2024</t>
+          <t>A 32959-2022</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18656,10 +18666,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45450</v>
+        <v>44784</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18671,13 +18681,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18720,7 +18725,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 7991-2024</t>
+          <t>A 37221-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18730,14 +18735,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45350</v>
+        <v>46274</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18750,7 +18755,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18793,7 +18798,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 28513-2026</t>
+          <t>A 13320-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18807,10 +18812,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46197</v>
+        <v>45386</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18823,7 +18828,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18866,7 +18871,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 11103-2022</t>
+          <t>A 37243-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18880,10 +18885,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44628</v>
+        <v>46274</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18896,7 +18901,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>5.7</v>
+        <v>13.9</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18939,7 +18944,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 29205-2026</t>
+          <t>A 59391-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18949,14 +18954,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46202</v>
+        <v>45989</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18969,7 +18974,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -19012,7 +19017,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 59542-2022</t>
+          <t>A 38517-2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -19026,10 +19031,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>44907</v>
+        <v>45546</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19042,7 +19047,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -19085,7 +19090,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 29222-2026</t>
+          <t>A 37119-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -19099,10 +19104,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46202</v>
+        <v>45539</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19115,7 +19120,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>3.3</v>
+        <v>6.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -19158,7 +19163,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 29191-2026</t>
+          <t>A 19802-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -19172,10 +19177,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46202</v>
+        <v>45432</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19187,8 +19192,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I235" t="n">
-        <v>5.1</v>
+        <v>2.5</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -19231,7 +19241,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 32302-2024</t>
+          <t>A 34580-2022</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19245,10 +19255,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45512</v>
+        <v>44795</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19260,13 +19270,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I236" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19309,7 +19314,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 32942-2026</t>
+          <t>A 19566-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19323,10 +19328,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>46244</v>
+        <v>45049</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19339,7 +19344,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19382,7 +19387,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 52848-2021</t>
+          <t>A 7272-2022</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19396,10 +19401,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>44467</v>
+        <v>44606</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19412,7 +19417,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19455,7 +19460,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 8361-2025</t>
+          <t>A 22822-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19469,10 +19474,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45708</v>
+        <v>45448</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19485,7 +19490,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19528,7 +19533,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 73310-2021</t>
+          <t>A 59542-2022</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19542,10 +19547,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>44547</v>
+        <v>44907</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19558,7 +19563,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>6.2</v>
+        <v>0.8</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19601,7 +19606,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 34538-2026</t>
+          <t>A 21402-2024</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19615,10 +19620,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>46255</v>
+        <v>45441</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19631,7 +19636,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19691,7 +19696,7 @@
         <v>44539</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19752,7 +19757,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 31034-2026</t>
+          <t>A 31930-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19762,14 +19767,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>46214</v>
+        <v>45510</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19782,7 +19787,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19825,7 +19830,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 8362-2025</t>
+          <t>A 3054-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19839,10 +19844,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45708</v>
+        <v>46039</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19855,7 +19860,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>7.7</v>
+        <v>2.3</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19898,7 +19903,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 30527-2022</t>
+          <t>A 73901-2021</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19912,10 +19917,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>44762</v>
+        <v>44552</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19928,7 +19933,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19971,7 +19976,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 17573-2025</t>
+          <t>A 26840-2023</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19985,10 +19990,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45757</v>
+        <v>45093</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20001,7 +20006,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -20044,7 +20049,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 9837-2023</t>
+          <t>A 13820-2024</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -20058,10 +20063,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>44984</v>
+        <v>45390</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20074,7 +20079,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>0.6</v>
+        <v>7.2</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -20117,7 +20122,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 19753-2024</t>
+          <t>A 5011-2024</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -20131,10 +20136,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45432</v>
+        <v>45329</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20147,7 +20152,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.5</v>
+        <v>22</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -20190,7 +20195,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 27443-2024</t>
+          <t>A 18341-2025</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -20204,10 +20209,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45474</v>
+        <v>45762</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20220,7 +20225,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -20263,7 +20268,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 32959-2022</t>
+          <t>A 52848-2021</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -20277,10 +20282,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>44784</v>
+        <v>44467</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20293,7 +20298,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -20336,7 +20341,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 30914-2023</t>
+          <t>A 19753-2024</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20350,10 +20355,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45113</v>
+        <v>45432</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20366,7 +20371,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20409,7 +20414,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 20369-2024</t>
+          <t>A 4982-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20423,10 +20428,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45435</v>
+        <v>45329</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20439,7 +20444,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20482,7 +20487,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 7272-2022</t>
+          <t>A 55227-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20496,10 +20501,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>44606</v>
+        <v>45231</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20512,7 +20517,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20555,7 +20560,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 31559-2026</t>
+          <t>A 9837-2023</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20569,10 +20574,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>46224</v>
+        <v>44984</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20585,7 +20590,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20628,7 +20633,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 26829-2023</t>
+          <t>A 1556-2025</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20642,10 +20647,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45093</v>
+        <v>45670</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20658,7 +20663,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20701,7 +20706,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 38517-2024</t>
+          <t>A 73033-2021</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20715,10 +20720,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45546</v>
+        <v>44550</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20731,7 +20736,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20774,7 +20779,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 63919-2021</t>
+          <t>A 64304-2023</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20788,10 +20793,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>44509</v>
+        <v>45280</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20804,7 +20809,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>5.2</v>
+        <v>1.2</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20847,7 +20852,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 4870-2024</t>
+          <t>A 8364-2025</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20861,10 +20866,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45329</v>
+        <v>45708</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20877,7 +20882,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>8.4</v>
+        <v>0.8</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20920,7 +20925,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 36646-2023</t>
+          <t>A 48553-2023</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20934,10 +20939,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45153</v>
+        <v>45208</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20950,7 +20955,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20993,7 +20998,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 37221-2026</t>
+          <t>A 17573-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -21007,10 +21012,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>46274</v>
+        <v>45757</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21023,7 +21028,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -21066,7 +21071,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 37243-2026</t>
+          <t>A 44048-2023</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -21080,10 +21085,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>46274</v>
+        <v>45188</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21096,7 +21101,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>13.9</v>
+        <v>2.5</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -21139,7 +21144,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 22822-2024</t>
+          <t>A 30914-2023</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -21153,10 +21158,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45448</v>
+        <v>45113</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21169,7 +21174,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -21212,7 +21217,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 19053-2024</t>
+          <t>A 8370-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -21226,10 +21231,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45427</v>
+        <v>44977</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21242,7 +21247,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -21285,7 +21290,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 11601-2025</t>
+          <t>A 12217-2025</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -21299,10 +21304,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45727</v>
+        <v>45729</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21315,7 +21320,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -21358,7 +21363,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 12175-2024</t>
+          <t>A 22133-2025</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21372,10 +21377,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45377</v>
+        <v>45785</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21388,7 +21393,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -21431,7 +21436,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 29577-2024</t>
+          <t>A 22537-2025</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21441,14 +21446,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45484</v>
+        <v>45787</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21460,13 +21465,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I266" t="n">
-        <v>10.1</v>
+        <v>0.8</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -21509,7 +21509,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 8370-2023</t>
+          <t>A 13289-2025</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21523,10 +21523,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>44977</v>
+        <v>45735</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21582,7 +21582,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 12217-2025</t>
+          <t>A 27218-2023</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21596,10 +21596,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45729</v>
+        <v>45096</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21655,7 +21655,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 22133-2025</t>
+          <t>A 36420-2023</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21669,10 +21669,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45785</v>
+        <v>45152</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21728,7 +21728,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 22537-2025</t>
+          <t>A 17399-2025</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21738,14 +21738,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45787</v>
+        <v>45757</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21818,7 +21818,7 @@
         <v>45099</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>45272</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>45846</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>45973</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>46035</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>

--- a/Översikt GRUMS.xlsx
+++ b/Översikt GRUMS.xlsx
@@ -601,7 +601,7 @@
         <v>44978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45343</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44788</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44498</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44819</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45615</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>46252</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>44981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45099</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>45078</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>44593</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>45898</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>44517</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>45245</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>44470</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45706</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44890</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>45099</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>44901</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44494</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>44588</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>44470</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>44792</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>45484</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>45019</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>45827</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>45368</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>45929</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45271</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>45427</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>46087</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44806</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45708</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>45412</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>45561</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>46252</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45527</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>45429</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>44484</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>44607</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>44781</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>44509</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44575</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>44795</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>44782</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>44860</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>44494</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44844</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>44838</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44690</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>44734</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44694</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44743</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>44467</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>44509</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>44498</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>44798</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44762</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44620</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>44627</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>44735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>44882</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>44806</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>44494</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>44467</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>44577</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>44732</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>44460</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>44755</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>44760</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>44547</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>44958</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>44552</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>44596</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>45477</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>44958</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>45757</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>45757</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>44550</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>45387</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>45245</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>45245</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44963</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>45201</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>45093</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>45762</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>44468</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>45539</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>45419</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>45310</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>44902</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>44861</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>45700</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>45336</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>45434</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>45240</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>45300</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>44760</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>45665</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>44924</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>45441</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>45107</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>45229</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>45049</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45107</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>45708</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>45272</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>44532</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>45635</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>45070</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>46024</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>45904</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>44785</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>45467</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>45159</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>45776</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>45700</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>45217</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>44795</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>44635</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>44831</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>44797</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>45896</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>44705</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
         <v>45896</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>45390</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>45757</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         <v>45505</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>45691</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>45916</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>45117</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>45316</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>45412</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>45350</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>44845</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>45930</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>45329</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>45229</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>45358</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>45939</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>45271</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         <v>45950</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>45329</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>45272</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>45510</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>45956</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>44543</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>45956</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13066,7 +13066,7 @@
         <v>44823</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>45343</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>45011</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>46154</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13363,7 +13363,7 @@
         <v>45761</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>45096</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>45153</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>45356</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>45986</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>44924</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>45441</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>45061</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>45986</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>44543</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>45681</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>45889</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>44627</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>44753</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>45996</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>46164</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>46167</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>45188</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>46164</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>46164</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>45272</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>45989</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         <v>44809</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>44847</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>44956</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>45240</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>45665</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>46039</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45391</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>45107</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>46171</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>45107</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>45432</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>45408</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>46066</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>44608</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>45670</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>46181</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>45378</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>45124</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>45386</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>45231</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45461</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>46087</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>45107</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>45377</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>45377</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>45329</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>45280</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>45208</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>45093</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>45411</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45089</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>46101</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>46106</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>46106</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>44517</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>45450</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>45350</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>46197</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>44628</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>46202</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>44907</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>46202</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>46202</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>44467</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>45708</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>46132</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>45512</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>45992</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>46244</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>44547</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>45824</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>44539</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>45708</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>44762</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>45757</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19039,7 +19039,7 @@
         <v>44984</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45432</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>45474</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>44784</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>45113</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>45435</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>44606</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>46255</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45093</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>46214</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>45546</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44509</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>45329</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>45153</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>45448</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>45427</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45727</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>45377</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>46224</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>45484</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>44977</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45729</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>46274</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>46274</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>45785</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>45787</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>45735</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>45096</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>45152</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>45757</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         <v>45824</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>45831</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45836</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>45708</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>45855</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>45877</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         <v>45877</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>45877</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45099</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>45272</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>45846</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>45973</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>46035</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>

--- a/Översikt GRUMS.xlsx
+++ b/Översikt GRUMS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE275"/>
+  <dimension ref="A1:AE273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45343</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44788</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44498</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44819</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45615</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>46252</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>44981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45099</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>45078</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 5280-2022</t>
+          <t>A 41113-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44593</v>
+        <v>45898</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1866,13 +1866,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>37.1</v>
+        <v>4.2</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1881,13 +1876,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1899,159 +1894,164 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>2</v>
       </c>
       <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Violmussling
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 41113-2025 artfynd.xlsx", "A 41113-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 41113-2025 karta.png", "A 41113-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 41113-2025 georefererad karta.tif", "A 41113-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 41113-2025 FSC-klagomål.docx", "A 41113-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 41113-2025 FSC-klagomål mail.docx", "A 41113-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 41113-2025 tillsynsbegäran.docx", "A 41113-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 41113-2025 tillsynsbegäran mail.docx", "A 41113-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 5280-2022</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>44593</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
         <v>4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U14" t="n">
         <v>1</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Ask
 Tjäder</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 5280-2022 artfynd.xlsx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 5280-2022 karta.png", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 5280-2022 georefererad karta.tif", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 5280-2022 FSC-klagomål.docx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 5280-2022 FSC-klagomål mail.docx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 5280-2022 tillsynsbegäran.docx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 5280-2022 tillsynsbegäran mail.docx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 5280-2022 prioriterade fågelarter.docx", "A 5280-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 41113-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45898</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Violmussling
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 41113-2025 artfynd.xlsx", "A 41113-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 41113-2025 karta.png", "A 41113-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 41113-2025 georefererad karta.tif", "A 41113-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 41113-2025 FSC-klagomål.docx", "A 41113-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 41113-2025 FSC-klagomål mail.docx", "A 41113-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 41113-2025 tillsynsbegäran.docx", "A 41113-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 41113-2025 tillsynsbegäran mail.docx", "A 41113-2025")</f>
         <v/>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
         <v>44517</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>45245</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>44470</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45706</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44890</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>45099</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>44901</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44494</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>44588</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>44470</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>44792</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>45484</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>45019</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>45827</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>45368</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>45929</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45271</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>45427</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>46087</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 37339-2022</t>
+          <t>A 34076-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44806</v>
+        <v>46252</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>4.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4273,7 +4273,7 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -4284,38 +4284,38 @@
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 37339-2022 artfynd.xlsx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 34076-2026 artfynd.xlsx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 37339-2022 karta.png", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 34076-2026 karta.png", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 37339-2022 georefererad karta.tif", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 34076-2026 georefererad karta.tif", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 37339-2022 FSC-klagomål.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 34076-2026 FSC-klagomål.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 37339-2022 FSC-klagomål mail.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 34076-2026 FSC-klagomål mail.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 37339-2022 tillsynsbegäran.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 34076-2026 tillsynsbegäran.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 37339-2022 tillsynsbegäran mail.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 34076-2026 tillsynsbegäran mail.docx", "A 34076-2026")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 8363-2025</t>
+          <t>A 37339-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45708</v>
+        <v>44806</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4345,17 +4345,17 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
@@ -4369,7 +4369,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4385,42 +4385,42 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 8363-2025 artfynd.xlsx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 37339-2022 artfynd.xlsx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 8363-2025 karta.png", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 37339-2022 karta.png", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 8363-2025 georefererad karta.tif", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 37339-2022 georefererad karta.tif", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 8363-2025 FSC-klagomål.docx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 37339-2022 FSC-klagomål.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 8363-2025 FSC-klagomål mail.docx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 37339-2022 FSC-klagomål mail.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 8363-2025 tillsynsbegäran.docx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 37339-2022 tillsynsbegäran.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 8363-2025 tillsynsbegäran mail.docx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 37339-2022 tillsynsbegäran mail.docx", "A 37339-2022")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 17122-2024</t>
+          <t>A 8363-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4430,14 +4430,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45412</v>
+        <v>45708</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4456,10 +4456,10 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4474,7 +4474,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4490,42 +4490,42 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 17122-2024 artfynd.xlsx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 8363-2025 artfynd.xlsx", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 17122-2024 karta.png", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 8363-2025 karta.png", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 17122-2024 georefererad karta.tif", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 8363-2025 georefererad karta.tif", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 17122-2024 FSC-klagomål.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 8363-2025 FSC-klagomål.docx", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 17122-2024 FSC-klagomål mail.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 8363-2025 FSC-klagomål mail.docx", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 17122-2024 tillsynsbegäran.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 8363-2025 tillsynsbegäran.docx", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 17122-2024 tillsynsbegäran mail.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 8363-2025 tillsynsbegäran mail.docx", "A 8363-2025")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 41878-2024</t>
+          <t>A 17122-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4535,14 +4535,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45561</v>
+        <v>45412</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4554,16 +4554,11 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>15.9</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -4600,46 +4595,42 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 41878-2024 artfynd.xlsx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 17122-2024 artfynd.xlsx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 41878-2024 karta.png", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 17122-2024 karta.png", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 41878-2024 georefererad karta.tif", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 17122-2024 georefererad karta.tif", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 41878-2024 FSC-klagomål.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 17122-2024 FSC-klagomål.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 41878-2024 FSC-klagomål mail.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 17122-2024 FSC-klagomål mail.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 41878-2024 tillsynsbegäran.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 17122-2024 tillsynsbegäran.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 41878-2024 tillsynsbegäran mail.docx", "A 41878-2024")</f>
-        <v/>
-      </c>
-      <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 41878-2024 prioriterade fågelarter.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 17122-2024 tillsynsbegäran mail.docx", "A 17122-2024")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 34076-2026</t>
+          <t>A 41878-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4653,10 +4644,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46252</v>
+        <v>45561</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4668,11 +4659,16 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>4.9</v>
+        <v>15.9</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -4702,42 +4698,46 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 34076-2026 artfynd.xlsx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 41878-2024 artfynd.xlsx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 34076-2026 karta.png", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 41878-2024 karta.png", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 34076-2026 georefererad karta.tif", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 41878-2024 georefererad karta.tif", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 34076-2026 FSC-klagomål.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 41878-2024 FSC-klagomål.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 34076-2026 FSC-klagomål mail.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 41878-2024 FSC-klagomål mail.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 34076-2026 tillsynsbegäran.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 41878-2024 tillsynsbegäran.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 34076-2026 tillsynsbegäran mail.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 41878-2024 tillsynsbegäran mail.docx", "A 41878-2024")</f>
+        <v/>
+      </c>
+      <c r="AE39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 41878-2024 prioriterade fågelarter.docx", "A 41878-2024")</f>
         <v/>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
         <v>45527</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>45429</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>44484</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>44607</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>44781</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>44509</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44575</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>44795</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>44782</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 49116-2022</t>
+          <t>A 59863-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5515,14 +5515,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44860</v>
+        <v>44494</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5578,7 +5578,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59863-2021</t>
+          <t>A 49116-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5588,14 +5588,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44494</v>
+        <v>44860</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
         <v>44844</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>44838</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44690</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>44734</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44694</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44743</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>44467</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>44509</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>44498</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>44798</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44762</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44620</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>44627</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>44735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>44882</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>44806</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>44494</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>44467</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 2089-2022</t>
+          <t>A 25694-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44577</v>
+        <v>44732</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7048,7 +7048,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 25694-2022</t>
+          <t>A 2089-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44732</v>
+        <v>44577</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7121,7 +7121,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 51203-2021</t>
+          <t>A 29699-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44460</v>
+        <v>44755</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7150,13 +7150,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>8</v>
+        <v>3.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7199,7 +7194,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 29699-2022</t>
+          <t>A 30334-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7213,10 +7208,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44755</v>
+        <v>44760</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7229,7 +7224,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7272,7 +7267,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30334-2022</t>
+          <t>A 73306-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7286,10 +7281,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44760</v>
+        <v>44547</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7302,7 +7297,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7345,7 +7340,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 73306-2021</t>
+          <t>A 5841-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7359,10 +7354,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44547</v>
+        <v>44596</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7375,7 +7370,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7418,7 +7413,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 5025-2023</t>
+          <t>A 5126-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7435,7 +7430,7 @@
         <v>44958</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7448,7 +7443,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>14.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7491,7 +7486,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 73901-2021</t>
+          <t>A 73033-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7505,10 +7500,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44552</v>
+        <v>44550</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7521,7 +7516,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7564,7 +7559,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 5841-2022</t>
+          <t>A 13382-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7578,10 +7573,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44596</v>
+        <v>45387</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7594,7 +7589,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7637,7 +7632,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 28228-2024</t>
+          <t>A 5025-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7651,10 +7646,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45477</v>
+        <v>44958</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7667,7 +7662,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7710,7 +7705,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 5126-2023</t>
+          <t>A 73901-2021</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7724,10 +7719,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44958</v>
+        <v>44552</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7740,7 +7735,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>14.3</v>
+        <v>1.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7783,7 +7778,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 17437-2025</t>
+          <t>A 28228-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7797,10 +7792,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45757</v>
+        <v>45477</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7813,7 +7808,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7856,7 +7851,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 17443-2025</t>
+          <t>A 57236-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7870,10 +7865,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45757</v>
+        <v>45245</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7886,7 +7881,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7929,7 +7924,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 73033-2021</t>
+          <t>A 57237-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7943,10 +7938,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44550</v>
+        <v>45245</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7959,7 +7954,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>18.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8002,7 +7997,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 13382-2024</t>
+          <t>A 5810-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8016,10 +8011,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45387</v>
+        <v>44963</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8032,7 +8027,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8075,7 +8070,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 57236-2023</t>
+          <t>A 47152-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8089,10 +8084,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45245</v>
+        <v>45201</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8105,7 +8100,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8148,7 +8143,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 57237-2023</t>
+          <t>A 26840-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8162,10 +8157,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45245</v>
+        <v>45093</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8178,7 +8173,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>18.2</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8221,7 +8216,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 5810-2023</t>
+          <t>A 18341-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8235,10 +8230,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44963</v>
+        <v>45762</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8251,7 +8246,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8294,7 +8289,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 47152-2023</t>
+          <t>A 58514-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8308,10 +8303,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45201</v>
+        <v>44902</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8324,7 +8319,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8367,7 +8362,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 26840-2023</t>
+          <t>A 53209-2021</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8381,10 +8376,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45093</v>
+        <v>44468</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8397,7 +8392,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>11.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8440,7 +8435,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 18341-2025</t>
+          <t>A 17437-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8454,10 +8449,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45762</v>
+        <v>45757</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8470,7 +8465,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8513,7 +8508,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 53209-2021</t>
+          <t>A 17443-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8527,10 +8522,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44468</v>
+        <v>45757</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8543,7 +8538,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>11.6</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8603,7 +8598,7 @@
         <v>45539</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8676,7 +8671,7 @@
         <v>45419</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8749,7 +8744,7 @@
         <v>45310</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8805,7 +8800,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 58514-2022</t>
+          <t>A 6721-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8819,10 +8814,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44902</v>
+        <v>45700</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8834,8 +8829,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>44861</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 6721-2025</t>
+          <t>A 5957-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8965,10 +8965,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45700</v>
+        <v>45336</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8980,13 +8980,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>5.7</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9029,7 +9024,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 5957-2024</t>
+          <t>A 56219-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9043,10 +9038,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45336</v>
+        <v>45240</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9059,7 +9054,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9102,7 +9097,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 20238-2024</t>
+          <t>A 680-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9116,10 +9111,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45434</v>
+        <v>45300</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9132,7 +9127,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9175,7 +9170,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 56219-2023</t>
+          <t>A 30339-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9189,10 +9184,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45240</v>
+        <v>44760</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9205,7 +9200,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9248,7 +9243,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 680-2024</t>
+          <t>A 975-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9262,10 +9257,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45300</v>
+        <v>45665</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9278,7 +9273,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9321,7 +9316,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 30339-2022</t>
+          <t>A 62557-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9335,10 +9330,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44760</v>
+        <v>44924</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9351,7 +9346,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9394,7 +9389,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 975-2025</t>
+          <t>A 21402-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9408,10 +9403,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45665</v>
+        <v>45441</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9424,7 +9419,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9467,7 +9462,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 62557-2022</t>
+          <t>A 29736-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9481,10 +9476,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44924</v>
+        <v>45107</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9497,7 +9492,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9540,7 +9535,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 21402-2024</t>
+          <t>A 20238-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9554,10 +9549,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45441</v>
+        <v>45434</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9613,7 +9608,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 29736-2023</t>
+          <t>A 53138-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9627,10 +9622,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45107</v>
+        <v>45229</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9643,7 +9638,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9686,7 +9681,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 53138-2023</t>
+          <t>A 19566-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9700,10 +9695,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45229</v>
+        <v>45049</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9716,7 +9711,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9759,7 +9754,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 19566-2023</t>
+          <t>A 29762-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9773,10 +9768,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45049</v>
+        <v>45107</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9789,7 +9784,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9832,7 +9827,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 29762-2023</t>
+          <t>A 8364-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9846,10 +9841,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45107</v>
+        <v>45708</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9862,7 +9857,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9905,7 +9900,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 8364-2025</t>
+          <t>A 62896-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9919,10 +9914,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45708</v>
+        <v>45272</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9935,7 +9930,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>13.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9978,7 +9973,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 62896-2023</t>
+          <t>A 69847-2021</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9992,10 +9987,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45272</v>
+        <v>44532</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10008,7 +10003,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>13.8</v>
+        <v>1.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10051,7 +10046,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 69847-2021</t>
+          <t>A 22347-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10065,10 +10060,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44532</v>
+        <v>45070</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10081,7 +10076,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10141,7 +10136,7 @@
         <v>45635</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10202,7 +10197,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 22347-2023</t>
+          <t>A 37515-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10216,10 +10211,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45070</v>
+        <v>45877</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10232,7 +10227,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10275,7 +10270,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 614-2026</t>
+          <t>A 37495-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10289,10 +10284,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46024</v>
+        <v>45877</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10305,7 +10300,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>5.3</v>
+        <v>1.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10348,7 +10343,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 42143-2025</t>
+          <t>A 37517-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10362,10 +10357,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45904</v>
+        <v>45877</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10378,7 +10373,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10421,7 +10416,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 33081-2022</t>
+          <t>A 59617-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10435,10 +10430,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44785</v>
+        <v>45992</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10451,7 +10446,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10494,7 +10489,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 25840-2024</t>
+          <t>A 29256-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10508,10 +10503,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45467</v>
+        <v>45824</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10524,7 +10519,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10567,7 +10562,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 37676-2023</t>
+          <t>A 614-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10577,14 +10572,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45159</v>
+        <v>46024</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10597,7 +10592,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10640,7 +10635,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 20784-2025</t>
+          <t>A 42143-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10654,10 +10649,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45776</v>
+        <v>45904</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10670,7 +10665,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>9.5</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10713,7 +10708,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 6751-2025</t>
+          <t>A 20784-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10727,10 +10722,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45700</v>
+        <v>45776</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10743,7 +10738,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.9</v>
+        <v>9.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10786,7 +10781,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 50640-2023</t>
+          <t>A 33081-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10800,10 +10795,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45217</v>
+        <v>44785</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10816,7 +10811,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10859,7 +10854,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 34580-2022</t>
+          <t>A 25840-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10873,10 +10868,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44795</v>
+        <v>45467</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10889,7 +10884,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10932,7 +10927,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 12000-2022</t>
+          <t>A 40524-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10946,10 +10941,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44635</v>
+        <v>45896</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10962,7 +10957,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11005,7 +11000,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 42557-2022</t>
+          <t>A 21248-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11019,10 +11014,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44831</v>
+        <v>44705</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11035,7 +11030,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>13.7</v>
+        <v>12.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11078,7 +11073,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 35253-2022</t>
+          <t>A 40522-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11092,10 +11087,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44797</v>
+        <v>45896</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11108,7 +11103,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11151,7 +11146,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 40524-2025</t>
+          <t>A 37676-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11161,14 +11156,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45896</v>
+        <v>45159</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11181,7 +11176,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11224,7 +11219,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 21248-2022</t>
+          <t>A 44497-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11238,10 +11233,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44705</v>
+        <v>45916</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11254,7 +11249,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>12.4</v>
+        <v>3.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11297,7 +11292,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 40522-2025</t>
+          <t>A 6751-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11311,10 +11306,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45896</v>
+        <v>45700</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11370,7 +11365,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 13820-2024</t>
+          <t>A 50640-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11384,10 +11379,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45390</v>
+        <v>45217</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11400,7 +11395,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11443,7 +11438,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 17565-2025</t>
+          <t>A 34580-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11457,10 +11452,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45757</v>
+        <v>44795</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11473,7 +11468,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11516,7 +11511,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 31362-2024</t>
+          <t>A 12000-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11526,14 +11521,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45505</v>
+        <v>44635</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11546,7 +11541,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11589,7 +11584,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 5214-2025</t>
+          <t>A 42557-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11603,10 +11598,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45691</v>
+        <v>44831</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11619,7 +11614,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.5</v>
+        <v>13.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11662,7 +11657,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 44497-2025</t>
+          <t>A 35253-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11676,10 +11671,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45916</v>
+        <v>44797</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11692,7 +11687,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11735,7 +11730,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 31561-2023</t>
+          <t>A 47507-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11749,10 +11744,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45117</v>
+        <v>45930</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11765,7 +11760,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11808,7 +11803,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 3065-2024</t>
+          <t>A 5214-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11822,10 +11817,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45316</v>
+        <v>45691</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11838,7 +11833,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11881,7 +11876,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 17081-2024</t>
+          <t>A 31561-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11895,10 +11890,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45412</v>
+        <v>45117</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11911,7 +11906,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11954,7 +11949,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 7993-2024</t>
+          <t>A 13820-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11968,10 +11963,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45350</v>
+        <v>45390</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11984,7 +11979,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.1</v>
+        <v>7.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12027,7 +12022,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 45467-2022</t>
+          <t>A 17565-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12041,10 +12036,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44845</v>
+        <v>45757</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12057,7 +12052,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12100,7 +12095,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 47507-2025</t>
+          <t>A 31362-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12110,14 +12105,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45930</v>
+        <v>45505</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12130,7 +12125,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12173,7 +12168,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 5011-2024</t>
+          <t>A 49507-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12187,10 +12182,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45329</v>
+        <v>45939</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12203,7 +12198,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>22</v>
+        <v>5.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12246,7 +12241,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 53137-2023</t>
+          <t>A 22406-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12260,10 +12255,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45229</v>
+        <v>46154</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12276,7 +12271,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12319,7 +12314,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 9144-2024</t>
+          <t>A 51509-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12329,14 +12324,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45358</v>
+        <v>45950</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12349,7 +12344,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12392,7 +12387,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 49507-2025</t>
+          <t>A 52699-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12406,10 +12401,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45939</v>
+        <v>45956</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12422,7 +12417,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>5.7</v>
+        <v>3.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12465,7 +12460,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 62682-2023</t>
+          <t>A 3065-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12479,10 +12474,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45271</v>
+        <v>45316</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12495,7 +12490,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12538,7 +12533,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 51509-2025</t>
+          <t>A 52700-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12548,14 +12543,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45950</v>
+        <v>45956</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12568,7 +12563,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12611,7 +12606,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 4982-2024</t>
+          <t>A 17081-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12625,10 +12620,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45329</v>
+        <v>45412</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12641,7 +12636,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12684,7 +12679,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 62947-2023</t>
+          <t>A 71903-2021</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12698,10 +12693,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45272</v>
+        <v>44543</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12714,7 +12709,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.7</v>
+        <v>6.3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12757,7 +12752,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 31930-2024</t>
+          <t>A 3779-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12767,14 +12762,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45510</v>
+        <v>45681</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12786,8 +12781,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>BillerudKorsnäs AB</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>0.6</v>
+        <v>7.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12830,7 +12830,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 52699-2025</t>
+          <t>A 7993-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12844,10 +12844,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45956</v>
+        <v>45350</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12903,7 +12903,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 71706-2021</t>
+          <t>A 39334-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12917,10 +12917,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44543</v>
+        <v>45889</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12976,7 +12976,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 52700-2025</t>
+          <t>A 45467-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12990,10 +12990,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45956</v>
+        <v>44845</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13049,7 +13049,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 40935-2022</t>
+          <t>A 5011-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13059,14 +13059,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44823</v>
+        <v>45329</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13078,13 +13078,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13127,7 +13122,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 6938-2024</t>
+          <t>A 53137-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13137,14 +13132,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45343</v>
+        <v>45229</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13157,7 +13152,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13200,7 +13195,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 14306-2023</t>
+          <t>A 23733-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13214,10 +13209,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45011</v>
+        <v>46164</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13229,8 +13224,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13273,7 +13273,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 22406-2026</t>
+          <t>A 23945-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13287,10 +13287,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46154</v>
+        <v>46167</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13302,8 +13302,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13346,7 +13351,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 17972-2025</t>
+          <t>A 23757-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13360,10 +13365,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45761</v>
+        <v>46164</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13376,7 +13381,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13419,7 +13424,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 27222-2023</t>
+          <t>A 23702-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13433,10 +13438,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45096</v>
+        <v>46164</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13448,8 +13453,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13492,7 +13502,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 36644-2023</t>
+          <t>A 9144-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13506,10 +13516,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45153</v>
+        <v>45358</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13522,7 +13532,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13565,7 +13575,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 8788-2024</t>
+          <t>A 62682-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13579,10 +13589,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45356</v>
+        <v>45271</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13595,7 +13605,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13655,7 +13665,7 @@
         <v>45986</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13711,7 +13721,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 62554-2022</t>
+          <t>A 58747-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13725,10 +13735,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44924</v>
+        <v>45986</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13741,7 +13751,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13784,7 +13794,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 21528-2024</t>
+          <t>A 4982-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13798,10 +13808,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45441</v>
+        <v>45329</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13814,7 +13824,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13857,7 +13867,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 20954-2023</t>
+          <t>A 62947-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13871,10 +13881,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45061</v>
+        <v>45272</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13887,7 +13897,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13930,7 +13940,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 58747-2025</t>
+          <t>A 31930-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13940,14 +13950,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45986</v>
+        <v>45510</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13960,7 +13970,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14003,7 +14013,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 71903-2021</t>
+          <t>A 71706-2021</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14020,7 +14030,7 @@
         <v>44543</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14033,7 +14043,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>6.3</v>
+        <v>1.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14076,7 +14086,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 3779-2025</t>
+          <t>A 40935-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14086,14 +14096,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45681</v>
+        <v>44823</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14107,11 +14117,11 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>BillerudKorsnäs AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14154,7 +14164,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 39334-2025</t>
+          <t>A 60656-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14168,10 +14178,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45889</v>
+        <v>45996</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14184,7 +14194,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14227,7 +14237,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 10892-2022</t>
+          <t>A 24754-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14241,10 +14251,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44627</v>
+        <v>46171</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14257,7 +14267,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14300,7 +14310,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 29426-2022</t>
+          <t>A 6938-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14310,14 +14320,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44753</v>
+        <v>45343</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14329,13 +14339,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>14.4</v>
+        <v>2.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14378,7 +14383,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 60656-2025</t>
+          <t>A 14306-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14392,10 +14397,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45996</v>
+        <v>45011</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14408,7 +14413,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14451,7 +14456,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 23733-2026</t>
+          <t>A 59391-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14461,14 +14466,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46164</v>
+        <v>45989</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14480,13 +14485,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14529,7 +14529,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 23945-2026</t>
+          <t>A 17972-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14543,10 +14543,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46167</v>
+        <v>45761</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14558,13 +14558,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14607,7 +14602,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 44048-2023</t>
+          <t>A 27222-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14621,10 +14616,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45188</v>
+        <v>45096</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14637,7 +14632,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14680,7 +14675,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 23757-2026</t>
+          <t>A 36644-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14694,10 +14689,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46164</v>
+        <v>45153</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14710,7 +14705,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14753,7 +14748,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 23702-2026</t>
+          <t>A 26015-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14763,14 +14758,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46164</v>
+        <v>46181</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14788,7 +14783,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14831,7 +14826,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 62905-2023</t>
+          <t>A 8788-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14845,10 +14840,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45272</v>
+        <v>45356</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14861,7 +14856,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>13.8</v>
+        <v>0.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14904,7 +14899,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 59391-2025</t>
+          <t>A 62554-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14914,14 +14909,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45989</v>
+        <v>44924</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14934,7 +14929,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14977,7 +14972,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 37486-2022</t>
+          <t>A 21528-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14991,10 +14986,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44809</v>
+        <v>45441</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15007,7 +15002,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>8.6</v>
+        <v>1.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15050,7 +15045,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 46299-2022</t>
+          <t>A 20954-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15064,10 +15059,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44847</v>
+        <v>45061</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15080,7 +15075,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15123,7 +15118,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 5236-2023</t>
+          <t>A 3054-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15137,10 +15132,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44956</v>
+        <v>46039</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15153,7 +15148,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15196,7 +15191,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 56220-2023</t>
+          <t>A 10892-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15210,10 +15205,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45240</v>
+        <v>44627</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15226,7 +15221,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15269,7 +15264,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 972-2025</t>
+          <t>A 29426-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15283,10 +15278,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45665</v>
+        <v>44753</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15298,8 +15293,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>1.1</v>
+        <v>14.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15342,7 +15342,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 3054-2026</t>
+          <t>A 44048-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15356,10 +15356,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46039</v>
+        <v>45188</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15415,7 +15415,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 13895-2024</t>
+          <t>A 62905-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15429,10 +15429,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45391</v>
+        <v>45272</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15444,13 +15444,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>3.9</v>
+        <v>13.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15493,7 +15488,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 29724-2023</t>
+          <t>A 8732-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15503,14 +15498,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45107</v>
+        <v>46066</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15523,7 +15518,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.7</v>
+        <v>6.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15566,7 +15561,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 24754-2026</t>
+          <t>A 28513-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15580,10 +15575,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46171</v>
+        <v>46197</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15639,7 +15634,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 31974-2023</t>
+          <t>A 11103-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15653,10 +15648,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45107</v>
+        <v>44628</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15669,7 +15664,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15712,7 +15707,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 19802-2024</t>
+          <t>A 37486-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15726,10 +15721,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45432</v>
+        <v>44809</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15741,13 +15736,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15790,7 +15780,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 16635-2024</t>
+          <t>A 29205-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15804,10 +15794,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45408</v>
+        <v>46202</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15820,7 +15810,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15863,7 +15853,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 8732-2026</t>
+          <t>A 46299-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15877,10 +15867,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46066</v>
+        <v>44847</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15893,7 +15883,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>6.1</v>
+        <v>2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15936,7 +15926,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 7922-2022</t>
+          <t>A 29222-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15950,10 +15940,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44608</v>
+        <v>46202</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15966,7 +15956,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16009,7 +15999,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 1556-2025</t>
+          <t>A 5236-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16023,10 +16013,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45670</v>
+        <v>44956</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16039,7 +16029,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16082,7 +16072,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 26015-2026</t>
+          <t>A 12283-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16092,14 +16082,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46181</v>
+        <v>46087</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16111,13 +16101,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16160,7 +16145,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 12311-2024</t>
+          <t>A 56220-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16174,10 +16159,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45378</v>
+        <v>45240</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16190,7 +16175,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16233,7 +16218,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 33948-2023</t>
+          <t>A 972-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16247,10 +16232,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45124</v>
+        <v>45665</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16263,7 +16248,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16306,7 +16291,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 13320-2024</t>
+          <t>A 29191-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16320,10 +16305,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45386</v>
+        <v>46202</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16336,7 +16321,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16379,7 +16364,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 55227-2023</t>
+          <t>A 32302-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16393,10 +16378,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45231</v>
+        <v>45512</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16408,8 +16393,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16452,7 +16442,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 25014-2024</t>
+          <t>A 14688-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16462,14 +16452,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45461</v>
+        <v>46101</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16482,7 +16472,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>12.8</v>
+        <v>2.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16525,7 +16515,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 12283-2026</t>
+          <t>A 13895-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16539,10 +16529,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46087</v>
+        <v>45391</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16554,8 +16544,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16598,7 +16593,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 31964-2023</t>
+          <t>A 15549-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16612,10 +16607,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45107</v>
+        <v>46106</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16628,7 +16623,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16671,7 +16666,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 12082-2024</t>
+          <t>A 29724-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16681,14 +16676,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45377</v>
+        <v>45107</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16701,7 +16696,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16744,7 +16739,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 12084-2024</t>
+          <t>A 15543-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16758,10 +16753,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45377</v>
+        <v>46106</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16774,7 +16769,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16817,7 +16812,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 4976-2024</t>
+          <t>A 31974-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16831,10 +16826,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45329</v>
+        <v>45107</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16847,7 +16842,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16890,7 +16885,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 64304-2023</t>
+          <t>A 19802-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16904,10 +16899,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45280</v>
+        <v>45432</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16919,8 +16914,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16963,7 +16963,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 48553-2023</t>
+          <t>A 16635-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16977,10 +16977,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45208</v>
+        <v>45408</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17036,7 +17036,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 26815-2023</t>
+          <t>A 7922-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17050,10 +17050,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45093</v>
+        <v>44608</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17109,7 +17109,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 16772-2024</t>
+          <t>A 1556-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17123,10 +17123,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45411</v>
+        <v>45670</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17182,7 +17182,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 25443-2023</t>
+          <t>A 12311-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17196,10 +17196,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45089</v>
+        <v>45378</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17255,7 +17255,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 14688-2026</t>
+          <t>A 33948-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17265,14 +17265,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46101</v>
+        <v>45124</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17328,7 +17328,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 15549-2026</t>
+          <t>A 13320-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17342,10 +17342,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46106</v>
+        <v>45386</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17401,7 +17401,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 15543-2026</t>
+          <t>A 55227-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17415,10 +17415,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46106</v>
+        <v>45231</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17431,7 +17431,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17474,7 +17474,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 66056-2021</t>
+          <t>A 25014-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17488,10 +17488,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44517</v>
+        <v>45461</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.7</v>
+        <v>12.8</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17547,7 +17547,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 23189-2024</t>
+          <t>A 31964-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17561,10 +17561,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45450</v>
+        <v>45107</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17576,13 +17576,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17625,7 +17620,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 7991-2024</t>
+          <t>A 12082-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17635,14 +17630,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45350</v>
+        <v>45377</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17655,7 +17650,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17698,7 +17693,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 28513-2026</t>
+          <t>A 12084-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17712,10 +17707,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46197</v>
+        <v>45377</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17728,7 +17723,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17771,7 +17766,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 11103-2022</t>
+          <t>A 4976-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17785,10 +17780,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44628</v>
+        <v>45329</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17801,7 +17796,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17844,7 +17839,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 29205-2026</t>
+          <t>A 64304-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17858,10 +17853,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46202</v>
+        <v>45280</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17874,7 +17869,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17917,7 +17912,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 59542-2022</t>
+          <t>A 48553-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17931,10 +17926,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44907</v>
+        <v>45208</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17947,7 +17942,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17990,7 +17985,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 29222-2026</t>
+          <t>A 26815-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18004,10 +17999,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46202</v>
+        <v>45093</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18020,7 +18015,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18063,7 +18058,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 29191-2026</t>
+          <t>A 34538-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18077,10 +18072,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46202</v>
+        <v>46255</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18093,7 +18088,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18136,7 +18131,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 52848-2021</t>
+          <t>A 16772-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18150,10 +18145,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44467</v>
+        <v>45411</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18166,7 +18161,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18209,7 +18204,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 8361-2025</t>
+          <t>A 25443-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18223,10 +18218,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45708</v>
+        <v>45089</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18239,7 +18234,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18282,7 +18277,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 19054-2026</t>
+          <t>A 31034-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18296,10 +18291,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46132</v>
+        <v>46214</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18312,7 +18307,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18355,7 +18350,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 32302-2024</t>
+          <t>A 66056-2021</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18369,10 +18364,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45512</v>
+        <v>44517</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18384,13 +18379,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18433,7 +18423,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 59617-2025</t>
+          <t>A 23189-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18447,10 +18437,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45992</v>
+        <v>45450</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18462,8 +18452,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18506,7 +18501,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 32942-2026</t>
+          <t>A 7991-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18516,14 +18511,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46244</v>
+        <v>45350</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18536,7 +18531,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18579,7 +18574,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 73310-2021</t>
+          <t>A 59542-2022</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18593,10 +18588,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44547</v>
+        <v>44907</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18609,7 +18604,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>6.2</v>
+        <v>0.8</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18652,7 +18647,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 29256-2025</t>
+          <t>A 52848-2021</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18666,10 +18661,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45824</v>
+        <v>44467</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18682,7 +18677,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18725,7 +18720,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 71781-2021</t>
+          <t>A 8361-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18739,10 +18734,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44539</v>
+        <v>45708</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18754,13 +18749,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18803,7 +18793,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 8362-2025</t>
+          <t>A 31559-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18817,10 +18807,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45708</v>
+        <v>46224</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18833,7 +18823,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>7.7</v>
+        <v>1.6</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18876,7 +18866,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 30527-2022</t>
+          <t>A 73310-2021</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18890,10 +18880,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44762</v>
+        <v>44547</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18906,7 +18896,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18949,7 +18939,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 17573-2025</t>
+          <t>A 71781-2021</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18963,10 +18953,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45757</v>
+        <v>44539</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18978,8 +18968,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I232" t="n">
-        <v>0.7</v>
+        <v>7</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -19022,7 +19017,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 9837-2023</t>
+          <t>A 8362-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -19036,10 +19031,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>44984</v>
+        <v>45708</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19052,7 +19047,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.6</v>
+        <v>7.7</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -19095,7 +19090,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 19753-2024</t>
+          <t>A 37221-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -19109,10 +19104,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45432</v>
+        <v>46274</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19125,7 +19120,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -19168,7 +19163,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 27443-2024</t>
+          <t>A 37243-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -19182,10 +19177,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45474</v>
+        <v>46274</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19198,7 +19193,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.8</v>
+        <v>13.9</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -19241,7 +19236,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 32959-2022</t>
+          <t>A 30527-2022</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19255,10 +19250,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>44784</v>
+        <v>44762</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19271,7 +19266,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19314,7 +19309,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 30914-2023</t>
+          <t>A 17573-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19328,10 +19323,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45113</v>
+        <v>45757</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19344,7 +19339,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19387,7 +19382,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 20369-2024</t>
+          <t>A 9837-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19401,10 +19396,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45435</v>
+        <v>44984</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19417,7 +19412,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19460,7 +19455,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 7272-2022</t>
+          <t>A 19753-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19474,10 +19469,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44606</v>
+        <v>45432</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19490,7 +19485,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19533,7 +19528,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 34538-2026</t>
+          <t>A 27443-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19547,10 +19542,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>46255</v>
+        <v>45474</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19563,7 +19558,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19606,7 +19601,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 26829-2023</t>
+          <t>A 32959-2022</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19620,10 +19615,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45093</v>
+        <v>44784</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19636,7 +19631,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19679,7 +19674,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 31034-2026</t>
+          <t>A 30914-2023</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19693,10 +19688,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46214</v>
+        <v>45113</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19709,7 +19704,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19752,7 +19747,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 38517-2024</t>
+          <t>A 20369-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19766,10 +19761,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45546</v>
+        <v>45435</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19782,7 +19777,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19825,7 +19820,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 63919-2021</t>
+          <t>A 7272-2022</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19839,10 +19834,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>44509</v>
+        <v>44606</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19855,7 +19850,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>5.2</v>
+        <v>1.4</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19898,7 +19893,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 4870-2024</t>
+          <t>A 26829-2023</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19912,10 +19907,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45329</v>
+        <v>45093</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19928,7 +19923,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>8.4</v>
+        <v>1.5</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19971,7 +19966,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 36646-2023</t>
+          <t>A 38517-2024</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19985,10 +19980,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45153</v>
+        <v>45546</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20001,7 +19996,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -20044,7 +20039,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 22822-2024</t>
+          <t>A 32942-2026</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -20058,10 +20053,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45448</v>
+        <v>46244</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20074,7 +20069,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -20117,7 +20112,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 19053-2024</t>
+          <t>A 63919-2021</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -20131,10 +20126,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45427</v>
+        <v>44509</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20147,7 +20142,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -20190,7 +20185,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 11601-2025</t>
+          <t>A 4870-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -20204,10 +20199,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45727</v>
+        <v>45329</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20220,7 +20215,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.8</v>
+        <v>8.4</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -20263,7 +20258,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 12175-2024</t>
+          <t>A 36646-2023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -20277,10 +20272,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45377</v>
+        <v>45153</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20293,7 +20288,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -20336,7 +20331,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 31559-2026</t>
+          <t>A 22822-2024</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20350,10 +20345,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>46224</v>
+        <v>45448</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20366,7 +20361,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20409,7 +20404,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 29577-2024</t>
+          <t>A 19053-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20423,10 +20418,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45484</v>
+        <v>45427</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20438,13 +20433,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I252" t="n">
-        <v>10.1</v>
+        <v>3.7</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20487,7 +20477,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 8370-2023</t>
+          <t>A 11601-2025</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20501,10 +20491,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>44977</v>
+        <v>45727</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20517,7 +20507,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20560,7 +20550,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 12217-2025</t>
+          <t>A 12175-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20574,10 +20564,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45729</v>
+        <v>45377</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20590,7 +20580,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20633,7 +20623,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 37221-2026</t>
+          <t>A 29577-2024</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20647,10 +20637,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>46274</v>
+        <v>45484</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20662,8 +20652,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I255" t="n">
-        <v>2.3</v>
+        <v>10.1</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20706,7 +20701,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 37243-2026</t>
+          <t>A 8370-2023</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20720,10 +20715,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>46274</v>
+        <v>44977</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20736,7 +20731,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>13.9</v>
+        <v>0.9</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20779,7 +20774,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 22133-2025</t>
+          <t>A 12217-2025</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20793,10 +20788,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45785</v>
+        <v>45729</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20809,7 +20804,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20852,7 +20847,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 22537-2025</t>
+          <t>A 22133-2025</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20862,14 +20857,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45787</v>
+        <v>45785</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20882,7 +20877,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20925,7 +20920,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 13289-2025</t>
+          <t>A 22537-2025</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20935,14 +20930,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45735</v>
+        <v>45787</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20955,7 +20950,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20998,7 +20993,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 27218-2023</t>
+          <t>A 13289-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -21012,10 +21007,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45096</v>
+        <v>45735</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21028,7 +21023,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -21071,7 +21066,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 36420-2023</t>
+          <t>A 27218-2023</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -21085,10 +21080,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45152</v>
+        <v>45096</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21101,7 +21096,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -21144,7 +21139,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 17399-2025</t>
+          <t>A 36420-2023</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -21158,10 +21153,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45757</v>
+        <v>45152</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21174,7 +21169,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -21217,7 +21212,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 29260-2025</t>
+          <t>A 17399-2025</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -21231,10 +21226,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45824</v>
+        <v>45757</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21247,7 +21242,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -21290,7 +21285,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 30563-2025</t>
+          <t>A 29260-2025</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -21304,10 +21299,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45831</v>
+        <v>45824</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21320,7 +21315,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -21363,7 +21358,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 32327-2025</t>
+          <t>A 30563-2025</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21377,10 +21372,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45836</v>
+        <v>45831</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21393,7 +21388,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -21436,7 +21431,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 8359-2025</t>
+          <t>A 32327-2025</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21450,10 +21445,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45708</v>
+        <v>45836</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21466,7 +21461,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -21509,7 +21504,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 35425-2025</t>
+          <t>A 8359-2025</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21523,10 +21518,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45855</v>
+        <v>45708</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21539,7 +21534,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21582,7 +21577,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 37515-2025</t>
+          <t>A 35425-2025</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21596,10 +21591,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45877</v>
+        <v>45855</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21655,24 +21650,24 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 37495-2025</t>
+          <t>S 2221-2023</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45877</v>
+        <v>45099</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21684,8 +21679,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I269" t="n">
-        <v>1.9</v>
+        <v>5.5</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21728,24 +21728,24 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 37517-2025</t>
+          <t>S 4473-2023</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45877</v>
+        <v>45272</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>2.9</v>
+        <v>43.7</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21801,7 +21801,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>S 2221-2023</t>
+          <t>S 2137-2025</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21811,14 +21811,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45099</v>
+        <v>45846</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21830,13 +21830,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I271" t="n">
-        <v>5.5</v>
+        <v>20.2</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21879,7 +21874,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>S 4473-2023</t>
+          <t>S 3158-2025</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21889,14 +21884,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>45272</v>
+        <v>45973</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21909,7 +21904,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>43.7</v>
+        <v>8.1</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21949,10 +21944,10 @@
       </c>
       <c r="V272" s="2" t="inlineStr"/>
     </row>
-    <row r="273" ht="15" customHeight="1">
+    <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>S 2137-2025</t>
+          <t>S 88-2026</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21966,10 +21961,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>45846</v>
+        <v>46035</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21981,8 +21976,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I273" t="n">
-        <v>20.2</v>
+        <v>1.8</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -22021,157 +22021,6 @@
         <v>0</v>
       </c>
       <c r="V273" s="2" t="inlineStr"/>
-    </row>
-    <row r="274" ht="15" customHeight="1">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>S 3158-2025</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D274" s="1" t="n">
-        <v>45973</v>
-      </c>
-      <c r="E274" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="I274" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J274" t="n">
-        <v>0</v>
-      </c>
-      <c r="K274" t="n">
-        <v>0</v>
-      </c>
-      <c r="L274" t="n">
-        <v>0</v>
-      </c>
-      <c r="M274" t="n">
-        <v>0</v>
-      </c>
-      <c r="N274" t="n">
-        <v>0</v>
-      </c>
-      <c r="O274" t="n">
-        <v>0</v>
-      </c>
-      <c r="P274" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
-      <c r="R274" t="n">
-        <v>0</v>
-      </c>
-      <c r="S274" t="n">
-        <v>0</v>
-      </c>
-      <c r="T274" t="n">
-        <v>0</v>
-      </c>
-      <c r="U274" t="n">
-        <v>0</v>
-      </c>
-      <c r="V274" s="2" t="inlineStr"/>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>S 88-2026</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D275" s="1" t="n">
-        <v>46035</v>
-      </c>
-      <c r="E275" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I275" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J275" t="n">
-        <v>0</v>
-      </c>
-      <c r="K275" t="n">
-        <v>0</v>
-      </c>
-      <c r="L275" t="n">
-        <v>0</v>
-      </c>
-      <c r="M275" t="n">
-        <v>0</v>
-      </c>
-      <c r="N275" t="n">
-        <v>0</v>
-      </c>
-      <c r="O275" t="n">
-        <v>0</v>
-      </c>
-      <c r="P275" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
-      <c r="R275" t="n">
-        <v>0</v>
-      </c>
-      <c r="S275" t="n">
-        <v>0</v>
-      </c>
-      <c r="T275" t="n">
-        <v>0</v>
-      </c>
-      <c r="U275" t="n">
-        <v>0</v>
-      </c>
-      <c r="V275" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GRUMS.xlsx
+++ b/Översikt GRUMS.xlsx
@@ -601,7 +601,7 @@
         <v>44978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45343</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44788</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44498</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44819</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45615</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>46252</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>44981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45099</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>45078</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45898</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 5280-2022</t>
+          <t>A 66053-2021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44593</v>
+        <v>44517</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1972,19 +1972,14 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>37.1</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1993,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2002,169 +1997,174 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Bronshjon</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 66053-2021 artfynd.xlsx", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 66053-2021 karta.png", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 66053-2021 georefererad karta.tif", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 66053-2021 FSC-klagomål.docx", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 66053-2021 FSC-klagomål mail.docx", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 66053-2021 tillsynsbegäran.docx", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 66053-2021 tillsynsbegäran mail.docx", "A 66053-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 5280-2022</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44593</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
         <v>4</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>1</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Ask
 Tjäder</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 5280-2022 artfynd.xlsx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 5280-2022 karta.png", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 5280-2022 georefererad karta.tif", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 5280-2022 FSC-klagomål.docx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 5280-2022 FSC-klagomål mail.docx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 5280-2022 tillsynsbegäran.docx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 5280-2022 tillsynsbegäran mail.docx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 5280-2022 prioriterade fågelarter.docx", "A 5280-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 66053-2021</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44517</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>6</v>
-      </c>
-      <c r="U15" t="n">
-        <v>6</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Bronshjon</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 66053-2021 artfynd.xlsx", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 66053-2021 karta.png", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 66053-2021 georefererad karta.tif", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 66053-2021 FSC-klagomål.docx", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 66053-2021 FSC-klagomål mail.docx", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 66053-2021 tillsynsbegäran.docx", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 66053-2021 tillsynsbegäran mail.docx", "A 66053-2021")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57233-2023</t>
+          <t>A 54042-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45245</v>
+        <v>44470</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2194,16 +2194,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>7.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2218,7 +2218,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2227,370 +2227,370 @@
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 54042-2021 artfynd.xlsx", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 54042-2021 karta.png", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 54042-2021 georefererad karta.tif", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 54042-2021 FSC-klagomål.docx", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 54042-2021 FSC-klagomål mail.docx", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 54042-2021 tillsynsbegäran.docx", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 54042-2021 tillsynsbegäran mail.docx", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 54042-2021 prioriterade fågelarter.docx", "A 54042-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 56386-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44890</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Vågfibbla
+Rönnfibbla</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 56386-2022 artfynd.xlsx", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 56386-2022 karta.png", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 56386-2022 georefererad karta.tif", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 56386-2022 FSC-klagomål.docx", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 56386-2022 FSC-klagomål mail.docx", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 56386-2022 tillsynsbegäran.docx", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 56386-2022 tillsynsbegäran mail.docx", "A 56386-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 57233-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45245</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
         <v>6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" t="n">
         <v>6</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin
 Skogsklocka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 57233-2023 artfynd.xlsx", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 57233-2023 karta.png", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 57233-2023 georefererad karta.tif", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 57233-2023 FSC-klagomål.docx", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 57233-2023 FSC-klagomål mail.docx", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 57233-2023 tillsynsbegäran.docx", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 57233-2023 tillsynsbegäran mail.docx", "A 57233-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 54042-2021</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44470</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J17" t="n">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 7931-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45706</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 54042-2021 artfynd.xlsx", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 54042-2021 karta.png", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 54042-2021 georefererad karta.tif", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 54042-2021 FSC-klagomål.docx", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 54042-2021 FSC-klagomål mail.docx", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 54042-2021 tillsynsbegäran.docx", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 54042-2021 tillsynsbegäran mail.docx", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 54042-2021 prioriterade fågelarter.docx", "A 54042-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 7931-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45706</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>1</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Skogsödla</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 7931-2025 artfynd.xlsx", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 7931-2025 karta.png", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 7931-2025 georefererad karta.tif", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 7931-2025 FSC-klagomål.docx", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 7931-2025 FSC-klagomål mail.docx", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 7931-2025 tillsynsbegäran.docx", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 7931-2025 tillsynsbegäran mail.docx", "A 7931-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 56386-2022</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44890</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Vågfibbla
-Rönnfibbla</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 56386-2022 artfynd.xlsx", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 56386-2022 karta.png", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 56386-2022 georefererad karta.tif", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 56386-2022 FSC-klagomål.docx", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 56386-2022 FSC-klagomål mail.docx", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 56386-2022 tillsynsbegäran.docx", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 56386-2022 tillsynsbegäran mail.docx", "A 56386-2022")</f>
         <v/>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
         <v>45099</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>44901</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44494</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>44588</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>44470</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>44792</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 29582-2024</t>
+          <t>A 15321-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45484</v>
+        <v>45019</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3280,16 +3280,11 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -3319,49 +3314,49 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 29582-2024 artfynd.xlsx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 15321-2023 artfynd.xlsx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 29582-2024 karta.png", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 15321-2023 karta.png", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 29582-2024 georefererad karta.tif", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 15321-2023 georefererad karta.tif", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 29582-2024 FSC-klagomål.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 15321-2023 FSC-klagomål.docx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 29582-2024 FSC-klagomål mail.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 15321-2023 FSC-klagomål mail.docx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 29582-2024 tillsynsbegäran.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 15321-2023 tillsynsbegäran.docx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 29582-2024 tillsynsbegäran mail.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 15321-2023 tillsynsbegäran mail.docx", "A 15321-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13121-2023</t>
+          <t>A 37339-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3371,14 +3366,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45002</v>
+        <v>44806</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3391,17 +3386,17 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
@@ -3415,7 +3410,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3427,46 +3422,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 13121-2023 artfynd.xlsx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 37339-2022 artfynd.xlsx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 13121-2023 karta.png", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 37339-2022 karta.png", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 13121-2023 georefererad karta.tif", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 37339-2022 georefererad karta.tif", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 13121-2023 FSC-klagomål.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 37339-2022 FSC-klagomål.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 13121-2023 FSC-klagomål mail.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 37339-2022 FSC-klagomål mail.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 13121-2023 tillsynsbegäran.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 37339-2022 tillsynsbegäran.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 13121-2023 tillsynsbegäran mail.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 37339-2022 tillsynsbegäran mail.docx", "A 37339-2022")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15321-2023</t>
+          <t>A 13121-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3476,14 +3471,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45019</v>
+        <v>45002</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3496,13 +3491,13 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3529,49 +3524,49 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 15321-2023 artfynd.xlsx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 13121-2023 artfynd.xlsx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 15321-2023 karta.png", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 13121-2023 karta.png", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 15321-2023 georefererad karta.tif", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 13121-2023 georefererad karta.tif", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 15321-2023 FSC-klagomål.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 13121-2023 FSC-klagomål.docx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 15321-2023 FSC-klagomål mail.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 13121-2023 FSC-klagomål mail.docx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 15321-2023 tillsynsbegäran.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 13121-2023 tillsynsbegäran.docx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 15321-2023 tillsynsbegäran mail.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 13121-2023 tillsynsbegäran mail.docx", "A 13121-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 30411-2025</t>
+          <t>A 10647-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3585,10 +3580,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45827</v>
+        <v>45368</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3601,7 +3596,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3637,46 +3632,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 30411-2025 artfynd.xlsx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 10647-2024 artfynd.xlsx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 30411-2025 karta.png", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 10647-2024 karta.png", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 30411-2025 georefererad karta.tif", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 10647-2024 georefererad karta.tif", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 30411-2025 FSC-klagomål.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 10647-2024 FSC-klagomål.docx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 30411-2025 FSC-klagomål mail.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 10647-2024 FSC-klagomål mail.docx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 30411-2025 tillsynsbegäran.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 10647-2024 tillsynsbegäran.docx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 30411-2025 tillsynsbegäran mail.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 10647-2024 tillsynsbegäran mail.docx", "A 10647-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 10647-2024</t>
+          <t>A 47146-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3690,10 +3685,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45368</v>
+        <v>45929</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3705,8 +3700,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3730,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3746,42 +3746,46 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 10647-2024 artfynd.xlsx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 47146-2025 artfynd.xlsx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 10647-2024 karta.png", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 47146-2025 karta.png", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 10647-2024 georefererad karta.tif", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 47146-2025 georefererad karta.tif", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 10647-2024 FSC-klagomål.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 47146-2025 FSC-klagomål.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 10647-2024 FSC-klagomål mail.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 47146-2025 FSC-klagomål mail.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 10647-2024 tillsynsbegäran.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 47146-2025 tillsynsbegäran.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 10647-2024 tillsynsbegäran mail.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 47146-2025 tillsynsbegäran mail.docx", "A 47146-2025")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 47146-2025 prioriterade fågelarter.docx", "A 47146-2025")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 47146-2025</t>
+          <t>A 41878-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3795,10 +3799,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45929</v>
+        <v>45561</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3816,7 +3820,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>7</v>
+        <v>15.9</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -3852,50 +3856,50 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 47146-2025 artfynd.xlsx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 41878-2024 artfynd.xlsx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 47146-2025 karta.png", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 41878-2024 karta.png", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 47146-2025 georefererad karta.tif", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 41878-2024 georefererad karta.tif", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 47146-2025 FSC-klagomål.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 41878-2024 FSC-klagomål.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 47146-2025 FSC-klagomål mail.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 41878-2024 FSC-klagomål mail.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 47146-2025 tillsynsbegäran.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 41878-2024 tillsynsbegäran.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 47146-2025 tillsynsbegäran mail.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 41878-2024 tillsynsbegäran mail.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 47146-2025 prioriterade fågelarter.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 41878-2024 prioriterade fågelarter.docx", "A 41878-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62675-2023</t>
+          <t>A 17122-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3909,10 +3913,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45271</v>
+        <v>45412</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3925,17 +3929,17 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
@@ -3949,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3965,42 +3969,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 62675-2023 artfynd.xlsx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 17122-2024 artfynd.xlsx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 62675-2023 karta.png", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 17122-2024 karta.png", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 62675-2023 georefererad karta.tif", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 17122-2024 georefererad karta.tif", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 62675-2023 FSC-klagomål.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 17122-2024 FSC-klagomål.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 62675-2023 FSC-klagomål mail.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 17122-2024 FSC-klagomål mail.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 62675-2023 tillsynsbegäran.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 17122-2024 tillsynsbegäran.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 62675-2023 tillsynsbegäran mail.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 17122-2024 tillsynsbegäran mail.docx", "A 17122-2024")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 19052-2024</t>
+          <t>A 19524-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4014,10 +4018,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45427</v>
+        <v>45429</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4030,22 +4034,22 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7.7</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4057,7 +4061,7 @@
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4070,42 +4074,46 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19052-2024 artfynd.xlsx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19524-2024 artfynd.xlsx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19052-2024 karta.png", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19524-2024 karta.png", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19052-2024 georefererad karta.tif", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19524-2024 georefererad karta.tif", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19052-2024 FSC-klagomål.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19524-2024 FSC-klagomål.docx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19052-2024 FSC-klagomål mail.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19524-2024 FSC-klagomål mail.docx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19052-2024 tillsynsbegäran.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19524-2024 tillsynsbegäran.docx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19052-2024 tillsynsbegäran mail.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19524-2024 tillsynsbegäran mail.docx", "A 19524-2024")</f>
+        <v/>
+      </c>
+      <c r="AE33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 19524-2024 prioriterade fågelarter.docx", "A 19524-2024")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12296-2026</t>
+          <t>A 8363-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4119,10 +4127,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46087</v>
+        <v>45708</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4135,16 +4143,16 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4159,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4175,42 +4183,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 12296-2026 artfynd.xlsx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 8363-2025 artfynd.xlsx", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 12296-2026 karta.png", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 8363-2025 karta.png", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 12296-2026 georefererad karta.tif", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 8363-2025 georefererad karta.tif", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 12296-2026 FSC-klagomål.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 8363-2025 FSC-klagomål.docx", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 12296-2026 FSC-klagomål mail.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 8363-2025 FSC-klagomål mail.docx", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 12296-2026 tillsynsbegäran.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 8363-2025 tillsynsbegäran.docx", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 12296-2026 tillsynsbegäran mail.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 8363-2025 tillsynsbegäran mail.docx", "A 8363-2025")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 34076-2026</t>
+          <t>A 19052-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4224,10 +4232,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46252</v>
+        <v>45427</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4240,7 +4248,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.9</v>
+        <v>7.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4249,13 +4257,13 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
         <v>1</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4267,55 +4275,55 @@
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 34076-2026 artfynd.xlsx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19052-2024 artfynd.xlsx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 34076-2026 karta.png", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19052-2024 karta.png", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 34076-2026 georefererad karta.tif", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19052-2024 georefererad karta.tif", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 34076-2026 FSC-klagomål.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19052-2024 FSC-klagomål.docx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 34076-2026 FSC-klagomål mail.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19052-2024 FSC-klagomål mail.docx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 34076-2026 tillsynsbegäran.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19052-2024 tillsynsbegäran.docx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 34076-2026 tillsynsbegäran mail.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19052-2024 tillsynsbegäran mail.docx", "A 19052-2024")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 37339-2022</t>
+          <t>A 35077-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4329,10 +4337,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44806</v>
+        <v>45527</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4345,19 +4353,19 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
         <v>1</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -4372,7 +4380,7 @@
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4385,42 +4393,46 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 37339-2022 artfynd.xlsx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 35077-2024 artfynd.xlsx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 37339-2022 karta.png", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 35077-2024 karta.png", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 37339-2022 georefererad karta.tif", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 35077-2024 georefererad karta.tif", "A 35077-2024")</f>
+        <v/>
+      </c>
+      <c r="Z36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/knärot/A 35077-2024 karta knärot.png", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 37339-2022 FSC-klagomål.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 35077-2024 FSC-klagomål.docx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 37339-2022 FSC-klagomål mail.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 35077-2024 FSC-klagomål mail.docx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 37339-2022 tillsynsbegäran.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 35077-2024 tillsynsbegäran.docx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 37339-2022 tillsynsbegäran mail.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 35077-2024 tillsynsbegäran mail.docx", "A 35077-2024")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8363-2025</t>
+          <t>A 12296-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4434,10 +4446,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45708</v>
+        <v>46087</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4450,17 +4462,17 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
         <v>1</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
@@ -4474,7 +4486,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4490,42 +4502,42 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 8363-2025 artfynd.xlsx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 12296-2026 artfynd.xlsx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 8363-2025 karta.png", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 12296-2026 karta.png", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 8363-2025 georefererad karta.tif", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 12296-2026 georefererad karta.tif", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 8363-2025 FSC-klagomål.docx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 12296-2026 FSC-klagomål.docx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 8363-2025 FSC-klagomål mail.docx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 12296-2026 FSC-klagomål mail.docx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 8363-2025 tillsynsbegäran.docx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 12296-2026 tillsynsbegäran.docx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 8363-2025 tillsynsbegäran mail.docx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 12296-2026 tillsynsbegäran mail.docx", "A 12296-2026")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17122-2024</t>
+          <t>A 29582-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4535,14 +4547,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45412</v>
+        <v>45484</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4554,17 +4566,22 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4579,7 +4596,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4595,42 +4612,42 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 17122-2024 artfynd.xlsx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 29582-2024 artfynd.xlsx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 17122-2024 karta.png", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 29582-2024 karta.png", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 17122-2024 georefererad karta.tif", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 29582-2024 georefererad karta.tif", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 17122-2024 FSC-klagomål.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 29582-2024 FSC-klagomål.docx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 17122-2024 FSC-klagomål mail.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 29582-2024 FSC-klagomål mail.docx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 17122-2024 tillsynsbegäran.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 29582-2024 tillsynsbegäran.docx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 17122-2024 tillsynsbegäran mail.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 29582-2024 tillsynsbegäran mail.docx", "A 29582-2024")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 41878-2024</t>
+          <t>A 30411-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4644,10 +4661,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45561</v>
+        <v>45827</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4659,13 +4676,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>15.9</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -4674,7 +4686,7 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4689,7 +4701,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -4705,46 +4717,42 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 41878-2024 artfynd.xlsx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 30411-2025 artfynd.xlsx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 41878-2024 karta.png", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 30411-2025 karta.png", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 41878-2024 georefererad karta.tif", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 30411-2025 georefererad karta.tif", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 41878-2024 FSC-klagomål.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 30411-2025 FSC-klagomål.docx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 41878-2024 FSC-klagomål mail.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 30411-2025 FSC-klagomål mail.docx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 41878-2024 tillsynsbegäran.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 30411-2025 tillsynsbegäran.docx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 41878-2024 tillsynsbegäran mail.docx", "A 41878-2024")</f>
-        <v/>
-      </c>
-      <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 41878-2024 prioriterade fågelarter.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 30411-2025 tillsynsbegäran mail.docx", "A 30411-2025")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 35077-2024</t>
+          <t>A 62675-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4754,14 +4762,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45527</v>
+        <v>45271</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4774,19 +4782,19 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
         <v>1</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -4798,10 +4806,10 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4814,46 +4822,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 35077-2024 artfynd.xlsx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 62675-2023 artfynd.xlsx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 35077-2024 karta.png", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 62675-2023 karta.png", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 35077-2024 georefererad karta.tif", "A 35077-2024")</f>
-        <v/>
-      </c>
-      <c r="Z40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/knärot/A 35077-2024 karta knärot.png", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 62675-2023 georefererad karta.tif", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 35077-2024 FSC-klagomål.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 62675-2023 FSC-klagomål.docx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 35077-2024 FSC-klagomål mail.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 62675-2023 FSC-klagomål mail.docx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 35077-2024 tillsynsbegäran.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 62675-2023 tillsynsbegäran.docx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 35077-2024 tillsynsbegäran mail.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 62675-2023 tillsynsbegäran mail.docx", "A 62675-2023")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19524-2024</t>
+          <t>A 34076-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4867,10 +4871,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45429</v>
+        <v>46252</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4883,10 +4887,10 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -4916,46 +4920,42 @@
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19524-2024 artfynd.xlsx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 34076-2026 artfynd.xlsx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19524-2024 karta.png", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 34076-2026 karta.png", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19524-2024 georefererad karta.tif", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 34076-2026 georefererad karta.tif", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19524-2024 FSC-klagomål.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 34076-2026 FSC-klagomål.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19524-2024 FSC-klagomål mail.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 34076-2026 FSC-klagomål mail.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19524-2024 tillsynsbegäran.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 34076-2026 tillsynsbegäran.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19524-2024 tillsynsbegäran mail.docx", "A 19524-2024")</f>
-        <v/>
-      </c>
-      <c r="AE41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 19524-2024 prioriterade fågelarter.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 34076-2026 tillsynsbegäran mail.docx", "A 34076-2026")</f>
         <v/>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
         <v>44484</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>44607</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>44781</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>44509</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44575</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>44795</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>44782</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59863-2021</t>
+          <t>A 49116-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5515,14 +5515,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44494</v>
+        <v>44860</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5578,7 +5578,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 49116-2022</t>
+          <t>A 59863-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5588,14 +5588,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44860</v>
+        <v>44494</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
         <v>44844</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>44838</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44690</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>44734</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44694</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44743</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>44467</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>44509</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>44498</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>44798</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44762</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44620</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>44627</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>44735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 54444-2022</t>
+          <t>A 22133-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44882</v>
+        <v>45785</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6756,7 +6756,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 37045-2022</t>
+          <t>A 8361-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6770,10 +6770,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44806</v>
+        <v>45708</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6829,7 +6829,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 59746-2021</t>
+          <t>A 54444-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6843,10 +6843,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44494</v>
+        <v>44882</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6902,7 +6902,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 52842-2021</t>
+          <t>A 37045-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44467</v>
+        <v>44806</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6975,7 +6975,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 25694-2022</t>
+          <t>A 59746-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44732</v>
+        <v>44494</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7048,7 +7048,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 2089-2022</t>
+          <t>A 31964-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44577</v>
+        <v>45107</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7121,7 +7121,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29699-2022</t>
+          <t>A 35253-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44755</v>
+        <v>44797</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7194,7 +7194,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 30334-2022</t>
+          <t>A 29699-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7208,10 +7208,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44760</v>
+        <v>44755</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7267,7 +7267,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 73306-2021</t>
+          <t>A 30334-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44547</v>
+        <v>44760</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7340,7 +7340,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 5841-2022</t>
+          <t>A 29426-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7354,10 +7354,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44596</v>
+        <v>44753</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7369,8 +7369,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>14.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7413,7 +7418,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 5126-2023</t>
+          <t>A 73306-2021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7427,10 +7432,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44958</v>
+        <v>44547</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7443,7 +7448,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>14.3</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7486,7 +7491,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 73033-2021</t>
+          <t>A 22537-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7496,14 +7501,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44550</v>
+        <v>45787</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7516,7 +7521,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7559,7 +7564,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13382-2024</t>
+          <t>A 30339-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7573,10 +7578,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45387</v>
+        <v>44760</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7589,7 +7594,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7632,7 +7637,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 5025-2023</t>
+          <t>A 52842-2021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7646,10 +7651,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44958</v>
+        <v>44467</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7662,7 +7667,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7705,7 +7710,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 73901-2021</t>
+          <t>A 25694-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7719,10 +7724,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44552</v>
+        <v>44732</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7735,7 +7740,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7778,7 +7783,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 28228-2024</t>
+          <t>A 2089-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7792,10 +7797,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45477</v>
+        <v>44577</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7808,7 +7813,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7851,7 +7856,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 57236-2023</t>
+          <t>A 6751-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7865,10 +7870,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45245</v>
+        <v>45700</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7881,7 +7886,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7924,7 +7929,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 57237-2023</t>
+          <t>A 975-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7938,10 +7943,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45245</v>
+        <v>45665</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7954,7 +7959,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>18.2</v>
+        <v>2.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7997,7 +8002,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 5810-2023</t>
+          <t>A 63919-2021</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8011,10 +8016,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44963</v>
+        <v>44509</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8027,7 +8032,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8070,7 +8075,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 47152-2023</t>
+          <t>A 9144-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8084,10 +8089,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45201</v>
+        <v>45358</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8100,7 +8105,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8143,7 +8148,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 26840-2023</t>
+          <t>A 12311-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8157,10 +8162,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45093</v>
+        <v>45378</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8173,7 +8178,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8216,7 +8221,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 18341-2025</t>
+          <t>A 37486-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8230,10 +8235,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45762</v>
+        <v>44809</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8246,7 +8251,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.1</v>
+        <v>8.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8289,7 +8294,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 58514-2022</t>
+          <t>A 20238-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8303,10 +8308,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44902</v>
+        <v>45434</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8319,7 +8324,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8362,7 +8367,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 53209-2021</t>
+          <t>A 21528-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8376,10 +8381,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44468</v>
+        <v>45441</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8392,7 +8397,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>11.6</v>
+        <v>1.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8435,7 +8440,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 17437-2025</t>
+          <t>A 33948-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8449,10 +8454,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45757</v>
+        <v>45124</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8465,7 +8470,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8508,7 +8513,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17443-2025</t>
+          <t>A 19053-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8522,10 +8527,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45757</v>
+        <v>45427</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8538,7 +8543,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8581,7 +8586,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 37119-2024</t>
+          <t>A 42557-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8595,10 +8600,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45539</v>
+        <v>44831</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8611,7 +8616,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>6.7</v>
+        <v>13.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8654,7 +8659,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 17910-2024</t>
+          <t>A 23189-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8668,10 +8673,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45419</v>
+        <v>45450</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8683,8 +8688,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>6.8</v>
+        <v>1.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8727,7 +8737,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 2253-2024</t>
+          <t>A 27222-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8741,10 +8751,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45310</v>
+        <v>45096</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8757,7 +8767,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8800,7 +8810,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 6721-2025</t>
+          <t>A 17972-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8814,10 +8824,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45700</v>
+        <v>45761</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8829,13 +8839,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8878,7 +8883,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 49300-2022</t>
+          <t>A 62896-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8892,10 +8897,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44861</v>
+        <v>45272</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8908,7 +8913,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>13.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8951,7 +8956,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 5957-2024</t>
+          <t>A 6938-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8961,14 +8966,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45336</v>
+        <v>45343</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8981,7 +8986,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9024,7 +9029,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 56219-2023</t>
+          <t>A 13382-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9038,10 +9043,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45240</v>
+        <v>45387</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9097,7 +9102,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 680-2024</t>
+          <t>A 13289-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9111,10 +9116,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45300</v>
+        <v>45735</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9127,7 +9132,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9170,7 +9175,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 30339-2022</t>
+          <t>A 26829-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9184,10 +9189,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44760</v>
+        <v>45093</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9200,7 +9205,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9243,7 +9248,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 975-2025</t>
+          <t>A 13895-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9257,10 +9262,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45665</v>
+        <v>45391</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9272,8 +9277,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9316,7 +9326,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 62557-2022</t>
+          <t>A 26815-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9330,10 +9340,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44924</v>
+        <v>45093</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9346,7 +9356,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9389,7 +9399,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 21402-2024</t>
+          <t>A 25840-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9403,10 +9413,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45441</v>
+        <v>45467</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9419,7 +9429,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9462,7 +9472,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 29736-2023</t>
+          <t>A 17565-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9476,10 +9486,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45107</v>
+        <v>45757</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9492,7 +9502,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9535,7 +9545,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 20238-2024</t>
+          <t>A 25443-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9549,10 +9559,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45434</v>
+        <v>45089</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9565,7 +9575,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9608,7 +9618,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 53138-2023</t>
+          <t>A 28228-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9622,10 +9632,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45229</v>
+        <v>45477</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9638,7 +9648,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9681,7 +9691,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 19566-2023</t>
+          <t>A 14306-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9695,10 +9705,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45049</v>
+        <v>45011</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9711,7 +9721,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9754,7 +9764,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 29762-2023</t>
+          <t>A 5025-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9768,10 +9778,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45107</v>
+        <v>44958</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9784,7 +9794,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9827,7 +9837,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 8364-2025</t>
+          <t>A 31974-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9841,10 +9851,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45708</v>
+        <v>45107</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9857,7 +9867,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9900,7 +9910,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 62896-2023</t>
+          <t>A 5957-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9914,10 +9924,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45272</v>
+        <v>45336</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9930,7 +9940,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>13.8</v>
+        <v>2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9973,7 +9983,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 69847-2021</t>
+          <t>A 25014-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9987,10 +9997,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44532</v>
+        <v>45461</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10003,7 +10013,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.3</v>
+        <v>12.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10046,7 +10056,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 22347-2023</t>
+          <t>A 17081-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10060,10 +10070,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45070</v>
+        <v>45412</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10076,7 +10086,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10119,7 +10129,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 58705-2024</t>
+          <t>A 62682-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10133,10 +10143,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45635</v>
+        <v>45271</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10148,13 +10158,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10197,7 +10202,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 37515-2025</t>
+          <t>A 2253-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10211,10 +10216,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45877</v>
+        <v>45310</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10227,7 +10232,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10270,7 +10275,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 37495-2025</t>
+          <t>A 4870-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10284,10 +10289,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45877</v>
+        <v>45329</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10300,7 +10305,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.9</v>
+        <v>8.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10343,7 +10348,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 37517-2025</t>
+          <t>A 53209-2021</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10357,10 +10362,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45877</v>
+        <v>44468</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10373,7 +10378,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.9</v>
+        <v>11.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10416,7 +10421,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 59617-2025</t>
+          <t>A 69847-2021</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10430,10 +10435,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45992</v>
+        <v>44532</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10489,7 +10494,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 29256-2025</t>
+          <t>A 58514-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10503,10 +10508,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45824</v>
+        <v>44902</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10519,7 +10524,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10562,7 +10567,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 614-2026</t>
+          <t>A 73310-2021</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10576,10 +10581,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46024</v>
+        <v>44547</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10592,7 +10597,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10635,7 +10640,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 42143-2025</t>
+          <t>A 71706-2021</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10649,10 +10654,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45904</v>
+        <v>44543</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10665,7 +10670,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10708,7 +10713,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 20784-2025</t>
+          <t>A 44497-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10722,10 +10727,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45776</v>
+        <v>45916</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10738,7 +10743,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>9.5</v>
+        <v>3.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10781,7 +10786,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 33081-2022</t>
+          <t>A 47152-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10795,10 +10800,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44785</v>
+        <v>45201</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10811,7 +10816,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10854,7 +10859,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 25840-2024</t>
+          <t>A 45467-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10868,10 +10873,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45467</v>
+        <v>44845</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10884,7 +10889,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10927,7 +10932,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 40524-2025</t>
+          <t>A 58705-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10941,10 +10946,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45896</v>
+        <v>45635</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10956,8 +10961,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11000,7 +11010,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 21248-2022</t>
+          <t>A 36644-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11014,10 +11024,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44705</v>
+        <v>45153</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11030,7 +11040,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>12.4</v>
+        <v>0.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11073,7 +11083,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 40522-2025</t>
+          <t>A 7922-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11087,10 +11097,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45896</v>
+        <v>44608</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11103,7 +11113,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11146,7 +11156,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 37676-2023</t>
+          <t>A 53138-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11156,14 +11166,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45159</v>
+        <v>45229</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11176,7 +11186,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11219,7 +11229,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 44497-2025</t>
+          <t>A 27218-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11233,10 +11243,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45916</v>
+        <v>45096</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11249,7 +11259,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11292,7 +11302,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 6751-2025</t>
+          <t>A 16772-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11306,10 +11316,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45700</v>
+        <v>45411</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11322,7 +11332,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11365,7 +11375,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 50640-2023</t>
+          <t>A 62905-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11379,10 +11389,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45217</v>
+        <v>45272</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11395,7 +11405,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.2</v>
+        <v>13.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11438,7 +11448,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 34580-2022</t>
+          <t>A 36420-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11452,10 +11462,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44795</v>
+        <v>45152</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11468,7 +11478,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11511,7 +11521,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 12000-2022</t>
+          <t>A 5126-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11525,10 +11535,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44635</v>
+        <v>44958</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11541,7 +11551,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.7</v>
+        <v>14.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11584,7 +11594,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 42557-2022</t>
+          <t>A 47507-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11598,10 +11608,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44831</v>
+        <v>45930</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11614,7 +11624,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>13.7</v>
+        <v>2.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11657,7 +11667,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 35253-2022</t>
+          <t>A 66056-2021</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11671,10 +11681,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44797</v>
+        <v>44517</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11730,7 +11740,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 47507-2025</t>
+          <t>A 10892-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11744,10 +11754,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45930</v>
+        <v>44627</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11760,7 +11770,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11803,7 +11813,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 5214-2025</t>
+          <t>A 3065-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11817,10 +11827,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45691</v>
+        <v>45316</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11833,7 +11843,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11876,7 +11886,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 31561-2023</t>
+          <t>A 12082-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11890,10 +11900,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45117</v>
+        <v>45377</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11949,7 +11959,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 13820-2024</t>
+          <t>A 12084-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11963,10 +11973,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45390</v>
+        <v>45377</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11979,7 +11989,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>7.2</v>
+        <v>1.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12022,7 +12032,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 17565-2025</t>
+          <t>A 49507-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12036,10 +12046,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45757</v>
+        <v>45939</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12052,7 +12062,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12112,7 +12122,7 @@
         <v>45505</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12168,7 +12178,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 49507-2025</t>
+          <t>A 20954-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12182,10 +12192,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45939</v>
+        <v>45061</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12198,7 +12208,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>5.7</v>
+        <v>1.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12241,7 +12251,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 22406-2026</t>
+          <t>A 17443-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12255,10 +12265,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46154</v>
+        <v>45757</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12271,7 +12281,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12314,7 +12324,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 51509-2025</t>
+          <t>A 62557-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12324,14 +12334,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45950</v>
+        <v>44924</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12344,7 +12354,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12387,7 +12397,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 52699-2025</t>
+          <t>A 7991-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12397,14 +12407,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45956</v>
+        <v>45350</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12417,7 +12427,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12460,7 +12470,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 3065-2024</t>
+          <t>A 51509-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12470,14 +12480,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45316</v>
+        <v>45950</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12490,7 +12500,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12533,7 +12543,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 52700-2025</t>
+          <t>A 17399-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12547,10 +12557,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45956</v>
+        <v>45757</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12563,7 +12573,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12606,7 +12616,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 17081-2024</t>
+          <t>A 5810-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12620,10 +12630,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45412</v>
+        <v>44963</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12636,7 +12646,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12679,7 +12689,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 71903-2021</t>
+          <t>A 20369-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12693,10 +12703,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44543</v>
+        <v>45435</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12709,7 +12719,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>6.3</v>
+        <v>1.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12752,7 +12762,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 3779-2025</t>
+          <t>A 11601-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12766,10 +12776,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45681</v>
+        <v>45727</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12781,13 +12791,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>BillerudKorsnäs AB</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>7.6</v>
+        <v>1.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12830,7 +12835,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 7993-2024</t>
+          <t>A 4976-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12844,10 +12849,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45350</v>
+        <v>45329</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12860,7 +12865,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12903,7 +12908,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 39334-2025</t>
+          <t>A 52700-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12917,10 +12922,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45889</v>
+        <v>45956</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12933,7 +12938,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12976,7 +12981,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 45467-2022</t>
+          <t>A 12175-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12990,10 +12995,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44845</v>
+        <v>45377</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13006,7 +13011,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13049,7 +13054,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 5011-2024</t>
+          <t>A 52699-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13063,10 +13068,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45329</v>
+        <v>45956</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13079,7 +13084,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>22</v>
+        <v>3.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13122,7 +13127,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 53137-2023</t>
+          <t>A 30527-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13136,10 +13141,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45229</v>
+        <v>44762</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13152,7 +13157,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13195,7 +13200,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 23733-2026</t>
+          <t>A 5236-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13209,10 +13214,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46164</v>
+        <v>44956</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13224,13 +13229,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13273,7 +13273,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 23945-2026</t>
+          <t>A 62947-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13287,10 +13287,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46167</v>
+        <v>45272</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13302,13 +13302,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13351,7 +13346,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 23757-2026</t>
+          <t>A 22347-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13365,10 +13360,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46164</v>
+        <v>45070</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13381,7 +13376,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13424,7 +13419,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 23702-2026</t>
+          <t>A 7993-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13438,10 +13433,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46164</v>
+        <v>45350</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13453,13 +13448,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13502,7 +13492,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 9144-2024</t>
+          <t>A 56220-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13516,10 +13506,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45358</v>
+        <v>45240</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13532,7 +13522,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13575,7 +13565,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 62682-2023</t>
+          <t>A 33081-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13589,10 +13579,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45271</v>
+        <v>44785</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13605,7 +13595,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13648,7 +13638,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 58751-2025</t>
+          <t>A 56219-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13662,10 +13652,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45986</v>
+        <v>45240</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13678,7 +13668,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13721,7 +13711,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 58747-2025</t>
+          <t>A 6721-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13735,10 +13725,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45986</v>
+        <v>45700</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13750,8 +13740,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13794,7 +13789,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 4982-2024</t>
+          <t>A 29260-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13808,10 +13803,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45329</v>
+        <v>45824</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13824,7 +13819,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13867,7 +13862,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 62947-2023</t>
+          <t>A 17437-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13881,10 +13876,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45272</v>
+        <v>45757</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13897,7 +13892,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13940,7 +13935,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 31930-2024</t>
+          <t>A 5841-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13950,14 +13945,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45510</v>
+        <v>44596</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13970,7 +13965,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14013,7 +14008,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 71706-2021</t>
+          <t>A 29762-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14027,10 +14022,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44543</v>
+        <v>45107</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14086,7 +14081,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 40935-2022</t>
+          <t>A 12000-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14096,14 +14091,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44823</v>
+        <v>44635</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14115,13 +14110,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14164,7 +14154,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 60656-2025</t>
+          <t>A 40935-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14174,14 +14164,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45996</v>
+        <v>44823</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14193,8 +14183,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14237,7 +14232,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 24754-2026</t>
+          <t>A 36646-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14251,10 +14246,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46171</v>
+        <v>45153</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14267,7 +14262,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14310,7 +14305,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 6938-2024</t>
+          <t>A 58747-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14320,14 +14315,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45343</v>
+        <v>45986</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14340,7 +14335,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14383,7 +14378,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 14306-2023</t>
+          <t>A 58751-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14397,10 +14392,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45011</v>
+        <v>45986</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14413,7 +14408,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14456,7 +14451,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 59391-2025</t>
+          <t>A 29736-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14466,14 +14461,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45989</v>
+        <v>45107</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14486,7 +14481,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14529,7 +14524,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 17972-2025</t>
+          <t>A 29724-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14539,14 +14534,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45761</v>
+        <v>45107</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14602,7 +14597,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 27222-2023</t>
+          <t>A 8362-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14616,10 +14611,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45096</v>
+        <v>45708</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14632,7 +14627,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14675,7 +14670,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 36644-2023</t>
+          <t>A 972-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14689,10 +14684,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45153</v>
+        <v>45665</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14705,7 +14700,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14748,7 +14743,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 26015-2026</t>
+          <t>A 49300-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14758,14 +14753,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46181</v>
+        <v>44861</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14777,13 +14772,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14826,7 +14816,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 8788-2024</t>
+          <t>A 50640-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14840,10 +14830,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45356</v>
+        <v>45217</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14856,7 +14846,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14899,7 +14889,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 62554-2022</t>
+          <t>A 16635-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14913,10 +14903,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44924</v>
+        <v>45408</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14929,7 +14919,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14972,7 +14962,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 21528-2024</t>
+          <t>A 30563-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14986,10 +14976,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45441</v>
+        <v>45831</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15002,7 +14992,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15045,7 +15035,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 20954-2023</t>
+          <t>A 17910-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15059,10 +15049,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45061</v>
+        <v>45419</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15075,7 +15065,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.8</v>
+        <v>6.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15118,7 +15108,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 3054-2026</t>
+          <t>A 37676-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15128,14 +15118,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46039</v>
+        <v>45159</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15148,7 +15138,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15191,7 +15181,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 10892-2022</t>
+          <t>A 60656-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15205,10 +15195,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44627</v>
+        <v>45996</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15221,7 +15211,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15264,7 +15254,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 29426-2022</t>
+          <t>A 53137-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15278,10 +15268,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44753</v>
+        <v>45229</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15293,13 +15283,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>14.4</v>
+        <v>1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15342,7 +15327,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 44048-2023</t>
+          <t>A 8788-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15356,10 +15341,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45188</v>
+        <v>45356</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15372,7 +15357,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15415,7 +15400,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 62905-2023</t>
+          <t>A 680-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15429,10 +15414,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45272</v>
+        <v>45300</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15445,7 +15430,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>13.8</v>
+        <v>0.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15488,7 +15473,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 8732-2026</t>
+          <t>A 46299-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15502,10 +15487,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46066</v>
+        <v>44847</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15518,7 +15503,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>6.1</v>
+        <v>2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15561,7 +15546,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 28513-2026</t>
+          <t>A 32327-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15575,10 +15560,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46197</v>
+        <v>45836</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15591,7 +15576,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15634,7 +15619,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 11103-2022</t>
+          <t>A 3054-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15648,10 +15633,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44628</v>
+        <v>46039</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15664,7 +15649,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>5.7</v>
+        <v>2.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15707,7 +15692,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 37486-2022</t>
+          <t>A 62554-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15721,10 +15706,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44809</v>
+        <v>44924</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15737,7 +15722,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15780,7 +15765,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 29205-2026</t>
+          <t>A 59391-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15790,14 +15775,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46202</v>
+        <v>45989</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15810,7 +15795,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15853,7 +15838,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 46299-2022</t>
+          <t>A 57236-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15867,10 +15852,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44847</v>
+        <v>45245</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15883,7 +15868,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15926,7 +15911,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 29222-2026</t>
+          <t>A 57237-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15940,10 +15925,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46202</v>
+        <v>45245</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15956,7 +15941,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>3.3</v>
+        <v>18.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15999,7 +15984,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 5236-2023</t>
+          <t>A 29577-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16013,10 +15998,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44956</v>
+        <v>45484</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16028,8 +16013,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>1</v>
+        <v>10.1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16072,7 +16062,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 12283-2026</t>
+          <t>A 27443-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16086,10 +16076,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46087</v>
+        <v>45474</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16102,7 +16092,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16145,7 +16135,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 56220-2023</t>
+          <t>A 32959-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16159,10 +16149,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45240</v>
+        <v>44784</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16175,7 +16165,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16218,7 +16208,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 972-2025</t>
+          <t>A 13320-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16232,10 +16222,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45665</v>
+        <v>45386</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16248,7 +16238,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16291,7 +16281,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 29191-2026</t>
+          <t>A 38517-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16305,10 +16295,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46202</v>
+        <v>45546</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16321,7 +16311,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16364,7 +16354,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 32302-2024</t>
+          <t>A 8732-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16378,10 +16368,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45512</v>
+        <v>46066</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16393,13 +16383,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16442,7 +16427,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 14688-2026</t>
+          <t>A 37119-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16452,14 +16437,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46101</v>
+        <v>45539</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16472,7 +16457,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.2</v>
+        <v>6.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16515,7 +16500,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 13895-2024</t>
+          <t>A 32942-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16529,10 +16514,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45391</v>
+        <v>46244</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16544,13 +16529,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16593,7 +16573,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 15549-2026</t>
+          <t>A 19802-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16607,10 +16587,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46106</v>
+        <v>45432</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16622,8 +16602,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16666,7 +16651,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 29724-2023</t>
+          <t>A 34580-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16676,14 +16661,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45107</v>
+        <v>44795</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16696,7 +16681,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16739,7 +16724,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 15543-2026</t>
+          <t>A 12283-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16753,10 +16738,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46106</v>
+        <v>46087</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16769,7 +16754,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16812,7 +16797,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 31974-2023</t>
+          <t>A 19566-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16826,10 +16811,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45107</v>
+        <v>45049</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16842,7 +16827,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16885,7 +16870,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 19802-2024</t>
+          <t>A 8359-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16899,10 +16884,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45432</v>
+        <v>45708</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16914,13 +16899,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16963,7 +16943,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 16635-2024</t>
+          <t>A 7272-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16977,10 +16957,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45408</v>
+        <v>44606</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16993,7 +16973,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17036,7 +17016,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 7922-2022</t>
+          <t>A 22822-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17050,10 +17030,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44608</v>
+        <v>45448</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17066,7 +17046,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17109,7 +17089,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 1556-2025</t>
+          <t>A 59542-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17123,10 +17103,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45670</v>
+        <v>44907</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17139,7 +17119,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17182,7 +17162,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 12311-2024</t>
+          <t>A 21402-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17196,10 +17176,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45378</v>
+        <v>45441</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17212,7 +17192,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17255,7 +17235,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 33948-2023</t>
+          <t>A 14688-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17265,14 +17245,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45124</v>
+        <v>46101</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17285,7 +17265,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17328,7 +17308,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 13320-2024</t>
+          <t>A 35425-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17342,10 +17322,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45386</v>
+        <v>45855</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17358,7 +17338,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17401,7 +17381,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 55227-2023</t>
+          <t>A 15543-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17415,10 +17395,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45231</v>
+        <v>46106</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17431,7 +17411,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17474,7 +17454,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 25014-2024</t>
+          <t>A 71781-2021</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17488,10 +17468,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45461</v>
+        <v>44539</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17503,8 +17483,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I212" t="n">
-        <v>12.8</v>
+        <v>7</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17547,7 +17532,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 31964-2023</t>
+          <t>A 15549-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17561,10 +17546,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45107</v>
+        <v>46106</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17577,7 +17562,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17620,7 +17605,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 12082-2024</t>
+          <t>A 31930-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17630,14 +17615,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45377</v>
+        <v>45510</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17650,7 +17635,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17693,7 +17678,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 12084-2024</t>
+          <t>A 73901-2021</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17707,10 +17692,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45377</v>
+        <v>44552</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17723,7 +17708,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17766,7 +17751,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 4976-2024</t>
+          <t>A 26840-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17780,10 +17765,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45329</v>
+        <v>45093</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17796,7 +17781,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17839,7 +17824,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 64304-2023</t>
+          <t>A 13820-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17853,10 +17838,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45280</v>
+        <v>45390</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17869,7 +17854,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.2</v>
+        <v>7.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17912,7 +17897,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 48553-2023</t>
+          <t>A 5011-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17926,10 +17911,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45208</v>
+        <v>45329</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17942,7 +17927,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.7</v>
+        <v>22</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17985,7 +17970,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 26815-2023</t>
+          <t>A 18341-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17999,10 +17984,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45093</v>
+        <v>45762</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18015,7 +18000,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18058,7 +18043,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 34538-2026</t>
+          <t>A 52848-2021</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18072,10 +18057,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46255</v>
+        <v>44467</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18088,7 +18073,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18131,7 +18116,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 16772-2024</t>
+          <t>A 19753-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18145,10 +18130,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45411</v>
+        <v>45432</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18161,7 +18146,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18204,7 +18189,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 25443-2023</t>
+          <t>A 29256-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18218,10 +18203,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45089</v>
+        <v>45824</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18234,7 +18219,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18277,7 +18262,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 31034-2026</t>
+          <t>A 37517-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18291,10 +18276,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46214</v>
+        <v>45877</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18350,7 +18335,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 66056-2021</t>
+          <t>A 21248-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18364,10 +18349,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44517</v>
+        <v>44705</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18380,7 +18365,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.7</v>
+        <v>12.4</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18423,7 +18408,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 23189-2024</t>
+          <t>A 4982-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18437,10 +18422,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45450</v>
+        <v>45329</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18452,13 +18437,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18501,7 +18481,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 7991-2024</t>
+          <t>A 37515-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18511,14 +18491,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45350</v>
+        <v>45877</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18531,7 +18511,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18574,7 +18554,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 59542-2022</t>
+          <t>A 37495-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18588,10 +18568,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44907</v>
+        <v>45877</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18604,7 +18584,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18647,7 +18627,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 52848-2021</t>
+          <t>A 55227-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18661,10 +18641,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44467</v>
+        <v>45231</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18677,7 +18657,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18720,7 +18700,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 8361-2025</t>
+          <t>A 9837-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18734,10 +18714,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45708</v>
+        <v>44984</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18750,7 +18730,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18793,7 +18773,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 31559-2026</t>
+          <t>A 42143-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18807,10 +18787,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46224</v>
+        <v>45904</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18823,7 +18803,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18866,7 +18846,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 73310-2021</t>
+          <t>A 1556-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18880,10 +18860,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44547</v>
+        <v>45670</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18896,7 +18876,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18939,7 +18919,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 71781-2021</t>
+          <t>A 40522-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18953,10 +18933,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44539</v>
+        <v>45896</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18968,13 +18948,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I232" t="n">
-        <v>7</v>
+        <v>0.9</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -19017,7 +18992,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 8362-2025</t>
+          <t>A 5214-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -19031,10 +19006,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45708</v>
+        <v>45691</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19047,7 +19022,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>7.7</v>
+        <v>2.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -19090,7 +19065,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 37221-2026</t>
+          <t>A 73033-2021</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -19104,10 +19079,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46274</v>
+        <v>44550</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19120,7 +19095,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -19163,7 +19138,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 37243-2026</t>
+          <t>A 20784-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -19177,10 +19152,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46274</v>
+        <v>45776</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19193,7 +19168,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>13.9</v>
+        <v>9.5</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -19236,7 +19211,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 30527-2022</t>
+          <t>A 614-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19250,10 +19225,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>44762</v>
+        <v>46024</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19266,7 +19241,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19309,7 +19284,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 17573-2025</t>
+          <t>A 64304-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19323,10 +19298,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45757</v>
+        <v>45280</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19339,7 +19314,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19382,7 +19357,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 9837-2023</t>
+          <t>A 40524-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19396,10 +19371,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>44984</v>
+        <v>45896</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19412,7 +19387,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19455,7 +19430,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 19753-2024</t>
+          <t>A 8364-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19469,10 +19444,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45432</v>
+        <v>45708</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19485,7 +19460,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19528,7 +19503,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 27443-2024</t>
+          <t>A 59617-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19542,10 +19517,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45474</v>
+        <v>45992</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19558,7 +19533,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19601,7 +19576,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 32959-2022</t>
+          <t>A 31561-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19615,10 +19590,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44784</v>
+        <v>45117</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19631,7 +19606,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19674,7 +19649,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 30914-2023</t>
+          <t>A 48553-2023</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19688,10 +19663,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45113</v>
+        <v>45208</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19704,7 +19679,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19747,7 +19722,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 20369-2024</t>
+          <t>A 17573-2025</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19761,10 +19736,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45435</v>
+        <v>45757</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19777,7 +19752,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19820,7 +19795,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 7272-2022</t>
+          <t>A 44048-2023</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19834,10 +19809,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>44606</v>
+        <v>45188</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19850,7 +19825,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19893,7 +19868,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 26829-2023</t>
+          <t>A 30914-2023</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19907,10 +19882,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45093</v>
+        <v>45113</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19923,7 +19898,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19966,7 +19941,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 38517-2024</t>
+          <t>A 8370-2023</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19980,10 +19955,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45546</v>
+        <v>44977</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19996,7 +19971,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -20039,7 +20014,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 32942-2026</t>
+          <t>A 12217-2025</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -20053,10 +20028,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>46244</v>
+        <v>45729</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20069,7 +20044,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -20112,7 +20087,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 63919-2021</t>
+          <t>A 22406-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -20126,10 +20101,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>44509</v>
+        <v>46154</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20185,7 +20160,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 4870-2024</t>
+          <t>A 39334-2025</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -20199,10 +20174,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45329</v>
+        <v>45889</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20215,7 +20190,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -20258,7 +20233,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 36646-2023</t>
+          <t>A 3779-2025</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -20272,10 +20247,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45153</v>
+        <v>45681</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20287,8 +20262,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>BillerudKorsnäs AB</t>
+        </is>
+      </c>
       <c r="I250" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -20331,7 +20311,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 22822-2024</t>
+          <t>A 71903-2021</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20345,10 +20325,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45448</v>
+        <v>44543</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20361,7 +20341,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>1.3</v>
+        <v>6.3</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20404,7 +20384,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 19053-2024</t>
+          <t>A 23702-2026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20418,10 +20398,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45427</v>
+        <v>46164</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20433,8 +20413,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I252" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20477,7 +20462,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 11601-2025</t>
+          <t>A 23733-2026</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20491,10 +20476,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45727</v>
+        <v>46164</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20506,8 +20491,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I253" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20550,7 +20540,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 12175-2024</t>
+          <t>A 23757-2026</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20564,10 +20554,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45377</v>
+        <v>46164</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20580,7 +20570,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20623,7 +20613,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 29577-2024</t>
+          <t>A 23945-2026</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20637,10 +20627,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45484</v>
+        <v>46167</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20654,11 +20644,11 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I255" t="n">
-        <v>10.1</v>
+        <v>1.3</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20701,7 +20691,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 8370-2023</t>
+          <t>A 24754-2026</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20715,10 +20705,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>44977</v>
+        <v>46171</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20731,7 +20721,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20774,7 +20764,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 12217-2025</t>
+          <t>A 26015-2026</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20784,14 +20774,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45729</v>
+        <v>46181</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20803,8 +20793,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I257" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20847,7 +20842,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 22133-2025</t>
+          <t>A 11103-2022</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20861,10 +20856,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45785</v>
+        <v>44628</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20877,7 +20872,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20920,7 +20915,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 22537-2025</t>
+          <t>A 28513-2026</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20930,14 +20925,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45787</v>
+        <v>46197</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20950,7 +20945,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20993,7 +20988,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 13289-2025</t>
+          <t>A 32302-2024</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -21007,10 +21002,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45735</v>
+        <v>45512</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21022,8 +21017,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I260" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -21066,7 +21066,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 27218-2023</t>
+          <t>A 29205-2026</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45096</v>
+        <v>46202</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -21139,7 +21139,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 36420-2023</t>
+          <t>A 29222-2026</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -21153,10 +21153,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45152</v>
+        <v>46202</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -21212,7 +21212,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 17399-2025</t>
+          <t>A 29191-2026</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -21226,10 +21226,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45757</v>
+        <v>46202</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 29260-2025</t>
+          <t>A 34538-2026</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -21299,10 +21299,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45824</v>
+        <v>46255</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -21358,7 +21358,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 30563-2025</t>
+          <t>A 31034-2026</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21372,10 +21372,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45831</v>
+        <v>46214</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -21431,7 +21431,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 32327-2025</t>
+          <t>A 31559-2026</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21445,10 +21445,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45836</v>
+        <v>46224</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -21504,7 +21504,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 8359-2025</t>
+          <t>A 37221-2026</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21518,10 +21518,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45708</v>
+        <v>46274</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21577,7 +21577,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 35425-2025</t>
+          <t>A 37243-2026</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21591,10 +21591,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45855</v>
+        <v>46274</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>0.5</v>
+        <v>13.9</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21667,7 +21667,7 @@
         <v>45099</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>45272</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45846</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>45973</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>46035</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>

--- a/Översikt GRUMS.xlsx
+++ b/Översikt GRUMS.xlsx
@@ -601,7 +601,7 @@
         <v>44978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45343</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44788</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44498</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44819</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45615</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>46252</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>44981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45099</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>45078</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45898</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 66053-2021</t>
+          <t>A 5280-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44517</v>
+        <v>44593</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1972,14 +1972,19 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>37.1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1988,7 +1993,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1997,174 +2002,169 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 5280-2022 artfynd.xlsx", "A 5280-2022")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 5280-2022 karta.png", "A 5280-2022")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 5280-2022 georefererad karta.tif", "A 5280-2022")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 5280-2022 FSC-klagomål.docx", "A 5280-2022")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 5280-2022 FSC-klagomål mail.docx", "A 5280-2022")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 5280-2022 tillsynsbegäran.docx", "A 5280-2022")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 5280-2022 tillsynsbegäran mail.docx", "A 5280-2022")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 5280-2022 prioriterade fågelarter.docx", "A 5280-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 66053-2021</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44517</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
         <v>6</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>6</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Bronshjon</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 66053-2021 artfynd.xlsx", "A 66053-2021")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 66053-2021 karta.png", "A 66053-2021")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 66053-2021 georefererad karta.tif", "A 66053-2021")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 66053-2021 FSC-klagomål.docx", "A 66053-2021")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 66053-2021 FSC-klagomål mail.docx", "A 66053-2021")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 66053-2021 tillsynsbegäran.docx", "A 66053-2021")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 66053-2021 tillsynsbegäran mail.docx", "A 66053-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 5280-2022</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44593</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 5280-2022 artfynd.xlsx", "A 5280-2022")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 5280-2022 karta.png", "A 5280-2022")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 5280-2022 georefererad karta.tif", "A 5280-2022")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 5280-2022 FSC-klagomål.docx", "A 5280-2022")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 5280-2022 FSC-klagomål mail.docx", "A 5280-2022")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 5280-2022 tillsynsbegäran.docx", "A 5280-2022")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 5280-2022 tillsynsbegäran mail.docx", "A 5280-2022")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 5280-2022 prioriterade fågelarter.docx", "A 5280-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 54042-2021</t>
+          <t>A 57233-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44470</v>
+        <v>45245</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2194,17 +2194,17 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.8</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2227,370 +2227,370 @@
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>6</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin
+Skogsklocka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 57233-2023 artfynd.xlsx", "A 57233-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 57233-2023 karta.png", "A 57233-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 57233-2023 georefererad karta.tif", "A 57233-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 57233-2023 FSC-klagomål.docx", "A 57233-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 57233-2023 FSC-klagomål mail.docx", "A 57233-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 57233-2023 tillsynsbegäran.docx", "A 57233-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 57233-2023 tillsynsbegäran mail.docx", "A 57233-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 54042-2021</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44470</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 54042-2021 artfynd.xlsx", "A 54042-2021")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 54042-2021 karta.png", "A 54042-2021")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 54042-2021 georefererad karta.tif", "A 54042-2021")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 54042-2021 FSC-klagomål.docx", "A 54042-2021")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 54042-2021 FSC-klagomål mail.docx", "A 54042-2021")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 54042-2021 tillsynsbegäran.docx", "A 54042-2021")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 54042-2021 tillsynsbegäran mail.docx", "A 54042-2021")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 54042-2021 prioriterade fågelarter.docx", "A 54042-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 7931-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45706</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 7931-2025 artfynd.xlsx", "A 7931-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 7931-2025 karta.png", "A 7931-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 7931-2025 georefererad karta.tif", "A 7931-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 7931-2025 FSC-klagomål.docx", "A 7931-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 7931-2025 FSC-klagomål mail.docx", "A 7931-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 7931-2025 tillsynsbegäran.docx", "A 7931-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 7931-2025 tillsynsbegäran mail.docx", "A 7931-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 56386-2022</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>44890</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>4.2</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M19" t="n">
         <v>1</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R19" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Vågfibbla
 Rönnfibbla</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 56386-2022 artfynd.xlsx", "A 56386-2022")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 56386-2022 karta.png", "A 56386-2022")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 56386-2022 georefererad karta.tif", "A 56386-2022")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 56386-2022 FSC-klagomål.docx", "A 56386-2022")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 56386-2022 FSC-klagomål mail.docx", "A 56386-2022")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 56386-2022 tillsynsbegäran.docx", "A 56386-2022")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 56386-2022 tillsynsbegäran mail.docx", "A 56386-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 57233-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45245</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>6</v>
-      </c>
-      <c r="U18" t="n">
-        <v>6</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Skogsklocka</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 57233-2023 artfynd.xlsx", "A 57233-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 57233-2023 karta.png", "A 57233-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 57233-2023 georefererad karta.tif", "A 57233-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 57233-2023 FSC-klagomål.docx", "A 57233-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 57233-2023 FSC-klagomål mail.docx", "A 57233-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 57233-2023 tillsynsbegäran.docx", "A 57233-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 57233-2023 tillsynsbegäran mail.docx", "A 57233-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 7931-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45706</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 7931-2025 artfynd.xlsx", "A 7931-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 7931-2025 karta.png", "A 7931-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 7931-2025 georefererad karta.tif", "A 7931-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 7931-2025 FSC-klagomål.docx", "A 7931-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 7931-2025 FSC-klagomål mail.docx", "A 7931-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 7931-2025 tillsynsbegäran.docx", "A 7931-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 7931-2025 tillsynsbegäran mail.docx", "A 7931-2025")</f>
         <v/>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
         <v>45099</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>44901</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44494</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>44588</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>44470</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>44792</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 15321-2023</t>
+          <t>A 29582-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45019</v>
+        <v>45484</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3280,11 +3280,16 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -3314,49 +3319,49 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 15321-2023 artfynd.xlsx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 29582-2024 artfynd.xlsx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 15321-2023 karta.png", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 29582-2024 karta.png", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 15321-2023 georefererad karta.tif", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 29582-2024 georefererad karta.tif", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 15321-2023 FSC-klagomål.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 29582-2024 FSC-klagomål.docx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 15321-2023 FSC-klagomål mail.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 29582-2024 FSC-klagomål mail.docx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 15321-2023 tillsynsbegäran.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 29582-2024 tillsynsbegäran.docx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 15321-2023 tillsynsbegäran mail.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 29582-2024 tillsynsbegäran mail.docx", "A 29582-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 37339-2022</t>
+          <t>A 13121-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3366,14 +3371,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44806</v>
+        <v>45002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3386,16 +3391,16 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3410,7 +3415,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3422,46 +3427,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 37339-2022 artfynd.xlsx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 13121-2023 artfynd.xlsx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 37339-2022 karta.png", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 13121-2023 karta.png", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 37339-2022 georefererad karta.tif", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 13121-2023 georefererad karta.tif", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 37339-2022 FSC-klagomål.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 13121-2023 FSC-klagomål.docx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 37339-2022 FSC-klagomål mail.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 13121-2023 FSC-klagomål mail.docx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 37339-2022 tillsynsbegäran.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 13121-2023 tillsynsbegäran.docx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 37339-2022 tillsynsbegäran mail.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 13121-2023 tillsynsbegäran mail.docx", "A 13121-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 13121-2023</t>
+          <t>A 15321-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3471,14 +3476,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45002</v>
+        <v>45019</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3491,13 +3496,13 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3524,49 +3529,49 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 13121-2023 artfynd.xlsx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 15321-2023 artfynd.xlsx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 13121-2023 karta.png", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 15321-2023 karta.png", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 13121-2023 georefererad karta.tif", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 15321-2023 georefererad karta.tif", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 13121-2023 FSC-klagomål.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 15321-2023 FSC-klagomål.docx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 13121-2023 FSC-klagomål mail.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 15321-2023 FSC-klagomål mail.docx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 13121-2023 tillsynsbegäran.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 15321-2023 tillsynsbegäran.docx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 13121-2023 tillsynsbegäran mail.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 15321-2023 tillsynsbegäran mail.docx", "A 15321-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10647-2024</t>
+          <t>A 30411-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3580,10 +3585,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45368</v>
+        <v>45827</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3596,7 +3601,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3632,46 +3637,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 10647-2024 artfynd.xlsx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 30411-2025 artfynd.xlsx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 10647-2024 karta.png", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 30411-2025 karta.png", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 10647-2024 georefererad karta.tif", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 30411-2025 georefererad karta.tif", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 10647-2024 FSC-klagomål.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 30411-2025 FSC-klagomål.docx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 10647-2024 FSC-klagomål mail.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 30411-2025 FSC-klagomål mail.docx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 10647-2024 tillsynsbegäran.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 30411-2025 tillsynsbegäran.docx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 10647-2024 tillsynsbegäran mail.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 30411-2025 tillsynsbegäran mail.docx", "A 30411-2025")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 47146-2025</t>
+          <t>A 10647-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3685,10 +3690,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45929</v>
+        <v>45368</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3700,13 +3705,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3730,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3746,46 +3746,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 47146-2025 artfynd.xlsx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 10647-2024 artfynd.xlsx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 47146-2025 karta.png", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 10647-2024 karta.png", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 47146-2025 georefererad karta.tif", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 10647-2024 georefererad karta.tif", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 47146-2025 FSC-klagomål.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 10647-2024 FSC-klagomål.docx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 47146-2025 FSC-klagomål mail.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 10647-2024 FSC-klagomål mail.docx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 47146-2025 tillsynsbegäran.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 10647-2024 tillsynsbegäran.docx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 47146-2025 tillsynsbegäran mail.docx", "A 47146-2025")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 47146-2025 prioriterade fågelarter.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 10647-2024 tillsynsbegäran mail.docx", "A 10647-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 41878-2024</t>
+          <t>A 47146-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3799,10 +3795,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45561</v>
+        <v>45929</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3820,7 +3816,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>15.9</v>
+        <v>7</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -3856,50 +3852,50 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 41878-2024 artfynd.xlsx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 47146-2025 artfynd.xlsx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 41878-2024 karta.png", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 47146-2025 karta.png", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 41878-2024 georefererad karta.tif", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 47146-2025 georefererad karta.tif", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 41878-2024 FSC-klagomål.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 47146-2025 FSC-klagomål.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 41878-2024 FSC-klagomål mail.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 47146-2025 FSC-klagomål mail.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 41878-2024 tillsynsbegäran.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 47146-2025 tillsynsbegäran.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 41878-2024 tillsynsbegäran mail.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 47146-2025 tillsynsbegäran mail.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 41878-2024 prioriterade fågelarter.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 47146-2025 prioriterade fågelarter.docx", "A 47146-2025")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 17122-2024</t>
+          <t>A 62675-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3913,10 +3909,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45412</v>
+        <v>45271</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3929,16 +3925,16 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3953,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3969,42 +3965,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 17122-2024 artfynd.xlsx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 62675-2023 artfynd.xlsx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 17122-2024 karta.png", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 62675-2023 karta.png", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 17122-2024 georefererad karta.tif", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 62675-2023 georefererad karta.tif", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 17122-2024 FSC-klagomål.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 62675-2023 FSC-klagomål.docx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 17122-2024 FSC-klagomål mail.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 62675-2023 FSC-klagomål mail.docx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 17122-2024 tillsynsbegäran.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 62675-2023 tillsynsbegäran.docx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 17122-2024 tillsynsbegäran mail.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 62675-2023 tillsynsbegäran mail.docx", "A 62675-2023")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 19524-2024</t>
+          <t>A 19052-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4018,10 +4014,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45429</v>
+        <v>45427</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4034,22 +4030,22 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>7.7</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4061,7 +4057,7 @@
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4074,46 +4070,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19524-2024 artfynd.xlsx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19052-2024 artfynd.xlsx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19524-2024 karta.png", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19052-2024 karta.png", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19524-2024 georefererad karta.tif", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19052-2024 georefererad karta.tif", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19524-2024 FSC-klagomål.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19052-2024 FSC-klagomål.docx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19524-2024 FSC-klagomål mail.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19052-2024 FSC-klagomål mail.docx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19524-2024 tillsynsbegäran.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19052-2024 tillsynsbegäran.docx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19524-2024 tillsynsbegäran mail.docx", "A 19524-2024")</f>
-        <v/>
-      </c>
-      <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 19524-2024 prioriterade fågelarter.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19052-2024 tillsynsbegäran mail.docx", "A 19052-2024")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8363-2025</t>
+          <t>A 12296-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4127,10 +4119,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45708</v>
+        <v>46087</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4143,17 +4135,17 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>1</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
@@ -4167,7 +4159,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4183,42 +4175,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 8363-2025 artfynd.xlsx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 12296-2026 artfynd.xlsx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 8363-2025 karta.png", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 12296-2026 karta.png", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 8363-2025 georefererad karta.tif", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 12296-2026 georefererad karta.tif", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 8363-2025 FSC-klagomål.docx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 12296-2026 FSC-klagomål.docx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 8363-2025 FSC-klagomål mail.docx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 12296-2026 FSC-klagomål mail.docx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 8363-2025 tillsynsbegäran.docx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 12296-2026 tillsynsbegäran.docx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 8363-2025 tillsynsbegäran mail.docx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 12296-2026 tillsynsbegäran mail.docx", "A 12296-2026")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 19052-2024</t>
+          <t>A 34076-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4232,10 +4224,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45427</v>
+        <v>46252</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4248,7 +4240,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>7.7</v>
+        <v>4.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4257,13 +4249,13 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4275,55 +4267,55 @@
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19052-2024 artfynd.xlsx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 34076-2026 artfynd.xlsx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19052-2024 karta.png", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 34076-2026 karta.png", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19052-2024 georefererad karta.tif", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 34076-2026 georefererad karta.tif", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19052-2024 FSC-klagomål.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 34076-2026 FSC-klagomål.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19052-2024 FSC-klagomål mail.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 34076-2026 FSC-klagomål mail.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19052-2024 tillsynsbegäran.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 34076-2026 tillsynsbegäran.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19052-2024 tillsynsbegäran mail.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 34076-2026 tillsynsbegäran mail.docx", "A 34076-2026")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 35077-2024</t>
+          <t>A 37339-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4337,10 +4329,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45527</v>
+        <v>44806</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4353,19 +4345,19 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -4380,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4393,46 +4385,42 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 35077-2024 artfynd.xlsx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 37339-2022 artfynd.xlsx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 35077-2024 karta.png", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 37339-2022 karta.png", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 35077-2024 georefererad karta.tif", "A 35077-2024")</f>
-        <v/>
-      </c>
-      <c r="Z36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/knärot/A 35077-2024 karta knärot.png", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 37339-2022 georefererad karta.tif", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 35077-2024 FSC-klagomål.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 37339-2022 FSC-klagomål.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 35077-2024 FSC-klagomål mail.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 37339-2022 FSC-klagomål mail.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 35077-2024 tillsynsbegäran.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 37339-2022 tillsynsbegäran.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 35077-2024 tillsynsbegäran mail.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 37339-2022 tillsynsbegäran mail.docx", "A 37339-2022")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12296-2026</t>
+          <t>A 8363-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4446,10 +4434,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46087</v>
+        <v>45708</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4462,16 +4450,16 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4486,7 +4474,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4502,42 +4490,42 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 12296-2026 artfynd.xlsx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 8363-2025 artfynd.xlsx", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 12296-2026 karta.png", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 8363-2025 karta.png", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 12296-2026 georefererad karta.tif", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 8363-2025 georefererad karta.tif", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 12296-2026 FSC-klagomål.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 8363-2025 FSC-klagomål.docx", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 12296-2026 FSC-klagomål mail.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 8363-2025 FSC-klagomål mail.docx", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 12296-2026 tillsynsbegäran.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 8363-2025 tillsynsbegäran.docx", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 12296-2026 tillsynsbegäran mail.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 8363-2025 tillsynsbegäran mail.docx", "A 8363-2025")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 29582-2024</t>
+          <t>A 17122-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4547,14 +4535,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45484</v>
+        <v>45412</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4566,37 +4554,32 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
         <v>1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
         <v>1</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4612,42 +4595,42 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 29582-2024 artfynd.xlsx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 17122-2024 artfynd.xlsx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 29582-2024 karta.png", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 17122-2024 karta.png", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 29582-2024 georefererad karta.tif", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 17122-2024 georefererad karta.tif", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 29582-2024 FSC-klagomål.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 17122-2024 FSC-klagomål.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 29582-2024 FSC-klagomål mail.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 17122-2024 FSC-klagomål mail.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 29582-2024 tillsynsbegäran.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 17122-2024 tillsynsbegäran.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 29582-2024 tillsynsbegäran mail.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 17122-2024 tillsynsbegäran mail.docx", "A 17122-2024")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 30411-2025</t>
+          <t>A 41878-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4661,10 +4644,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45827</v>
+        <v>45561</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4676,8 +4659,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>15.9</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -4686,7 +4674,7 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4701,7 +4689,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -4717,42 +4705,46 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 30411-2025 artfynd.xlsx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 41878-2024 artfynd.xlsx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 30411-2025 karta.png", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 41878-2024 karta.png", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 30411-2025 georefererad karta.tif", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 41878-2024 georefererad karta.tif", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 30411-2025 FSC-klagomål.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 41878-2024 FSC-klagomål.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 30411-2025 FSC-klagomål mail.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 41878-2024 FSC-klagomål mail.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 30411-2025 tillsynsbegäran.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 41878-2024 tillsynsbegäran.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 30411-2025 tillsynsbegäran mail.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 41878-2024 tillsynsbegäran mail.docx", "A 41878-2024")</f>
+        <v/>
+      </c>
+      <c r="AE39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 41878-2024 prioriterade fågelarter.docx", "A 41878-2024")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62675-2023</t>
+          <t>A 35077-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4762,14 +4754,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45271</v>
+        <v>45527</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4782,20 +4774,20 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
         <v>1</v>
       </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
@@ -4806,10 +4798,10 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4822,42 +4814,46 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 62675-2023 artfynd.xlsx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 35077-2024 artfynd.xlsx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 62675-2023 karta.png", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 35077-2024 karta.png", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 62675-2023 georefererad karta.tif", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 35077-2024 georefererad karta.tif", "A 35077-2024")</f>
+        <v/>
+      </c>
+      <c r="Z40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/knärot/A 35077-2024 karta knärot.png", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 62675-2023 FSC-klagomål.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 35077-2024 FSC-klagomål.docx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 62675-2023 FSC-klagomål mail.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 35077-2024 FSC-klagomål mail.docx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 62675-2023 tillsynsbegäran.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 35077-2024 tillsynsbegäran.docx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 62675-2023 tillsynsbegäran mail.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 35077-2024 tillsynsbegäran mail.docx", "A 35077-2024")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 34076-2026</t>
+          <t>A 19524-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4871,10 +4867,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46252</v>
+        <v>45429</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4887,10 +4883,10 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -4920,42 +4916,46 @@
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 34076-2026 artfynd.xlsx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19524-2024 artfynd.xlsx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 34076-2026 karta.png", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19524-2024 karta.png", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 34076-2026 georefererad karta.tif", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19524-2024 georefererad karta.tif", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 34076-2026 FSC-klagomål.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19524-2024 FSC-klagomål.docx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 34076-2026 FSC-klagomål mail.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19524-2024 FSC-klagomål mail.docx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 34076-2026 tillsynsbegäran.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19524-2024 tillsynsbegäran.docx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 34076-2026 tillsynsbegäran mail.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19524-2024 tillsynsbegäran mail.docx", "A 19524-2024")</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 19524-2024 prioriterade fågelarter.docx", "A 19524-2024")</f>
         <v/>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
         <v>44484</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>44607</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>44781</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>44509</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44575</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>44795</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>44782</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>44860</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>44494</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44844</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>44838</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44690</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>44734</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44694</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44743</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>44467</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>44509</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>44498</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>44798</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44762</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44620</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>44627</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>44735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 22133-2025</t>
+          <t>A 54444-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45785</v>
+        <v>44882</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6756,7 +6756,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 8361-2025</t>
+          <t>A 37045-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6770,10 +6770,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45708</v>
+        <v>44806</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6829,7 +6829,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 54444-2022</t>
+          <t>A 59746-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6843,10 +6843,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44882</v>
+        <v>44494</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6902,7 +6902,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 37045-2022</t>
+          <t>A 52842-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44806</v>
+        <v>44467</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6975,7 +6975,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59746-2021</t>
+          <t>A 2089-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44494</v>
+        <v>44577</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7048,7 +7048,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 31964-2023</t>
+          <t>A 25694-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45107</v>
+        <v>44732</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7121,7 +7121,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 35253-2022</t>
+          <t>A 29699-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44797</v>
+        <v>44755</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7194,7 +7194,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 29699-2022</t>
+          <t>A 30334-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7208,10 +7208,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44755</v>
+        <v>44760</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7267,7 +7267,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30334-2022</t>
+          <t>A 73306-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44760</v>
+        <v>44547</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7340,7 +7340,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 29426-2022</t>
+          <t>A 5025-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7354,10 +7354,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44753</v>
+        <v>44958</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7369,13 +7369,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>14.4</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7418,7 +7413,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 73306-2021</t>
+          <t>A 73901-2021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7432,10 +7427,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44547</v>
+        <v>44552</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7448,7 +7443,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7491,7 +7486,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 22537-2025</t>
+          <t>A 28228-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7501,14 +7496,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45787</v>
+        <v>45477</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7521,7 +7516,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7564,7 +7559,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 30339-2022</t>
+          <t>A 17437-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7578,10 +7573,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44760</v>
+        <v>45757</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7594,7 +7589,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7637,7 +7632,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 52842-2021</t>
+          <t>A 17443-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7651,10 +7646,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44467</v>
+        <v>45757</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7667,7 +7662,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7710,7 +7705,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 25694-2022</t>
+          <t>A 5841-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7724,10 +7719,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44732</v>
+        <v>44596</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7740,7 +7735,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7783,7 +7778,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 2089-2022</t>
+          <t>A 73033-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7797,10 +7792,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44577</v>
+        <v>44550</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7813,7 +7808,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7856,7 +7851,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 6751-2025</t>
+          <t>A 13382-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7870,10 +7865,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45700</v>
+        <v>45387</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7886,7 +7881,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7929,7 +7924,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 975-2025</t>
+          <t>A 5126-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7943,10 +7938,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45665</v>
+        <v>44958</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7959,7 +7954,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.4</v>
+        <v>14.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8002,7 +7997,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 63919-2021</t>
+          <t>A 57236-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8016,10 +8011,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44509</v>
+        <v>45245</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8032,7 +8027,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5.2</v>
+        <v>1.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8075,7 +8070,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 9144-2024</t>
+          <t>A 57237-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8089,10 +8084,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45358</v>
+        <v>45245</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8105,7 +8100,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>18.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8148,7 +8143,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 12311-2024</t>
+          <t>A 5810-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8162,10 +8157,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45378</v>
+        <v>44963</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8178,7 +8173,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8221,7 +8216,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37486-2022</t>
+          <t>A 47152-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8235,10 +8230,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44809</v>
+        <v>45201</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8251,7 +8246,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>8.6</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8294,7 +8289,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 20238-2024</t>
+          <t>A 26840-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8308,10 +8303,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45434</v>
+        <v>45093</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8324,7 +8319,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8367,7 +8362,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 21528-2024</t>
+          <t>A 18341-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8381,10 +8376,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45441</v>
+        <v>45762</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8397,7 +8392,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8440,7 +8435,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 33948-2023</t>
+          <t>A 58514-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8454,10 +8449,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45124</v>
+        <v>44902</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8470,7 +8465,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8513,7 +8508,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 19053-2024</t>
+          <t>A 17910-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8527,10 +8522,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45427</v>
+        <v>45419</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8543,7 +8538,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8586,7 +8581,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 42557-2022</t>
+          <t>A 2253-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8600,10 +8595,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44831</v>
+        <v>45310</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8616,7 +8611,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>13.7</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8659,7 +8654,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 23189-2024</t>
+          <t>A 6721-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8673,10 +8668,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45450</v>
+        <v>45700</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8694,7 +8689,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8737,7 +8732,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 27222-2023</t>
+          <t>A 49300-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8751,10 +8746,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45096</v>
+        <v>44861</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8767,7 +8762,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8810,7 +8805,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 17972-2025</t>
+          <t>A 5957-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8824,10 +8819,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45761</v>
+        <v>45336</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8840,7 +8835,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8883,7 +8878,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 62896-2023</t>
+          <t>A 53209-2021</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8897,10 +8892,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45272</v>
+        <v>44468</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8913,7 +8908,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>13.8</v>
+        <v>11.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8956,7 +8951,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 6938-2024</t>
+          <t>A 20238-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8966,14 +8961,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45343</v>
+        <v>45434</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8986,7 +8981,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9029,7 +9024,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 13382-2024</t>
+          <t>A 56219-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9043,10 +9038,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45387</v>
+        <v>45240</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9102,7 +9097,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 13289-2025</t>
+          <t>A 680-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9116,10 +9111,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45735</v>
+        <v>45300</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9132,7 +9127,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9175,7 +9170,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 26829-2023</t>
+          <t>A 30339-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9189,10 +9184,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45093</v>
+        <v>44760</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9205,7 +9200,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9248,7 +9243,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 13895-2024</t>
+          <t>A 975-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9262,10 +9257,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45391</v>
+        <v>45665</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9277,13 +9272,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9326,7 +9316,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 26815-2023</t>
+          <t>A 62557-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9340,10 +9330,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45093</v>
+        <v>44924</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9356,7 +9346,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9399,7 +9389,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 25840-2024</t>
+          <t>A 21402-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9413,10 +9403,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45467</v>
+        <v>45441</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9429,7 +9419,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9472,7 +9462,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 17565-2025</t>
+          <t>A 37119-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9486,10 +9476,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45757</v>
+        <v>45539</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9502,7 +9492,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>6.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9545,7 +9535,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 25443-2023</t>
+          <t>A 53138-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9559,10 +9549,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45089</v>
+        <v>45229</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9575,7 +9565,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9618,7 +9608,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 28228-2024</t>
+          <t>A 19566-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9632,10 +9622,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45477</v>
+        <v>45049</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9648,7 +9638,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9691,7 +9681,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 14306-2023</t>
+          <t>A 29762-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9705,10 +9695,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45011</v>
+        <v>45107</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9721,7 +9711,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9764,7 +9754,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 5025-2023</t>
+          <t>A 8364-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9778,10 +9768,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44958</v>
+        <v>45708</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9794,7 +9784,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9837,7 +9827,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 31974-2023</t>
+          <t>A 29736-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9854,7 +9844,7 @@
         <v>45107</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9867,7 +9857,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9910,7 +9900,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 5957-2024</t>
+          <t>A 62896-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9924,10 +9914,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45336</v>
+        <v>45272</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9940,7 +9930,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>13.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9983,7 +9973,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 25014-2024</t>
+          <t>A 69847-2021</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9997,10 +9987,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45461</v>
+        <v>44532</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10013,7 +10003,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>12.8</v>
+        <v>1.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10056,7 +10046,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 17081-2024</t>
+          <t>A 58705-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10070,10 +10060,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45412</v>
+        <v>45635</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10085,8 +10075,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10129,7 +10124,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 62682-2023</t>
+          <t>A 22347-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10143,10 +10138,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45271</v>
+        <v>45070</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10202,7 +10197,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 2253-2024</t>
+          <t>A 37515-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10216,10 +10211,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45310</v>
+        <v>45877</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10232,7 +10227,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10275,7 +10270,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 4870-2024</t>
+          <t>A 59617-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10289,10 +10284,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45329</v>
+        <v>45992</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10305,7 +10300,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10348,7 +10343,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 53209-2021</t>
+          <t>A 37495-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10362,10 +10357,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44468</v>
+        <v>45877</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10378,7 +10373,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>11.6</v>
+        <v>1.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10421,7 +10416,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 69847-2021</t>
+          <t>A 37517-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10435,10 +10430,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44532</v>
+        <v>45877</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10451,7 +10446,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10494,7 +10489,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 58514-2022</t>
+          <t>A 29256-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10508,10 +10503,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44902</v>
+        <v>45824</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10524,7 +10519,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10567,7 +10562,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 73310-2021</t>
+          <t>A 614-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10581,10 +10576,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44547</v>
+        <v>46024</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10597,7 +10592,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10640,7 +10635,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 71706-2021</t>
+          <t>A 42143-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10654,10 +10649,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44543</v>
+        <v>45904</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10670,7 +10665,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10713,7 +10708,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 44497-2025</t>
+          <t>A 33081-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10727,10 +10722,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45916</v>
+        <v>44785</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10743,7 +10738,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10786,7 +10781,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 47152-2023</t>
+          <t>A 25840-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10800,10 +10795,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45201</v>
+        <v>45467</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10816,7 +10811,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10859,7 +10854,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 45467-2022</t>
+          <t>A 37676-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10869,14 +10864,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44845</v>
+        <v>45159</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10889,7 +10884,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10932,7 +10927,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 58705-2024</t>
+          <t>A 6751-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10946,10 +10941,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45635</v>
+        <v>45700</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10961,13 +10956,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11010,7 +11000,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 36644-2023</t>
+          <t>A 44497-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11024,10 +11014,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45153</v>
+        <v>45916</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11040,7 +11030,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11083,7 +11073,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 7922-2022</t>
+          <t>A 50640-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11097,10 +11087,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44608</v>
+        <v>45217</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11156,7 +11146,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 53138-2023</t>
+          <t>A 34580-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11170,10 +11160,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45229</v>
+        <v>44795</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11186,7 +11176,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11229,7 +11219,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 27218-2023</t>
+          <t>A 12000-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11243,10 +11233,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45096</v>
+        <v>44635</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11259,7 +11249,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11302,7 +11292,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 16772-2024</t>
+          <t>A 42557-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11316,10 +11306,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45411</v>
+        <v>44831</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11332,7 +11322,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>13.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11375,7 +11365,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 62905-2023</t>
+          <t>A 35253-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11389,10 +11379,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45272</v>
+        <v>44797</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11405,7 +11395,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>13.8</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11448,7 +11438,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 36420-2023</t>
+          <t>A 20784-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11462,10 +11452,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45152</v>
+        <v>45776</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11478,7 +11468,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11521,7 +11511,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 5126-2023</t>
+          <t>A 47507-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11535,10 +11525,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44958</v>
+        <v>45930</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11551,7 +11541,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>14.3</v>
+        <v>2.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11594,7 +11584,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 47507-2025</t>
+          <t>A 13820-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11608,10 +11598,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45930</v>
+        <v>45390</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11624,7 +11614,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.9</v>
+        <v>7.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11667,7 +11657,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 66056-2021</t>
+          <t>A 17565-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11681,10 +11671,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44517</v>
+        <v>45757</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11697,7 +11687,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11740,7 +11730,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 10892-2022</t>
+          <t>A 31362-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11750,14 +11740,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44627</v>
+        <v>45505</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11770,7 +11760,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11813,7 +11803,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 3065-2024</t>
+          <t>A 40524-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11827,10 +11817,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45316</v>
+        <v>45896</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11843,7 +11833,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11886,7 +11876,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 12082-2024</t>
+          <t>A 21248-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11900,10 +11890,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45377</v>
+        <v>44705</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11916,7 +11906,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.2</v>
+        <v>12.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11959,7 +11949,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 12084-2024</t>
+          <t>A 40522-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11973,10 +11963,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45377</v>
+        <v>45896</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11989,7 +11979,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12049,7 +12039,7 @@
         <v>45939</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12105,7 +12095,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 31362-2024</t>
+          <t>A 51509-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12119,10 +12109,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45505</v>
+        <v>45950</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12135,7 +12125,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12178,7 +12168,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 20954-2023</t>
+          <t>A 3065-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12192,10 +12182,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45061</v>
+        <v>45316</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12208,7 +12198,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12251,7 +12241,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 17443-2025</t>
+          <t>A 17081-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12265,10 +12255,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45757</v>
+        <v>45412</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12281,7 +12271,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12324,7 +12314,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 62557-2022</t>
+          <t>A 52699-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12338,10 +12328,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44924</v>
+        <v>45956</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12354,7 +12344,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12397,7 +12387,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 7991-2024</t>
+          <t>A 7993-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12407,14 +12397,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
         <v>45350</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12427,7 +12417,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12470,7 +12460,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 51509-2025</t>
+          <t>A 52700-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12480,14 +12470,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45950</v>
+        <v>45956</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12500,7 +12490,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12543,7 +12533,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 17399-2025</t>
+          <t>A 45467-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12557,10 +12547,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45757</v>
+        <v>44845</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12573,7 +12563,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12616,7 +12606,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 5810-2023</t>
+          <t>A 5011-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12630,10 +12620,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44963</v>
+        <v>45329</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12646,7 +12636,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.8</v>
+        <v>22</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12689,7 +12679,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 20369-2024</t>
+          <t>A 53137-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12703,10 +12693,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45435</v>
+        <v>45229</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12719,7 +12709,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12762,7 +12752,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 11601-2025</t>
+          <t>A 5214-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12776,10 +12766,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45727</v>
+        <v>45691</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12792,7 +12782,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12835,7 +12825,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 4976-2024</t>
+          <t>A 9144-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12849,10 +12839,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45329</v>
+        <v>45358</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12865,7 +12855,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12908,7 +12898,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 52700-2025</t>
+          <t>A 62682-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12922,10 +12912,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45956</v>
+        <v>45271</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12938,7 +12928,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12981,7 +12971,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 12175-2024</t>
+          <t>A 31561-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12995,10 +12985,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45377</v>
+        <v>45117</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13011,7 +13001,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>5.6</v>
+        <v>1.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13054,7 +13044,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 52699-2025</t>
+          <t>A 4982-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13068,10 +13058,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45956</v>
+        <v>45329</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13084,7 +13074,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13127,7 +13117,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 30527-2022</t>
+          <t>A 62947-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13141,10 +13131,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44762</v>
+        <v>45272</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13157,7 +13147,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13200,7 +13190,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 5236-2023</t>
+          <t>A 31930-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13210,14 +13200,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44956</v>
+        <v>45510</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13230,7 +13220,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13273,7 +13263,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 62947-2023</t>
+          <t>A 58751-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13287,10 +13277,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45272</v>
+        <v>45986</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13303,7 +13293,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13346,7 +13336,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 22347-2023</t>
+          <t>A 71706-2021</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13360,10 +13350,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45070</v>
+        <v>44543</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13376,7 +13366,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13419,7 +13409,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 7993-2024</t>
+          <t>A 40935-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13429,14 +13419,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45350</v>
+        <v>44823</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13448,8 +13438,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13492,7 +13487,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 56220-2023</t>
+          <t>A 58747-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13506,10 +13501,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45240</v>
+        <v>45986</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13522,7 +13517,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13565,7 +13560,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 33081-2022</t>
+          <t>A 6938-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13575,14 +13570,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44785</v>
+        <v>45343</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13595,7 +13590,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13638,7 +13633,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 56219-2023</t>
+          <t>A 60656-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13652,10 +13647,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45240</v>
+        <v>45996</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13668,7 +13663,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13711,7 +13706,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 6721-2025</t>
+          <t>A 22406-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13725,10 +13720,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45700</v>
+        <v>46154</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13740,13 +13735,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13789,7 +13779,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 29260-2025</t>
+          <t>A 14306-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13803,10 +13793,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45824</v>
+        <v>45011</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13819,7 +13809,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13862,7 +13852,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 17437-2025</t>
+          <t>A 17972-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13876,10 +13866,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45757</v>
+        <v>45761</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13892,7 +13882,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13935,7 +13925,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 5841-2022</t>
+          <t>A 27222-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13949,10 +13939,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44596</v>
+        <v>45096</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13965,7 +13955,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14008,7 +13998,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 29762-2023</t>
+          <t>A 59391-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14018,14 +14008,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45107</v>
+        <v>45989</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14038,7 +14028,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14081,7 +14071,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 12000-2022</t>
+          <t>A 36644-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14095,10 +14085,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44635</v>
+        <v>45153</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14111,7 +14101,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14154,7 +14144,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 40935-2022</t>
+          <t>A 8788-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14164,14 +14154,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44823</v>
+        <v>45356</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14183,13 +14173,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14232,7 +14217,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 36646-2023</t>
+          <t>A 71903-2021</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14246,10 +14231,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45153</v>
+        <v>44543</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14262,7 +14247,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.4</v>
+        <v>6.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14305,7 +14290,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 58747-2025</t>
+          <t>A 62554-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14319,10 +14304,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45986</v>
+        <v>44924</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14335,7 +14320,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14378,7 +14363,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 58751-2025</t>
+          <t>A 3779-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14392,10 +14377,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45986</v>
+        <v>45681</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14407,8 +14392,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>BillerudKorsnäs AB</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>0.6</v>
+        <v>7.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14451,7 +14441,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 29736-2023</t>
+          <t>A 21528-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14465,10 +14455,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45107</v>
+        <v>45441</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14481,7 +14471,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14524,7 +14514,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 29724-2023</t>
+          <t>A 20954-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14534,14 +14524,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45107</v>
+        <v>45061</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14554,7 +14544,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14597,7 +14587,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 8362-2025</t>
+          <t>A 39334-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14611,10 +14601,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45708</v>
+        <v>45889</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14627,7 +14617,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>7.7</v>
+        <v>1.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14670,7 +14660,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 972-2025</t>
+          <t>A 3054-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14684,10 +14674,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45665</v>
+        <v>46039</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14700,7 +14690,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14743,7 +14733,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 49300-2022</t>
+          <t>A 10892-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14757,10 +14747,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44861</v>
+        <v>44627</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14773,7 +14763,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14816,7 +14806,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 50640-2023</t>
+          <t>A 29426-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14830,10 +14820,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45217</v>
+        <v>44753</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14845,8 +14835,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>1.2</v>
+        <v>14.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14889,7 +14884,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 16635-2024</t>
+          <t>A 23733-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14903,10 +14898,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45408</v>
+        <v>46164</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14918,8 +14913,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14962,7 +14962,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 30563-2025</t>
+          <t>A 23945-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14976,10 +14976,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45831</v>
+        <v>46167</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14991,8 +14991,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15035,7 +15040,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 17910-2024</t>
+          <t>A 23757-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15049,10 +15054,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45419</v>
+        <v>46164</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15065,7 +15070,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15108,7 +15113,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 37676-2023</t>
+          <t>A 23702-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15118,14 +15123,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45159</v>
+        <v>46164</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15137,8 +15142,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15181,7 +15191,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 60656-2025</t>
+          <t>A 44048-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15195,10 +15205,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45996</v>
+        <v>45188</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15254,7 +15264,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 53137-2023</t>
+          <t>A 62905-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15268,10 +15278,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45229</v>
+        <v>45272</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15284,7 +15294,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1</v>
+        <v>13.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15327,7 +15337,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 8788-2024</t>
+          <t>A 37486-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15341,10 +15351,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45356</v>
+        <v>44809</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15357,7 +15367,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.9</v>
+        <v>8.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15400,7 +15410,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 680-2024</t>
+          <t>A 46299-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15414,10 +15424,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45300</v>
+        <v>44847</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15430,7 +15440,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15473,7 +15483,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 46299-2022</t>
+          <t>A 8732-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15487,10 +15497,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44847</v>
+        <v>46066</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15503,7 +15513,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2</v>
+        <v>6.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15546,7 +15556,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 32327-2025</t>
+          <t>A 5236-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15560,10 +15570,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45836</v>
+        <v>44956</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15576,7 +15586,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15619,7 +15629,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 3054-2026</t>
+          <t>A 56220-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15633,10 +15643,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46039</v>
+        <v>45240</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15649,7 +15659,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15692,7 +15702,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 62554-2022</t>
+          <t>A 972-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15706,10 +15716,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44924</v>
+        <v>45665</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15722,7 +15732,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15765,7 +15775,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 59391-2025</t>
+          <t>A 24754-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15775,14 +15785,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45989</v>
+        <v>46171</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15795,7 +15805,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15838,7 +15848,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 57236-2023</t>
+          <t>A 12283-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15852,10 +15862,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45245</v>
+        <v>46087</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15911,7 +15921,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 57237-2023</t>
+          <t>A 13895-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15925,10 +15935,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45245</v>
+        <v>45391</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15940,8 +15950,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>18.2</v>
+        <v>3.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15984,7 +15999,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 29577-2024</t>
+          <t>A 29724-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15994,14 +16009,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45484</v>
+        <v>45107</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16013,13 +16028,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>10.1</v>
+        <v>0.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16062,7 +16072,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 27443-2024</t>
+          <t>A 31974-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16076,10 +16086,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45474</v>
+        <v>45107</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16092,7 +16102,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16135,7 +16145,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 32959-2022</t>
+          <t>A 14688-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16145,14 +16155,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44784</v>
+        <v>46101</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16165,7 +16175,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16208,7 +16218,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 13320-2024</t>
+          <t>A 26015-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16218,14 +16228,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45386</v>
+        <v>46181</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16237,8 +16247,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16281,7 +16296,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 38517-2024</t>
+          <t>A 19802-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16295,10 +16310,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45546</v>
+        <v>45432</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16310,8 +16325,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16354,7 +16374,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 8732-2026</t>
+          <t>A 15549-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16368,10 +16388,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46066</v>
+        <v>46106</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16384,7 +16404,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>6.1</v>
+        <v>1.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16427,7 +16447,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 37119-2024</t>
+          <t>A 15543-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16441,10 +16461,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45539</v>
+        <v>46106</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16457,7 +16477,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>6.7</v>
+        <v>3.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16500,7 +16520,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 32942-2026</t>
+          <t>A 16635-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16514,10 +16534,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46244</v>
+        <v>45408</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16530,7 +16550,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16573,7 +16593,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 19802-2024</t>
+          <t>A 7922-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16587,10 +16607,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45432</v>
+        <v>44608</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16602,13 +16622,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16651,7 +16666,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 34580-2022</t>
+          <t>A 1556-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16665,10 +16680,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44795</v>
+        <v>45670</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16681,7 +16696,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16724,7 +16739,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 12283-2026</t>
+          <t>A 12311-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16738,10 +16753,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46087</v>
+        <v>45378</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16754,7 +16769,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16797,7 +16812,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 19566-2023</t>
+          <t>A 33948-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16811,10 +16826,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45049</v>
+        <v>45124</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16827,7 +16842,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16870,7 +16885,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 8359-2025</t>
+          <t>A 13320-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16884,10 +16899,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45708</v>
+        <v>45386</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16900,7 +16915,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16943,7 +16958,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 7272-2022</t>
+          <t>A 55227-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16957,10 +16972,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44606</v>
+        <v>45231</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16973,7 +16988,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17016,7 +17031,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 22822-2024</t>
+          <t>A 25014-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17030,10 +17045,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45448</v>
+        <v>45461</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17046,7 +17061,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.3</v>
+        <v>12.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17089,7 +17104,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 59542-2022</t>
+          <t>A 31964-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17103,10 +17118,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44907</v>
+        <v>45107</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17119,7 +17134,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17162,7 +17177,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 21402-2024</t>
+          <t>A 12082-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17176,10 +17191,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45441</v>
+        <v>45377</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17192,7 +17207,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17235,7 +17250,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 14688-2026</t>
+          <t>A 12084-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17245,14 +17260,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46101</v>
+        <v>45377</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17265,7 +17280,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17308,7 +17323,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 35425-2025</t>
+          <t>A 28513-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17322,10 +17337,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45855</v>
+        <v>46197</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17338,7 +17353,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17381,7 +17396,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 15543-2026</t>
+          <t>A 11103-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17395,10 +17410,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46106</v>
+        <v>44628</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17411,7 +17426,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17454,7 +17469,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 71781-2021</t>
+          <t>A 29205-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17468,10 +17483,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44539</v>
+        <v>46202</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17483,13 +17498,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I212" t="n">
-        <v>7</v>
+        <v>1.4</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17532,7 +17542,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 15549-2026</t>
+          <t>A 4976-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17546,10 +17556,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46106</v>
+        <v>45329</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17562,7 +17572,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17605,7 +17615,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 31930-2024</t>
+          <t>A 29222-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17615,14 +17625,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45510</v>
+        <v>46202</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17635,7 +17645,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17678,7 +17688,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 73901-2021</t>
+          <t>A 64304-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17692,10 +17702,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44552</v>
+        <v>45280</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17708,7 +17718,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17751,7 +17761,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 26840-2023</t>
+          <t>A 48553-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17765,10 +17775,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45093</v>
+        <v>45208</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17781,7 +17791,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17824,7 +17834,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 13820-2024</t>
+          <t>A 26815-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17838,10 +17848,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45390</v>
+        <v>45093</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17854,7 +17864,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>7.2</v>
+        <v>1.1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17897,7 +17907,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 5011-2024</t>
+          <t>A 29191-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17911,10 +17921,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45329</v>
+        <v>46202</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17927,7 +17937,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>22</v>
+        <v>5.1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17970,7 +17980,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 18341-2025</t>
+          <t>A 16772-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17984,10 +17994,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45762</v>
+        <v>45411</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18000,7 +18010,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18043,7 +18053,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 52848-2021</t>
+          <t>A 25443-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18057,10 +18067,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44467</v>
+        <v>45089</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18073,7 +18083,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18116,7 +18126,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 19753-2024</t>
+          <t>A 32302-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18130,10 +18140,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45432</v>
+        <v>45512</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18145,8 +18155,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I221" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18189,7 +18204,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 29256-2025</t>
+          <t>A 66056-2021</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18203,10 +18218,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45824</v>
+        <v>44517</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18219,7 +18234,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18262,7 +18277,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 37517-2025</t>
+          <t>A 23189-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18276,10 +18291,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45877</v>
+        <v>45450</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18291,8 +18306,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I223" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18335,7 +18355,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 21248-2022</t>
+          <t>A 7991-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18345,14 +18365,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44705</v>
+        <v>45350</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18365,7 +18385,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>12.4</v>
+        <v>1.1</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18408,7 +18428,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 4982-2024</t>
+          <t>A 59542-2022</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18422,10 +18442,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45329</v>
+        <v>44907</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18438,7 +18458,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18481,7 +18501,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 37515-2025</t>
+          <t>A 52848-2021</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18495,10 +18515,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45877</v>
+        <v>44467</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18511,7 +18531,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18554,7 +18574,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 37495-2025</t>
+          <t>A 8361-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18568,10 +18588,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45877</v>
+        <v>45708</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18584,7 +18604,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18627,7 +18647,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 55227-2023</t>
+          <t>A 34538-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18641,10 +18661,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45231</v>
+        <v>46255</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18657,7 +18677,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18700,7 +18720,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 9837-2023</t>
+          <t>A 31034-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18714,10 +18734,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44984</v>
+        <v>46214</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18730,7 +18750,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18773,7 +18793,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 42143-2025</t>
+          <t>A 73310-2021</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18787,10 +18807,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45904</v>
+        <v>44547</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18803,7 +18823,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>2</v>
+        <v>6.2</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18846,7 +18866,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 1556-2025</t>
+          <t>A 71781-2021</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18860,10 +18880,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45670</v>
+        <v>44539</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18875,8 +18895,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I231" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18919,7 +18944,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 40522-2025</t>
+          <t>A 8362-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18933,10 +18958,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45896</v>
+        <v>45708</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18949,7 +18974,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>0.9</v>
+        <v>7.7</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18992,7 +19017,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 5214-2025</t>
+          <t>A 30527-2022</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -19006,10 +19031,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45691</v>
+        <v>44762</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19022,7 +19047,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -19065,7 +19090,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 73033-2021</t>
+          <t>A 17573-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -19079,10 +19104,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>44550</v>
+        <v>45757</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19095,7 +19120,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -19138,7 +19163,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 20784-2025</t>
+          <t>A 31559-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -19152,10 +19177,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45776</v>
+        <v>46224</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19168,7 +19193,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>9.5</v>
+        <v>1.6</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -19211,7 +19236,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 614-2026</t>
+          <t>A 9837-2023</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19225,10 +19250,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46024</v>
+        <v>44984</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19241,7 +19266,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19284,7 +19309,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 64304-2023</t>
+          <t>A 19753-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19298,10 +19323,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45280</v>
+        <v>45432</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19314,7 +19339,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19357,7 +19382,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 40524-2025</t>
+          <t>A 27443-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19371,10 +19396,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45896</v>
+        <v>45474</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19387,7 +19412,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19430,7 +19455,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 8364-2025</t>
+          <t>A 32959-2022</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19444,10 +19469,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45708</v>
+        <v>44784</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19460,7 +19485,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19503,7 +19528,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 59617-2025</t>
+          <t>A 30914-2023</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19517,10 +19542,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45992</v>
+        <v>45113</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19533,7 +19558,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19576,7 +19601,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 31561-2023</t>
+          <t>A 20369-2024</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19590,10 +19615,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45117</v>
+        <v>45435</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19606,7 +19631,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19649,7 +19674,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 48553-2023</t>
+          <t>A 7272-2022</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19663,10 +19688,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45208</v>
+        <v>44606</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19679,7 +19704,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19722,7 +19747,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 17573-2025</t>
+          <t>A 26829-2023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19736,10 +19761,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45757</v>
+        <v>45093</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19752,7 +19777,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19795,7 +19820,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 44048-2023</t>
+          <t>A 38517-2024</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19809,10 +19834,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45188</v>
+        <v>45546</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19825,7 +19850,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19868,7 +19893,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 30914-2023</t>
+          <t>A 37221-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19882,10 +19907,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45113</v>
+        <v>46274</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19898,7 +19923,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19941,7 +19966,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 8370-2023</t>
+          <t>A 37243-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19955,10 +19980,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>44977</v>
+        <v>46274</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19971,7 +19996,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>0.9</v>
+        <v>13.9</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -20014,7 +20039,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 12217-2025</t>
+          <t>A 63919-2021</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -20028,10 +20053,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45729</v>
+        <v>44509</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20044,7 +20069,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -20087,7 +20112,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 22406-2026</t>
+          <t>A 4870-2024</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -20101,10 +20126,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>46154</v>
+        <v>45329</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20117,7 +20142,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -20160,7 +20185,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 39334-2025</t>
+          <t>A 36646-2023</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -20174,10 +20199,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45889</v>
+        <v>45153</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20190,7 +20215,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -20233,7 +20258,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 3779-2025</t>
+          <t>A 22822-2024</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -20247,10 +20272,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45681</v>
+        <v>45448</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20262,13 +20287,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>BillerudKorsnäs AB</t>
-        </is>
-      </c>
       <c r="I250" t="n">
-        <v>7.6</v>
+        <v>1.3</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -20311,7 +20331,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 71903-2021</t>
+          <t>A 19053-2024</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20325,10 +20345,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>44543</v>
+        <v>45427</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20341,7 +20361,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>6.3</v>
+        <v>3.7</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20384,7 +20404,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 23702-2026</t>
+          <t>A 11601-2025</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20398,10 +20418,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>46164</v>
+        <v>45727</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20413,13 +20433,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I252" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20462,7 +20477,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 23733-2026</t>
+          <t>A 12175-2024</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20476,10 +20491,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>46164</v>
+        <v>45377</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20491,13 +20506,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I253" t="n">
-        <v>0.9</v>
+        <v>5.6</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20540,7 +20550,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 23757-2026</t>
+          <t>A 29577-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20554,10 +20564,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>46164</v>
+        <v>45484</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20569,8 +20579,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I254" t="n">
-        <v>1.5</v>
+        <v>10.1</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20613,7 +20628,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 23945-2026</t>
+          <t>A 8370-2023</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20627,10 +20642,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>46167</v>
+        <v>44977</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20642,13 +20657,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I255" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20691,7 +20701,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 24754-2026</t>
+          <t>A 12217-2025</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20705,10 +20715,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>46171</v>
+        <v>45729</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20721,7 +20731,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20764,7 +20774,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 26015-2026</t>
+          <t>A 32942-2026</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20774,14 +20784,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>46181</v>
+        <v>46244</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20793,13 +20803,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I257" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20842,7 +20847,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 11103-2022</t>
+          <t>A 22133-2025</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20856,10 +20861,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>44628</v>
+        <v>45785</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20872,7 +20877,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20915,7 +20920,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 28513-2026</t>
+          <t>A 22537-2025</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20925,14 +20930,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>46197</v>
+        <v>45787</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20945,7 +20950,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20988,7 +20993,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 32302-2024</t>
+          <t>A 13289-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -21002,10 +21007,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45512</v>
+        <v>45735</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21017,13 +21022,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I260" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -21066,7 +21066,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 29205-2026</t>
+          <t>A 27218-2023</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>46202</v>
+        <v>45096</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -21139,7 +21139,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 29222-2026</t>
+          <t>A 36420-2023</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -21153,10 +21153,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>46202</v>
+        <v>45152</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -21212,7 +21212,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 29191-2026</t>
+          <t>A 17399-2025</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -21226,10 +21226,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>46202</v>
+        <v>45757</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 34538-2026</t>
+          <t>A 29260-2025</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -21299,10 +21299,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>46255</v>
+        <v>45824</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -21358,7 +21358,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 31034-2026</t>
+          <t>A 30563-2025</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21372,10 +21372,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>46214</v>
+        <v>45831</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -21431,7 +21431,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 31559-2026</t>
+          <t>A 32327-2025</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21445,10 +21445,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>46224</v>
+        <v>45836</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -21504,7 +21504,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 37221-2026</t>
+          <t>A 8359-2025</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21518,10 +21518,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>46274</v>
+        <v>45708</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21577,7 +21577,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 37243-2026</t>
+          <t>A 35425-2025</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21591,10 +21591,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>46274</v>
+        <v>45855</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>13.9</v>
+        <v>0.5</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21667,7 +21667,7 @@
         <v>45099</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>45272</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45846</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>45973</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>46035</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>

--- a/Översikt GRUMS.xlsx
+++ b/Översikt GRUMS.xlsx
@@ -601,7 +601,7 @@
         <v>44978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45343</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44788</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44498</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44819</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45615</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>46252</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>44981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45099</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 23860-2023</t>
+          <t>A 41113-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1741,10 +1741,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45078</v>
+        <v>45898</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1766,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1790,160 +1790,160 @@
         <v>2</v>
       </c>
       <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Violmussling
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 41113-2025 artfynd.xlsx", "A 41113-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 41113-2025 karta.png", "A 41113-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 41113-2025 georefererad karta.tif", "A 41113-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 41113-2025 FSC-klagomål.docx", "A 41113-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 41113-2025 FSC-klagomål mail.docx", "A 41113-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 41113-2025 tillsynsbegäran.docx", "A 41113-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 41113-2025 tillsynsbegäran mail.docx", "A 41113-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 23860-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Gullpudra
 Gulsparv</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 23860-2023 artfynd.xlsx", "A 23860-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 23860-2023 karta.png", "A 23860-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 23860-2023 georefererad karta.tif", "A 23860-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 23860-2023 FSC-klagomål.docx", "A 23860-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 23860-2023 FSC-klagomål mail.docx", "A 23860-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 23860-2023 tillsynsbegäran.docx", "A 23860-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 23860-2023 tillsynsbegäran mail.docx", "A 23860-2023")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 23860-2023 prioriterade fågelarter.docx", "A 23860-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 41113-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45898</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Violmussling
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 41113-2025 artfynd.xlsx", "A 41113-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 41113-2025 karta.png", "A 41113-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 41113-2025 georefererad karta.tif", "A 41113-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 41113-2025 FSC-klagomål.docx", "A 41113-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 41113-2025 FSC-klagomål mail.docx", "A 41113-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 41113-2025 tillsynsbegäran.docx", "A 41113-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 41113-2025 tillsynsbegäran mail.docx", "A 41113-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 5280-2022</t>
+          <t>A 66053-2021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44593</v>
+        <v>44517</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1972,19 +1972,14 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>37.1</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1993,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2002,169 +1997,174 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Bronshjon</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 66053-2021 artfynd.xlsx", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 66053-2021 karta.png", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 66053-2021 georefererad karta.tif", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 66053-2021 FSC-klagomål.docx", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 66053-2021 FSC-klagomål mail.docx", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 66053-2021 tillsynsbegäran.docx", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 66053-2021 tillsynsbegäran mail.docx", "A 66053-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 5280-2022</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44593</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
         <v>4</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>1</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Ask
 Tjäder</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 5280-2022 artfynd.xlsx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 5280-2022 karta.png", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 5280-2022 georefererad karta.tif", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 5280-2022 FSC-klagomål.docx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 5280-2022 FSC-klagomål mail.docx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 5280-2022 tillsynsbegäran.docx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 5280-2022 tillsynsbegäran mail.docx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 5280-2022 prioriterade fågelarter.docx", "A 5280-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 66053-2021</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44517</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>6</v>
-      </c>
-      <c r="U15" t="n">
-        <v>6</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Bronshjon</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 66053-2021 artfynd.xlsx", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 66053-2021 karta.png", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 66053-2021 georefererad karta.tif", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 66053-2021 FSC-klagomål.docx", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 66053-2021 FSC-klagomål mail.docx", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 66053-2021 tillsynsbegäran.docx", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 66053-2021 tillsynsbegäran mail.docx", "A 66053-2021")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57233-2023</t>
+          <t>A 54042-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45245</v>
+        <v>44470</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2194,16 +2194,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>7.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2218,7 +2218,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2227,370 +2227,370 @@
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 54042-2021 artfynd.xlsx", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 54042-2021 karta.png", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 54042-2021 georefererad karta.tif", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 54042-2021 FSC-klagomål.docx", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 54042-2021 FSC-klagomål mail.docx", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 54042-2021 tillsynsbegäran.docx", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 54042-2021 tillsynsbegäran mail.docx", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 54042-2021 prioriterade fågelarter.docx", "A 54042-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 56386-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44890</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Vågfibbla
+Rönnfibbla</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 56386-2022 artfynd.xlsx", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 56386-2022 karta.png", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 56386-2022 georefererad karta.tif", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 56386-2022 FSC-klagomål.docx", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 56386-2022 FSC-klagomål mail.docx", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 56386-2022 tillsynsbegäran.docx", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 56386-2022 tillsynsbegäran mail.docx", "A 56386-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 57233-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45245</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
         <v>6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" t="n">
         <v>6</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin
 Skogsklocka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 57233-2023 artfynd.xlsx", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 57233-2023 karta.png", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 57233-2023 georefererad karta.tif", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 57233-2023 FSC-klagomål.docx", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 57233-2023 FSC-klagomål mail.docx", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 57233-2023 tillsynsbegäran.docx", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 57233-2023 tillsynsbegäran mail.docx", "A 57233-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 54042-2021</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44470</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J17" t="n">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 7931-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45706</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 54042-2021 artfynd.xlsx", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 54042-2021 karta.png", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 54042-2021 georefererad karta.tif", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 54042-2021 FSC-klagomål.docx", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 54042-2021 FSC-klagomål mail.docx", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 54042-2021 tillsynsbegäran.docx", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 54042-2021 tillsynsbegäran mail.docx", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 54042-2021 prioriterade fågelarter.docx", "A 54042-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 7931-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45706</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>1</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Skogsödla</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 7931-2025 artfynd.xlsx", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 7931-2025 karta.png", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 7931-2025 georefererad karta.tif", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 7931-2025 FSC-klagomål.docx", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 7931-2025 FSC-klagomål mail.docx", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 7931-2025 tillsynsbegäran.docx", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 7931-2025 tillsynsbegäran mail.docx", "A 7931-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 56386-2022</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44890</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Vågfibbla
-Rönnfibbla</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 56386-2022 artfynd.xlsx", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 56386-2022 karta.png", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 56386-2022 georefererad karta.tif", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 56386-2022 FSC-klagomål.docx", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 56386-2022 FSC-klagomål mail.docx", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 56386-2022 tillsynsbegäran.docx", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 56386-2022 tillsynsbegäran mail.docx", "A 56386-2022")</f>
         <v/>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
         <v>45099</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>44901</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44494</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>44588</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>44470</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>44792</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 29582-2024</t>
+          <t>A 37339-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45484</v>
+        <v>44806</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3280,37 +3280,32 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3326,42 +3321,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 29582-2024 artfynd.xlsx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 37339-2022 artfynd.xlsx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 29582-2024 karta.png", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 37339-2022 karta.png", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 29582-2024 georefererad karta.tif", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 37339-2022 georefererad karta.tif", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 29582-2024 FSC-klagomål.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 37339-2022 FSC-klagomål.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 29582-2024 FSC-klagomål mail.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 37339-2022 FSC-klagomål mail.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 29582-2024 tillsynsbegäran.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 37339-2022 tillsynsbegäran.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 29582-2024 tillsynsbegäran mail.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 37339-2022 tillsynsbegäran mail.docx", "A 37339-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13121-2023</t>
+          <t>A 10647-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3371,14 +3366,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45002</v>
+        <v>45368</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3391,7 +3386,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3431,42 +3426,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 13121-2023 artfynd.xlsx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 10647-2024 artfynd.xlsx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 13121-2023 karta.png", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 10647-2024 karta.png", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 13121-2023 georefererad karta.tif", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 10647-2024 georefererad karta.tif", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 13121-2023 FSC-klagomål.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 10647-2024 FSC-klagomål.docx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 13121-2023 FSC-klagomål mail.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 10647-2024 FSC-klagomål mail.docx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 13121-2023 tillsynsbegäran.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 10647-2024 tillsynsbegäran.docx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 13121-2023 tillsynsbegäran mail.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 10647-2024 tillsynsbegäran mail.docx", "A 10647-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15321-2023</t>
+          <t>A 41878-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3480,10 +3475,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45019</v>
+        <v>45561</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3495,18 +3490,23 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>15.9</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3529,49 +3529,53 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 15321-2023 artfynd.xlsx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 41878-2024 artfynd.xlsx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 15321-2023 karta.png", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 41878-2024 karta.png", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 15321-2023 georefererad karta.tif", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 41878-2024 georefererad karta.tif", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 15321-2023 FSC-klagomål.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 41878-2024 FSC-klagomål.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 15321-2023 FSC-klagomål mail.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 41878-2024 FSC-klagomål mail.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 15321-2023 tillsynsbegäran.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 41878-2024 tillsynsbegäran.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 15321-2023 tillsynsbegäran mail.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 41878-2024 tillsynsbegäran mail.docx", "A 41878-2024")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 41878-2024 prioriterade fågelarter.docx", "A 41878-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 30411-2025</t>
+          <t>A 17122-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3581,14 +3585,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45827</v>
+        <v>45412</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3601,17 +3605,17 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
@@ -3625,7 +3629,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3641,42 +3645,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 30411-2025 artfynd.xlsx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 17122-2024 artfynd.xlsx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 30411-2025 karta.png", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 17122-2024 karta.png", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 30411-2025 georefererad karta.tif", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 17122-2024 georefererad karta.tif", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 30411-2025 FSC-klagomål.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 17122-2024 FSC-klagomål.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 30411-2025 FSC-klagomål mail.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 17122-2024 FSC-klagomål mail.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 30411-2025 tillsynsbegäran.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 17122-2024 tillsynsbegäran.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 30411-2025 tillsynsbegäran mail.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 17122-2024 tillsynsbegäran mail.docx", "A 17122-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 10647-2024</t>
+          <t>A 47146-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3690,10 +3694,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45368</v>
+        <v>45929</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3705,8 +3709,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3715,7 +3724,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3730,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3746,42 +3755,46 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 10647-2024 artfynd.xlsx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 47146-2025 artfynd.xlsx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 10647-2024 karta.png", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 47146-2025 karta.png", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 10647-2024 georefererad karta.tif", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 47146-2025 georefererad karta.tif", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 10647-2024 FSC-klagomål.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 47146-2025 FSC-klagomål.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 10647-2024 FSC-klagomål mail.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 47146-2025 FSC-klagomål mail.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 10647-2024 tillsynsbegäran.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 47146-2025 tillsynsbegäran.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 10647-2024 tillsynsbegäran mail.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 47146-2025 tillsynsbegäran mail.docx", "A 47146-2025")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 47146-2025 prioriterade fågelarter.docx", "A 47146-2025")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 47146-2025</t>
+          <t>A 12296-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3795,10 +3808,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45929</v>
+        <v>46087</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3810,16 +3823,11 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -3852,50 +3860,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 47146-2025 artfynd.xlsx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 12296-2026 artfynd.xlsx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 47146-2025 karta.png", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 12296-2026 karta.png", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 47146-2025 georefererad karta.tif", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 12296-2026 georefererad karta.tif", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 47146-2025 FSC-klagomål.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 12296-2026 FSC-klagomål.docx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 47146-2025 FSC-klagomål mail.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 12296-2026 FSC-klagomål mail.docx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 47146-2025 tillsynsbegäran.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 12296-2026 tillsynsbegäran.docx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 47146-2025 tillsynsbegäran mail.docx", "A 47146-2025")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 47146-2025 prioriterade fågelarter.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 12296-2026 tillsynsbegäran mail.docx", "A 12296-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62675-2023</t>
+          <t>A 19524-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3905,14 +3909,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45271</v>
+        <v>45429</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3925,17 +3929,17 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
@@ -3949,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3961,39 +3965,43 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 62675-2023 artfynd.xlsx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19524-2024 artfynd.xlsx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 62675-2023 karta.png", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19524-2024 karta.png", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 62675-2023 georefererad karta.tif", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19524-2024 georefererad karta.tif", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 62675-2023 FSC-klagomål.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19524-2024 FSC-klagomål.docx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 62675-2023 FSC-klagomål mail.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19524-2024 FSC-klagomål mail.docx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 62675-2023 tillsynsbegäran.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19524-2024 tillsynsbegäran.docx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 62675-2023 tillsynsbegäran mail.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19524-2024 tillsynsbegäran mail.docx", "A 19524-2024")</f>
+        <v/>
+      </c>
+      <c r="AE32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 19524-2024 prioriterade fågelarter.docx", "A 19524-2024")</f>
         <v/>
       </c>
     </row>
@@ -4017,7 +4025,7 @@
         <v>45427</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4105,7 +4113,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12296-2026</t>
+          <t>A 15321-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4119,10 +4127,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46087</v>
+        <v>45019</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4135,16 +4143,16 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.3</v>
+        <v>5.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4159,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4168,49 +4176,49 @@
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 12296-2026 artfynd.xlsx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 15321-2023 artfynd.xlsx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 12296-2026 karta.png", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 15321-2023 karta.png", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 12296-2026 georefererad karta.tif", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 15321-2023 georefererad karta.tif", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 12296-2026 FSC-klagomål.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 15321-2023 FSC-klagomål.docx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 12296-2026 FSC-klagomål mail.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 15321-2023 FSC-klagomål mail.docx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 12296-2026 tillsynsbegäran.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 15321-2023 tillsynsbegäran.docx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 12296-2026 tillsynsbegäran mail.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 15321-2023 tillsynsbegäran mail.docx", "A 15321-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 34076-2026</t>
+          <t>A 30411-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4224,10 +4232,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46252</v>
+        <v>45827</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4240,16 +4248,16 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4264,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4273,49 +4281,49 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 34076-2026 artfynd.xlsx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 30411-2025 artfynd.xlsx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 34076-2026 karta.png", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 30411-2025 karta.png", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 34076-2026 georefererad karta.tif", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 30411-2025 georefererad karta.tif", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 34076-2026 FSC-klagomål.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 30411-2025 FSC-klagomål.docx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 34076-2026 FSC-klagomål mail.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 30411-2025 FSC-klagomål mail.docx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 34076-2026 tillsynsbegäran.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 30411-2025 tillsynsbegäran.docx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 34076-2026 tillsynsbegäran mail.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 30411-2025 tillsynsbegäran mail.docx", "A 30411-2025")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 37339-2022</t>
+          <t>A 13121-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4325,14 +4333,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44806</v>
+        <v>45002</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4345,16 +4353,16 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4369,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4381,46 +4389,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 37339-2022 artfynd.xlsx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 13121-2023 artfynd.xlsx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 37339-2022 karta.png", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 13121-2023 karta.png", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 37339-2022 georefererad karta.tif", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 13121-2023 georefererad karta.tif", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 37339-2022 FSC-klagomål.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 13121-2023 FSC-klagomål.docx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 37339-2022 FSC-klagomål mail.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 13121-2023 FSC-klagomål mail.docx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 37339-2022 tillsynsbegäran.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 13121-2023 tillsynsbegäran.docx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 37339-2022 tillsynsbegäran mail.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 13121-2023 tillsynsbegäran mail.docx", "A 13121-2023")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8363-2025</t>
+          <t>A 34076-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4434,10 +4442,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45708</v>
+        <v>46252</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4450,17 +4458,17 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
         <v>1</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
@@ -4474,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4483,49 +4491,49 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 8363-2025 artfynd.xlsx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 34076-2026 artfynd.xlsx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 8363-2025 karta.png", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 34076-2026 karta.png", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 8363-2025 georefererad karta.tif", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 34076-2026 georefererad karta.tif", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 8363-2025 FSC-klagomål.docx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 34076-2026 FSC-klagomål.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 8363-2025 FSC-klagomål mail.docx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 34076-2026 FSC-klagomål mail.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 8363-2025 tillsynsbegäran.docx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 34076-2026 tillsynsbegäran.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 8363-2025 tillsynsbegäran mail.docx", "A 8363-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 34076-2026 tillsynsbegäran mail.docx", "A 34076-2026")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17122-2024</t>
+          <t>A 8363-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4535,14 +4543,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45412</v>
+        <v>45708</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4561,10 +4569,10 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4579,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4595,42 +4603,42 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 17122-2024 artfynd.xlsx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 8363-2025 artfynd.xlsx", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 17122-2024 karta.png", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 8363-2025 karta.png", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 17122-2024 georefererad karta.tif", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 8363-2025 georefererad karta.tif", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 17122-2024 FSC-klagomål.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 8363-2025 FSC-klagomål.docx", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 17122-2024 FSC-klagomål mail.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 8363-2025 FSC-klagomål mail.docx", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 17122-2024 tillsynsbegäran.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 8363-2025 tillsynsbegäran.docx", "A 8363-2025")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 17122-2024 tillsynsbegäran mail.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 8363-2025 tillsynsbegäran mail.docx", "A 8363-2025")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 41878-2024</t>
+          <t>A 35077-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4644,10 +4652,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45561</v>
+        <v>45527</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4659,13 +4667,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>15.9</v>
+        <v>2.1</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -4674,10 +4677,10 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>1</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -4692,7 +4695,7 @@
         <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4705,46 +4708,46 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 41878-2024 artfynd.xlsx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 35077-2024 artfynd.xlsx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 41878-2024 karta.png", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 35077-2024 karta.png", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 41878-2024 georefererad karta.tif", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 35077-2024 georefererad karta.tif", "A 35077-2024")</f>
+        <v/>
+      </c>
+      <c r="Z39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/knärot/A 35077-2024 karta knärot.png", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 41878-2024 FSC-klagomål.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 35077-2024 FSC-klagomål.docx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 41878-2024 FSC-klagomål mail.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 35077-2024 FSC-klagomål mail.docx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 41878-2024 tillsynsbegäran.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 35077-2024 tillsynsbegäran.docx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 41878-2024 tillsynsbegäran mail.docx", "A 41878-2024")</f>
-        <v/>
-      </c>
-      <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 41878-2024 prioriterade fågelarter.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 35077-2024 tillsynsbegäran mail.docx", "A 35077-2024")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 35077-2024</t>
+          <t>A 29582-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4758,10 +4761,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45527</v>
+        <v>45484</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4773,20 +4776,25 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -4798,10 +4806,10 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4814,46 +4822,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 35077-2024 artfynd.xlsx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 29582-2024 artfynd.xlsx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 35077-2024 karta.png", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 29582-2024 karta.png", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 35077-2024 georefererad karta.tif", "A 35077-2024")</f>
-        <v/>
-      </c>
-      <c r="Z40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/knärot/A 35077-2024 karta knärot.png", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 29582-2024 georefererad karta.tif", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 35077-2024 FSC-klagomål.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 29582-2024 FSC-klagomål.docx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 35077-2024 FSC-klagomål mail.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 29582-2024 FSC-klagomål mail.docx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 35077-2024 tillsynsbegäran.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 29582-2024 tillsynsbegäran.docx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 35077-2024 tillsynsbegäran mail.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 29582-2024 tillsynsbegäran mail.docx", "A 29582-2024")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19524-2024</t>
+          <t>A 62675-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4863,14 +4867,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45429</v>
+        <v>45271</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4883,16 +4887,16 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -4907,7 +4911,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -4919,43 +4923,39 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19524-2024 artfynd.xlsx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 62675-2023 artfynd.xlsx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19524-2024 karta.png", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 62675-2023 karta.png", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19524-2024 georefererad karta.tif", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 62675-2023 georefererad karta.tif", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19524-2024 FSC-klagomål.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 62675-2023 FSC-klagomål.docx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19524-2024 FSC-klagomål mail.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 62675-2023 FSC-klagomål mail.docx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19524-2024 tillsynsbegäran.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 62675-2023 tillsynsbegäran.docx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19524-2024 tillsynsbegäran mail.docx", "A 19524-2024")</f>
-        <v/>
-      </c>
-      <c r="AE41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 19524-2024 prioriterade fågelarter.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 62675-2023 tillsynsbegäran mail.docx", "A 62675-2023")</f>
         <v/>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
         <v>44484</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>44607</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>44781</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>44509</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44575</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>44795</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>44782</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>44860</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>44494</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44844</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>44838</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44690</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>44734</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44694</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44743</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>44467</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>44509</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>44498</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>44798</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44762</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44620</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>44627</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>44735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>44882</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>44806</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>44494</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>44467</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 2089-2022</t>
+          <t>A 25694-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44577</v>
+        <v>44732</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7048,7 +7048,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 25694-2022</t>
+          <t>A 2089-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44732</v>
+        <v>44577</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7138,7 +7138,7 @@
         <v>44755</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>44760</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>44547</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 5025-2023</t>
+          <t>A 12311-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7354,10 +7354,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44958</v>
+        <v>45378</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7413,7 +7413,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 73901-2021</t>
+          <t>A 37486-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7427,10 +7427,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44552</v>
+        <v>44809</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>8.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7486,7 +7486,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 28228-2024</t>
+          <t>A 20238-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7500,10 +7500,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45477</v>
+        <v>45434</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7559,7 +7559,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17437-2025</t>
+          <t>A 21528-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45757</v>
+        <v>45441</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7632,7 +7632,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 17443-2025</t>
+          <t>A 42557-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7646,10 +7646,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45757</v>
+        <v>44831</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>13.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7705,7 +7705,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 5841-2022</t>
+          <t>A 23189-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44596</v>
+        <v>45450</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7734,8 +7734,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7778,7 +7783,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 73033-2021</t>
+          <t>A 19053-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7792,10 +7797,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44550</v>
+        <v>45427</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7808,7 +7813,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7868,7 +7873,7 @@
         <v>45387</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7924,7 +7929,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 5126-2023</t>
+          <t>A 25840-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7938,10 +7943,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44958</v>
+        <v>45467</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7954,7 +7959,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>14.3</v>
+        <v>2.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7997,7 +8002,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 57236-2023</t>
+          <t>A 28228-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8011,10 +8016,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45245</v>
+        <v>45477</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8027,7 +8032,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8070,7 +8075,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 57237-2023</t>
+          <t>A 59391-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8080,14 +8085,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45245</v>
+        <v>45989</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8100,7 +8105,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>18.2</v>
+        <v>4.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8143,7 +8148,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 5810-2023</t>
+          <t>A 25014-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8157,10 +8162,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44963</v>
+        <v>45461</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8173,7 +8178,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>12.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8216,7 +8221,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 47152-2023</t>
+          <t>A 17081-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8230,10 +8235,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45201</v>
+        <v>45412</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8246,7 +8251,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8289,7 +8294,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 26840-2023</t>
+          <t>A 62682-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8303,10 +8308,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45093</v>
+        <v>45271</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8319,7 +8324,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8362,7 +8367,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 18341-2025</t>
+          <t>A 13289-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8376,10 +8381,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45762</v>
+        <v>45735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8392,7 +8397,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8435,7 +8440,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 58514-2022</t>
+          <t>A 53209-2021</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8449,10 +8454,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44902</v>
+        <v>44468</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8465,7 +8470,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.1</v>
+        <v>11.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8508,7 +8513,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17910-2024</t>
+          <t>A 73310-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8522,10 +8527,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45419</v>
+        <v>44547</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8538,7 +8543,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8581,7 +8586,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 2253-2024</t>
+          <t>A 45467-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8595,10 +8600,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45310</v>
+        <v>44845</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8611,7 +8616,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8654,7 +8659,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 6721-2025</t>
+          <t>A 58705-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8668,10 +8673,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45700</v>
+        <v>45635</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8689,7 +8694,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8732,7 +8737,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 49300-2022</t>
+          <t>A 3054-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8746,10 +8751,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44861</v>
+        <v>46039</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8762,7 +8767,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8805,7 +8810,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 5957-2024</t>
+          <t>A 36644-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8819,10 +8824,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45336</v>
+        <v>45153</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8835,7 +8840,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8878,7 +8883,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 53209-2021</t>
+          <t>A 7922-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8892,10 +8897,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44468</v>
+        <v>44608</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8908,7 +8913,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>11.6</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8951,7 +8956,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 20238-2024</t>
+          <t>A 62905-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8965,10 +8970,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45434</v>
+        <v>45272</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8981,7 +8986,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>13.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9024,7 +9029,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 56219-2023</t>
+          <t>A 5126-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9038,10 +9043,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45240</v>
+        <v>44958</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9054,7 +9059,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>14.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9097,7 +9102,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 680-2024</t>
+          <t>A 44497-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9111,10 +9116,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45300</v>
+        <v>45916</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9127,7 +9132,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9170,7 +9175,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 30339-2022</t>
+          <t>A 10892-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9184,10 +9189,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44760</v>
+        <v>44627</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9200,7 +9205,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9243,7 +9248,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 975-2025</t>
+          <t>A 8732-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9257,10 +9262,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45665</v>
+        <v>46066</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9273,7 +9278,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9316,7 +9321,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 62557-2022</t>
+          <t>A 31362-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9326,14 +9331,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44924</v>
+        <v>45505</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9346,7 +9351,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9389,7 +9394,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 21402-2024</t>
+          <t>A 62557-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9403,10 +9408,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45441</v>
+        <v>44924</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9419,7 +9424,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9462,7 +9467,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 37119-2024</t>
+          <t>A 7991-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9472,14 +9477,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45539</v>
+        <v>45350</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9492,7 +9497,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>6.7</v>
+        <v>1.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9535,7 +9540,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 53138-2023</t>
+          <t>A 27218-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9549,10 +9554,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45229</v>
+        <v>45096</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9565,7 +9570,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9608,7 +9613,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 19566-2023</t>
+          <t>A 36420-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9622,10 +9627,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45049</v>
+        <v>45152</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9638,7 +9643,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9681,7 +9686,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 29762-2023</t>
+          <t>A 47507-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9695,10 +9700,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45107</v>
+        <v>45930</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9711,7 +9716,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9754,7 +9759,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 8364-2025</t>
+          <t>A 12283-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9768,10 +9773,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45708</v>
+        <v>46087</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9784,7 +9789,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9827,7 +9832,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 29736-2023</t>
+          <t>A 5810-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9841,10 +9846,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45107</v>
+        <v>44963</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9857,7 +9862,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9900,7 +9905,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 62896-2023</t>
+          <t>A 49507-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9914,10 +9919,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45272</v>
+        <v>45939</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9930,7 +9935,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>13.8</v>
+        <v>5.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9973,7 +9978,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 69847-2021</t>
+          <t>A 5236-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9987,10 +9992,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44532</v>
+        <v>44956</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10003,7 +10008,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10046,7 +10051,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 58705-2024</t>
+          <t>A 14688-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10056,14 +10061,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45635</v>
+        <v>46101</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10075,13 +10080,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10124,7 +10124,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 22347-2023</t>
+          <t>A 51509-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10134,14 +10134,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45070</v>
+        <v>45950</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 37515-2025</t>
+          <t>A 62947-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10211,10 +10211,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45877</v>
+        <v>45272</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10270,7 +10270,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 59617-2025</t>
+          <t>A 15543-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45992</v>
+        <v>46106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10343,7 +10343,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 37495-2025</t>
+          <t>A 15549-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10357,10 +10357,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45877</v>
+        <v>46106</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10416,7 +10416,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 37517-2025</t>
+          <t>A 7993-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10430,10 +10430,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45877</v>
+        <v>45350</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10489,7 +10489,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 29256-2025</t>
+          <t>A 52700-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10503,10 +10503,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45824</v>
+        <v>45956</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10562,7 +10562,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 614-2026</t>
+          <t>A 33081-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10576,10 +10576,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46024</v>
+        <v>44785</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10635,7 +10635,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 42143-2025</t>
+          <t>A 52699-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10649,10 +10649,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45904</v>
+        <v>45956</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10708,7 +10708,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 33081-2022</t>
+          <t>A 29762-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10722,10 +10722,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44785</v>
+        <v>45107</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10781,7 +10781,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 25840-2024</t>
+          <t>A 29736-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10795,10 +10795,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45467</v>
+        <v>45107</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10854,7 +10854,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 37676-2023</t>
+          <t>A 58747-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10864,14 +10864,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45159</v>
+        <v>45986</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10927,7 +10927,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 6751-2025</t>
+          <t>A 17399-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10941,10 +10941,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45700</v>
+        <v>45757</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11000,7 +11000,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 44497-2025</t>
+          <t>A 58751-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11014,10 +11014,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45916</v>
+        <v>45986</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11090,7 +11090,7 @@
         <v>45217</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 34580-2022</t>
+          <t>A 17910-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11160,10 +11160,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44795</v>
+        <v>45419</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.9</v>
+        <v>6.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11219,7 +11219,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 12000-2022</t>
+          <t>A 29256-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11233,10 +11233,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44635</v>
+        <v>45824</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11292,7 +11292,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 42557-2022</t>
+          <t>A 8361-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11306,10 +11306,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44831</v>
+        <v>45708</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>13.7</v>
+        <v>2.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11365,7 +11365,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 35253-2022</t>
+          <t>A 21248-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11379,10 +11379,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44797</v>
+        <v>44705</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>12.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11438,7 +11438,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 20784-2025</t>
+          <t>A 31964-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11452,10 +11452,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45776</v>
+        <v>45107</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>9.5</v>
+        <v>2.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11511,7 +11511,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 47507-2025</t>
+          <t>A 35253-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11525,10 +11525,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45930</v>
+        <v>44797</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11584,7 +11584,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 13820-2024</t>
+          <t>A 42143-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11598,10 +11598,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45390</v>
+        <v>45904</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>7.2</v>
+        <v>2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11657,7 +11657,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 17565-2025</t>
+          <t>A 60656-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11671,10 +11671,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45757</v>
+        <v>45996</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11730,7 +11730,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 31362-2024</t>
+          <t>A 40522-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11740,14 +11740,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45505</v>
+        <v>45896</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11803,7 +11803,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 40524-2025</t>
+          <t>A 5214-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11817,10 +11817,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45896</v>
+        <v>45691</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11876,7 +11876,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 21248-2022</t>
+          <t>A 29426-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11890,10 +11890,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44705</v>
+        <v>44753</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11905,8 +11905,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>12.4</v>
+        <v>14.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11949,7 +11954,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 40522-2025</t>
+          <t>A 30339-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11963,10 +11968,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45896</v>
+        <v>44760</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11979,7 +11984,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12022,7 +12027,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 49507-2025</t>
+          <t>A 6751-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12036,10 +12041,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45939</v>
+        <v>45700</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12052,7 +12057,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12095,7 +12100,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 51509-2025</t>
+          <t>A 975-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12105,14 +12110,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45950</v>
+        <v>45665</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12125,7 +12130,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12168,7 +12173,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 3065-2024</t>
+          <t>A 63919-2021</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12182,10 +12187,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45316</v>
+        <v>44509</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12198,7 +12203,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12241,7 +12246,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 17081-2024</t>
+          <t>A 20784-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12255,10 +12260,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45412</v>
+        <v>45776</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12271,7 +12276,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.8</v>
+        <v>9.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12314,7 +12319,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 52699-2025</t>
+          <t>A 614-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12328,10 +12333,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45956</v>
+        <v>46024</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12344,7 +12349,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12387,7 +12392,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 7993-2024</t>
+          <t>A 9144-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12401,10 +12406,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45350</v>
+        <v>45358</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12417,7 +12422,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12460,7 +12465,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 52700-2025</t>
+          <t>A 29260-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12474,10 +12479,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45956</v>
+        <v>45824</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12490,7 +12495,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12533,7 +12538,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 45467-2022</t>
+          <t>A 40524-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12547,10 +12552,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44845</v>
+        <v>45896</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12563,7 +12568,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12606,7 +12611,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 5011-2024</t>
+          <t>A 59617-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12620,10 +12625,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45329</v>
+        <v>45992</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12636,7 +12641,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>22</v>
+        <v>1.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12679,7 +12684,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 53137-2023</t>
+          <t>A 31561-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12693,10 +12698,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45229</v>
+        <v>45117</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12709,7 +12714,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12752,7 +12757,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 5214-2025</t>
+          <t>A 30563-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12766,10 +12771,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45691</v>
+        <v>45831</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12782,7 +12787,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12825,7 +12830,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 9144-2024</t>
+          <t>A 33948-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12839,10 +12844,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45358</v>
+        <v>45124</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12855,7 +12860,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12898,7 +12903,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 62682-2023</t>
+          <t>A 27222-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12912,10 +12917,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45271</v>
+        <v>45096</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12928,7 +12933,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12971,7 +12976,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 31561-2023</t>
+          <t>A 17972-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12985,10 +12990,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45117</v>
+        <v>45761</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13001,7 +13006,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13044,7 +13049,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 4982-2024</t>
+          <t>A 62896-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13058,10 +13063,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45329</v>
+        <v>45272</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13074,7 +13079,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.6</v>
+        <v>13.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13117,7 +13122,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 62947-2023</t>
+          <t>A 6938-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13127,14 +13132,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45272</v>
+        <v>45343</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13147,7 +13152,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13190,7 +13195,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 31930-2024</t>
+          <t>A 22406-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13200,14 +13205,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45510</v>
+        <v>46154</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13220,7 +13225,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13263,7 +13268,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 58751-2025</t>
+          <t>A 26829-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13277,10 +13282,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45986</v>
+        <v>45093</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13293,7 +13298,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13336,7 +13341,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 71706-2021</t>
+          <t>A 13895-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13350,10 +13355,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44543</v>
+        <v>45391</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13365,8 +13370,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13409,7 +13419,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 40935-2022</t>
+          <t>A 26815-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13419,14 +13429,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44823</v>
+        <v>45093</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13438,13 +13448,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13487,7 +13492,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 58747-2025</t>
+          <t>A 32327-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13501,10 +13506,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45986</v>
+        <v>45836</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13517,7 +13522,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13560,7 +13565,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 6938-2024</t>
+          <t>A 39334-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13570,14 +13575,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45343</v>
+        <v>45889</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13590,7 +13595,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13633,7 +13638,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 60656-2025</t>
+          <t>A 3779-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13647,10 +13652,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45996</v>
+        <v>45681</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13662,8 +13667,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>BillerudKorsnäs AB</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>2.5</v>
+        <v>7.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13706,7 +13716,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 22406-2026</t>
+          <t>A 71903-2021</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13720,10 +13730,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46154</v>
+        <v>44543</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13736,7 +13746,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13779,7 +13789,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 14306-2023</t>
+          <t>A 17565-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13793,10 +13803,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45011</v>
+        <v>45757</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13809,7 +13819,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13852,7 +13862,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 17972-2025</t>
+          <t>A 25443-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13866,10 +13876,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45761</v>
+        <v>45089</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13882,7 +13892,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13925,7 +13935,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 27222-2023</t>
+          <t>A 14306-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13939,10 +13949,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45096</v>
+        <v>45011</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13955,7 +13965,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13998,7 +14008,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 59391-2025</t>
+          <t>A 23702-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14008,14 +14018,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45989</v>
+        <v>46164</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14027,8 +14037,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14071,7 +14086,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 36644-2023</t>
+          <t>A 5025-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14085,10 +14100,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45153</v>
+        <v>44958</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14101,7 +14116,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14144,7 +14159,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 8788-2024</t>
+          <t>A 31974-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14158,10 +14173,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45356</v>
+        <v>45107</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14174,7 +14189,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14217,7 +14232,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 71903-2021</t>
+          <t>A 23733-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14231,10 +14246,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44543</v>
+        <v>46164</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14246,8 +14261,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>6.3</v>
+        <v>0.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14290,7 +14310,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 62554-2022</t>
+          <t>A 23757-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14304,10 +14324,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44924</v>
+        <v>46164</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14320,7 +14340,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14363,7 +14383,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 3779-2025</t>
+          <t>A 5957-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14377,10 +14397,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45681</v>
+        <v>45336</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14392,13 +14412,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>BillerudKorsnäs AB</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>7.6</v>
+        <v>2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14441,7 +14456,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 21528-2024</t>
+          <t>A 8359-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14455,10 +14470,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45441</v>
+        <v>45708</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14471,7 +14486,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14514,7 +14529,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 20954-2023</t>
+          <t>A 23945-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14528,10 +14543,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45061</v>
+        <v>46167</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14543,8 +14558,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14587,7 +14607,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 39334-2025</t>
+          <t>A 35425-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14601,10 +14621,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45889</v>
+        <v>45855</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14617,7 +14637,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14660,7 +14680,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 3054-2026</t>
+          <t>A 2253-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14674,10 +14694,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46039</v>
+        <v>45310</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14690,7 +14710,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14733,7 +14753,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 10892-2022</t>
+          <t>A 4870-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14747,10 +14767,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44627</v>
+        <v>45329</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14763,7 +14783,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.4</v>
+        <v>8.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14806,7 +14826,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 29426-2022</t>
+          <t>A 69847-2021</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14820,10 +14840,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44753</v>
+        <v>44532</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14835,13 +14855,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>14.4</v>
+        <v>1.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14884,7 +14899,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 23733-2026</t>
+          <t>A 58514-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14898,10 +14913,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46164</v>
+        <v>44902</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14913,13 +14928,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14962,7 +14972,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 23945-2026</t>
+          <t>A 24754-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14976,10 +14986,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46167</v>
+        <v>46171</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14991,13 +15001,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15040,7 +15045,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 23757-2026</t>
+          <t>A 71706-2021</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15054,10 +15059,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46164</v>
+        <v>44543</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15070,7 +15075,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15113,7 +15118,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 23702-2026</t>
+          <t>A 47152-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15127,10 +15132,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46164</v>
+        <v>45201</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15142,13 +15147,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15191,7 +15191,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 44048-2023</t>
+          <t>A 26015-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15201,14 +15201,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45188</v>
+        <v>46181</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15220,8 +15220,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15264,7 +15269,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 62905-2023</t>
+          <t>A 53138-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15278,10 +15283,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45272</v>
+        <v>45229</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15294,7 +15299,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>13.8</v>
+        <v>3.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15337,7 +15342,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 37486-2022</t>
+          <t>A 16772-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15351,10 +15356,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44809</v>
+        <v>45411</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15367,7 +15372,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>8.6</v>
+        <v>0.7</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15410,7 +15415,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 46299-2022</t>
+          <t>A 66056-2021</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15424,10 +15429,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44847</v>
+        <v>44517</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15440,7 +15445,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15483,7 +15488,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 8732-2026</t>
+          <t>A 3065-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15497,10 +15502,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46066</v>
+        <v>45316</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15513,7 +15518,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>6.1</v>
+        <v>0.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15556,7 +15561,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 5236-2023</t>
+          <t>A 12082-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15570,10 +15575,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44956</v>
+        <v>45377</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15586,7 +15591,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15629,7 +15634,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 56220-2023</t>
+          <t>A 12084-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15643,10 +15648,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45240</v>
+        <v>45377</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15659,7 +15664,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15702,7 +15707,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 972-2025</t>
+          <t>A 11103-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15716,10 +15721,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45665</v>
+        <v>44628</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15732,7 +15737,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15775,7 +15780,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 24754-2026</t>
+          <t>A 20954-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15789,10 +15794,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46171</v>
+        <v>45061</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15805,7 +15810,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15848,7 +15853,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 12283-2026</t>
+          <t>A 37517-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15862,10 +15867,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46087</v>
+        <v>45877</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15878,7 +15883,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15921,7 +15926,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 13895-2024</t>
+          <t>A 28513-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15935,10 +15940,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45391</v>
+        <v>46197</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15950,13 +15955,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15999,7 +15999,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 29724-2023</t>
+          <t>A 17443-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16009,14 +16009,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45107</v>
+        <v>45757</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16072,7 +16072,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 31974-2023</t>
+          <t>A 37515-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16086,10 +16086,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45107</v>
+        <v>45877</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 14688-2026</t>
+          <t>A 37495-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16155,14 +16155,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46101</v>
+        <v>45877</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16218,7 +16218,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 26015-2026</t>
+          <t>A 32302-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16228,14 +16228,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46181</v>
+        <v>45512</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16249,11 +16249,11 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16296,7 +16296,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 19802-2024</t>
+          <t>A 29205-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16310,10 +16310,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45432</v>
+        <v>46202</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16325,13 +16325,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16374,7 +16369,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 15549-2026</t>
+          <t>A 29222-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16388,10 +16383,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46106</v>
+        <v>46202</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16404,7 +16399,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16447,7 +16442,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 15543-2026</t>
+          <t>A 20369-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16461,10 +16456,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46106</v>
+        <v>45435</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16477,7 +16472,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16520,7 +16515,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 16635-2024</t>
+          <t>A 11601-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16534,10 +16529,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45408</v>
+        <v>45727</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16550,7 +16545,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16593,7 +16588,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 7922-2022</t>
+          <t>A 29191-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16607,10 +16602,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44608</v>
+        <v>46202</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16623,7 +16618,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16666,7 +16661,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 1556-2025</t>
+          <t>A 4976-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16680,10 +16675,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45670</v>
+        <v>45329</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16696,7 +16691,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.8</v>
+        <v>5.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16739,7 +16734,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 12311-2024</t>
+          <t>A 12175-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16753,10 +16748,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45378</v>
+        <v>45377</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16769,7 +16764,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2</v>
+        <v>5.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16812,7 +16807,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 33948-2023</t>
+          <t>A 30527-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16826,10 +16821,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45124</v>
+        <v>44762</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16842,7 +16837,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16885,7 +16880,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 13320-2024</t>
+          <t>A 22347-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16899,10 +16894,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45386</v>
+        <v>45070</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16915,7 +16910,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16958,7 +16953,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 55227-2023</t>
+          <t>A 56220-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16972,10 +16967,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45231</v>
+        <v>45240</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16988,7 +16983,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17031,7 +17026,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 25014-2024</t>
+          <t>A 56219-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17045,10 +17040,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45461</v>
+        <v>45240</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17061,7 +17056,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>12.8</v>
+        <v>1.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17104,7 +17099,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 31964-2023</t>
+          <t>A 6721-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17118,10 +17113,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45107</v>
+        <v>45700</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17133,8 +17128,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>2.3</v>
+        <v>5.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17177,7 +17177,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 12082-2024</t>
+          <t>A 34538-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17191,10 +17191,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45377</v>
+        <v>46255</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17250,7 +17250,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 12084-2024</t>
+          <t>A 31034-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17264,10 +17264,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45377</v>
+        <v>46214</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17323,7 +17323,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 28513-2026</t>
+          <t>A 17437-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17337,10 +17337,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46197</v>
+        <v>45757</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17396,7 +17396,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 11103-2022</t>
+          <t>A 5841-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17410,10 +17410,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44628</v>
+        <v>44596</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17469,7 +17469,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 29205-2026</t>
+          <t>A 12000-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17483,10 +17483,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46202</v>
+        <v>44635</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17542,7 +17542,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 4976-2024</t>
+          <t>A 40935-2022</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17552,14 +17552,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45329</v>
+        <v>44823</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17571,8 +17571,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17615,7 +17620,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 29222-2026</t>
+          <t>A 36646-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17629,10 +17634,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46202</v>
+        <v>45153</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17645,7 +17650,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17688,7 +17693,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 64304-2023</t>
+          <t>A 29724-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17698,14 +17703,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45280</v>
+        <v>45107</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17718,7 +17723,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17761,7 +17766,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 48553-2023</t>
+          <t>A 8362-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17775,10 +17780,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45208</v>
+        <v>45708</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17791,7 +17796,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.7</v>
+        <v>7.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17834,7 +17839,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 26815-2023</t>
+          <t>A 972-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17848,10 +17853,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45093</v>
+        <v>45665</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17907,7 +17912,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 29191-2026</t>
+          <t>A 49300-2022</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17921,10 +17926,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46202</v>
+        <v>44861</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17937,7 +17942,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17980,7 +17985,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 16772-2024</t>
+          <t>A 16635-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17994,10 +17999,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45411</v>
+        <v>45408</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18053,7 +18058,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 25443-2023</t>
+          <t>A 37676-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18063,14 +18068,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45089</v>
+        <v>45159</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18083,7 +18088,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18126,7 +18131,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 32302-2024</t>
+          <t>A 53137-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18140,10 +18145,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45512</v>
+        <v>45229</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18155,13 +18160,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18204,7 +18204,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 66056-2021</t>
+          <t>A 31559-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18218,10 +18218,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44517</v>
+        <v>46224</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18277,7 +18277,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 23189-2024</t>
+          <t>A 8788-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18291,10 +18291,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45450</v>
+        <v>45356</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18306,13 +18306,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18355,7 +18350,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 7991-2024</t>
+          <t>A 680-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18365,14 +18360,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45350</v>
+        <v>45300</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18385,7 +18380,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18428,7 +18423,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 59542-2022</t>
+          <t>A 46299-2022</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18442,10 +18437,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44907</v>
+        <v>44847</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18458,7 +18453,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18501,7 +18496,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 52848-2021</t>
+          <t>A 62554-2022</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18515,10 +18510,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44467</v>
+        <v>44924</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18531,7 +18526,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18574,7 +18569,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 8361-2025</t>
+          <t>A 37221-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18588,10 +18583,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45708</v>
+        <v>46274</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18647,7 +18642,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 34538-2026</t>
+          <t>A 37243-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18661,10 +18656,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46255</v>
+        <v>46274</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18677,7 +18672,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>3.3</v>
+        <v>13.9</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18720,7 +18715,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 31034-2026</t>
+          <t>A 57236-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18734,10 +18729,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46214</v>
+        <v>45245</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18750,7 +18745,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18793,7 +18788,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 73310-2021</t>
+          <t>A 57237-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18807,10 +18802,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44547</v>
+        <v>45245</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18823,7 +18818,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>6.2</v>
+        <v>18.2</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18866,7 +18861,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 71781-2021</t>
+          <t>A 29577-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18880,10 +18875,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44539</v>
+        <v>45484</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18901,7 +18896,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>7</v>
+        <v>10.1</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18944,7 +18939,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 8362-2025</t>
+          <t>A 27443-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18958,10 +18953,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45708</v>
+        <v>45474</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18974,7 +18969,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>7.7</v>
+        <v>1.8</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -19017,7 +19012,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 30527-2022</t>
+          <t>A 32959-2022</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -19031,10 +19026,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>44762</v>
+        <v>44784</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19047,7 +19042,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -19090,7 +19085,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 17573-2025</t>
+          <t>A 13320-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -19104,10 +19099,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45757</v>
+        <v>45386</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19120,7 +19115,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -19163,7 +19158,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 31559-2026</t>
+          <t>A 38517-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -19177,10 +19172,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46224</v>
+        <v>45546</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19193,7 +19188,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -19236,7 +19231,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 9837-2023</t>
+          <t>A 37119-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19250,10 +19245,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>44984</v>
+        <v>45539</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19266,7 +19261,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.6</v>
+        <v>6.7</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19309,7 +19304,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 19753-2024</t>
+          <t>A 19802-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19326,7 +19321,7 @@
         <v>45432</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19338,8 +19333,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I237" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19382,7 +19382,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 27443-2024</t>
+          <t>A 34580-2022</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19396,10 +19396,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45474</v>
+        <v>44795</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19455,7 +19455,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 32959-2022</t>
+          <t>A 32942-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19469,10 +19469,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44784</v>
+        <v>46244</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19528,7 +19528,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 30914-2023</t>
+          <t>A 19566-2023</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19542,10 +19542,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45113</v>
+        <v>45049</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19601,7 +19601,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 20369-2024</t>
+          <t>A 7272-2022</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19615,10 +19615,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45435</v>
+        <v>44606</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 7272-2022</t>
+          <t>A 22822-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19688,10 +19688,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>44606</v>
+        <v>45448</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19747,7 +19747,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 26829-2023</t>
+          <t>A 59542-2022</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19761,10 +19761,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45093</v>
+        <v>44907</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19820,7 +19820,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 38517-2024</t>
+          <t>A 21402-2024</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19834,10 +19834,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45546</v>
+        <v>45441</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 37221-2026</t>
+          <t>A 71781-2021</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19907,10 +19907,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46274</v>
+        <v>44539</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19922,8 +19922,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I245" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19966,7 +19971,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 37243-2026</t>
+          <t>A 31930-2024</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19976,14 +19981,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46274</v>
+        <v>45510</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19996,7 +20001,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>13.9</v>
+        <v>0.6</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -20039,7 +20044,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 63919-2021</t>
+          <t>A 73901-2021</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -20053,10 +20058,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>44509</v>
+        <v>44552</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20069,7 +20074,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>5.2</v>
+        <v>1.9</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -20112,7 +20117,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 4870-2024</t>
+          <t>A 26840-2023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -20126,10 +20131,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45329</v>
+        <v>45093</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20142,7 +20147,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>8.4</v>
+        <v>1.1</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -20185,7 +20190,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 36646-2023</t>
+          <t>A 13820-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -20199,10 +20204,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45153</v>
+        <v>45390</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20215,7 +20220,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>2.4</v>
+        <v>7.2</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -20258,7 +20263,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 22822-2024</t>
+          <t>A 5011-2024</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -20272,10 +20277,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45448</v>
+        <v>45329</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20288,7 +20293,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>1.3</v>
+        <v>22</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -20331,7 +20336,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 19053-2024</t>
+          <t>A 18341-2025</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20345,10 +20350,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45427</v>
+        <v>45762</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20361,7 +20366,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20404,7 +20409,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 11601-2025</t>
+          <t>A 52848-2021</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20418,10 +20423,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45727</v>
+        <v>44467</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20434,7 +20439,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20477,7 +20482,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 12175-2024</t>
+          <t>A 19753-2024</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20491,10 +20496,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45377</v>
+        <v>45432</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20507,7 +20512,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20550,7 +20555,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 29577-2024</t>
+          <t>A 4982-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20564,10 +20569,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45484</v>
+        <v>45329</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20579,13 +20584,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I254" t="n">
-        <v>10.1</v>
+        <v>1.6</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20628,7 +20628,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 8370-2023</t>
+          <t>A 55227-2023</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20642,10 +20642,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>44977</v>
+        <v>45231</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20701,7 +20701,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 12217-2025</t>
+          <t>A 9837-2023</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20715,10 +20715,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45729</v>
+        <v>44984</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>4.6</v>
+        <v>0.6</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20774,7 +20774,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 32942-2026</t>
+          <t>A 1556-2025</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20788,10 +20788,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>46244</v>
+        <v>45670</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 22133-2025</t>
+          <t>A 73033-2021</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20861,10 +20861,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45785</v>
+        <v>44550</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20920,7 +20920,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 22537-2025</t>
+          <t>A 64304-2023</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20930,14 +20930,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45787</v>
+        <v>45280</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20993,7 +20993,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 13289-2025</t>
+          <t>A 8364-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -21007,10 +21007,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45735</v>
+        <v>45708</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21023,7 +21023,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -21066,7 +21066,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 27218-2023</t>
+          <t>A 48553-2023</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45096</v>
+        <v>45208</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -21139,7 +21139,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 36420-2023</t>
+          <t>A 17573-2025</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -21153,10 +21153,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45152</v>
+        <v>45757</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -21212,7 +21212,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 17399-2025</t>
+          <t>A 44048-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -21226,10 +21226,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45757</v>
+        <v>45188</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 29260-2025</t>
+          <t>A 30914-2023</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -21299,10 +21299,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45824</v>
+        <v>45113</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -21358,7 +21358,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 30563-2025</t>
+          <t>A 8370-2023</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21372,10 +21372,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45831</v>
+        <v>44977</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -21431,7 +21431,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 32327-2025</t>
+          <t>A 12217-2025</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21445,10 +21445,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45836</v>
+        <v>45729</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -21504,7 +21504,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 8359-2025</t>
+          <t>A 22133-2025</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21518,10 +21518,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45708</v>
+        <v>45785</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21577,7 +21577,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 35425-2025</t>
+          <t>A 22537-2025</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21587,14 +21587,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45855</v>
+        <v>45787</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21667,7 +21667,7 @@
         <v>45099</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>45272</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45846</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>45973</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>46035</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>

--- a/Översikt GRUMS.xlsx
+++ b/Översikt GRUMS.xlsx
@@ -601,7 +601,7 @@
         <v>44978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45343</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44788</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44498</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44819</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45615</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>46252</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>44981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45099</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>45898</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45078</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>44517</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>44593</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>44470</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>44890</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45245</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>45706</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>45099</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>44901</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44494</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>44588</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>44470</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>44792</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44806</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45368</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>45561</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>45412</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>45929</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>46087</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>45429</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>45427</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>45019</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>45827</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>45002</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>46252</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>45708</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>45527</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45484</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>45271</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>44484</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>44607</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>44781</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>44509</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44575</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>44795</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>44782</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>44860</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>44494</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44844</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>44838</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44690</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>44734</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44694</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44743</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>44467</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>44509</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>44498</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>44798</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44762</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44620</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>44627</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>44735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>44882</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>44806</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>44494</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>44467</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>44732</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>44577</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>44755</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>44760</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>44547</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>45378</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>44809</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>45434</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>45441</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>44831</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>45450</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>45427</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>45387</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>45467</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>45477</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>45989</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>45461</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>45412</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>45271</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>45735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>44468</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>44547</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>44845</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>45635</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>46039</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>45153</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>44608</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>45272</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>44958</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>45916</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>44627</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>46066</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45505</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>44924</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>45350</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>45096</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>45152</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>45930</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>46087</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>44963</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>45939</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>44956</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>46101</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>45950</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>45272</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>46106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>46106</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10433,7 +10433,7 @@
         <v>45350</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>45956</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>44785</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>45956</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>45107</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>45107</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>45986</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>45757</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>45986</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>45217</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>45419</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>45824</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>45708</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>44705</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>45107</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>44797</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>45904</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>45996</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11747,7 +11747,7 @@
         <v>45896</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>45691</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>44753</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>44760</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>45700</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>45665</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>44509</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>45776</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>46024</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>45358</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>45824</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         <v>45896</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>45992</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>45117</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>45831</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>45124</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>45096</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>45761</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13066,7 +13066,7 @@
         <v>45272</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
         <v>45343</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>46154</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>45093</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>45391</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>45093</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>45836</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>45889</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>45681</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>44543</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>45757</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>45089</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>45011</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>46164</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>44958</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14176,7 +14176,7 @@
         <v>45107</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>46164</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>46164</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>45336</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>45708</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>46167</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>45855</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>45310</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>45329</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>44532</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>44902</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>46171</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44543</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>45201</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>46181</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>45229</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>45411</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44517</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         <v>45316</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>45377</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>45377</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>44628</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>45061</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45877</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>46197</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>45757</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>45877</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>45877</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>45512</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>46202</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>46202</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>45435</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>45727</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>46202</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>45329</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>45377</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>44762</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>45070</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16970,7 +16970,7 @@
         <v>45240</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>45240</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>45700</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>46255</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>46214</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>45757</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>44596</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>44635</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>44823</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>45153</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>45107</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>45708</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>45665</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>44861</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>45408</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45159</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>45229</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>46224</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45356</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45300</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>44847</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>44924</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>46274</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>46274</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>45245</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>45245</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>45484</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>45474</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>44784</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>45386</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>45546</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>45539</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>45432</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>44795</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>46244</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>45049</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>44606</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19691,7 +19691,7 @@
         <v>45448</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>44907</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>45441</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44539</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>45510</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>44552</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>45093</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45390</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>45329</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>45762</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>44467</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>45432</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>45329</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         <v>45231</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>44984</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>45670</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>44550</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>45280</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21010,7 +21010,7 @@
         <v>45708</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>45208</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>45757</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45188</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>45113</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>44977</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>45729</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>45785</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>45787</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>45099</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>45272</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45846</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>45973</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>46035</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>

--- a/Översikt GRUMS.xlsx
+++ b/Översikt GRUMS.xlsx
@@ -601,7 +601,7 @@
         <v>44978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45343</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44788</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44498</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44819</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45615</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>46252</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>44981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45099</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>45898</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45078</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>44517</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>44593</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>44470</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>44890</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45245</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>45706</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>45099</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>44901</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44494</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>44588</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>44470</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>44792</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44806</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45368</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>45561</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>45412</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>45929</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>46087</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>45429</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>45427</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>45019</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>45827</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>45002</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>46252</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>45708</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>45527</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45484</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>45271</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>44484</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>44607</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>44781</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>44509</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44575</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>44795</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>44782</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>44860</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>44494</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44844</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>44838</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44690</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>44734</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44694</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44743</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>44467</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>44509</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>44498</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>44798</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44762</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44620</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>44627</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>44735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>44882</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>44806</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>44494</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>44467</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>44732</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>44577</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>44755</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>44760</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>44547</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>45378</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>44809</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>45434</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>45441</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>44831</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>45450</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>45427</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>45387</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>45467</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>45477</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>45989</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>45461</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>45412</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>45271</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>45735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>44468</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>44547</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>44845</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>45635</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>46039</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>45153</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>44608</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>45272</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>44958</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>45916</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>44627</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>46066</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45505</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>44924</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>45350</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>45096</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>45152</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>45930</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>46087</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>44963</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>45939</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>44956</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>46101</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>45950</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>45272</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>46106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>46106</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10433,7 +10433,7 @@
         <v>45350</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>45956</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>44785</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>45956</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>45107</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>45107</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>45986</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>45757</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>45986</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>45217</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>45419</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>45824</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>45708</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>44705</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>45107</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>44797</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>45904</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>45996</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11747,7 +11747,7 @@
         <v>45896</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>45691</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>44753</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>44760</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>45700</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>45665</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>44509</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>45776</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>46024</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>45358</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>45824</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         <v>45896</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>45992</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>45117</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>45831</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>45124</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>45096</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>45761</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13066,7 +13066,7 @@
         <v>45272</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
         <v>45343</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>46154</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>45093</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>45391</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>45093</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>45836</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>45889</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>45681</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>44543</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>45757</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>45089</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>45011</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>46164</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>44958</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14176,7 +14176,7 @@
         <v>45107</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>46164</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>46164</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>45336</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>45708</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>46167</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>45855</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>45310</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>45329</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>44532</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>44902</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>46171</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44543</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>45201</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>46181</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>45229</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>45411</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44517</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         <v>45316</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>45377</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>45377</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>44628</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>45061</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45877</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>46197</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>45757</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>45877</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>45877</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>45512</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>46202</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>46202</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>45435</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>45727</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>46202</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>45329</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>45377</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>44762</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>45070</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16970,7 +16970,7 @@
         <v>45240</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>45240</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>45700</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>46255</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>46214</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>45757</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>44596</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>44635</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>44823</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>45153</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>45107</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>45708</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>45665</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>44861</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>45408</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45159</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>45229</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>46224</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45356</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45300</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>44847</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>44924</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>46274</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>46274</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>45245</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>45245</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>45484</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>45474</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>44784</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>45386</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>45546</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>45539</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>45432</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>44795</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>46244</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>45049</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>44606</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19691,7 +19691,7 @@
         <v>45448</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>44907</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>45441</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44539</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>45510</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>44552</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>45093</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45390</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>45329</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>45762</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>44467</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>45432</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>45329</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         <v>45231</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>44984</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>45670</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>44550</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>45280</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21010,7 +21010,7 @@
         <v>45708</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>45208</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>45757</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45188</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>45113</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>44977</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>45729</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>45785</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>45787</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>45099</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>45272</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45846</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>45973</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>46035</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>

--- a/Översikt GRUMS.xlsx
+++ b/Översikt GRUMS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE270"/>
+  <dimension ref="A1:AE269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45343</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44788</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44498</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44819</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45615</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>46252</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>44981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45099</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>45898</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45078</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 5280-2022</t>
+          <t>A 66053-2021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44593</v>
+        <v>44517</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1972,19 +1972,14 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>37.1</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1993,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2002,169 +1997,174 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Bronshjon</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 66053-2021 artfynd.xlsx", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 66053-2021 karta.png", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 66053-2021 georefererad karta.tif", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 66053-2021 FSC-klagomål.docx", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 66053-2021 FSC-klagomål mail.docx", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 66053-2021 tillsynsbegäran.docx", "A 66053-2021")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 66053-2021 tillsynsbegäran mail.docx", "A 66053-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 5280-2022</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44593</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
         <v>4</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>1</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Ask
 Tjäder</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 5280-2022 artfynd.xlsx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 5280-2022 karta.png", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 5280-2022 georefererad karta.tif", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 5280-2022 FSC-klagomål.docx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 5280-2022 FSC-klagomål mail.docx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 5280-2022 tillsynsbegäran.docx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 5280-2022 tillsynsbegäran mail.docx", "A 5280-2022")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 5280-2022 prioriterade fågelarter.docx", "A 5280-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 66053-2021</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44517</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>6</v>
-      </c>
-      <c r="U15" t="n">
-        <v>6</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Bronshjon</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 66053-2021 artfynd.xlsx", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 66053-2021 karta.png", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 66053-2021 georefererad karta.tif", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 66053-2021 FSC-klagomål.docx", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 66053-2021 FSC-klagomål mail.docx", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 66053-2021 tillsynsbegäran.docx", "A 66053-2021")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 66053-2021 tillsynsbegäran mail.docx", "A 66053-2021")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57233-2023</t>
+          <t>A 54042-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45245</v>
+        <v>44470</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2194,16 +2194,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>7.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2218,7 +2218,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2227,370 +2227,370 @@
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 54042-2021 artfynd.xlsx", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 54042-2021 karta.png", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 54042-2021 georefererad karta.tif", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 54042-2021 FSC-klagomål.docx", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 54042-2021 FSC-klagomål mail.docx", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 54042-2021 tillsynsbegäran.docx", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 54042-2021 tillsynsbegäran mail.docx", "A 54042-2021")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 54042-2021 prioriterade fågelarter.docx", "A 54042-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 56386-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44890</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Vågfibbla
+Rönnfibbla</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 56386-2022 artfynd.xlsx", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 56386-2022 karta.png", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 56386-2022 georefererad karta.tif", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 56386-2022 FSC-klagomål.docx", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 56386-2022 FSC-klagomål mail.docx", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 56386-2022 tillsynsbegäran.docx", "A 56386-2022")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 56386-2022 tillsynsbegäran mail.docx", "A 56386-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 57233-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45245</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
         <v>6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" t="n">
         <v>6</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin
 Skogsklocka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 57233-2023 artfynd.xlsx", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 57233-2023 karta.png", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 57233-2023 georefererad karta.tif", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 57233-2023 FSC-klagomål.docx", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 57233-2023 FSC-klagomål mail.docx", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 57233-2023 tillsynsbegäran.docx", "A 57233-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 57233-2023 tillsynsbegäran mail.docx", "A 57233-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 54042-2021</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44470</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J17" t="n">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 7931-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45706</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 54042-2021 artfynd.xlsx", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 54042-2021 karta.png", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 54042-2021 georefererad karta.tif", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 54042-2021 FSC-klagomål.docx", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 54042-2021 FSC-klagomål mail.docx", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 54042-2021 tillsynsbegäran.docx", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 54042-2021 tillsynsbegäran mail.docx", "A 54042-2021")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 54042-2021 prioriterade fågelarter.docx", "A 54042-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 7931-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45706</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>1</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Skogsödla</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 7931-2025 artfynd.xlsx", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 7931-2025 karta.png", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 7931-2025 georefererad karta.tif", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 7931-2025 FSC-klagomål.docx", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 7931-2025 FSC-klagomål mail.docx", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 7931-2025 tillsynsbegäran.docx", "A 7931-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 7931-2025 tillsynsbegäran mail.docx", "A 7931-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 56386-2022</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44890</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Vågfibbla
-Rönnfibbla</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 56386-2022 artfynd.xlsx", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 56386-2022 karta.png", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 56386-2022 georefererad karta.tif", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 56386-2022 FSC-klagomål.docx", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 56386-2022 FSC-klagomål mail.docx", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 56386-2022 tillsynsbegäran.docx", "A 56386-2022")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 56386-2022 tillsynsbegäran mail.docx", "A 56386-2022")</f>
         <v/>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
         <v>45099</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>44901</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44494</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>44588</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>44470</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>44792</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 29582-2024</t>
+          <t>A 37339-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45484</v>
+        <v>44806</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3280,37 +3280,32 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3326,42 +3321,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 29582-2024 artfynd.xlsx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 37339-2022 artfynd.xlsx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 29582-2024 karta.png", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 37339-2022 karta.png", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 29582-2024 georefererad karta.tif", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 37339-2022 georefererad karta.tif", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 29582-2024 FSC-klagomål.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 37339-2022 FSC-klagomål.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 29582-2024 FSC-klagomål mail.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 37339-2022 FSC-klagomål mail.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 29582-2024 tillsynsbegäran.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 37339-2022 tillsynsbegäran.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 29582-2024 tillsynsbegäran mail.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 37339-2022 tillsynsbegäran mail.docx", "A 37339-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13121-2023</t>
+          <t>A 10647-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3371,14 +3366,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45002</v>
+        <v>45368</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3391,7 +3386,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3431,42 +3426,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 13121-2023 artfynd.xlsx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 10647-2024 artfynd.xlsx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 13121-2023 karta.png", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 10647-2024 karta.png", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 13121-2023 georefererad karta.tif", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 10647-2024 georefererad karta.tif", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 13121-2023 FSC-klagomål.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 10647-2024 FSC-klagomål.docx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 13121-2023 FSC-klagomål mail.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 10647-2024 FSC-klagomål mail.docx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 13121-2023 tillsynsbegäran.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 10647-2024 tillsynsbegäran.docx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 13121-2023 tillsynsbegäran mail.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 10647-2024 tillsynsbegäran mail.docx", "A 10647-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15321-2023</t>
+          <t>A 41878-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3480,10 +3475,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45019</v>
+        <v>45561</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3495,18 +3490,23 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>15.9</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3529,49 +3529,53 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 15321-2023 artfynd.xlsx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 41878-2024 artfynd.xlsx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 15321-2023 karta.png", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 41878-2024 karta.png", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 15321-2023 georefererad karta.tif", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 41878-2024 georefererad karta.tif", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 15321-2023 FSC-klagomål.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 41878-2024 FSC-klagomål.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 15321-2023 FSC-klagomål mail.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 41878-2024 FSC-klagomål mail.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 15321-2023 tillsynsbegäran.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 41878-2024 tillsynsbegäran.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 15321-2023 tillsynsbegäran mail.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 41878-2024 tillsynsbegäran mail.docx", "A 41878-2024")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 41878-2024 prioriterade fågelarter.docx", "A 41878-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 47146-2025</t>
+          <t>A 17122-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3581,14 +3585,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45929</v>
+        <v>45412</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3600,16 +3604,11 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3642,50 +3641,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 47146-2025 artfynd.xlsx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 17122-2024 artfynd.xlsx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 47146-2025 karta.png", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 17122-2024 karta.png", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 47146-2025 georefererad karta.tif", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 17122-2024 georefererad karta.tif", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 47146-2025 FSC-klagomål.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 17122-2024 FSC-klagomål.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 47146-2025 FSC-klagomål mail.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 17122-2024 FSC-klagomål mail.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 47146-2025 tillsynsbegäran.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 17122-2024 tillsynsbegäran.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 47146-2025 tillsynsbegäran mail.docx", "A 47146-2025")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 47146-2025 prioriterade fågelarter.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 17122-2024 tillsynsbegäran mail.docx", "A 17122-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 10647-2024</t>
+          <t>A 47146-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3699,10 +3694,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45368</v>
+        <v>45929</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3714,8 +3709,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3724,7 +3724,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3739,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3755,42 +3755,46 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 10647-2024 artfynd.xlsx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 47146-2025 artfynd.xlsx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 10647-2024 karta.png", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 47146-2025 karta.png", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 10647-2024 georefererad karta.tif", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 47146-2025 georefererad karta.tif", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 10647-2024 FSC-klagomål.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 47146-2025 FSC-klagomål.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 10647-2024 FSC-klagomål mail.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 47146-2025 FSC-klagomål mail.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 10647-2024 tillsynsbegäran.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 47146-2025 tillsynsbegäran.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 10647-2024 tillsynsbegäran mail.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 47146-2025 tillsynsbegäran mail.docx", "A 47146-2025")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 47146-2025 prioriterade fågelarter.docx", "A 47146-2025")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12296-2026</t>
+          <t>A 19524-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3804,10 +3808,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46087</v>
+        <v>45429</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3820,10 +3824,10 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -3856,46 +3860,50 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 12296-2026 artfynd.xlsx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19524-2024 artfynd.xlsx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 12296-2026 karta.png", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19524-2024 karta.png", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 12296-2026 georefererad karta.tif", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19524-2024 georefererad karta.tif", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 12296-2026 FSC-klagomål.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19524-2024 FSC-klagomål.docx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 12296-2026 FSC-klagomål mail.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19524-2024 FSC-klagomål mail.docx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 12296-2026 tillsynsbegäran.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19524-2024 tillsynsbegäran.docx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 12296-2026 tillsynsbegäran mail.docx", "A 12296-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19524-2024 tillsynsbegäran mail.docx", "A 19524-2024")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 19524-2024 prioriterade fågelarter.docx", "A 19524-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62675-2023</t>
+          <t>A 19052-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3905,14 +3913,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45271</v>
+        <v>45427</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3925,23 +3933,23 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>7.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>1</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
@@ -3949,10 +3957,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3961,46 +3969,46 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 62675-2023 artfynd.xlsx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19052-2024 artfynd.xlsx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 62675-2023 karta.png", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19052-2024 karta.png", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 62675-2023 georefererad karta.tif", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19052-2024 georefererad karta.tif", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 62675-2023 FSC-klagomål.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19052-2024 FSC-klagomål.docx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 62675-2023 FSC-klagomål mail.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19052-2024 FSC-klagomål mail.docx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 62675-2023 tillsynsbegäran.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19052-2024 tillsynsbegäran.docx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 62675-2023 tillsynsbegäran mail.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19052-2024 tillsynsbegäran mail.docx", "A 19052-2024")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30411-2025</t>
+          <t>A 15321-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4014,10 +4022,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45827</v>
+        <v>45019</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4030,13 +4038,13 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -4063,49 +4071,49 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 30411-2025 artfynd.xlsx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 15321-2023 artfynd.xlsx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 30411-2025 karta.png", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 15321-2023 karta.png", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 30411-2025 georefererad karta.tif", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 15321-2023 georefererad karta.tif", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 30411-2025 FSC-klagomål.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 15321-2023 FSC-klagomål.docx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 30411-2025 FSC-klagomål mail.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 15321-2023 FSC-klagomål mail.docx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 30411-2025 tillsynsbegäran.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 15321-2023 tillsynsbegäran.docx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 30411-2025 tillsynsbegäran mail.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 15321-2023 tillsynsbegäran mail.docx", "A 15321-2023")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 19052-2024</t>
+          <t>A 12296-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4119,10 +4127,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45427</v>
+        <v>46087</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4135,7 +4143,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>7.7</v>
+        <v>2.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4144,13 +4152,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4162,7 +4170,7 @@
         <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4171,46 +4179,46 @@
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19052-2024 artfynd.xlsx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 12296-2026 artfynd.xlsx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19052-2024 karta.png", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 12296-2026 karta.png", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19052-2024 georefererad karta.tif", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 12296-2026 georefererad karta.tif", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19052-2024 FSC-klagomål.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 12296-2026 FSC-klagomål.docx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19052-2024 FSC-klagomål mail.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 12296-2026 FSC-klagomål mail.docx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19052-2024 tillsynsbegäran.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 12296-2026 tillsynsbegäran.docx", "A 12296-2026")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19052-2024 tillsynsbegäran mail.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 12296-2026 tillsynsbegäran mail.docx", "A 12296-2026")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 34076-2026</t>
+          <t>A 13121-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4220,14 +4228,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46252</v>
+        <v>45002</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4240,16 +4248,16 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4264,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4273,49 +4281,49 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 34076-2026 artfynd.xlsx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 13121-2023 artfynd.xlsx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 34076-2026 karta.png", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 13121-2023 karta.png", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 34076-2026 georefererad karta.tif", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 13121-2023 georefererad karta.tif", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 34076-2026 FSC-klagomål.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 13121-2023 FSC-klagomål.docx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 34076-2026 FSC-klagomål mail.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 13121-2023 FSC-klagomål mail.docx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 34076-2026 tillsynsbegäran.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 13121-2023 tillsynsbegäran.docx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 34076-2026 tillsynsbegäran mail.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 13121-2023 tillsynsbegäran mail.docx", "A 13121-2023")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 37339-2022</t>
+          <t>A 30411-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4329,10 +4337,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44806</v>
+        <v>45827</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4345,16 +4353,16 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4369,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4385,35 +4393,35 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 37339-2022 artfynd.xlsx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 30411-2025 artfynd.xlsx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 37339-2022 karta.png", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 30411-2025 karta.png", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 37339-2022 georefererad karta.tif", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 30411-2025 georefererad karta.tif", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 37339-2022 FSC-klagomål.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 30411-2025 FSC-klagomål.docx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 37339-2022 FSC-klagomål mail.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 30411-2025 FSC-klagomål mail.docx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 37339-2022 tillsynsbegäran.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 30411-2025 tillsynsbegäran.docx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 37339-2022 tillsynsbegäran mail.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 30411-2025 tillsynsbegäran mail.docx", "A 30411-2025")</f>
         <v/>
       </c>
     </row>
@@ -4437,7 +4445,7 @@
         <v>45708</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4525,7 +4533,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17122-2024</t>
+          <t>A 35077-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4535,14 +4543,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45412</v>
+        <v>45527</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4555,19 +4563,19 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
         <v>1</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -4582,7 +4590,7 @@
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4595,42 +4603,46 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 17122-2024 artfynd.xlsx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 35077-2024 artfynd.xlsx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 17122-2024 karta.png", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 35077-2024 karta.png", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 17122-2024 georefererad karta.tif", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 35077-2024 georefererad karta.tif", "A 35077-2024")</f>
+        <v/>
+      </c>
+      <c r="Z38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/knärot/A 35077-2024 karta knärot.png", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 17122-2024 FSC-klagomål.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 35077-2024 FSC-klagomål.docx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 17122-2024 FSC-klagomål mail.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 35077-2024 FSC-klagomål mail.docx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 17122-2024 tillsynsbegäran.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 35077-2024 tillsynsbegäran.docx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 17122-2024 tillsynsbegäran mail.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 35077-2024 tillsynsbegäran mail.docx", "A 35077-2024")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 41878-2024</t>
+          <t>A 29582-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4644,10 +4656,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45561</v>
+        <v>45484</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4665,16 +4677,16 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>15.9</v>
+        <v>3.1</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4689,7 +4701,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -4705,46 +4717,42 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 41878-2024 artfynd.xlsx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 29582-2024 artfynd.xlsx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 41878-2024 karta.png", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 29582-2024 karta.png", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 41878-2024 georefererad karta.tif", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 29582-2024 georefererad karta.tif", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 41878-2024 FSC-klagomål.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 29582-2024 FSC-klagomål.docx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 41878-2024 FSC-klagomål mail.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 29582-2024 FSC-klagomål mail.docx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 41878-2024 tillsynsbegäran.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 29582-2024 tillsynsbegäran.docx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 41878-2024 tillsynsbegäran mail.docx", "A 41878-2024")</f>
-        <v/>
-      </c>
-      <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 41878-2024 prioriterade fågelarter.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 29582-2024 tillsynsbegäran mail.docx", "A 29582-2024")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 35077-2024</t>
+          <t>A 62675-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4754,14 +4762,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45527</v>
+        <v>45271</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4774,19 +4782,19 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
         <v>1</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -4798,10 +4806,10 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4814,46 +4822,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 35077-2024 artfynd.xlsx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 62675-2023 artfynd.xlsx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 35077-2024 karta.png", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 62675-2023 karta.png", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 35077-2024 georefererad karta.tif", "A 35077-2024")</f>
-        <v/>
-      </c>
-      <c r="Z40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/knärot/A 35077-2024 karta knärot.png", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 62675-2023 georefererad karta.tif", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 35077-2024 FSC-klagomål.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 62675-2023 FSC-klagomål.docx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 35077-2024 FSC-klagomål mail.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 62675-2023 FSC-klagomål mail.docx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 35077-2024 tillsynsbegäran.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 62675-2023 tillsynsbegäran.docx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 35077-2024 tillsynsbegäran mail.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 62675-2023 tillsynsbegäran mail.docx", "A 62675-2023")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19524-2024</t>
+          <t>A 34076-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4867,10 +4871,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45429</v>
+        <v>46252</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4883,10 +4887,10 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -4916,46 +4920,42 @@
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19524-2024 artfynd.xlsx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 34076-2026 artfynd.xlsx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19524-2024 karta.png", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 34076-2026 karta.png", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19524-2024 georefererad karta.tif", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 34076-2026 georefererad karta.tif", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19524-2024 FSC-klagomål.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 34076-2026 FSC-klagomål.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19524-2024 FSC-klagomål mail.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 34076-2026 FSC-klagomål mail.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19524-2024 tillsynsbegäran.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 34076-2026 tillsynsbegäran.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19524-2024 tillsynsbegäran mail.docx", "A 19524-2024")</f>
-        <v/>
-      </c>
-      <c r="AE41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 19524-2024 prioriterade fågelarter.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 34076-2026 tillsynsbegäran mail.docx", "A 34076-2026")</f>
         <v/>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
         <v>44484</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>44607</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>44781</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>44509</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44575</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32443-2022</t>
+          <t>A 34652-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44782</v>
+        <v>44795</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5432,7 +5432,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 34652-2022</t>
+          <t>A 32443-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5446,10 +5446,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44795</v>
+        <v>44782</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
         <v>44860</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>44494</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44844</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>44838</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44690</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>44734</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44694</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44743</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>44509</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>44498</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>44798</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>44762</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44620</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44627</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>44735</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>44882</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>44806</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>44494</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 2089-2022</t>
+          <t>A 25694-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6843,10 +6843,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44577</v>
+        <v>44732</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6902,7 +6902,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 25694-2022</t>
+          <t>A 2089-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44732</v>
+        <v>44577</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6992,7 +6992,7 @@
         <v>44755</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>44760</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>44547</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 5841-2022</t>
+          <t>A 12311-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7208,10 +7208,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44596</v>
+        <v>45378</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7267,7 +7267,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 5025-2023</t>
+          <t>A 37486-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44958</v>
+        <v>44809</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>8.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7340,7 +7340,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 73901-2021</t>
+          <t>A 20238-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7354,10 +7354,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44552</v>
+        <v>45434</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7413,7 +7413,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 28228-2024</t>
+          <t>A 21528-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7427,10 +7427,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45477</v>
+        <v>45441</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7486,7 +7486,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 5126-2023</t>
+          <t>A 19053-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7500,10 +7500,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44958</v>
+        <v>45427</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>14.3</v>
+        <v>3.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7559,7 +7559,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17437-2025</t>
+          <t>A 42557-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45757</v>
+        <v>44831</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>13.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7632,7 +7632,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 17443-2025</t>
+          <t>A 23189-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7646,10 +7646,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45757</v>
+        <v>45450</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7661,8 +7661,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7705,7 +7710,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 73033-2021</t>
+          <t>A 13382-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7719,10 +7724,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44550</v>
+        <v>45387</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7735,7 +7740,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7778,7 +7783,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13382-2024</t>
+          <t>A 25840-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7792,10 +7797,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45387</v>
+        <v>45467</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7808,7 +7813,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7851,7 +7856,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 57236-2023</t>
+          <t>A 28228-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7865,10 +7870,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45245</v>
+        <v>45477</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7881,7 +7886,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7924,7 +7929,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 57237-2023</t>
+          <t>A 59391-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7934,14 +7939,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45245</v>
+        <v>45989</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7954,7 +7959,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>18.2</v>
+        <v>4.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7997,7 +8002,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 5810-2023</t>
+          <t>A 25014-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8011,10 +8016,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44963</v>
+        <v>45461</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8027,7 +8032,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.8</v>
+        <v>12.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8070,7 +8075,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 47152-2023</t>
+          <t>A 17081-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8084,10 +8089,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45201</v>
+        <v>45412</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8100,7 +8105,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8143,7 +8148,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 26840-2023</t>
+          <t>A 62682-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8157,10 +8162,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45093</v>
+        <v>45271</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8173,7 +8178,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8216,7 +8221,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 18341-2025</t>
+          <t>A 13289-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8230,10 +8235,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45762</v>
+        <v>45735</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8246,7 +8251,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8289,7 +8294,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 58514-2022</t>
+          <t>A 73310-2021</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8303,10 +8308,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44902</v>
+        <v>44547</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8319,7 +8324,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8362,7 +8367,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 53209-2021</t>
+          <t>A 45467-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8376,10 +8381,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44468</v>
+        <v>44845</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8392,7 +8397,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>11.6</v>
+        <v>4.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8435,7 +8440,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 37119-2024</t>
+          <t>A 58705-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8449,10 +8454,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45539</v>
+        <v>45635</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8464,8 +8469,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>6.7</v>
+        <v>4.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8508,7 +8518,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17910-2024</t>
+          <t>A 27218-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8522,10 +8532,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45419</v>
+        <v>45096</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8538,7 +8548,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8581,7 +8591,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 2253-2024</t>
+          <t>A 36420-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8595,10 +8605,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45310</v>
+        <v>45152</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8611,7 +8621,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8654,7 +8664,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 13289-2025</t>
+          <t>A 36644-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8668,10 +8678,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45735</v>
+        <v>45153</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8684,7 +8694,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8727,7 +8737,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 6721-2025</t>
+          <t>A 7922-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8741,10 +8751,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45700</v>
+        <v>44608</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8756,13 +8766,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>5.7</v>
+        <v>1.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8805,7 +8810,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 49300-2022</t>
+          <t>A 62905-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8819,10 +8824,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44861</v>
+        <v>45272</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8835,7 +8840,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.2</v>
+        <v>13.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8878,7 +8883,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 5957-2024</t>
+          <t>A 17399-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8892,10 +8897,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45336</v>
+        <v>45757</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8908,7 +8913,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8951,7 +8956,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 27218-2023</t>
+          <t>A 5126-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8965,10 +8970,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45096</v>
+        <v>44958</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8981,7 +8986,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.2</v>
+        <v>14.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9024,7 +9029,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 59391-2025</t>
+          <t>A 29260-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9034,14 +9039,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45989</v>
+        <v>45824</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9054,7 +9059,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9097,7 +9102,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 36420-2023</t>
+          <t>A 44497-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9111,10 +9116,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45152</v>
+        <v>45916</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9127,7 +9132,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9170,7 +9175,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 17399-2025</t>
+          <t>A 10892-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9184,10 +9189,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45757</v>
+        <v>44627</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9243,7 +9248,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20238-2024</t>
+          <t>A 3054-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9257,10 +9262,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45434</v>
+        <v>46039</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9273,7 +9278,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9316,7 +9321,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 44497-2025</t>
+          <t>A 30563-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9330,10 +9335,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45916</v>
+        <v>45831</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9346,7 +9351,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9389,7 +9394,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 29260-2025</t>
+          <t>A 31362-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9399,14 +9404,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45824</v>
+        <v>45505</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9419,7 +9424,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9462,7 +9467,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 30563-2025</t>
+          <t>A 32327-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9476,10 +9481,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45831</v>
+        <v>45836</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9492,7 +9497,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9535,7 +9540,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 56219-2023</t>
+          <t>A 62557-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9549,10 +9554,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45240</v>
+        <v>44924</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9565,7 +9570,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9608,7 +9613,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 680-2024</t>
+          <t>A 7991-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9618,14 +9623,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45300</v>
+        <v>45350</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9638,7 +9643,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9681,7 +9686,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 30339-2022</t>
+          <t>A 47507-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9695,10 +9700,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44760</v>
+        <v>45930</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9711,7 +9716,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9754,7 +9759,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 47507-2025</t>
+          <t>A 5810-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9768,10 +9773,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45930</v>
+        <v>44963</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9784,7 +9789,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9827,7 +9832,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 32327-2025</t>
+          <t>A 8359-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9841,10 +9846,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45836</v>
+        <v>45708</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9857,7 +9862,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9917,7 +9922,7 @@
         <v>45939</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9973,7 +9978,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 975-2025</t>
+          <t>A 35425-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9987,10 +9992,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45665</v>
+        <v>45855</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10003,7 +10008,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10046,7 +10051,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 62557-2022</t>
+          <t>A 5236-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10060,10 +10065,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44924</v>
+        <v>44956</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10076,7 +10081,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10119,7 +10124,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 8359-2025</t>
+          <t>A 51509-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10129,14 +10134,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45708</v>
+        <v>45950</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10149,7 +10154,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10192,7 +10197,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 21402-2024</t>
+          <t>A 62947-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10206,10 +10211,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45441</v>
+        <v>45272</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10222,7 +10227,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10265,7 +10270,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 51509-2025</t>
+          <t>A 52700-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10275,14 +10280,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45950</v>
+        <v>45956</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10295,7 +10300,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10338,7 +10343,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 35425-2025</t>
+          <t>A 7993-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10352,10 +10357,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45855</v>
+        <v>45350</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10368,7 +10373,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10411,7 +10416,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 52699-2025</t>
+          <t>A 37517-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10425,10 +10430,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45956</v>
+        <v>45877</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10441,7 +10446,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10484,7 +10489,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 29736-2023</t>
+          <t>A 33081-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10498,10 +10503,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45107</v>
+        <v>44785</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10514,7 +10519,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10557,7 +10562,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 52700-2025</t>
+          <t>A 37515-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10571,10 +10576,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45956</v>
+        <v>45877</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10587,7 +10592,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10630,7 +10635,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 53138-2023</t>
+          <t>A 52699-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10644,10 +10649,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45229</v>
+        <v>45956</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10660,7 +10665,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10703,7 +10708,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 19566-2023</t>
+          <t>A 37495-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10717,10 +10722,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45049</v>
+        <v>45877</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10733,7 +10738,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10793,7 +10798,7 @@
         <v>45107</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10849,7 +10854,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 37515-2025</t>
+          <t>A 8732-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10863,10 +10868,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45877</v>
+        <v>46066</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10879,7 +10884,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10922,7 +10927,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 37495-2025</t>
+          <t>A 29736-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10936,10 +10941,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45877</v>
+        <v>45107</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10952,7 +10957,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10995,7 +11000,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 37517-2025</t>
+          <t>A 58747-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11009,10 +11014,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45877</v>
+        <v>45986</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11025,7 +11030,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11068,7 +11073,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 8364-2025</t>
+          <t>A 58751-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11082,10 +11087,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45708</v>
+        <v>45986</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11098,7 +11103,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11141,7 +11146,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 3054-2026</t>
+          <t>A 50640-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11155,10 +11160,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46039</v>
+        <v>45217</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11171,7 +11176,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11214,7 +11219,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 62896-2023</t>
+          <t>A 17910-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11228,10 +11233,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45272</v>
+        <v>45419</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11244,7 +11249,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>13.8</v>
+        <v>6.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11287,7 +11292,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 69847-2021</t>
+          <t>A 8361-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11301,10 +11306,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44532</v>
+        <v>45708</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11317,7 +11322,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11360,7 +11365,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 58705-2024</t>
+          <t>A 31964-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11374,10 +11379,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45635</v>
+        <v>45107</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11389,13 +11394,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11438,7 +11438,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 22347-2023</t>
+          <t>A 35253-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11452,10 +11452,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45070</v>
+        <v>44797</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11511,7 +11511,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 58751-2025</t>
+          <t>A 29426-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11525,10 +11525,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45986</v>
+        <v>44753</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11540,8 +11540,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>0.6</v>
+        <v>14.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11584,7 +11589,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 58747-2025</t>
+          <t>A 60656-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11598,10 +11603,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45986</v>
+        <v>45996</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11614,7 +11619,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11657,7 +11662,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 60656-2025</t>
+          <t>A 30339-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11671,10 +11676,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45996</v>
+        <v>44760</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11687,7 +11692,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11730,7 +11735,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 33081-2022</t>
+          <t>A 6751-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11744,10 +11749,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44785</v>
+        <v>45700</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11760,7 +11765,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11803,7 +11808,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 25840-2024</t>
+          <t>A 12283-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11817,10 +11822,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45467</v>
+        <v>46087</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11833,7 +11838,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11876,7 +11881,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 37676-2023</t>
+          <t>A 975-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11886,14 +11891,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45159</v>
+        <v>45665</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11906,7 +11911,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11949,7 +11954,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 6751-2025</t>
+          <t>A 63919-2021</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11963,10 +11968,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45700</v>
+        <v>44509</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11979,7 +11984,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12022,7 +12027,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 8732-2026</t>
+          <t>A 14688-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12032,14 +12037,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46066</v>
+        <v>46101</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12052,7 +12057,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>6.1</v>
+        <v>2.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12095,7 +12100,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 50640-2023</t>
+          <t>A 9144-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12109,10 +12114,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45217</v>
+        <v>45358</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12125,7 +12130,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12168,7 +12173,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 34580-2022</t>
+          <t>A 15543-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12182,10 +12187,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44795</v>
+        <v>46106</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12198,7 +12203,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12241,7 +12246,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 12000-2022</t>
+          <t>A 15549-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12255,10 +12260,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44635</v>
+        <v>46106</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12271,7 +12276,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12314,7 +12319,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 42557-2022</t>
+          <t>A 33948-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12328,10 +12333,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44831</v>
+        <v>45124</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12344,7 +12349,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>13.7</v>
+        <v>5.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12387,7 +12392,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 35253-2022</t>
+          <t>A 27222-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12401,10 +12406,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44797</v>
+        <v>45096</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12417,7 +12422,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12460,7 +12465,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 13820-2024</t>
+          <t>A 17972-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12474,10 +12479,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45390</v>
+        <v>45761</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12490,7 +12495,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>7.2</v>
+        <v>0.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12533,7 +12538,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 17565-2025</t>
+          <t>A 62896-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12547,10 +12552,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45757</v>
+        <v>45272</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12563,7 +12568,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.1</v>
+        <v>13.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12606,7 +12611,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 12283-2026</t>
+          <t>A 6938-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12616,14 +12621,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46087</v>
+        <v>45343</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12636,7 +12641,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12679,7 +12684,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 31362-2024</t>
+          <t>A 26829-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12689,14 +12694,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45505</v>
+        <v>45093</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12709,7 +12714,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12752,7 +12757,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 14688-2026</t>
+          <t>A 13895-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12762,14 +12767,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46101</v>
+        <v>45391</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12781,8 +12786,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12825,7 +12835,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 3065-2024</t>
+          <t>A 26815-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12839,10 +12849,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45316</v>
+        <v>45093</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12855,7 +12865,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12898,7 +12908,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 17081-2024</t>
+          <t>A 17565-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12912,10 +12922,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45412</v>
+        <v>45757</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12928,7 +12938,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12971,7 +12981,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 15549-2026</t>
+          <t>A 25443-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12985,10 +12995,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46106</v>
+        <v>45089</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13001,7 +13011,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13044,7 +13054,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 15543-2026</t>
+          <t>A 14306-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13058,10 +13068,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46106</v>
+        <v>45011</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13074,7 +13084,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13117,7 +13127,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 7993-2024</t>
+          <t>A 29256-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13131,10 +13141,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45350</v>
+        <v>45824</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13147,7 +13157,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13190,7 +13200,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 45467-2022</t>
+          <t>A 5025-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13204,10 +13214,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44845</v>
+        <v>44958</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13220,7 +13230,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13263,7 +13273,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 5011-2024</t>
+          <t>A 31974-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13277,10 +13287,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45329</v>
+        <v>45107</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13293,7 +13303,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>22</v>
+        <v>3.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13336,7 +13346,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 53137-2023</t>
+          <t>A 21248-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13350,10 +13360,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45229</v>
+        <v>44705</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13366,7 +13376,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>12.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13409,7 +13419,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 9144-2024</t>
+          <t>A 5957-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13423,10 +13433,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45358</v>
+        <v>45336</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13439,7 +13449,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13482,7 +13492,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 62682-2023</t>
+          <t>A 42143-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13496,10 +13506,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45271</v>
+        <v>45904</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13512,7 +13522,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13555,7 +13565,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 4982-2024</t>
+          <t>A 40522-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13569,10 +13579,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45329</v>
+        <v>45896</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13585,7 +13595,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13628,7 +13638,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 62947-2023</t>
+          <t>A 5214-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13642,10 +13652,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45272</v>
+        <v>45691</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13658,7 +13668,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13701,7 +13711,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 31930-2024</t>
+          <t>A 2253-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13711,14 +13721,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45510</v>
+        <v>45310</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13731,7 +13741,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13774,7 +13784,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 71706-2021</t>
+          <t>A 4870-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13788,10 +13798,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44543</v>
+        <v>45329</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13804,7 +13814,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.1</v>
+        <v>8.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13847,7 +13857,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 40935-2022</t>
+          <t>A 69847-2021</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13857,14 +13867,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44823</v>
+        <v>44532</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13876,13 +13886,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13925,7 +13930,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 59617-2025</t>
+          <t>A 58514-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13939,10 +13944,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45992</v>
+        <v>44902</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13955,7 +13960,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13998,7 +14003,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 29256-2025</t>
+          <t>A 71706-2021</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14012,10 +14017,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45824</v>
+        <v>44543</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14028,7 +14033,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14071,7 +14076,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 6938-2024</t>
+          <t>A 47152-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14081,14 +14086,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45343</v>
+        <v>45201</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14101,7 +14106,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14144,7 +14149,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 614-2026</t>
+          <t>A 20784-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14158,10 +14163,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46024</v>
+        <v>45776</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14174,7 +14179,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5.3</v>
+        <v>9.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14217,7 +14222,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 42143-2025</t>
+          <t>A 614-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14231,10 +14236,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45904</v>
+        <v>46024</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14247,7 +14252,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14290,7 +14295,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 14306-2023</t>
+          <t>A 40524-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14304,10 +14309,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45011</v>
+        <v>45896</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14320,7 +14325,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14363,7 +14368,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 20784-2025</t>
+          <t>A 59617-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14377,10 +14382,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45776</v>
+        <v>45992</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14393,7 +14398,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>9.5</v>
+        <v>1.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14436,7 +14441,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 17972-2025</t>
+          <t>A 53138-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14450,10 +14455,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45761</v>
+        <v>45229</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14466,7 +14471,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14509,7 +14514,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 27222-2023</t>
+          <t>A 16772-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14523,10 +14528,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45096</v>
+        <v>45411</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14539,7 +14544,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14582,7 +14587,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 40524-2025</t>
+          <t>A 31561-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14596,10 +14601,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45896</v>
+        <v>45117</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14612,7 +14617,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14655,7 +14660,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 21248-2022</t>
+          <t>A 66056-2021</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14669,10 +14674,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44705</v>
+        <v>44517</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14685,7 +14690,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>12.4</v>
+        <v>0.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14728,7 +14733,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 40522-2025</t>
+          <t>A 3065-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14742,10 +14747,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45896</v>
+        <v>45316</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14758,7 +14763,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14801,7 +14806,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 36644-2023</t>
+          <t>A 12082-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14815,10 +14820,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45153</v>
+        <v>45377</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14831,7 +14836,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14874,7 +14879,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 8788-2024</t>
+          <t>A 12084-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14888,10 +14893,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45356</v>
+        <v>45377</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14904,7 +14909,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14947,7 +14952,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 62554-2022</t>
+          <t>A 20954-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14961,10 +14966,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44924</v>
+        <v>45061</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14977,7 +14982,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15020,7 +15025,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 21528-2024</t>
+          <t>A 17443-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15034,10 +15039,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45441</v>
+        <v>45757</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15050,7 +15055,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15093,7 +15098,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 20954-2023</t>
+          <t>A 20369-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15107,10 +15112,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45061</v>
+        <v>45435</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15123,7 +15128,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15166,7 +15171,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 5214-2025</t>
+          <t>A 11601-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15180,10 +15185,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45691</v>
+        <v>45727</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15196,7 +15201,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15239,7 +15244,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 31561-2023</t>
+          <t>A 4976-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15253,10 +15258,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45117</v>
+        <v>45329</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15269,7 +15274,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15312,7 +15317,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 10892-2022</t>
+          <t>A 22406-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15326,10 +15331,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44627</v>
+        <v>46154</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15342,7 +15347,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15385,7 +15390,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 29426-2022</t>
+          <t>A 12175-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15399,10 +15404,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44753</v>
+        <v>45377</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15414,13 +15419,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>14.4</v>
+        <v>5.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15463,7 +15463,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 44048-2023</t>
+          <t>A 30527-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15477,10 +15477,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45188</v>
+        <v>44762</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15536,7 +15536,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 62905-2023</t>
+          <t>A 39334-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15550,10 +15550,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45272</v>
+        <v>45889</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>13.8</v>
+        <v>1.3</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15609,7 +15609,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 37486-2022</t>
+          <t>A 3779-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15623,10 +15623,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44809</v>
+        <v>45681</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15638,8 +15638,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>BillerudKorsnäs AB</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15682,7 +15687,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 22406-2026</t>
+          <t>A 71903-2021</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15696,10 +15701,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46154</v>
+        <v>44543</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15712,7 +15717,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15755,7 +15760,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 46299-2022</t>
+          <t>A 22347-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15769,10 +15774,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44847</v>
+        <v>45070</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15785,7 +15790,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15828,7 +15833,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 5236-2023</t>
+          <t>A 56220-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15842,10 +15847,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44956</v>
+        <v>45240</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15858,7 +15863,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15901,7 +15906,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 71903-2021</t>
+          <t>A 23702-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15915,10 +15920,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44543</v>
+        <v>46164</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15930,8 +15935,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>6.3</v>
+        <v>2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15974,7 +15984,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 3779-2025</t>
+          <t>A 23733-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15988,10 +15998,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45681</v>
+        <v>46164</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16005,11 +16015,11 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>BillerudKorsnäs AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I192" t="n">
-        <v>7.6</v>
+        <v>0.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16052,7 +16062,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 56220-2023</t>
+          <t>A 23757-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16066,10 +16076,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45240</v>
+        <v>46164</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16082,7 +16092,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16125,7 +16135,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 39334-2025</t>
+          <t>A 56219-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16139,10 +16149,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45889</v>
+        <v>45240</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16155,7 +16165,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16198,7 +16208,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 972-2025</t>
+          <t>A 6721-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16212,10 +16222,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45665</v>
+        <v>45700</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16227,8 +16237,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16271,7 +16286,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 23733-2026</t>
+          <t>A 23945-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16285,10 +16300,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16306,7 +16321,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16349,7 +16364,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 23945-2026</t>
+          <t>A 17437-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16363,10 +16378,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46167</v>
+        <v>45757</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16376,11 +16391,6 @@
       <c r="G197" t="inlineStr">
         <is>
           <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I197" t="n">
@@ -16427,7 +16437,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 23757-2026</t>
+          <t>A 5841-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16441,10 +16451,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46164</v>
+        <v>44596</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16457,7 +16467,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16500,7 +16510,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 23702-2026</t>
+          <t>A 12000-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16514,10 +16524,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46164</v>
+        <v>44635</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16529,13 +16539,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16578,7 +16583,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 13895-2024</t>
+          <t>A 40935-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16588,14 +16593,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45391</v>
+        <v>44823</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16613,7 +16618,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16656,7 +16661,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 29724-2023</t>
+          <t>A 36646-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16666,14 +16671,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45107</v>
+        <v>45153</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16686,7 +16691,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16729,7 +16734,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 31974-2023</t>
+          <t>A 24754-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16743,10 +16748,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45107</v>
+        <v>46171</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16759,7 +16764,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16802,7 +16807,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 19802-2024</t>
+          <t>A 29724-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16812,14 +16817,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45432</v>
+        <v>45107</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16831,13 +16836,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16880,7 +16880,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 16635-2024</t>
+          <t>A 8362-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16894,10 +16894,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45408</v>
+        <v>45708</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16953,7 +16953,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 24754-2026</t>
+          <t>A 972-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16967,10 +16967,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46171</v>
+        <v>45665</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17026,7 +17026,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 7922-2022</t>
+          <t>A 49300-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17040,10 +17040,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44608</v>
+        <v>44861</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17099,7 +17099,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 1556-2025</t>
+          <t>A 16635-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17113,10 +17113,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45670</v>
+        <v>45408</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17172,7 +17172,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 26015-2026</t>
+          <t>A 37676-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17186,10 +17186,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46181</v>
+        <v>45159</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17201,13 +17201,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17250,7 +17245,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 12311-2024</t>
+          <t>A 26015-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17260,14 +17255,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45378</v>
+        <v>46181</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17279,8 +17274,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17323,7 +17323,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 33948-2023</t>
+          <t>A 53137-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17337,10 +17337,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45124</v>
+        <v>45229</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17396,7 +17396,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 13320-2024</t>
+          <t>A 8788-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17410,10 +17410,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45386</v>
+        <v>45356</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>6</v>
+        <v>0.9</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17469,7 +17469,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 55227-2023</t>
+          <t>A 680-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17483,10 +17483,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45231</v>
+        <v>45300</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17542,7 +17542,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 25014-2024</t>
+          <t>A 46299-2022</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17556,10 +17556,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45461</v>
+        <v>44847</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>12.8</v>
+        <v>2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17615,7 +17615,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 31964-2023</t>
+          <t>A 62554-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17629,10 +17629,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45107</v>
+        <v>44924</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17688,7 +17688,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 12082-2024</t>
+          <t>A 57236-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17702,10 +17702,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45377</v>
+        <v>45245</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17761,7 +17761,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 12084-2024</t>
+          <t>A 57237-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17775,10 +17775,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45377</v>
+        <v>45245</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.1</v>
+        <v>18.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17834,7 +17834,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 4976-2024</t>
+          <t>A 11103-2022</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17848,10 +17848,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45329</v>
+        <v>44628</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17907,7 +17907,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 64304-2023</t>
+          <t>A 28513-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17921,10 +17921,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45280</v>
+        <v>46197</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17980,7 +17980,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 48553-2023</t>
+          <t>A 29577-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17994,10 +17994,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45208</v>
+        <v>45484</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18009,8 +18009,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>1.7</v>
+        <v>10.1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18053,7 +18058,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 26815-2023</t>
+          <t>A 27443-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18067,10 +18072,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45093</v>
+        <v>45474</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18083,7 +18088,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18126,7 +18131,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 16772-2024</t>
+          <t>A 32959-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18140,10 +18145,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45411</v>
+        <v>44784</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18156,7 +18161,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18199,7 +18204,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 25443-2023</t>
+          <t>A 13320-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18213,10 +18218,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45089</v>
+        <v>45386</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18229,7 +18234,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18272,7 +18277,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 66056-2021</t>
+          <t>A 38517-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18286,10 +18291,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>44517</v>
+        <v>45546</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18302,7 +18307,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18345,7 +18350,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 28513-2026</t>
+          <t>A 32302-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18359,10 +18364,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46197</v>
+        <v>45512</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18374,8 +18379,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18418,7 +18428,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 11103-2022</t>
+          <t>A 29205-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18432,10 +18442,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44628</v>
+        <v>46202</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18448,7 +18458,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>5.7</v>
+        <v>1.4</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18491,7 +18501,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 29205-2026</t>
+          <t>A 29222-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18508,7 +18518,7 @@
         <v>46202</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18521,7 +18531,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18564,7 +18574,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 23189-2024</t>
+          <t>A 37119-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18578,10 +18588,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45450</v>
+        <v>45539</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18593,13 +18603,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I227" t="n">
-        <v>1.9</v>
+        <v>6.7</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18642,7 +18647,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 29222-2026</t>
+          <t>A 29191-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18659,7 +18664,7 @@
         <v>46202</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18672,7 +18677,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18715,7 +18720,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 7991-2024</t>
+          <t>A 19802-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18725,14 +18730,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45350</v>
+        <v>45432</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18744,8 +18749,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18788,7 +18798,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 29191-2026</t>
+          <t>A 34580-2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18802,10 +18812,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46202</v>
+        <v>44795</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18818,7 +18828,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18861,7 +18871,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 59542-2022</t>
+          <t>A 19566-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18875,10 +18885,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44907</v>
+        <v>45049</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18891,7 +18901,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18934,7 +18944,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 32302-2024</t>
+          <t>A 7272-2022</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18948,10 +18958,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45512</v>
+        <v>44606</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18963,13 +18973,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I232" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -19012,7 +19017,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 8361-2025</t>
+          <t>A 22822-2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -19026,10 +19031,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45708</v>
+        <v>45448</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19042,7 +19047,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -19085,7 +19090,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 73310-2021</t>
+          <t>A 59542-2022</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -19099,10 +19104,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>44547</v>
+        <v>44907</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19115,7 +19120,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>6.2</v>
+        <v>0.8</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -19158,7 +19163,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 34538-2026</t>
+          <t>A 21402-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -19172,10 +19177,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46255</v>
+        <v>45441</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19188,7 +19193,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -19231,7 +19236,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 71781-2021</t>
+          <t>A 34538-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19245,10 +19250,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>44539</v>
+        <v>46255</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19260,13 +19265,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I236" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19309,7 +19309,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 31034-2026</t>
+          <t>A 71781-2021</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19323,10 +19323,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>46214</v>
+        <v>44539</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19338,8 +19338,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I237" t="n">
-        <v>2.9</v>
+        <v>7</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19382,7 +19387,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 8362-2025</t>
+          <t>A 31930-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19392,14 +19397,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45708</v>
+        <v>45510</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19412,7 +19417,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>7.7</v>
+        <v>0.6</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19455,7 +19460,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 30527-2022</t>
+          <t>A 31034-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19469,10 +19474,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44762</v>
+        <v>46214</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19485,7 +19490,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19528,7 +19533,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 17573-2025</t>
+          <t>A 73901-2021</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19542,10 +19547,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45757</v>
+        <v>44552</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19558,7 +19563,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19601,7 +19606,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 9837-2023</t>
+          <t>A 26840-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19615,10 +19620,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44984</v>
+        <v>45093</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19631,7 +19636,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19674,7 +19679,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 19753-2024</t>
+          <t>A 13820-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19688,10 +19693,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45432</v>
+        <v>45390</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19704,7 +19709,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19747,7 +19752,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 27443-2024</t>
+          <t>A 5011-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19761,10 +19766,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45474</v>
+        <v>45329</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19777,7 +19782,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.8</v>
+        <v>22</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19820,7 +19825,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 32959-2022</t>
+          <t>A 18341-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19834,10 +19839,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>44784</v>
+        <v>45762</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19850,7 +19855,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19893,7 +19898,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 30914-2023</t>
+          <t>A 31559-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19907,10 +19912,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45113</v>
+        <v>46224</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19923,7 +19928,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19966,7 +19971,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 31559-2026</t>
+          <t>A 19753-2024</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19980,10 +19985,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46224</v>
+        <v>45432</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19996,7 +20001,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -20039,7 +20044,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 20369-2024</t>
+          <t>A 4982-2024</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -20053,10 +20058,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45435</v>
+        <v>45329</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20069,7 +20074,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -20112,7 +20117,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 7272-2022</t>
+          <t>A 37221-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -20126,10 +20131,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>44606</v>
+        <v>46274</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20142,7 +20147,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -20185,7 +20190,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 26829-2023</t>
+          <t>A 37243-2026</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -20199,10 +20204,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45093</v>
+        <v>46274</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20215,7 +20220,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.5</v>
+        <v>13.9</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -20258,7 +20263,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 38517-2024</t>
+          <t>A 55227-2023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -20272,10 +20277,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45546</v>
+        <v>45231</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20288,7 +20293,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -20331,7 +20336,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 63919-2021</t>
+          <t>A 9837-2023</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20345,10 +20350,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>44509</v>
+        <v>44984</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20361,7 +20366,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20404,7 +20409,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 4870-2024</t>
+          <t>A 1556-2025</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20418,10 +20423,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45329</v>
+        <v>45670</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20434,7 +20439,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>8.4</v>
+        <v>1.8</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20477,7 +20482,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 36646-2023</t>
+          <t>A 73033-2021</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20491,10 +20496,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45153</v>
+        <v>44550</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20507,7 +20512,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20550,7 +20555,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 37221-2026</t>
+          <t>A 64304-2023</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20564,10 +20569,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>46274</v>
+        <v>45280</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20580,7 +20585,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20623,7 +20628,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 37243-2026</t>
+          <t>A 8364-2025</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20637,10 +20642,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>46274</v>
+        <v>45708</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20653,7 +20658,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>13.9</v>
+        <v>0.8</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20696,7 +20701,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 22822-2024</t>
+          <t>A 48553-2023</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20710,10 +20715,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45448</v>
+        <v>45208</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20726,7 +20731,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20769,7 +20774,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 19053-2024</t>
+          <t>A 17573-2025</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20783,10 +20788,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45427</v>
+        <v>45757</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20799,7 +20804,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20842,7 +20847,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 11601-2025</t>
+          <t>A 32942-2026</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20856,10 +20861,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45727</v>
+        <v>46244</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20872,7 +20877,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20915,7 +20920,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 12175-2024</t>
+          <t>A 44048-2023</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20929,10 +20934,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45377</v>
+        <v>45188</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20945,7 +20950,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20988,7 +20993,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 29577-2024</t>
+          <t>A 30914-2023</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -21002,10 +21007,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45484</v>
+        <v>45113</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21017,13 +21022,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I260" t="n">
-        <v>10.1</v>
+        <v>2.1</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -21083,7 +21083,7 @@
         <v>44977</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>45729</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45785</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>45787</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21358,24 +21358,24 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 32942-2026</t>
+          <t>S 2221-2023</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>46244</v>
+        <v>45099</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21387,8 +21387,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I265" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -21431,7 +21436,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>S 2221-2023</t>
+          <t>S 4473-2023</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21445,10 +21450,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45099</v>
+        <v>45272</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21460,13 +21465,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I266" t="n">
-        <v>5.5</v>
+        <v>43.7</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -21509,7 +21509,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>S 4473-2023</t>
+          <t>S 2137-2025</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21519,14 +21519,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45272</v>
+        <v>45846</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>43.7</v>
+        <v>20.2</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21582,7 +21582,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>S 2137-2025</t>
+          <t>S 3158-2025</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21592,87 +21592,87 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D268" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="E268" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="I268" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J268" t="n">
+        <v>0</v>
+      </c>
+      <c r="K268" t="n">
+        <v>0</v>
+      </c>
+      <c r="L268" t="n">
+        <v>0</v>
+      </c>
+      <c r="M268" t="n">
+        <v>0</v>
+      </c>
+      <c r="N268" t="n">
+        <v>0</v>
+      </c>
+      <c r="O268" t="n">
+        <v>0</v>
+      </c>
+      <c r="P268" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>0</v>
+      </c>
+      <c r="R268" t="n">
+        <v>0</v>
+      </c>
+      <c r="S268" t="n">
+        <v>0</v>
+      </c>
+      <c r="T268" t="n">
+        <v>0</v>
+      </c>
+      <c r="U268" t="n">
+        <v>0</v>
+      </c>
+      <c r="V268" s="2" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>S 88-2026</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
           <t>Skogsgödsling</t>
         </is>
       </c>
-      <c r="D268" s="1" t="n">
-        <v>45846</v>
-      </c>
-      <c r="E268" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="I268" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="J268" t="n">
-        <v>0</v>
-      </c>
-      <c r="K268" t="n">
-        <v>0</v>
-      </c>
-      <c r="L268" t="n">
-        <v>0</v>
-      </c>
-      <c r="M268" t="n">
-        <v>0</v>
-      </c>
-      <c r="N268" t="n">
-        <v>0</v>
-      </c>
-      <c r="O268" t="n">
-        <v>0</v>
-      </c>
-      <c r="P268" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
-      <c r="R268" t="n">
-        <v>0</v>
-      </c>
-      <c r="S268" t="n">
-        <v>0</v>
-      </c>
-      <c r="T268" t="n">
-        <v>0</v>
-      </c>
-      <c r="U268" t="n">
-        <v>0</v>
-      </c>
-      <c r="V268" s="2" t="inlineStr"/>
-    </row>
-    <row r="269" ht="15" customHeight="1">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>S 3158-2025</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
       <c r="D269" s="1" t="n">
-        <v>45973</v>
+        <v>46035</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21684,8 +21684,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I269" t="n">
-        <v>8.1</v>
+        <v>1.8</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21724,84 +21729,6 @@
         <v>0</v>
       </c>
       <c r="V269" s="2" t="inlineStr"/>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>S 88-2026</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D270" s="1" t="n">
-        <v>46035</v>
-      </c>
-      <c r="E270" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I270" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J270" t="n">
-        <v>0</v>
-      </c>
-      <c r="K270" t="n">
-        <v>0</v>
-      </c>
-      <c r="L270" t="n">
-        <v>0</v>
-      </c>
-      <c r="M270" t="n">
-        <v>0</v>
-      </c>
-      <c r="N270" t="n">
-        <v>0</v>
-      </c>
-      <c r="O270" t="n">
-        <v>0</v>
-      </c>
-      <c r="P270" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
-      <c r="R270" t="n">
-        <v>0</v>
-      </c>
-      <c r="S270" t="n">
-        <v>0</v>
-      </c>
-      <c r="T270" t="n">
-        <v>0</v>
-      </c>
-      <c r="U270" t="n">
-        <v>0</v>
-      </c>
-      <c r="V270" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GRUMS.xlsx
+++ b/Översikt GRUMS.xlsx
@@ -601,7 +601,7 @@
         <v>44978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45343</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44788</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44498</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44819</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45615</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>46252</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>44981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45099</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>45898</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45078</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 66053-2021</t>
+          <t>A 5280-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44517</v>
+        <v>44593</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1972,14 +1972,19 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>37.1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1988,7 +1993,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1997,174 +2002,169 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 5280-2022 artfynd.xlsx", "A 5280-2022")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 5280-2022 karta.png", "A 5280-2022")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 5280-2022 georefererad karta.tif", "A 5280-2022")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 5280-2022 FSC-klagomål.docx", "A 5280-2022")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 5280-2022 FSC-klagomål mail.docx", "A 5280-2022")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 5280-2022 tillsynsbegäran.docx", "A 5280-2022")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 5280-2022 tillsynsbegäran mail.docx", "A 5280-2022")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 5280-2022 prioriterade fågelarter.docx", "A 5280-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 66053-2021</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44517</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
         <v>6</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>6</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Bronshjon</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 66053-2021 artfynd.xlsx", "A 66053-2021")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 66053-2021 karta.png", "A 66053-2021")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 66053-2021 georefererad karta.tif", "A 66053-2021")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 66053-2021 FSC-klagomål.docx", "A 66053-2021")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 66053-2021 FSC-klagomål mail.docx", "A 66053-2021")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 66053-2021 tillsynsbegäran.docx", "A 66053-2021")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 66053-2021 tillsynsbegäran mail.docx", "A 66053-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 5280-2022</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44593</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 5280-2022 artfynd.xlsx", "A 5280-2022")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 5280-2022 karta.png", "A 5280-2022")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 5280-2022 georefererad karta.tif", "A 5280-2022")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 5280-2022 FSC-klagomål.docx", "A 5280-2022")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 5280-2022 FSC-klagomål mail.docx", "A 5280-2022")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 5280-2022 tillsynsbegäran.docx", "A 5280-2022")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 5280-2022 tillsynsbegäran mail.docx", "A 5280-2022")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 5280-2022 prioriterade fågelarter.docx", "A 5280-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 56386-2022</t>
+          <t>A 57233-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44890</v>
+        <v>45245</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2203,10 +2203,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2221,266 +2221,266 @@
         <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>6</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin
+Skogsklocka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 57233-2023 artfynd.xlsx", "A 57233-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 57233-2023 karta.png", "A 57233-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 57233-2023 georefererad karta.tif", "A 57233-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 57233-2023 FSC-klagomål.docx", "A 57233-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 57233-2023 FSC-klagomål mail.docx", "A 57233-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 57233-2023 tillsynsbegäran.docx", "A 57233-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 57233-2023 tillsynsbegäran mail.docx", "A 57233-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 7931-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45706</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 7931-2025 artfynd.xlsx", "A 7931-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 7931-2025 karta.png", "A 7931-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 7931-2025 georefererad karta.tif", "A 7931-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 7931-2025 FSC-klagomål.docx", "A 7931-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 7931-2025 FSC-klagomål mail.docx", "A 7931-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 7931-2025 tillsynsbegäran.docx", "A 7931-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 7931-2025 tillsynsbegäran mail.docx", "A 7931-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 56386-2022</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44890</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>GRUMS</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Vågfibbla
 Rönnfibbla</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 56386-2022 artfynd.xlsx", "A 56386-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 56386-2022 karta.png", "A 56386-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 56386-2022 georefererad karta.tif", "A 56386-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 56386-2022 FSC-klagomål.docx", "A 56386-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 56386-2022 FSC-klagomål mail.docx", "A 56386-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 56386-2022 tillsynsbegäran.docx", "A 56386-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 56386-2022 tillsynsbegäran mail.docx", "A 56386-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 57233-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45245</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>6</v>
-      </c>
-      <c r="U17" t="n">
-        <v>6</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Skogsklocka</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 57233-2023 artfynd.xlsx", "A 57233-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 57233-2023 karta.png", "A 57233-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 57233-2023 georefererad karta.tif", "A 57233-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 57233-2023 FSC-klagomål.docx", "A 57233-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 57233-2023 FSC-klagomål mail.docx", "A 57233-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 57233-2023 tillsynsbegäran.docx", "A 57233-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 57233-2023 tillsynsbegäran mail.docx", "A 57233-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 7931-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45706</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 7931-2025 artfynd.xlsx", "A 7931-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 7931-2025 karta.png", "A 7931-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 7931-2025 georefererad karta.tif", "A 7931-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 7931-2025 FSC-klagomål.docx", "A 7931-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 7931-2025 FSC-klagomål mail.docx", "A 7931-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 7931-2025 tillsynsbegäran.docx", "A 7931-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 7931-2025 tillsynsbegäran mail.docx", "A 7931-2025")</f>
         <v/>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
         <v>45099</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>44901</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>44494</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>44588</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>44792</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 37339-2022</t>
+          <t>A 29582-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3046,10 +3046,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44806</v>
+        <v>45484</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3061,17 +3061,22 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3086,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3102,42 +3107,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 37339-2022 artfynd.xlsx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 29582-2024 artfynd.xlsx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 37339-2022 karta.png", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 29582-2024 karta.png", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 37339-2022 georefererad karta.tif", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 29582-2024 georefererad karta.tif", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 37339-2022 FSC-klagomål.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 29582-2024 FSC-klagomål.docx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 37339-2022 FSC-klagomål mail.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 29582-2024 FSC-klagomål mail.docx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 37339-2022 tillsynsbegäran.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 29582-2024 tillsynsbegäran.docx", "A 29582-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 37339-2022 tillsynsbegäran mail.docx", "A 37339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 29582-2024 tillsynsbegäran mail.docx", "A 29582-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 10647-2024</t>
+          <t>A 13121-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3147,14 +3152,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45368</v>
+        <v>45002</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3167,7 +3172,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3207,42 +3212,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 10647-2024 artfynd.xlsx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 13121-2023 artfynd.xlsx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 10647-2024 karta.png", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 13121-2023 karta.png", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 10647-2024 georefererad karta.tif", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 13121-2023 georefererad karta.tif", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 10647-2024 FSC-klagomål.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 13121-2023 FSC-klagomål.docx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 10647-2024 FSC-klagomål mail.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 13121-2023 FSC-klagomål mail.docx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 10647-2024 tillsynsbegäran.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 13121-2023 tillsynsbegäran.docx", "A 13121-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 10647-2024 tillsynsbegäran mail.docx", "A 10647-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 13121-2023 tillsynsbegäran mail.docx", "A 13121-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 47146-2025</t>
+          <t>A 15321-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3256,10 +3261,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45929</v>
+        <v>45019</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3271,22 +3276,17 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3301,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3310,53 +3310,49 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 47146-2025 artfynd.xlsx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 15321-2023 artfynd.xlsx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 47146-2025 karta.png", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 15321-2023 karta.png", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 47146-2025 georefererad karta.tif", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 15321-2023 georefererad karta.tif", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 47146-2025 FSC-klagomål.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 15321-2023 FSC-klagomål.docx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 47146-2025 FSC-klagomål mail.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 15321-2023 FSC-klagomål mail.docx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 47146-2025 tillsynsbegäran.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 15321-2023 tillsynsbegäran.docx", "A 15321-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 47146-2025 tillsynsbegäran mail.docx", "A 47146-2025")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 47146-2025 prioriterade fågelarter.docx", "A 47146-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 15321-2023 tillsynsbegäran mail.docx", "A 15321-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 41878-2024</t>
+          <t>A 47146-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3370,10 +3366,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45561</v>
+        <v>45929</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3391,7 +3387,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>15.9</v>
+        <v>7</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3427,43 +3423,43 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 41878-2024 artfynd.xlsx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 47146-2025 artfynd.xlsx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 41878-2024 karta.png", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 47146-2025 karta.png", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 41878-2024 georefererad karta.tif", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 47146-2025 georefererad karta.tif", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 41878-2024 FSC-klagomål.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 47146-2025 FSC-klagomål.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 41878-2024 FSC-klagomål mail.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 47146-2025 FSC-klagomål mail.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 41878-2024 tillsynsbegäran.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 47146-2025 tillsynsbegäran.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 41878-2024 tillsynsbegäran mail.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 47146-2025 tillsynsbegäran mail.docx", "A 47146-2025")</f>
         <v/>
       </c>
       <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 41878-2024 prioriterade fågelarter.docx", "A 41878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 47146-2025 prioriterade fågelarter.docx", "A 47146-2025")</f>
         <v/>
       </c>
     </row>
@@ -3487,7 +3483,7 @@
         <v>46087</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3575,7 +3571,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17122-2024</t>
+          <t>A 10647-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3585,14 +3581,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45412</v>
+        <v>45368</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,16 +3601,16 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3629,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3641,46 +3637,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 17122-2024 artfynd.xlsx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 10647-2024 artfynd.xlsx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 17122-2024 karta.png", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 10647-2024 karta.png", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 17122-2024 georefererad karta.tif", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 10647-2024 georefererad karta.tif", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 17122-2024 FSC-klagomål.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 10647-2024 FSC-klagomål.docx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 17122-2024 FSC-klagomål mail.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 10647-2024 FSC-klagomål mail.docx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 17122-2024 tillsynsbegäran.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 10647-2024 tillsynsbegäran.docx", "A 10647-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 17122-2024 tillsynsbegäran mail.docx", "A 17122-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 10647-2024 tillsynsbegäran mail.docx", "A 10647-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 19524-2024</t>
+          <t>A 30411-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3694,10 +3690,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45429</v>
+        <v>45827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3710,7 +3706,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3719,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3734,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3746,50 +3742,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19524-2024 artfynd.xlsx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 30411-2025 artfynd.xlsx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19524-2024 karta.png", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 30411-2025 karta.png", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19524-2024 georefererad karta.tif", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 30411-2025 georefererad karta.tif", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19524-2024 FSC-klagomål.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 30411-2025 FSC-klagomål.docx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19524-2024 FSC-klagomål mail.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 30411-2025 FSC-klagomål mail.docx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19524-2024 tillsynsbegäran.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 30411-2025 tillsynsbegäran.docx", "A 30411-2025")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19524-2024 tillsynsbegäran mail.docx", "A 19524-2024")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 19524-2024 prioriterade fågelarter.docx", "A 19524-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 30411-2025 tillsynsbegäran mail.docx", "A 30411-2025")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 19052-2024</t>
+          <t>A 62675-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3799,14 +3791,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45427</v>
+        <v>45271</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3819,13 +3811,13 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>7.7</v>
+        <v>3.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3834,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -3843,10 +3835,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3855,46 +3847,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19052-2024 artfynd.xlsx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 62675-2023 artfynd.xlsx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19052-2024 karta.png", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 62675-2023 karta.png", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19052-2024 georefererad karta.tif", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 62675-2023 georefererad karta.tif", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19052-2024 FSC-klagomål.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 62675-2023 FSC-klagomål.docx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19052-2024 FSC-klagomål mail.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 62675-2023 FSC-klagomål mail.docx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19052-2024 tillsynsbegäran.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 62675-2023 tillsynsbegäran.docx", "A 62675-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19052-2024 tillsynsbegäran mail.docx", "A 19052-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 62675-2023 tillsynsbegäran mail.docx", "A 62675-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 15321-2023</t>
+          <t>A 19052-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3908,10 +3900,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45019</v>
+        <v>45427</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3924,23 +3916,23 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5.2</v>
+        <v>7.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>1</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
@@ -3948,58 +3940,58 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 15321-2023 artfynd.xlsx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19052-2024 artfynd.xlsx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 15321-2023 karta.png", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19052-2024 karta.png", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 15321-2023 georefererad karta.tif", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19052-2024 georefererad karta.tif", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 15321-2023 FSC-klagomål.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19052-2024 FSC-klagomål.docx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 15321-2023 FSC-klagomål mail.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19052-2024 FSC-klagomål mail.docx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 15321-2023 tillsynsbegäran.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19052-2024 tillsynsbegäran.docx", "A 19052-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 15321-2023 tillsynsbegäran mail.docx", "A 15321-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19052-2024 tillsynsbegäran mail.docx", "A 19052-2024")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30411-2025</t>
+          <t>A 37339-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4013,10 +4005,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45827</v>
+        <v>44806</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4029,17 +4021,17 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
@@ -4053,7 +4045,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4069,42 +4061,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 30411-2025 artfynd.xlsx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 37339-2022 artfynd.xlsx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 30411-2025 karta.png", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 37339-2022 karta.png", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 30411-2025 georefererad karta.tif", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 37339-2022 georefererad karta.tif", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 30411-2025 FSC-klagomål.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 37339-2022 FSC-klagomål.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 30411-2025 FSC-klagomål mail.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 37339-2022 FSC-klagomål mail.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 30411-2025 tillsynsbegäran.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 37339-2022 tillsynsbegäran.docx", "A 37339-2022")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 30411-2025 tillsynsbegäran mail.docx", "A 30411-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 37339-2022 tillsynsbegäran mail.docx", "A 37339-2022")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13121-2023</t>
+          <t>A 34076-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4114,14 +4106,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45002</v>
+        <v>46252</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4134,17 +4126,17 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
@@ -4158,7 +4150,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4167,42 +4159,42 @@
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 13121-2023 artfynd.xlsx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 34076-2026 artfynd.xlsx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 13121-2023 karta.png", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 34076-2026 karta.png", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 13121-2023 georefererad karta.tif", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 34076-2026 georefererad karta.tif", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 13121-2023 FSC-klagomål.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 34076-2026 FSC-klagomål.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 13121-2023 FSC-klagomål mail.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 34076-2026 FSC-klagomål mail.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 13121-2023 tillsynsbegäran.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 34076-2026 tillsynsbegäran.docx", "A 34076-2026")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 13121-2023 tillsynsbegäran mail.docx", "A 13121-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 34076-2026 tillsynsbegäran mail.docx", "A 34076-2026")</f>
         <v/>
       </c>
     </row>
@@ -4226,7 +4218,7 @@
         <v>45708</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4314,7 +4306,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 35077-2024</t>
+          <t>A 17122-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4324,14 +4316,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45527</v>
+        <v>45412</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4344,19 +4336,19 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -4371,7 +4363,7 @@
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4384,46 +4376,42 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 35077-2024 artfynd.xlsx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 17122-2024 artfynd.xlsx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 35077-2024 karta.png", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 17122-2024 karta.png", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 35077-2024 georefererad karta.tif", "A 35077-2024")</f>
-        <v/>
-      </c>
-      <c r="Z36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/knärot/A 35077-2024 karta knärot.png", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 17122-2024 georefererad karta.tif", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 35077-2024 FSC-klagomål.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 17122-2024 FSC-klagomål.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 35077-2024 FSC-klagomål mail.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 17122-2024 FSC-klagomål mail.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 35077-2024 tillsynsbegäran.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 17122-2024 tillsynsbegäran.docx", "A 17122-2024")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 35077-2024 tillsynsbegäran mail.docx", "A 35077-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 17122-2024 tillsynsbegäran mail.docx", "A 17122-2024")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 34076-2026</t>
+          <t>A 41878-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4437,10 +4425,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46252</v>
+        <v>45561</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4452,11 +4440,16 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>4.9</v>
+        <v>15.9</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -4486,49 +4479,53 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 34076-2026 artfynd.xlsx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 41878-2024 artfynd.xlsx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 34076-2026 karta.png", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 41878-2024 karta.png", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 34076-2026 georefererad karta.tif", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 41878-2024 georefererad karta.tif", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 34076-2026 FSC-klagomål.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 41878-2024 FSC-klagomål.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 34076-2026 FSC-klagomål mail.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 41878-2024 FSC-klagomål mail.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 34076-2026 tillsynsbegäran.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 41878-2024 tillsynsbegäran.docx", "A 41878-2024")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 34076-2026 tillsynsbegäran mail.docx", "A 34076-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 41878-2024 tillsynsbegäran mail.docx", "A 41878-2024")</f>
+        <v/>
+      </c>
+      <c r="AE37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 41878-2024 prioriterade fågelarter.docx", "A 41878-2024")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 29582-2024</t>
+          <t>A 35077-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4542,10 +4539,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45484</v>
+        <v>45527</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4557,26 +4554,21 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
       </c>
       <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
         <v>1</v>
       </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
@@ -4587,10 +4579,10 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4603,42 +4595,46 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 29582-2024 artfynd.xlsx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 35077-2024 artfynd.xlsx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 29582-2024 karta.png", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 35077-2024 karta.png", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 29582-2024 georefererad karta.tif", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 35077-2024 georefererad karta.tif", "A 35077-2024")</f>
+        <v/>
+      </c>
+      <c r="Z38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/knärot/A 35077-2024 karta knärot.png", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 29582-2024 FSC-klagomål.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 35077-2024 FSC-klagomål.docx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 29582-2024 FSC-klagomål mail.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 35077-2024 FSC-klagomål mail.docx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 29582-2024 tillsynsbegäran.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 35077-2024 tillsynsbegäran.docx", "A 35077-2024")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 29582-2024 tillsynsbegäran mail.docx", "A 29582-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 35077-2024 tillsynsbegäran mail.docx", "A 35077-2024")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62675-2023</t>
+          <t>A 19524-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4648,14 +4644,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45271</v>
+        <v>45429</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4668,17 +4664,17 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
         <v>1</v>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
@@ -4692,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -4704,39 +4700,43 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 62675-2023 artfynd.xlsx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/artfynd/A 19524-2024 artfynd.xlsx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 62675-2023 karta.png", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor/A 19524-2024 karta.png", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 62675-2023 georefererad karta.tif", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/kartor_geotiff/A 19524-2024 georefererad karta.tif", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 62675-2023 FSC-klagomål.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomål/A 19524-2024 FSC-klagomål.docx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 62675-2023 FSC-klagomål mail.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/klagomålsmail/A 19524-2024 FSC-klagomål mail.docx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 62675-2023 tillsynsbegäran.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsyn/A 19524-2024 tillsynsbegäran.docx", "A 19524-2024")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 62675-2023 tillsynsbegäran mail.docx", "A 62675-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/tillsynsmail/A 19524-2024 tillsynsbegäran mail.docx", "A 19524-2024")</f>
+        <v/>
+      </c>
+      <c r="AE39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1764/fåglar/A 19524-2024 prioriterade fågelarter.docx", "A 19524-2024")</f>
         <v/>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
         <v>44484</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>44607</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>44781</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>44509</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>44575</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>44795</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>44782</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44860</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>44494</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>44844</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>44838</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>44690</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>44734</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>44694</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>44743</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>44509</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44498</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44798</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>44762</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>44620</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>44627</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>44735</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44882</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44806</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>44494</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>44732</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>44577</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30334-2022</t>
+          <t>A 29699-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6770,10 +6770,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44760</v>
+        <v>44755</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6829,7 +6829,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29699-2022</t>
+          <t>A 30334-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6843,10 +6843,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44755</v>
+        <v>44760</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6919,7 +6919,7 @@
         <v>44547</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 12311-2024</t>
+          <t>A 5841-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45378</v>
+        <v>44596</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7048,7 +7048,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 37486-2022</t>
+          <t>A 5025-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44809</v>
+        <v>44958</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>8.6</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7121,7 +7121,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 20238-2024</t>
+          <t>A 73901-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45434</v>
+        <v>44552</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7194,7 +7194,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 21528-2024</t>
+          <t>A 5126-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7208,10 +7208,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45441</v>
+        <v>44958</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>14.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7267,7 +7267,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 42557-2022</t>
+          <t>A 28228-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44831</v>
+        <v>45477</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>13.7</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7340,7 +7340,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 23189-2024</t>
+          <t>A 73033-2021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7354,10 +7354,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45450</v>
+        <v>44550</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7369,13 +7369,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7418,7 +7413,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 19053-2024</t>
+          <t>A 13382-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7432,10 +7427,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45427</v>
+        <v>45387</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7448,7 +7443,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7491,7 +7486,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13382-2024</t>
+          <t>A 17437-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7505,10 +7500,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45387</v>
+        <v>45757</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7521,7 +7516,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7564,7 +7559,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 25840-2024</t>
+          <t>A 17443-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7578,10 +7573,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45467</v>
+        <v>45757</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7594,7 +7589,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7637,7 +7632,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 59391-2025</t>
+          <t>A 57236-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7647,14 +7642,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45989</v>
+        <v>45245</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7667,7 +7662,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7710,7 +7705,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 28228-2024</t>
+          <t>A 57237-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7724,10 +7719,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45477</v>
+        <v>45245</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7740,7 +7735,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>18.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7783,7 +7778,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 25014-2024</t>
+          <t>A 5810-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7797,10 +7792,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45461</v>
+        <v>44963</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7813,7 +7808,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>12.8</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7856,7 +7851,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 17081-2024</t>
+          <t>A 47152-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7870,10 +7865,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45412</v>
+        <v>45201</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7886,7 +7881,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7929,7 +7924,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 62682-2023</t>
+          <t>A 26840-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7943,10 +7938,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45271</v>
+        <v>45093</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7959,7 +7954,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8002,7 +7997,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 3054-2026</t>
+          <t>A 18341-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8016,10 +8011,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46039</v>
+        <v>45762</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8032,7 +8027,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8075,7 +8070,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 73310-2021</t>
+          <t>A 58514-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8089,10 +8084,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44547</v>
+        <v>44902</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8105,7 +8100,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8148,7 +8143,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 13289-2025</t>
+          <t>A 37119-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8162,10 +8157,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45735</v>
+        <v>45539</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8178,7 +8173,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>6.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8221,7 +8216,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 45467-2022</t>
+          <t>A 17910-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8235,10 +8230,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44845</v>
+        <v>45419</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8251,7 +8246,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8294,7 +8289,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 58705-2024</t>
+          <t>A 2253-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8308,10 +8303,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45635</v>
+        <v>45310</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8323,13 +8318,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8372,7 +8362,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 44497-2025</t>
+          <t>A 59391-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8382,14 +8372,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45916</v>
+        <v>45989</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8402,7 +8392,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8445,7 +8435,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 8732-2026</t>
+          <t>A 6721-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8459,10 +8449,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46066</v>
+        <v>45700</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8474,8 +8464,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8518,7 +8513,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 36644-2023</t>
+          <t>A 49300-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8532,10 +8527,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45153</v>
+        <v>44861</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8548,7 +8543,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8591,7 +8586,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 7922-2022</t>
+          <t>A 5957-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8605,10 +8600,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44608</v>
+        <v>45336</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8621,7 +8616,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8664,7 +8659,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 62905-2023</t>
+          <t>A 3054-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8678,10 +8673,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45272</v>
+        <v>46039</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8694,7 +8689,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>13.8</v>
+        <v>2.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8737,7 +8732,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 5126-2023</t>
+          <t>A 20238-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8751,10 +8746,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44958</v>
+        <v>45434</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8767,7 +8762,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>14.3</v>
+        <v>1.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8810,7 +8805,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 10892-2022</t>
+          <t>A 44497-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8824,10 +8819,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44627</v>
+        <v>45916</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8840,7 +8835,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8883,7 +8878,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 47507-2025</t>
+          <t>A 13289-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8897,10 +8892,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45930</v>
+        <v>45735</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8913,7 +8908,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8956,7 +8951,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 31362-2024</t>
+          <t>A 56219-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8966,14 +8961,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45505</v>
+        <v>45240</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8986,7 +8981,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9029,7 +9024,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 12283-2026</t>
+          <t>A 680-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9043,10 +9038,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46087</v>
+        <v>45300</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9059,7 +9054,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9102,7 +9097,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 49507-2025</t>
+          <t>A 30339-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9116,10 +9111,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45939</v>
+        <v>44760</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9132,7 +9127,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9192,7 +9187,7 @@
         <v>45096</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9248,7 +9243,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 62557-2022</t>
+          <t>A 47507-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9262,10 +9257,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44924</v>
+        <v>45930</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9278,7 +9273,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9321,7 +9316,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 7991-2024</t>
+          <t>A 975-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9331,14 +9326,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45350</v>
+        <v>45665</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9351,7 +9346,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9394,7 +9389,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 36420-2023</t>
+          <t>A 8732-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9408,10 +9403,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45152</v>
+        <v>46066</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9424,7 +9419,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>6.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9467,7 +9462,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 51509-2025</t>
+          <t>A 62557-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9477,14 +9472,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45950</v>
+        <v>44924</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9497,7 +9492,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9540,7 +9535,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 5810-2023</t>
+          <t>A 49507-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9554,10 +9549,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44963</v>
+        <v>45939</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9570,7 +9565,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.8</v>
+        <v>5.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9613,7 +9608,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 14688-2026</t>
+          <t>A 21402-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9623,14 +9618,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46101</v>
+        <v>45441</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9643,7 +9638,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9686,7 +9681,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 52700-2025</t>
+          <t>A 36420-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9700,10 +9695,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45956</v>
+        <v>45152</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9716,7 +9711,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9759,7 +9754,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 52699-2025</t>
+          <t>A 29736-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9773,10 +9768,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45956</v>
+        <v>45107</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9789,7 +9784,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9832,7 +9827,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 15543-2026</t>
+          <t>A 53138-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9846,10 +9841,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46106</v>
+        <v>45229</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9862,7 +9857,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9905,7 +9900,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 15549-2026</t>
+          <t>A 51509-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9915,14 +9910,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46106</v>
+        <v>45950</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9935,7 +9930,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9978,7 +9973,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 5236-2023</t>
+          <t>A 19566-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9992,10 +9987,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44956</v>
+        <v>45049</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10008,7 +10003,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10051,7 +10046,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 62947-2023</t>
+          <t>A 29762-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10065,10 +10060,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45272</v>
+        <v>45107</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10081,7 +10076,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10124,7 +10119,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 7993-2024</t>
+          <t>A 52699-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10138,10 +10133,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45350</v>
+        <v>45956</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10154,7 +10149,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10197,7 +10192,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 33081-2022</t>
+          <t>A 52700-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10211,10 +10206,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44785</v>
+        <v>45956</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10227,7 +10222,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10270,7 +10265,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 17399-2025</t>
+          <t>A 12283-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10284,10 +10279,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45757</v>
+        <v>46087</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10300,7 +10295,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10343,7 +10338,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 29762-2023</t>
+          <t>A 8364-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10357,10 +10352,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45107</v>
+        <v>45708</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10373,7 +10368,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10416,7 +10411,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 58747-2025</t>
+          <t>A 62896-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10430,10 +10425,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45986</v>
+        <v>45272</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10446,7 +10441,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>13.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10489,7 +10484,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 58751-2025</t>
+          <t>A 17399-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10503,10 +10498,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45986</v>
+        <v>45757</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10519,7 +10514,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10562,7 +10557,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 29736-2023</t>
+          <t>A 69847-2021</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10576,10 +10571,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45107</v>
+        <v>44532</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10592,7 +10587,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10635,7 +10630,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 29256-2025</t>
+          <t>A 58705-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10649,10 +10644,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45824</v>
+        <v>45635</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10664,8 +10659,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10708,7 +10708,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 21248-2022</t>
+          <t>A 22347-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10722,10 +10722,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44705</v>
+        <v>45070</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>12.4</v>
+        <v>1.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10781,7 +10781,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 50640-2023</t>
+          <t>A 14688-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10791,14 +10791,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45217</v>
+        <v>46101</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10854,7 +10854,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 17910-2024</t>
+          <t>A 15549-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10868,10 +10868,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45419</v>
+        <v>46106</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10927,7 +10927,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 42143-2025</t>
+          <t>A 15543-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10941,10 +10941,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45904</v>
+        <v>46106</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11000,7 +11000,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 29260-2025</t>
+          <t>A 58751-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11014,10 +11014,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45824</v>
+        <v>45986</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11073,7 +11073,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 60656-2025</t>
+          <t>A 58747-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11087,10 +11087,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45996</v>
+        <v>45986</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11146,7 +11146,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 40522-2025</t>
+          <t>A 29260-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11160,10 +11160,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45896</v>
+        <v>45824</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11219,7 +11219,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 8361-2025</t>
+          <t>A 33081-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11233,10 +11233,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45708</v>
+        <v>44785</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11292,7 +11292,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 5214-2025</t>
+          <t>A 25840-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11306,10 +11306,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45691</v>
+        <v>45467</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11365,7 +11365,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 31964-2023</t>
+          <t>A 60656-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11379,10 +11379,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45107</v>
+        <v>45996</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11438,7 +11438,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 35253-2022</t>
+          <t>A 30563-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11452,10 +11452,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44797</v>
+        <v>45831</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11511,7 +11511,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 29426-2022</t>
+          <t>A 37676-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11521,14 +11521,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44753</v>
+        <v>45159</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11540,13 +11540,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>14.4</v>
+        <v>0.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11589,7 +11584,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 20784-2025</t>
+          <t>A 6751-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11603,10 +11598,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45776</v>
+        <v>45700</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11619,7 +11614,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>9.5</v>
+        <v>0.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11662,7 +11657,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 30339-2022</t>
+          <t>A 50640-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11676,10 +11671,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44760</v>
+        <v>45217</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11692,7 +11687,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>5.3</v>
+        <v>1.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11735,7 +11730,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 614-2026</t>
+          <t>A 34580-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11749,10 +11744,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46024</v>
+        <v>44795</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11765,7 +11760,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11808,7 +11803,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 6751-2025</t>
+          <t>A 12000-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11822,10 +11817,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45700</v>
+        <v>44635</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11838,7 +11833,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11881,7 +11876,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 975-2025</t>
+          <t>A 42557-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11895,10 +11890,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45665</v>
+        <v>44831</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11911,7 +11906,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.4</v>
+        <v>13.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11954,7 +11949,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 30563-2025</t>
+          <t>A 35253-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11968,10 +11963,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45831</v>
+        <v>44797</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11984,7 +11979,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12027,7 +12022,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 63919-2021</t>
+          <t>A 59617-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12041,10 +12036,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44509</v>
+        <v>45992</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12057,7 +12052,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12117,7 +12112,7 @@
         <v>45836</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12173,7 +12168,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 8359-2025</t>
+          <t>A 29256-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12187,10 +12182,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45708</v>
+        <v>45824</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12203,7 +12198,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12246,7 +12241,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 9144-2024</t>
+          <t>A 614-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12260,10 +12255,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45358</v>
+        <v>46024</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12276,7 +12271,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12319,7 +12314,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 35425-2025</t>
+          <t>A 13820-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12333,10 +12328,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45855</v>
+        <v>45390</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12349,7 +12344,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.5</v>
+        <v>7.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12392,7 +12387,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 40524-2025</t>
+          <t>A 17565-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12406,10 +12401,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45896</v>
+        <v>45757</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12422,7 +12417,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12465,7 +12460,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 59617-2025</t>
+          <t>A 42143-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12479,10 +12474,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45992</v>
+        <v>45904</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12495,7 +12490,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12538,7 +12533,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 31561-2023</t>
+          <t>A 31362-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12548,14 +12543,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45117</v>
+        <v>45505</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12568,7 +12563,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12611,7 +12606,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 37517-2025</t>
+          <t>A 8359-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12625,10 +12620,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45877</v>
+        <v>45708</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12641,7 +12636,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12684,7 +12679,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 37515-2025</t>
+          <t>A 20784-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12698,10 +12693,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45877</v>
+        <v>45776</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12714,7 +12709,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.5</v>
+        <v>9.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12757,7 +12752,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 37495-2025</t>
+          <t>A 35425-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12771,10 +12766,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45877</v>
+        <v>45855</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12787,7 +12782,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12830,7 +12825,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 33948-2023</t>
+          <t>A 40524-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12844,10 +12839,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45124</v>
+        <v>45896</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12860,7 +12855,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>5.5</v>
+        <v>1.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12903,7 +12898,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 27222-2023</t>
+          <t>A 21248-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12917,10 +12912,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45096</v>
+        <v>44705</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12933,7 +12928,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.3</v>
+        <v>12.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12976,7 +12971,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 17972-2025</t>
+          <t>A 40522-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12990,10 +12985,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45761</v>
+        <v>45896</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13006,7 +13001,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13049,7 +13044,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 62896-2023</t>
+          <t>A 3065-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13063,10 +13058,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45272</v>
+        <v>45316</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13079,7 +13074,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>13.8</v>
+        <v>0.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13122,7 +13117,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 6938-2024</t>
+          <t>A 17081-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13132,14 +13127,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45343</v>
+        <v>45412</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13152,7 +13147,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13195,7 +13190,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 26829-2023</t>
+          <t>A 7993-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13209,10 +13204,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45093</v>
+        <v>45350</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13225,7 +13220,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13268,7 +13263,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 13895-2024</t>
+          <t>A 45467-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13282,10 +13277,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45391</v>
+        <v>44845</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13297,13 +13292,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13346,7 +13336,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 26815-2023</t>
+          <t>A 5011-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13360,10 +13350,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45093</v>
+        <v>45329</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13376,7 +13366,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.1</v>
+        <v>22</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13419,7 +13409,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 17565-2025</t>
+          <t>A 53137-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13433,10 +13423,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45757</v>
+        <v>45229</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13449,7 +13439,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13492,7 +13482,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 25443-2023</t>
+          <t>A 5214-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13506,10 +13496,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45089</v>
+        <v>45691</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13522,7 +13512,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13565,7 +13555,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 22406-2026</t>
+          <t>A 9144-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13579,10 +13569,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46154</v>
+        <v>45358</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13595,7 +13585,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13638,7 +13628,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 14306-2023</t>
+          <t>A 62682-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13652,10 +13642,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45011</v>
+        <v>45271</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13668,7 +13658,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13711,7 +13701,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 39334-2025</t>
+          <t>A 31561-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13725,10 +13715,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45889</v>
+        <v>45117</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13741,7 +13731,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13784,7 +13774,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 3779-2025</t>
+          <t>A 4982-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13798,10 +13788,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45681</v>
+        <v>45329</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13813,13 +13803,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>BillerudKorsnäs AB</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13862,7 +13847,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 5025-2023</t>
+          <t>A 62947-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13876,10 +13861,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44958</v>
+        <v>45272</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13892,7 +13877,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13935,7 +13920,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 31974-2023</t>
+          <t>A 31930-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13945,14 +13930,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45107</v>
+        <v>45510</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13965,7 +13950,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14008,7 +13993,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 5957-2024</t>
+          <t>A 71706-2021</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14022,10 +14007,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45336</v>
+        <v>44543</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14038,7 +14023,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14081,7 +14066,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 71903-2021</t>
+          <t>A 40935-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14091,14 +14076,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44543</v>
+        <v>44823</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14110,8 +14095,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14154,7 +14144,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 2253-2024</t>
+          <t>A 6938-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14164,14 +14154,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45310</v>
+        <v>45343</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14184,7 +14174,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14227,7 +14217,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 4870-2024</t>
+          <t>A 22406-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14241,10 +14231,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45329</v>
+        <v>46154</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14257,7 +14247,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14300,7 +14290,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 23702-2026</t>
+          <t>A 14306-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14314,10 +14304,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46164</v>
+        <v>45011</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14329,13 +14319,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14378,7 +14363,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 23733-2026</t>
+          <t>A 71903-2021</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14392,10 +14377,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46164</v>
+        <v>44543</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14407,13 +14392,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>0.9</v>
+        <v>6.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14456,7 +14436,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 23757-2026</t>
+          <t>A 3779-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14470,10 +14450,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46164</v>
+        <v>45681</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14485,8 +14465,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>BillerudKorsnäs AB</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>1.5</v>
+        <v>7.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14529,7 +14514,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 69847-2021</t>
+          <t>A 39334-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14543,10 +14528,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44532</v>
+        <v>45889</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14602,7 +14587,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 58514-2022</t>
+          <t>A 17972-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14616,10 +14601,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44902</v>
+        <v>45761</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14632,7 +14617,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14675,7 +14660,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 71706-2021</t>
+          <t>A 37515-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14689,10 +14674,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44543</v>
+        <v>45877</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14705,7 +14690,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14748,7 +14733,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 23945-2026</t>
+          <t>A 27222-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14762,10 +14747,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46167</v>
+        <v>45096</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14775,11 +14760,6 @@
       <c r="G176" t="inlineStr">
         <is>
           <t>GRUMS</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I176" t="n">
@@ -14826,7 +14806,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 47152-2023</t>
+          <t>A 23733-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14840,10 +14820,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45201</v>
+        <v>46164</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14855,8 +14835,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14899,7 +14884,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 24754-2026</t>
+          <t>A 23945-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14913,10 +14898,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46171</v>
+        <v>46167</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14928,8 +14913,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14972,7 +14962,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 53138-2023</t>
+          <t>A 37495-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14986,10 +14976,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45229</v>
+        <v>45877</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15002,7 +14992,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15045,7 +15035,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 16772-2024</t>
+          <t>A 23757-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15059,10 +15049,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45411</v>
+        <v>46164</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15075,7 +15065,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15118,7 +15108,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 66056-2021</t>
+          <t>A 36644-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15132,10 +15122,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44517</v>
+        <v>45153</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15148,7 +15138,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15191,7 +15181,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 3065-2024</t>
+          <t>A 23702-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15205,10 +15195,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45316</v>
+        <v>46164</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15220,8 +15210,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15264,7 +15259,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 12082-2024</t>
+          <t>A 37517-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15278,10 +15273,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45377</v>
+        <v>45877</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15294,7 +15289,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15337,7 +15332,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 12084-2024</t>
+          <t>A 8788-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15351,10 +15346,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45377</v>
+        <v>45356</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15367,7 +15362,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15410,7 +15405,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 20954-2023</t>
+          <t>A 62554-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15424,10 +15419,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45061</v>
+        <v>44924</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15440,7 +15435,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15483,7 +15478,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 26015-2026</t>
+          <t>A 21528-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15493,14 +15488,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46181</v>
+        <v>45441</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15512,13 +15507,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15561,7 +15551,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 17443-2025</t>
+          <t>A 20954-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15575,10 +15565,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45757</v>
+        <v>45061</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15591,7 +15581,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15634,7 +15624,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 20369-2024</t>
+          <t>A 24754-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15648,10 +15638,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45435</v>
+        <v>46171</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15664,7 +15654,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15707,7 +15697,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 11601-2025</t>
+          <t>A 10892-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15721,10 +15711,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45727</v>
+        <v>44627</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15737,7 +15727,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15780,7 +15770,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 4976-2024</t>
+          <t>A 29426-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15794,10 +15784,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45329</v>
+        <v>44753</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15809,8 +15799,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>5.1</v>
+        <v>14.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15853,7 +15848,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 12175-2024</t>
+          <t>A 26015-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15863,14 +15858,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45377</v>
+        <v>46181</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15882,8 +15877,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15926,7 +15926,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 30527-2022</t>
+          <t>A 44048-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15940,10 +15940,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44762</v>
+        <v>45188</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15999,7 +15999,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 22347-2023</t>
+          <t>A 62905-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16013,10 +16013,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45070</v>
+        <v>45272</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.7</v>
+        <v>13.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16072,7 +16072,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 11103-2022</t>
+          <t>A 37486-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16086,10 +16086,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44628</v>
+        <v>44809</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 28513-2026</t>
+          <t>A 46299-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16159,10 +16159,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46197</v>
+        <v>44847</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16218,7 +16218,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 56220-2023</t>
+          <t>A 28513-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16232,10 +16232,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45240</v>
+        <v>46197</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16291,7 +16291,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 56219-2023</t>
+          <t>A 11103-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16305,10 +16305,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45240</v>
+        <v>44628</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16364,7 +16364,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 32302-2024</t>
+          <t>A 29205-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16378,10 +16378,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45512</v>
+        <v>46202</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16393,13 +16393,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16442,7 +16437,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 6721-2025</t>
+          <t>A 29222-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16456,10 +16451,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45700</v>
+        <v>46202</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16471,13 +16466,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>5.7</v>
+        <v>3.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16520,7 +16510,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 29205-2026</t>
+          <t>A 5236-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16534,10 +16524,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46202</v>
+        <v>44956</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16550,7 +16540,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16593,7 +16583,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 29222-2026</t>
+          <t>A 29191-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16610,7 +16600,7 @@
         <v>46202</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16623,7 +16613,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16666,7 +16656,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 29191-2026</t>
+          <t>A 56220-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16680,10 +16670,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46202</v>
+        <v>45240</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16696,7 +16686,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16739,7 +16729,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 17437-2025</t>
+          <t>A 972-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16753,10 +16743,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45757</v>
+        <v>45665</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16769,7 +16759,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16812,7 +16802,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 5841-2022</t>
+          <t>A 32302-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16826,10 +16816,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44596</v>
+        <v>45512</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16841,8 +16831,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16885,7 +16880,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 12000-2022</t>
+          <t>A 13895-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16899,10 +16894,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44635</v>
+        <v>45391</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16914,8 +16909,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16958,7 +16958,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 40935-2022</t>
+          <t>A 29724-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16972,10 +16972,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44823</v>
+        <v>45107</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16987,13 +16987,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17036,7 +17031,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 36646-2023</t>
+          <t>A 31034-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17050,10 +17045,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45153</v>
+        <v>46214</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17066,7 +17061,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17109,7 +17104,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 29724-2023</t>
+          <t>A 31974-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17119,14 +17114,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17139,7 +17134,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17182,7 +17177,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 8362-2025</t>
+          <t>A 19802-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17196,10 +17191,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45708</v>
+        <v>45432</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17211,8 +17206,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>7.7</v>
+        <v>2.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17255,7 +17255,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 972-2025</t>
+          <t>A 16635-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17269,10 +17269,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45665</v>
+        <v>45408</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17328,7 +17328,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 49300-2022</t>
+          <t>A 31559-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17342,10 +17342,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44861</v>
+        <v>46224</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17401,7 +17401,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 16635-2024</t>
+          <t>A 7922-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17415,10 +17415,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45408</v>
+        <v>44608</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17431,7 +17431,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17474,7 +17474,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 34538-2026</t>
+          <t>A 1556-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17488,10 +17488,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46255</v>
+        <v>45670</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17547,7 +17547,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 37676-2023</t>
+          <t>A 12311-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17557,14 +17557,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45159</v>
+        <v>45378</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17620,7 +17620,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 31034-2026</t>
+          <t>A 33948-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17634,10 +17634,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46214</v>
+        <v>45124</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17693,7 +17693,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 53137-2023</t>
+          <t>A 37221-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17707,10 +17707,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45229</v>
+        <v>46274</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17723,7 +17723,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17766,7 +17766,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 8788-2024</t>
+          <t>A 37243-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17780,10 +17780,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45356</v>
+        <v>46274</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.9</v>
+        <v>13.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17839,7 +17839,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 680-2024</t>
+          <t>A 13320-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17853,10 +17853,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45300</v>
+        <v>45386</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17912,7 +17912,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 46299-2022</t>
+          <t>A 55227-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17926,10 +17926,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44847</v>
+        <v>45231</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17985,7 +17985,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 62554-2022</t>
+          <t>A 25014-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17999,10 +17999,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44924</v>
+        <v>45461</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.6</v>
+        <v>12.8</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18058,7 +18058,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 31559-2026</t>
+          <t>A 31964-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18072,10 +18072,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46224</v>
+        <v>45107</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18131,7 +18131,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 57236-2023</t>
+          <t>A 12082-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18145,10 +18145,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45245</v>
+        <v>45377</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18204,7 +18204,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 57237-2023</t>
+          <t>A 12084-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18218,10 +18218,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45245</v>
+        <v>45377</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>18.2</v>
+        <v>1.1</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18277,7 +18277,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 37221-2026</t>
+          <t>A 4976-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18291,10 +18291,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46274</v>
+        <v>45329</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18350,7 +18350,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 29577-2024</t>
+          <t>A 64304-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18364,10 +18364,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45484</v>
+        <v>45280</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18379,13 +18379,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>10.1</v>
+        <v>1.2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18428,7 +18423,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 37243-2026</t>
+          <t>A 48553-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18442,10 +18437,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46274</v>
+        <v>45208</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18458,7 +18453,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>13.9</v>
+        <v>1.7</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18501,7 +18496,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 27443-2024</t>
+          <t>A 26815-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18515,10 +18510,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45474</v>
+        <v>45093</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18531,7 +18526,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18574,7 +18569,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 32959-2022</t>
+          <t>A 16772-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18588,10 +18583,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44784</v>
+        <v>45411</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18604,7 +18599,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18647,7 +18642,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 13320-2024</t>
+          <t>A 25443-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18661,10 +18656,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45386</v>
+        <v>45089</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18677,7 +18672,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18720,7 +18715,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 38517-2024</t>
+          <t>A 32942-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18734,10 +18729,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45546</v>
+        <v>46244</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18750,7 +18745,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18793,7 +18788,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 37119-2024</t>
+          <t>A 66056-2021</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18807,10 +18802,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45539</v>
+        <v>44517</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18823,7 +18818,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>6.7</v>
+        <v>0.7</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18866,7 +18861,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 19802-2024</t>
+          <t>A 23189-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18880,10 +18875,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45432</v>
+        <v>45450</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18901,7 +18896,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18944,7 +18939,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 34580-2022</t>
+          <t>A 7991-2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18954,14 +18949,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>44795</v>
+        <v>45350</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18974,7 +18969,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -19017,7 +19012,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 19566-2023</t>
+          <t>A 59542-2022</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -19031,10 +19026,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45049</v>
+        <v>44907</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19047,7 +19042,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -19090,7 +19085,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 7272-2022</t>
+          <t>A 8361-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -19104,10 +19099,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44606</v>
+        <v>45708</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19120,7 +19115,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -19163,7 +19158,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 22822-2024</t>
+          <t>A 73310-2021</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19177,10 +19172,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45448</v>
+        <v>44547</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19193,7 +19188,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.3</v>
+        <v>6.2</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19236,7 +19231,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 59542-2022</t>
+          <t>A 71781-2021</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19250,10 +19245,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44907</v>
+        <v>44539</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19265,8 +19260,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I237" t="n">
-        <v>0.8</v>
+        <v>7</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19309,7 +19309,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 21402-2024</t>
+          <t>A 8362-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19323,10 +19323,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45441</v>
+        <v>45708</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19382,7 +19382,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 71781-2021</t>
+          <t>A 34538-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19396,10 +19396,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44539</v>
+        <v>46255</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19411,13 +19411,8 @@
           <t>GRUMS</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I239" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19460,7 +19455,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 31930-2024</t>
+          <t>A 30527-2022</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19470,14 +19465,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45510</v>
+        <v>44762</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19490,7 +19485,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19533,7 +19528,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 73901-2021</t>
+          <t>A 17573-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19547,10 +19542,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44552</v>
+        <v>45757</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19563,7 +19558,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19606,7 +19601,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 32942-2026</t>
+          <t>A 9837-2023</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19620,10 +19615,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46244</v>
+        <v>44984</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19636,7 +19631,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19679,7 +19674,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 26840-2023</t>
+          <t>A 19753-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19693,10 +19688,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45093</v>
+        <v>45432</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19709,7 +19704,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19752,7 +19747,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 13820-2024</t>
+          <t>A 27443-2024</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19766,10 +19761,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45390</v>
+        <v>45474</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19782,7 +19777,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>7.2</v>
+        <v>1.8</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19825,7 +19820,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 5011-2024</t>
+          <t>A 32959-2022</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19839,10 +19834,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45329</v>
+        <v>44784</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19855,7 +19850,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>22</v>
+        <v>3.5</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19898,7 +19893,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 18341-2025</t>
+          <t>A 30914-2023</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19912,10 +19907,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45762</v>
+        <v>45113</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19928,7 +19923,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19971,7 +19966,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 19753-2024</t>
+          <t>A 20369-2024</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19985,10 +19980,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45432</v>
+        <v>45435</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20001,7 +19996,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -20044,7 +20039,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 4982-2024</t>
+          <t>A 7272-2022</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -20058,10 +20053,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45329</v>
+        <v>44606</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20074,7 +20069,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -20117,7 +20112,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 55227-2023</t>
+          <t>A 26829-2023</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -20131,10 +20126,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45231</v>
+        <v>45093</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20147,7 +20142,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -20190,7 +20185,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 9837-2023</t>
+          <t>A 38517-2024</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -20204,10 +20199,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>44984</v>
+        <v>45546</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20220,7 +20215,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -20263,7 +20258,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 1556-2025</t>
+          <t>A 63919-2021</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20277,10 +20272,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45670</v>
+        <v>44509</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20293,7 +20288,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20336,7 +20331,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 73033-2021</t>
+          <t>A 4870-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20350,10 +20345,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>44550</v>
+        <v>45329</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20366,7 +20361,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>0.9</v>
+        <v>8.4</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20409,7 +20404,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 64304-2023</t>
+          <t>A 36646-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20423,10 +20418,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45280</v>
+        <v>45153</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20439,7 +20434,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20482,7 +20477,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 8364-2025</t>
+          <t>A 22822-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20496,10 +20491,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45708</v>
+        <v>45448</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20512,7 +20507,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20555,7 +20550,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 48553-2023</t>
+          <t>A 19053-2024</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20569,10 +20564,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45208</v>
+        <v>45427</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20585,7 +20580,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20628,7 +20623,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 17573-2025</t>
+          <t>A 11601-2025</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20642,10 +20637,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45757</v>
+        <v>45727</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20658,7 +20653,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20701,7 +20696,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 44048-2023</t>
+          <t>A 12175-2024</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20715,10 +20710,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45188</v>
+        <v>45377</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20731,7 +20726,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20774,7 +20769,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 30914-2023</t>
+          <t>A 29577-2024</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20788,10 +20783,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45113</v>
+        <v>45484</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20803,8 +20798,13 @@
           <t>GRUMS</t>
         </is>
       </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I258" t="n">
-        <v>2.1</v>
+        <v>10.1</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20864,7 +20864,7 @@
         <v>44977</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>45729</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21010,7 +21010,7 @@
         <v>45785</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>45787</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>45099</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         <v>45272</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>45846</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45973</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>46035</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>

--- a/Översikt GRUMS.xlsx
+++ b/Översikt GRUMS.xlsx
@@ -601,7 +601,7 @@
         <v>44978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45343</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44788</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44498</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44819</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45615</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>46252</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>44981</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45099</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>45898</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45078</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>44593</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>44517</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>45245</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>45706</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>44890</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>45099</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>44901</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>44494</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>44588</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>44792</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>45484</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45002</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>45019</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>45929</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3483,